--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$I$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
@@ -438,7 +438,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>組織・サービス</t>
+          <t>企業・組織名</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -480,17 +480,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している</t>
+          <t>国家公務員共済組合連合会</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 KKR京都くに荘のメールサーバに不正アクセス 国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56404.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
         </is>
       </c>
     </row>
@@ -522,19 +522,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.6 Tue 8:00 Apache HTTP Server 2.4 に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.6 Tue 8:00 Apache HTTP Server 2.4 に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -547,7 +547,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。</t>
+          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -579,36 +579,36 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社</t>
+          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -621,31 +621,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190961</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。</t>
+          <t>日本とデンマークの企業や機関が、数百万人分のデータを流出させたサイバー攻撃を発表 - Informat.ro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -653,89 +653,73 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQNDc5dXF1bnZIUHZ6U1dOazhhYzZ0T1I0VDdHamhKRTRTeVJTblFuTDRnLUtCTEJLazhtYTQ5YzYxQXNNb1JVNW92dDdWaVoySGJ5eUtIdFB0TENjMk9XUmd0eEZ5U2FlNDk5QmZqd2N0dm9lU0VOeEFoVjlzblF5Z2pDLW1qNjIwLTdjT1RDZzk2TEIwcXV5dGs4UkNUY1U0WVhDQ0pRcVZlTVBGZFRSUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yakiniku King (Monogatari)</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yakiniku King (Monogatari)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>10.79M records (confirmed)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SmartScope / Yagura</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://www.security-next.com/191072</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>White Essence</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>White Essence — Vulnerability</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.05M accounts (confirmed)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
+          <t>国内不正アクセス 過去最多ペース - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -748,39 +732,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBmRHN4SnNEUzh2Ukp2bmhDNVN1T1ZDT05oU2M3TWt6V1VlZEhqc1RoMWZGRTIyd3g3V1BRUl84UXQ0QVlxcV9BS2J3ekI0RHY4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daiwa Securities</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Daiwa Securities — Entry point not stated; at a contractor or third party</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>220K records (possible)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Entry point not stated; at a contractor or third party</t>
-        </is>
-      </c>
+          <t>企業や自治体への不正アクセス、9月末で600件 昨年1年間上回る AI自動攻撃痕跡も - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -793,39 +769,31 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVlNMaWZ0TkVwZnh3Rkx6MlU2RF9EMDZZTVAyMFhpcUM3ZVUyU29UZGVnczlJeW5feTZ1T0VES29tRXBCXzl2cVZhcTA4czNpc2JqRkN2dlFhMWFLSW9YYkM1OGNXUm1hdjlFc0JQdkN0RFRqcnVwZnlfbnNLQjJYQmVsaUR3Mm5GRzRNNmU4ZFJ2V1RSdGhjQzJiLTRVNnpyaDBrVlR5MkjSAagBQVVfeXFMTlZTTGlmdE5FcGZ4d0ZMejJVNkRfRDA2WU1QMjBYaXFDN2VVMlNvVGRlZ3M5SXluX3k2dU9FREtvbUVwQl85dnFWYXEwOHMzaXNiakZDdnZRYTFhS0lvWGJDNThjV1JtYXY5RXNCUHZDdERUanJ1cGZ5X25zS0IyWEJlbGlEdzJuRkc0TTZlOGRSdldUUnRoY0MyYi00VTZ6cmgwa1ZUeTJI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daiki Suisan (app)</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daiki Suisan (app) — Entry point not stated</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>175K people (possible)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>不正アクセス・情報漏洩はなぜ急増しているのか？ など 日刊出版ニュースまとめ 2026.10.07 - HON.jp</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -838,31 +806,31 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5Sa0dDa0VrLWRURlFYaGFnTDNmbnh6T05vOWNMWkU3STM1am9TMEdFd1F3aWYtclB3bWRvVm5XQlF3cmNmWUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便</t>
+          <t>不正アクセスなぜ急増 原因はAIか、それとも…… 専門家の見解は - Infoseek</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -870,36 +838,36 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190952</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE90VDhRd2FvNDhqNmhxNFk4WndubVpWQ3BDV1ZuWTRhM3hCZHY1WGpDWF9zbTVFY282LUNpRWo0RndFTGRTNEZfT1lNVGdhNE9yaHA5aXhhNUFHMlZtTmxMZlJxUkpFcHQxVEtUSFdSaEFObHdaYlE?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE8wWW5MTEtkYkNzSGFsU2NmN1dUQlFwNkZTVEhwcGMxRk80ZU9kWl83cmk1RXJzZjhWenNjN3Q1WjFmanhsb011bmlGYloxb1FoaVNsaXpXOEF0cWxIQkxGUlZOR2VPUGQ4MVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.2 Fri 8:00 PFU 製 Image Scanner Driver for Linux に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月29日、PFU製Image Scanner Driver for Linuxにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.2 Fri 8:00 PFU 製 Image Scanner Driver for Linux に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月29日、PFU製Image Scanner Driver for Linuxにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>ランサムウェア集団「Qilin」幹部を日本で拘束 ドイツへの身柄引き渡しが完了 - 東京報道新聞</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -907,36 +875,36 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5ab3lPX250TDFMX2dFaGR6ampBVHk2V3VFMTNOdjRxWm5WYnZuRkEyWWo4bS11UHZGdXlnNVQtMWUtbEEtcFE3UTY3OVdLd0xKMDFF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。</t>
+          <t>ミスターマックス</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。</t>
+          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -944,44 +912,36 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dai-ichi Life</t>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dai-ichi Life — Entry point not stated</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>120K people (possible)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.6 Tue 8:00 Apache HTTP Server 2.4 に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -994,68 +954,68 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大</t>
+          <t>シチズン時計</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大</t>
+          <t>シチズン時計10万人分漏えいか 個人情報、委託業者不正アクセス - Infoseek</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News / SmartScope</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190842</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5 / https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。</t>
+          <t>シチズン、顧客情報10万人漏洩か 業務委託先に不正アクセス - 日本経済新聞</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1068,31 +1028,31 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE45aEJtMHFJQWtRU1N6RTFXWGRNZjZrUERVOXA5NWwxVnprOWJoX09BVGZMR1hsbjMxNmNjbUNfckJsQTRZTHE1bWNlVnRyRjlpTW9CNjRNUnVpWkttYU55ZmpOblZGLVhJUlpocw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>エクスプロイト 株式会社ラック デジタルペンテスト部 2026.10.1 Thu 8:20 Microsoft Malware Protection Engine における任意の特権ファイルの書き込みが可能となるファイル操作での検証不備（Scan Tech Report） 2026 年 5 月に修正された Microsoft Defender を構成するソフトウェアの脆弱性を悪用するエクスプロイトコードが公開されています。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>エクスプロイト 株式会社ラック デジタルペンテスト部 2026.10.1 Thu 8:20 Microsoft Malware Protection Engine における任意の特権ファイルの書き込みが可能となるファイル操作での検証不備（Scan Tech Report） 2026 年 5 月に修正された Microsoft Defender を構成するソフトウェアの脆弱性を悪用するエクスプロイトコードが公開されています。</t>
+          <t>サイバー攻撃による情報流出続発、「大変深刻に受け止め」＝官房長官 - Reuters</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1100,29 +1060,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPZjZteWd2alI2ZmU3QXRGZTh6bzlZaGpPWmdVMG5BYmVveDRkQ3N1NlRmcGRnb0JndVZ3dUQzeWRSdUNlZWtKcTRCZ193WENLVm9WQ19aRFBDR1RsY1d2dktvWTFacTllWUx0TW14NTA2N0V2UVQ1eU1xMkRwOTdEWEZVeG1CQQ?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE5qVzJ4TU44R0psLTl3SEE5OHNjaTV0TG0xTldac2VsQWRmUDI3WnFTVVBKNGhIOWtyWG1CZVNKcFpmOE1uaURmSVZLWUNzRFlVSkk5SnlRVTJhQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 CMSプラグインの脆弱性公表を受け更新作業中に不正アクセスを発見 神奈川県川崎市は9月11日、かわさき新産業創造センター（KBIC）Webサイトへの不正アクセスについて発表した。</t>
+          <t>信濃毎日新聞</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 CMSプラグインの脆弱性公表を受け更新作業中に不正アクセスを発見 神奈川県川崎市は9月11日、かわさき新産業創造センター（KBIC）Webサイトへの不正アクセスについて発表した。</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1137,44 +1097,36 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OZmall (Starts Publishing)</t>
+          <t>株式会社ベネフィット・ワンは9月30日</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OZmall (Starts Publishing) — Vulnerability</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>443K people (up to, possible)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1182,36 +1134,36 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.30 Wed 8:00 ランサムウェア被害件数が過去最多の123件に、警察庁が対策情報を紹介 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.30 Wed 8:00 ランサムウェア被害件数が過去最多の123件に、警察庁が対策情報を紹介 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。</t>
+          <t>アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1224,31 +1176,31 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
+          <t>https://www.security-next.com/191070</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.30 Wed 8:00 山口東京理科大チームが優勝 ～ 県警ら主催「サイバー攻撃共同対処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.30 Wed 8:00 山口東京理科大チームが優勝 ～ 県警ら主催「サイバー攻撃共同対処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。</t>
+          <t>なぜ不正アクセス急増 識者の見解 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1261,31 +1213,31 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5VOHNTV2d3ZjNnanhXcjVpSGhocWp1UVRaZ1RSa191bXdEV2hxVmlCMXp5OHNRYnhUWm0ycFlfb2xqYk1iU09GQzQwdWFVU3ph?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。</t>
+          <t>【11月10日】AIで武装強化されたランサムウエア攻撃が拡大、長期のシステム停止を回避する最善策は？ - 日経クロステック Active</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1293,76 +1245,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPNUNOTkFwcEdyY2p6Y0NtWmtyS09tQ3hMeWFDQklmNWRXNDNsaldzcklyVWdPV04xOENYUW9ZWXFvOV9zODd6dVJhU2NDSnpZS3pMVVBFaXBJdDJRRmJGNVR1T2hzandQRXk0Rmg2S2JyUnVQd3hVaEo1UFpNWXJ0SXVKNGprWWhUN0NMY0NNWVFnMlVZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>「代金後払いサービス」で侵害、サービスを停止 - ヤマト運輸</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「代金後払いサービス」で侵害、サービスを停止 - ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>521 records (nimoca card number, date of birth, registered email address). No leak of names, addresses, phone numbers, gender or usage history confirmed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Security NEXT / ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VOISING</t>
+          <t>Yaomasa（ news report ）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VOISING — Vulnerability</t>
+          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>170K records (confirmed)</t>
+          <t>— (attacker published a business-file list; no Yaomasa disclosure found)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vulnerability</t>
+          <t>Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1387,24 +1347,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁が注意喚起する「WaterPlum」の手口 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁が注意喚起する「WaterPlum」の手口 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。</t>
+          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1417,31 +1377,31 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>モンベルのグローバルサイトに不正アクセス - 個人情報流出の可能性</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>モンベルのグローバルサイトに不正アクセス - 個人情報流出の可能性</t>
+          <t>連日の不正アクセスの件、マジでシャレにならないが、こんなやばいの日本だけ？他の国で問題になってないん？「今世界中で起きてる」 - Togetter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1454,31 +1414,31 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190798</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5qa0dJTnZnOFV3bjdRa05NaXNvelk4a1hrNXU0S2pKdFpoVXBSRUo1SEdWZlBkaWU2TUJyLWRyS3pOUWVmOGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.29 Tue 8:00 baserCMS 用プラグイン「アドオンマイグレーター」 に信頼できない制御領域からの機能の組み込みに関する脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月25日、baserCMS用プラグイン「アドオンマイグレーター」 における信頼できない制御領域からの機能の組み込みに関する脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.29 Tue 8:00 baserCMS 用プラグイン「アドオンマイグレーター」 に信頼できない制御領域からの機能の組み込みに関する脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月25日、baserCMS用プラグイン「アドオンマイグレーター」 における信頼できない制御領域からの機能の組み込みに関する脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1491,31 +1451,31 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html</t>
+          <t>https://www.security-next.com/190961</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.29 Tue 8:05 「スマレジEC・リピート」「スマレジEC・B2B」に不正アクセス、一部の個人データが閲覧・取得された可能性 株式会社スマレジは9月25日、同社が提供する「スマレジEC・リピート」および「スマレジEC・B2B」への不正アクセスについて発表した。</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.29 Tue 8:05 「スマレジEC・リピート」「スマレジEC・B2B」に不正アクセス、一部の個人データが閲覧・取得された可能性 株式会社スマレジは9月25日、同社が提供する「スマレジEC・リピート」および「スマレジEC・B2B」への不正アクセスについて発表した。</t>
+          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - INTERNET Watch</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1528,31 +1488,31 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ</t>
+          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1565,43 +1525,35 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190791</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Seicomart (app)</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seicomart (app)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>570K accounts (possible)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ニコニコニュース</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SmartScope / ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1610,68 +1562,68 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5 / https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大、金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大、金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。</t>
+          <t>大和証券、口座番号など顧客情報22万件が漏洩か 委託先に不正アクセス - 日本経済新聞</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News / SmartScope / Security NEXT</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5qLXVieEl0Yi1PclpmdmlmdmpJY1VrdkVGZEVkWlBEWC1tWlVGckZaX25oaUhkT3BsMmJjMWJ2TXhxYnBhNkY0X09hb3dSdE9Bb0QxYzRSNWppcFJSXzloa253UmZZVHhDelFxaQ?oc=5 / https://news.google.com/rss/articles/CBMiZEFVX3lxTFBjb1pfNE1BYjFCUWs3b283enV1ME1RYzRJLV9oVHI5RmdyQ2JtZkdGYlRRVHpJLW9LTExpUVdndFphVXhjMmZyeFZ5aEE3dFpRT2Nfd1hwNkUzUW5SV3M3NHl5LW8?oc=5 / https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBrSzlmUndaWU1VTlM2cXB2LUhDZ2IyY1c4TDRkeFJ3R3MydExVc0QzT0lZYUFaU2dvTWNham9uZGc0al80c09icHVXaXpnc0ZCTTk1bXZNdk83clBvelVfZVdXeUtRMHc?oc=5 / https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5 / https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://www.security-next.com/191068</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中</t>
+          <t>大和証、22万件漏えいか 不正アクセス、個人情報も - Infoseek</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1679,36 +1631,36 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190734</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9YSUl5cHRmeFBoYjN4azJGdV9ySTBmczRaVDV5bEhvQnZjYm5fUG56X01UUW8yM2xObEFxcXVVODZlU0xOUjFLNmVta25zSl9PZHFDMkFmTHBCWURUX0VCMC0yRi10Q2JEdzNRVkcxb9IBdEFVX3lxTE8tQ0F4bWxWX1BsWnZJV1dab0dLb09jN0VGaEZaTkR6OHlzbE9fMkRZMU5qcE5XVVZMZXhORm9XcC04ODZRc2VPa2hJakFjd01sVmlfTEUyYWI0LVl0dndtYzZTdFpwSHdqSl9FZ2NBWFJ3V3c1?oc=5 / https://news.google.com/rss/articles/CBMikwFBVV95cUxOQ2VtSFNuVDUtTXE1bjhSS0ZYTUlVY0FoRGl2NjV4VkdicHhPSEFxamtQYlZMdnpadC1ZZnhYa3R0a3dDQk9aNWVIWUFUSXYzRW5BNERHTTRIbHlkTHdTUF94ZXV0NkZUNnoxNFQzSERYekZMX1pfaHNYS0N6YVU3cy1lNTlxQjQ3ZjhMajZkR0NDcUnSAZMBQVVfeXFMTkNlbUhTblQ1LU1xNW44UktGWE1JVWNBaERpdjY1eFZHYnB4T0hBcWprUGJWTHZ6WnQtWWZ4WGt0dGt3Q0JPWjVlSFlBVEl2M0VuQTRER000SGx5ZEx3U1BfeGV1dDZGVDZ6MTRUM0hEWHpGTF9aX2hzWEtDemFVN3MtZTU5cUI0N2Y4TGo2ZEdDQ3FJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大</t>
+          <t>国際的サイバー攻撃集団「キリン」 中心メンバー、日本で拘束 ドイツで恐喝容疑、引き渡し - 朝日新聞</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1721,31 +1673,31 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190319</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9RZ3NyZDA2UUJfX2tYbE5tZ3lCVjVyV2FoWDZmakhSS2FjemVhLTdTWjEwUGxwSU5udGVVSktuOEhmVXc2SVgtQVZqZGZLN2FHM21JUkl5eUVVLUo5?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄</t>
+          <t>原子力研究機関から身分証200件が漏えい マイナンバー含む6人分も：2419件が不正アクセス被害 - ITmedia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1758,31 +1710,31 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190761</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE13UkxSeTZ0UjdLNm9FNTVCTm9XM3JTTlNWX003ODdyV3BXbXNKbEJRY3doUXlYRjBSeHdsSmdCSXJTZGxDTzVUb3RGY0VUSXRuaVduTjVqaDdUNHU4T05CUEZCU3JrQ0d4djJ2VjBBMEFCUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.28 Mon 8:00 Apache Tomcat に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月24日、Apache Tomcatにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.28 Mon 8:00 Apache Tomcat に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月24日、Apache Tomcatにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>ランサムウェア集団「KillSec」が摘発、管理者とされる人物はなんと16歳 - Korben</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1790,36 +1742,36 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBKblVNdnBuT0lCT29iSDlpUC1iS19qVzhnSDRLck16VGtzSThnbGZYUWc1ajMweVl0TDBDdXBqNmRYcUcxMFNQYWpDaXVPYTdRSVJuUmNEeHhKVUU0eE1SanE5SHVzZzJCaW5sVy1n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉鎖 遠州夢咲農業協同組合（JA遠州夢咲）は9月9日、不正アクセスによるホームページの一時閉鎖について発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉鎖 遠州夢咲農業協同組合（JA遠州夢咲）は9月9日、不正アクセスによるホームページの一時閉鎖について発表した。</t>
+          <t>ランサムウェア集団 Qilin（キリン）の中心メンバー日本で拘束、アサヒ攻撃にも関与 - ビジネス+IT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1827,74 +1779,66 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFB6ejVWZHZJdXdXZVRxWnVucG92MERnMVJBcEZOVDEtSHJPbDFfR0NVVjhhRWstd1NsTjVybEdmRkJWb1FYZV9vSFhQZkN3TmpLZG9Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Times Car (Park24)</t>
+          <t>合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Times Car (Park24)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>6.6M accounts (confirmed)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>ランサムウェア グループ Qilinの中核メンバーとされるロシア人、日本からドイツへ引き渡し―大阪で拘束、RaaSへの国際捜査 - 合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SmartScope / ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOWFZYOTBFQVBzei1paVI0S1B5MWktT2V6cmxraHpYeU5pd05MYkxYNFlUbW9VbF9HT250bVpuR0wyNEZjQU1YSDFLckhMWkJONFB2YU52bWpPbUVQdlg3UXBaWFhPclh2dlp4RFo0ei1abkdYUnF6c0xjczBWNFdOald4QkNHc2lxWmVlM1JTSy1GVXpwcjhHX0pVbFVpdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.25 Fri 8:00 ランサムウェアの被害報告件数が過去最多に ～ 警察庁 サイバー警察局便り 警察庁は9月10日、サイバー警察局便りR8Vol.15「「サイバー空間の脅威情勢」が公表されました 」を公開した。</t>
+          <t>anNetSecurity 2026.10.5 Mon 8:05 日本大学</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.25 Fri 8:00 ランサムウェアの被害報告件数が過去最多に ～ 警察庁 サイバー警察局便り 警察庁は9月10日、サイバー警察局便りR8Vol.15「「サイバー空間の脅威情勢」が公表されました 」を公開した。</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 日本大学の計 5 名の教員アカウントに不正アクセス、スパムメール送信の踏み台に 日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1914,31 +1858,31 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>川崎市施設のサイトに不正アクセス - サイト更新時に判明</t>
+          <t>株式会社LEAN BODYは9月15日</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>川崎市施設のサイトに不正アクセス - サイト更新時に判明</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 LEAN BODY が利用する分析ツール「Metabase」の脆弱性を悪用した不正アクセス 株式会社LEAN BODYは9月15日、同社が利用する分析ツールへの不正アクセスについて発表した。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1946,36 +1890,36 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190242</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>女性向け情報サイトの管理画面に不正アクセス - ハルメクHD</t>
+          <t>原田産業</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>女性向け情報サイトの管理画面に不正アクセス - ハルメクHD</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1988,68 +1932,68 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190247</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>コラム リーク・東郷 2026.9.25 Fri 8:10 今日もどこかで情報漏えい 第52回「2026年8月の情報漏えい」約一割で逮捕・懲戒・行政指導 8 月に最も件数換算の被害規模が大きかったのは、株式会社Eストアーによる「「ショップサーブ」に不正アクセス、不正なプログラムを実行し購入者情報を外部に送信」の 8,853,839 件であった。</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>コラム リーク・東郷 2026.9.25 Fri 8:10 今日もどこかで情報漏えい 第52回「2026年8月の情報漏えい」約一割で逮捕・懲戒・行政指導 8 月に最も件数換算の被害規模が大きかったのは、株式会社Eストアーによる「「ショップサーブ」に不正アクセス、不正なプログラムを実行し購入者情報を外部に送信」の 8,853,839 件であった。</t>
+          <t>「焼肉きんぐ」、会員情報漏えい - ｄメニューニュース</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News / SmartScope / Yagura</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5 / https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/ / https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5 / https://news.google.com/rss/articles/CBMiVkFVX3lxTE10RWhfeVpscm1XX19semJVbldGOFVzXzMzQ21aOXp4eUUzZklXUkVNVkQzSFh0LXY2NXI5UXRjaFNUM21neWlTWmI4eDQ2Qmc4VDdxVlJB?oc=5 / https://news.google.com/rss/articles/CBMijAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMtIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.25 Fri 8:05 ApplyNow 提供の採用管理プラットフォームに不正アクセス、マイナンバー含む個人データが漏えいした可能性 株式会社ApplyNowは9月9日、同社が提供する採用管理プラットフォーム「Interview Cloud」「ApplyNow」「ApplyNow Sign」への不正アクセスによる顧客および応募者の個人データが漏えいした可能性について発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.25 Fri 8:05 ApplyNow 提供の採用管理プラットフォームに不正アクセス、マイナンバー含む個人データが漏えいした可能性 株式会社ApplyNowは9月9日、同社が提供する採用管理プラットフォーム「Interview Cloud」「ApplyNow」「ApplyNow Sign」への不正アクセスによる顧客および応募者の個人データが漏えいした可能性について発表した。</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2057,39 +2001,39 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fines</t>
+          <t>White Essence（ disclosure ）</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fines — Entry point not stated</t>
+          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.54M records (in scope)</t>
+          <t>About 1.05M accounts (confirmed exfiltration), including customers, franchise staff and headquarters employees</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Entry point not stated</t>
+          <t>A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2114,24 +2058,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。</t>
+          <t>The Japan Times（tracker headline）</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Under investigation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2144,31 +2096,39 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.24 Thu 8:00 ISC BIND に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月18日、ISC BINDにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>Safer Internet Association（tracker headline）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.24 Thu 8:00 ISC BIND に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月18日、ISC BINDにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Unauthorized access to a server used by the association.</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2176,36 +2136,44 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.24 Thu 8:05 「paperlogic」に不正アクセス、現時点で情報の閲覧や外部への持ち出しが行われた痕跡は見つからず ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。</t>
+          <t>Osaka Metropolitan University（ news report ）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.24 Thu 8:05 「paperlogic」に不正アクセス、現時点で情報の閲覧や外部への持ち出しが行われた痕跡は見つからず ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>About 500 servers stopped; many backups encrypted. Personal data of at least 130,000 students and graduates stored; leak under investigation, per press-conference reports</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2213,39 +2181,39 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe</t>
+          <t>JOGMEC（tracker headline）</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe — Entry point not stated</t>
+          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22.18M rows (confirmed)</t>
+          <t>About 8,500 email addresses possibly affected</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Entry point not stated</t>
+          <t>Unauthorized access.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2270,24 +2238,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>理工学部教職員がフィッシング被害、不審メールが送信 - 日大</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>理工学部教職員がフィッシング被害、不審メールが送信 - 日大</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Up to 948,498 records (confirmed exfiltration; all personal data held). Also 611 point exchanges worth JPY 2,869,500 fraudulently converted into Amazon gift codes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2300,31 +2276,39 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190198</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.18 Fri 8:00 xxx.soumu.go.jp などのサブドメインも拒否に ～ 総務省を装うフィッシングメール対策強化 総務省は9月11日、同省を装ったなりすましメールへの対策強化について発表した。</t>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.18 Fri 8:00 xxx.soumu.go.jp などのサブドメインも拒否に ～ 総務省を装うフィッシングメール対策強化 総務省は9月11日、同省を装ったなりすましメールへの対策強化について発表した。</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>174,933 people; possible leak, with no actual leak confirmed</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2337,31 +2321,39 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>不正アクセスでサイト改ざん、内部に個人情報 - コンサル会社</t>
+          <t>777CON-PASS（tracker headline）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>不正アクセスでサイト改ざん、内部に個人情報 - コンサル会社</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2374,31 +2366,31 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189792</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.18 Fri 8:00 Android アプリ「【保護者専用】まなびポケット」にアクセス制限不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月15日、Androidアプリ「【保護者専用】まなびポケット」におけるアクセス制限不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.18 Fri 8:00 Android アプリ「【保護者専用】まなびポケット」にアクセス制限不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月15日、Androidアプリ「【保護者専用】まなびポケット」におけるアクセス制限不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2406,36 +2398,36 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.18 Fri 8:05 サーバ上にバックドア等の不正プログラムを設置 ～ 繋が運営するコーポレートサイトに不正アクセス 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.18 Fri 8:05 サーバ上にバックドア等の不正プログラムを設置 ～ 繋が運営するコーポレートサイトに不正アクセス 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2443,44 +2435,36 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PFU (PFU Direct)</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PFU (PFU Direct) — Entry point not stated; at a contractor or third party</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>169K records (up to, possible)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Entry point not stated; at a contractor or third party</t>
-        </is>
-      </c>
+          <t>日経に不正ログイン、1646人分の個人情報漏洩か - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2493,31 +2477,31 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1YRlYwQ2FEaWF6eW1yeU5Tb1phT0xzZEVLR1NOZzJKdDlvdDNibUNqYnFhTlFVT0RETHNYRURZVVZUZDBMRUxUU0FMQV81d1NGNW1CY3U3aDk0aXgwUkFMbU9RMUdaUFQwS0VNeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>従業員アカウントが侵害、なりすましメールが送信 - ホテル運営会社</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>従業員アカウントが侵害、なりすましメールが送信 - ホテル運営会社</t>
+          <t>日経にサイバー攻撃 情報漏洩、不審メール9000件送信 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2530,31 +2514,31 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189987</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9ieWIzdmlWUEVQcERJOUpzRDF0bU5lbTYyTG5TbWZIWUVYV05oampDY2E0cTJram1fMHRSdHNldmFtMTN6WVRXdFlzTGt2Zm8tZ0REQjNWRmVQblhDYWViMUlOOHVSemx5WjJfQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 さくらインターネットが不正アクセス調査結果を発表「さくらのレンタルサーバ」全サーバ再構築など再発防止策を掲げる さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 さくらインターネットが不正アクセス調査結果を発表「さくらのレンタルサーバ」全サーバ再構築など再発防止策を掲げる さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2562,36 +2546,36 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性</t>
+          <t>【アゴラ】岡本 裕明：身近に迫る不正アクセス：情報漏洩を前提とした自己防衛の必要性 - アゴラ 言論プラットフォーム</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2604,31 +2588,39 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190377</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE4zTGxURlBDZml5MDdMTTFLN0YwdEg0aGgweWFMVXJPbnNTbUxSTlY1cEFUeGhCQllqVEF6bDNmWWV6SU5vZzhUSG0zMzdpOGhVQzg3eGl2eUJ6Um8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>マルウェアの挙動をリアルタイム監視するOSSを公開 - JPCERT/CC</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>マルウェアの挙動をリアルタイム監視するOSSを公開 - JPCERT/CC</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>26 records (names, emails; possible leak)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2641,31 +2633,31 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/177455</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.16 Wed 8:00 a-blog cms にパストラバーサルの脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月11日、a-blog cmsにおけるパストラバーサルの脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.16 Wed 8:00 a-blog cms にパストラバーサルの脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月11日、a-blog cmsにおけるパストラバーサルの脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>AIの自律型サイバー攻撃が実環境へ、日本は中国国家支援型攻撃の標的3位-Microsoft Digital Defense Report 2026 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2678,31 +2670,31 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVHE0YWdDN0hDeEJ5dk5HVXBzZVY1NW56VTVUZ20wSnRnRmlwWGNKN082ZFR2cmc4bkVVNTBXNFhDME02cjlSS2UzRjFHNmFucUFXbzlBbldiaEtaRWZVS1I4RENKejVZT0RyNzlqcHlpaERjMmlCMWdRci1uY1RPbUJoamF6Y1pLSGtsdkRoTTVIUUJMLWJSZ0I5SHFrdHMwZHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2715,31 +2707,31 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189866</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.16 Wed 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 つるみ観光株式会社は8月27日、4月10日に公表した同社が運営するホテル白菊が利用する宿泊予約・販売管理システムへの不正アクセスの可能性について、調査結果を発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.16 Wed 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 つるみ観光株式会社は8月27日、4月10日に公表した同社が運営するホテル白菊が利用する宿泊予約・販売管理システムへの不正アクセスの可能性について、調査結果を発表した。</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2752,31 +2744,39 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5 / https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>「SonicWall SMA 100」にアップデート - 既知マルウェアの除去機能を追加</t>
+          <t>MoonStar（tracker headline）</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「SonicWall SMA 100」にアップデート - 既知マルウェアの除去機能を追加</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Customer information possibly affected</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2789,31 +2789,39 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/174925</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>「Citrix NetScaler」に複数脆弱性 - 2件で悪用を確認、侵害調査を</t>
+          <t>Abahouse（tracker headline）</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「Citrix NetScaler」に複数脆弱性 - 2件で悪用を確認、侵害調査を</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Member and order information</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2826,31 +2834,31 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190746</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>「Catalyst SD-WAN Manager」にゼロデイ脆弱性 - 更新や侵害調査を</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「Catalyst SD-WAN Manager」にゼロデイ脆弱性 - 更新や侵害調査を</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2863,39 +2871,31 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190883</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gyazo (Helpfeel)</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gyazo (Helpfeel) — Vulnerability</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>23.62M records (confirmed)</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2908,31 +2908,31 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.15 Tue 8:00 IPA「経営者のためのランサムウェア対策ハンドブック」公開 ～ 脅威に立ち向かうには経営者の関与が不可欠 独立行政法人情報処理推進機構（IPA）は9月8日、「ランサムウェア被害から学ぶ教訓集～経営者のためのランサムウェア対策ハンドブック～」を公開した。</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.15 Tue 8:00 IPA「経営者のためのランサムウェア対策ハンドブック」公開 ～ 脅威に立ち向かうには経営者の関与が不可欠 独立行政法人情報処理推進機構（IPA）は9月8日、「ランサムウェア被害から学ぶ教訓集～経営者のためのランサムウェア対策ハンドブック～」を公開した。</t>
+          <t>本当に怖い情報流出---日本を狙うサイバー攻撃 - 日経クロステック（xTECH）</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2945,31 +2945,31 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQdmFuWXlsYWRBNU94UUZvQUU5QlM0aHdNNVViTnFMaG00aGtwV0lOQlVYTVdHR3NLNjZGWXlsRFA0OUFhc2lLMTZfcjJEbDRmVW44V0JVblZqTmkyd0xPcHpfaVJWMDhLX2tvQXU1TVoxMXNwU28yTTNTN1Q0RVNkbk1XWm9ueGNyejZnTmhsaERPUldXVHdLZGRtajZiUmxzZmNOY0xQTFdyN0dQTFpjR2dISkhvOTdab0hOa2V3R21yWUNNVGxfZ2MzTEhiMTVjVWVtN2RfcndLZWh1bnFKbE92TW81S3pDM3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2982,31 +2982,31 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190315</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>予約サイトなどで侵害、影響など調査中 - 審美歯科チェーン</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>予約サイトなどで侵害、影響など調査中 - 審美歯科チェーン</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3014,66 +3014,66 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189665</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5 / https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>サイト改ざん被害、CMS脆弱性で - 東京都管工事工業協同組合</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>サイト改ざん被害、CMS脆弱性で - 東京都管工事工業協同組合</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News / Security NEXT</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189799</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5 / https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.15 Tue 8:05 MAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」に不正アクセス 株式会社RBW JAPANは9月3日、同社が運営するMAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」への不正アクセスについて発表した。</t>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.15 Tue 8:05 MAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」に不正アクセス 株式会社RBW JAPANは9月3日、同社が運営するMAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」への不正アクセスについて発表した。</t>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.2 Fri 8:00 PFU 製 Image Scanner Driver for Linux に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月29日、PFU製Image Scanner Driver for Linuxにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3093,39 +3093,31 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LEAN BODY</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEAN BODY — Vulnerability</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>440K accounts (confirmed)</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:00 日本標準時の供給サービスで異常、誤った時刻を配信 国立研究開発法人情報通信研究機構（NICT）は9月11日、日本標準時の供給サービスでの異常の発生について発表した。</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3133,36 +3125,36 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.14 Mon 8:00 不正アクセスや報告遅れを中心に民間 98 件へ指導 ～ 個人情報保護委員会が第367回会合を開催 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.14 Mon 8:00 不正アクセスや報告遅れを中心に民間 98 件へ指導 ～ 個人情報保護委員会が第367回会合を開催 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。</t>
+          <t>「PC調達はもはや経営層が考えるべき課題」 “侵入前提”時代に問われるエンドポイントの真価 (1/3) - ASCII.jp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3175,31 +3167,39 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1KSHFOenp1MVlHOEd1dDd2REo2eVE0UmlaLW9iR1RoRThRRWVtTFJXb1ZFN2FoTDN4QlFfZkpUSThBOWRNeHQzTEJwNUpJX1FscTRkZg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県</t>
+          <t>Toyobo MC（tracker headline）</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>About 1,500 suspicious emails</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Two employees' accounts accessed via phishing.</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3212,31 +3212,39 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189985</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.14 Mon 8:00 SHIRASAGI に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月10日、SHIRASAGIにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>Three educational institutions（tracker headline）</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.14 Mon 8:00 SHIRASAGI に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月10日、SHIRASAGIにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3249,31 +3257,39 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.14 Mon 8:05 TRUNK 従業員のメールアカウントに不正アクセス、不審メール送信も確認 ホテル企画運営を行う株式会社TRUNKは9月1日、同社従業員のメールアカウントへの不正アクセスについて発表した。</t>
+          <t>Kodansha BECK（ news report ）</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.14 Mon 8:05 TRUNK 従業員のメールアカウントに不正アクセス、不審メール送信も確認 ホテル企画運営を行う株式会社TRUNKは9月1日、同社従業員のメールアカウントへの不正アクセスについて発表した。</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>50 suspicious emails; traces of mailbox-data acquisition</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3281,36 +3297,44 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4,026 phishing emails</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Unauthorized access to Microsoft 365.</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3323,31 +3347,39 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>政府共通の業務実施環境「GSS」に不正アクセス - VPN機器の脆弱性を悪用</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>政府共通の業務実施環境「GSS」に不正アクセス - VPN機器の脆弱性を悪用</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>13 passports and other data</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3360,31 +3392,39 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190208</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.11 Fri 8:00 baserCMS用プラグイン「BurgerEditor」に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月9日、baserCMS用プラグイン「BurgerEditor」における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.11 Fri 8:00 baserCMS用プラグイン「BurgerEditor」に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月9日、baserCMS用プラグイン「BurgerEditor」における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>About 120,000 people (about 50,000 employees, about 70,000 former employees); possibly viewed or leaked</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3397,31 +3437,31 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3429,36 +3469,36 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188880</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.11 Fri 8:00 立教大学利用のGoogeアカウントに不正アクセス、合計17,668件の迷惑メールを送信 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.11 Fri 8:00 立教大学利用のGoogeアカウントに不正アクセス、合計17,668件の迷惑メールを送信 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。</t>
+          <t>日本原子力機構に不正アクセス 研究者の個人情報が漏えい（共同通信） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3466,36 +3506,36 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>「東京外環プロジェクト」サイトで侵害のおそれ - 公開を一時停止</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「東京外環プロジェクト」サイトで侵害のおそれ - 公開を一時停止</t>
+          <t>日本原子力機構に不正アクセス 研究者の個人情報が漏えい - Infoseek</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3508,24 +3548,24 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済</t>
+          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3545,39 +3585,31 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS) — Vulnerability</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>246K records (possible)</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
+          <t>グッズ作成サービス、クレカ情報含む個人情報流出の可能性</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -3590,31 +3622,31 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190511</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社</t>
+          <t>株式会社ラック デジタルペンテスト部 2026.10.1 Thu 8:20 Micro</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社</t>
+          <t>エクスプロイト 株式会社ラック デジタルペンテスト部 2026.10.1 Thu 8:20 Microsoft Malware Protection Engine における任意の特権ファイルの書き込みが可能となるファイル操作での検証不備（Scan Tech Report） 2026 年 5 月に修正された Microsoft Defender を構成するソフトウェアの脆弱性を悪用するエクスプロイトコードが公開されています。</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -3627,31 +3659,31 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>システムがランサム被害、一部業務を停止 - インキメーカー</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>システムがランサム被害、一部業務を停止 - インキメーカー</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 CMSプラグインの脆弱性公表を受け更新作業中に不正アクセスを発見 神奈川県川崎市は9月11日、かわさき新産業創造センター（KBIC）Webサイトへの不正アクセスについて発表した。</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3659,36 +3691,36 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 NEXCO東日本の東京外環プロジェクトホームページで不正アクセス疑い 東日本高速道路株式会社（NEXCO東日本）は9月4日、東京外環プロジェクトホームページの一時公開停止について発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 NEXCO東日本の東京外環プロジェクトホームページで不正アクセス疑い 東日本高速道路株式会社（NEXCO東日本）は9月4日、東京外環プロジェクトホームページの一時公開停止について発表した。</t>
+          <t>『【経営層向け】ランサムウェア被害の6割は中小企業、「うちは狙われない」が危ない』というテーマのウェビナーを開催 - ニコニコニュース</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3696,44 +3728,36 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9pR0FLVEV0WlFjNDZLeGFneXVwbEh2WjhpSTBMaXNzd1lMYnh6XzUwNFNkYWVhbG5OWUp2Qi1qZFlsSlBlSlMxc3R2M2VqbHBfX3lpZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sakura Internet</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sakura Internet — Entry point not stated</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.36M accounts (up to, possible)</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3746,31 +3770,39 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1,463 refund records, including 751 bank-account records</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3783,31 +3815,39 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>学生の複数アカウントに不正アクセス、スパム踏み台に - 立教大</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>学生の複数アカウントに不正アクセス、スパム踏み台に - 立教大</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>About 128GB and 159,901 files (attacker claim)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Unauthorized access and data theft claimed by ransomware group Everest.</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3820,31 +3860,39 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190050</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.9.9 Wed 8:00 「フィッシング対策セミナー2026」11 / 19 開催 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.9.9 Wed 8:00 「フィッシング対策セミナー2026」11 / 19 開催 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Up to 442,779 people; possibly viewed</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3857,31 +3905,39 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.9 Wed 8:05 DAIKO NEXT LINK のメールアカウントに不正アクセス、二次被害と不正送信の拡大防止のためメールシステムを一時的に停止 DAIKO NEXT LINK株式会社は8月19日、同社メールシステムへの不正アクセスについて発表した。</t>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.9 Wed 8:05 DAIKO NEXT LINK のメールアカウントに不正アクセス、二次被害と不正送信の拡大防止のためメールシステムを一時的に停止 DAIKO NEXT LINK株式会社は8月19日、同社メールシステムへの不正アクセスについて発表した。</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Some history data erased</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Unauthorized access to point-exchange system.</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3889,36 +3945,44 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.8 Tue 8:00 サイバー攻撃の「被害経験なし」企業は約 6 割へ減少 ～ 東商2026年アンケート調査 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。</t>
+          <t>Lashinbang（tracker headline）</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.8 Tue 8:00 サイバー攻撃の「被害経験なし」企業は約 6 割へ減少 ～ 東商2026年アンケート調査 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Under investigation</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -3926,36 +3990,44 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>グループのシステムに不正アクセス、個人情報流出の可能性 - 三井不動産</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>グループのシステムに不正アクセス、個人情報流出の可能性 - 三井不動産</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>175 people; 367 files</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Unauthorized access and unauthorized downloads.</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -3968,31 +4040,39 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189789</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.8 Tue 8:05 さくらインターネットへの不正アクセス、案内ページを公開 さくらインターネット株式会社は8月20日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについての案内ページを公開した。最新のニュースリリース、FAQの他、必要な案内を随時掲載している。</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.8 Tue 8:05 さくらインターネットへの不正アクセス、案内ページを公開 さくらインターネット株式会社は8月20日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについての案内ページを公開した。最新のニュースリリース、FAQの他、必要な案内を随時掲載している。</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>134 records possibly viewed; investigation found no evidence of a leak</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4000,36 +4080,36 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TheRegister The Register誌特約記事 2026.9.8 Tue 8:20 AI がランサムウェア攻撃全工程を実行、被害企業に 80 ページにわたる“セキュリティ監査報告書”まで提出 「攻撃者は戦術面での実行を AI エージェントに委ね、エージェントは監視・評価・行動・再計画のサイクルをリアルタイムで繰り返し、攻撃の各段階の"継ぎ目"で（人間による判断なら必ず発生する）遅れをなくすことで、侵入工程全体を一貫して高速化した」</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TheRegister The Register誌特約記事 2026.9.8 Tue 8:20 AI がランサムウェア攻撃全工程を実行、被害企業に 80 ページにわたる“セキュリティ監査報告書”まで提出 「攻撃者は戦術面での実行を AI エージェントに委ね、エージェントは監視・評価・行動・再計画のサイクルをリアルタイムで繰り返し、攻撃の各段階の"継ぎ目"で（人間による判断なら必ず発生する）遅れをなくすことで、侵入工程全体を一貫して高速化した」</t>
+          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -4037,36 +4117,36 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>社内ファイルサーバが侵害、情報流出が判明 - アンビションDX</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>社内ファイルサーバが侵害、情報流出が判明 - アンビションDX</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4079,24 +4159,24 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>東産業 公式サイトにwp2shell を悪用した不正アクセス</t>
+          <t>警察庁が対策情報を紹介 警察庁</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>東産業 公式サイトにwp2shell を悪用した不正アクセス</t>
+          <t>脅威動向 ScanNetSecurity 2026.9.30 Wed 8:00 ランサムウェア被害件数が過去最多の123件に、警察庁が対策情報を紹介 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -4116,31 +4196,31 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>日本大学の計 5 名の教員アカウントに不正アクセス、スパムメール送信の踏み台に</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>日本大学の計 5 名の教員アカウントに不正アクセス、スパムメール送信の踏み台に</t>
+          <t>生成AIのセキュリティー事故、企業の8割弱が経験 情報漏洩が最多 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -4153,68 +4233,68 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE93WlkzOEpUREtCN2VCNm5lWnYwamlTaGtNRl94TEVRT2w2d3JCSjBsS0JzR2Nvb3JuM0xLR0RMcDBZbE56OF9HZG1lNG5ORF96QXk0N2ZRcUhJVmIzZ3dxbGk1dnVCSGJESmRLNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ムラウチドットコムに不正アクセス、7,716,811件の個人情報が漏えい</t>
+          <t>名が Micro Hardening 演習 山陽小野田市立山口東京理科大学</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ムラウチドットコムに不正アクセス、7,716,811件の個人情報が漏えい</t>
+          <t>業界動向 ScanNetSecurity 2026.9.30 Wed 8:00 山口東京理科大チームが優勝 ～ 県警ら主催「サイバー攻撃共同対処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ScanNetSecurity / SmartScope / Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/ / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.7 Mon 8:00 PALLET CONTROL 製品にアクセス制御不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.7 Mon 8:00 PALLET CONTROL 製品にアクセス制御不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+          <t>大阪ガス系2社で顧客情報漏洩の可能性 不正アクセス、約8260件 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -4222,36 +4302,36 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5KMkxuSnlqWlVzSjhsMVlFRWpYa3lZWHJ2YVFocXB1SHFhZUd6ZmFPOWk3TkVtY2ZRY2syLXdMZkxlNElWeWdXYXBDRkhpblNxeFJyQlhCeDJBdks2MXl4amN6aWxIZmdCZ0tjdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 01銀行のシステムに不正アクセス、最大100社の情報が漏えい 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 01銀行のシステムに不正アクセス、最大100社の情報が漏えい 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。</t>
+          <t>サイバー攻撃の兆候、インフラ企業に報告義務 被害未然防止へ法施行 - 日本経済新聞</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -4259,29 +4339,29 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE84a0ZKWkwzQnZ5SXktLUdfSnZENURqMUJkTm1YaDRXcnc1d2dJUzVLdmYxeUR0ZmVaaEFlTHltOGdQQUx3bkYyaEw4N05vNkNsSEU4WTZvLUI5eXNjU3pvS0Z6b3MyU21YbF83cQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 保育上の不適切な対応も確認 ～ 鎌倉市児童発達支援センターあおぞら園で個人情報を誤送付 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -4296,36 +4376,36 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>「まんだらけ」サーバに不正侵入、情報流出か - 通販やオークションは再開</t>
+          <t>株式会社ハルメクホールディングス</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「まんだらけ」サーバに不正侵入、情報流出か - 通販やオークションは再開</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -4338,31 +4418,31 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189663</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性</t>
+          <t>「郵便局アプリ」に不正アクセス 氏名や送り先住所など漏えい 19人分・69件 - ITmedia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -4375,94 +4455,5353 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Coop Yamaguchi (LINE mini app)</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coop Yamaguchi (LINE mini app) — Entry point not stated</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>217K records (possible)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Entry point not stated</t>
-        </is>
-      </c>
+          <t>「代金後払いサービス」で侵害、サービスを停止 - ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT / ScanNetSecurity / Google News</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html / https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/09/15 宮崎県教育委員会、県立学校の西都地区生徒寮でサポート詐欺被害 — 運営受託先の業務用パソコンが遠隔操作され、入寮者76人・寮職員10人の情報が流出した可能性 続報を注視中 中程度 宮崎県教育委員会は2026年9月6日、西都市内の「西都地区生徒寮」で業務用パソコンがインターネットを通じて不正アクセスを受け、個人情報が漏えいした可能性があると公表した。2026年9月4日夕方、寮の管理人が防災気象情報を調べていた際に「ウイルスに感染した」とする警告画面が表示され、画面に記載された電話番号へ連絡したところ、パソコン関連会社の社員を名乗る人物の指示で業務用パソコンを遠隔操作された。2020年度から2026年度までの入寮者76人と、2024年度から2026年度までの寮職員10人の情報が対象となっている。 →</t>
+          <t>VOISING</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026/09/15 宮崎県教育委員会、県立学校の西都地区生徒寮でサポート詐欺被害 — 運営受託先の業務用パソコンが遠隔操作され、入寮者76人・寮職員10人の情報が流出した可能性 続報を注視中 中程度 宮崎県教育委員会は2026年9月6日、西都市内の「西都地区生徒寮」で業務用パソコンがインターネットを通じて不正アクセスを受け、個人情報が漏えいした可能性があると公表した。2026年9月4日夕方、寮の管理人が防災気象情報を調べていた際に「ウイルスに感染した」とする警告画面が表示され、画面に記載された電話番号へ連絡したところ、パソコン関連会社の社員を名乗る人物の指示で業務用パソコンを遠隔操作された。2020年度から2026年度までの入寮者76人と、2024年度から2026年度までの寮職員10人の情報が対象となっている。 →</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>About 170,000 records; confirmed leak</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19 people; 69 records</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Up to about 70,000 records</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Australia says OpenAI hacked government website, checks for breaches OpenAI、豪政府サイトに不正アクセス 「意図せぬ行動」再び - 朝日新聞</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE83MWJkTXdUWVhLTUpqeDdaYTB2RVc1emxlY2tXakxmdDBlcHJ5MTV1YmZhY3dfeFRLb0R2eFNHd2VXZHFBenlOZE9USTZjWE1VZkdDVXpB?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁が注意喚起する「WaterPlum」の手口 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>東京メトロ、配信停止中のメアド5.9万件漏洩か 不正アクセスで - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9BU2lreXpEWmpfTWpSVmJncHp4Zy12bTBPQUMyTHZmRHZ4aDluaGdkYVhaZ2lBbnRfVDU1SnNiVEVQMk5xVTNqZjQzbzBMclNfSkg3YTJBX1ZRbjM4V290WWx1NnR6UHFyY2Iybg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>モンベルのグローバルサイトに不正アクセス - 個人情報流出の可能性</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190798</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>セコマ57万件情報流出か アプリサーバーに不正アクセス - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5VVjI5aXhVTVR1MGVkWEFmZ0ZBUmtkT2h0Tm1YSmdyeHp6WDhoZzkybzlSUklIQ3RsQkFrOWxSUEZRdmtmYmt6NEJaMmZGbGZPaHk2WGUyRzhoR0k0Mmh5VFEyNGVORnlQaHBzYQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.29 Tue 8:00 baserCMS 用プラグイン「アドオンマイグレーター」 に信頼できない制御領域からの機能の組み込みに関する脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月25日、baserCMS用プラグイン「アドオンマイグレーター」 における信頼できない制御領域からの機能の組み込みに関する脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>株式会社スマレジは9月25日</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.29 Tue 8:05 「スマレジEC・リピート」「スマレジEC・B2B」に不正アクセス、一部の個人データが閲覧・取得された可能性 株式会社スマレジは9月25日、同社が提供する「スマレジEC・リピート」および「スマレジEC・B2B」への不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190791</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 (2026年9月29日掲載) - ライブドアニュース</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Toyobo Textile（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>About 1,500 phishing emails</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Unauthorized access to an email account.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Saga University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Saga University（tracker headline） — Ransomware.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NAS files</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ransomware.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>QUO Card（ news report ）</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>The number of people affected is under investigation; LINE display names and prize data possibly viewed/leaked</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>International House of Japan (library)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Some company names and passwords possibly leaked</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Unauthorized access to library catalog system (OPAC).</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>— (no information leak confirmed)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Unauthorized access to internal network.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 →</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>Yagura</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>10日間のうちに国内有名企業10社超で情報漏洩・障害・サイバー攻撃被害……まだまだ増える可能性 - EnterpriseZine</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9aMWJJa01JVzdWTkpEX0traTRqRXJjUVo3SkQwRy1OUUItSGY1Tm9vTFIyckluZndKZ1d4SGdXcWRHWTRJZkRQX2ttNmNCblVDTHViRlV3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>脅威動向 ScanNetSecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大、金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190734</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190319</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>タイムズカー､個人情報最大660万件流出 不正アクセスで免許証画像も - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Google News / ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-15-miyazaki-saito-dormitory-support-scam/ / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/ / https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/ / https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/ / https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/ / https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/ / https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9DSHRJZklXRUpsU2pqeDBjcmY1SV9pYm5KUE5rX20yM0VRQUlBcGppWDNMT011VW54SVVjUm1RRmpBbzB6STRqN0dhcVVSRndGRmpjZ0tvdDdtTmxqN2h0VkNlVDNMaFJ6bHU0ZA?oc=5 / https://news.google.com/rss/articles/CBMickFVX3lxTE92eVZBNl9JYW84SjNCZDdmclBUMTRmWTZXbVpCVWZnWGJkaEd2Mm9tYmFoQXA4aWpqSWwwdTVjdjVUOUxLYWFhc3czbVp6b1RadFU3WU9sdWNrNzJRSWVkQTgxVDdPdWlxbWtGSno4OFg3UQ?oc=5 / https://news.google.com/rss/articles/CBMib0FVX3lxTE1QWWJJZnByYU1NMVZwQ2xxM09hOE9rMlNjTVZoOUFuZWZodUs1RG9HRXpkZnBwa1F6djNtYXUzUUJiOHR3SjZVMUs3bWxrUFZRNlA5eVJzZ21SLWl6UG1mZnBEUXZCZXZOWWJMcllJMNIBdEFVX3lxTE94emZZWExhbWRzWFhLaDl0VzRabzUtSFdCWjhqSUxtMHZQN0M5SEVUNHVheDY1LUdIWVduQjJDRG1nMXduOFVNTFFlcnBNdjc1X1dxWVBsUWR3UF9wa0dSNExrVlBac3FhWDY4aFNQX3lMTUR5?oc=5 / https://news.google.com/rss/articles/CBMiaEFVX3lxTE1nTl93d1ppRW9DVWNIeDFhMTRiUkJoM1VmZVBGdHhxdWpUVzk2a21kUjVlQm0zVmhyZjJCNEVDMHcxM3ExMmxjUzNfUTBVVTlZZFFXR0JRSThiVlpYN1oyei1iZ3hib1Ny?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://news.google.com/rss/articles/CBMif0FVX3lxTFBKYmRXbHFjZUtERmVtSVRiT0sxOVRnSmtkSlRCTG96RTl1ME82QTk3b1FoXzBQbE9yT0xiZnQ2WW96bmRfVFNDZVdvcVVBZWx3ZVI0dERERkY4ZXVWaDV4RGppVGlnanVRV0tUVmJFVUZhMTdPWG81czBxRXBfR2s?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://news.google.com/rss/articles/CBMihwFBVV95cUxQZXhpTWN6dFYxcUE1RTFMaml4NjBOLWhCTEc2bF9QbHhRYlZERFpQNzJVb1Y3WEhQVXl3T1dLaGZ6RWFLMUhnLTRFc2dxYjlUZVFPOG16azlZLUFPZWdHUVM0MHNrRUZRbkZ4cFRWcjFpZ1NEU1ZWMjJJSXlGdF9LSGtSenVlUjQ?oc=5 / https://news.google.com/rss/articles/CBMiUkFVX3lxTE1CSnE2ZnFFVHJVNGdxTFBiVlpWUEQ5bGJ0ckdfYWRkaFBDZUtWcVdGQlludURmbGN1amxibTM5SFZienpPNUVCQjcydGVlMVNkS1E?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE5CeWszRFptYlQ5SEF5MkhUMXFnT080T2w0WTRzbkZRZFlvSkdBdTU3TGVram1Oc1FVR2lvd3BJX0NLaXZEcGUzRHFZNGx4WnlmV1V5SzMyZHlnaWFydW04YTZTekZHeUZDZVlDLWE2ZlNEMEJPS1k0ZjdZR1B1b2s?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.28 Mon 8:00 Apache Tomcat に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月24日、Apache Tomcatにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>旭化成</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity / Google News</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html / https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5 / https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉鎖 遠州夢咲農業協同組合（JA遠州夢咲）は9月9日、不正アクセスによるホームページの一時閉鎖について発表した。</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tokyo Metro (Metpo)（news report）</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>About 59,000 email addresses</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Unauthorized access; cause under investigation.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>レゴランド・ジャパン・ホテル、Amadeus予約基盤への不正アクセスで1,557件の個人情報へ影響 - 合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQ0VnZl9JMW9YS2dqRlZPcWlDVXE0ckFhYW5IbUdIWlpHZGRYMG9iUFRGeXdrWWNQajdsSWZuQXF0R3hKR25PRmkzbmxMQjJ3UkJuUC1pTE9SLWU5VU9wTjJQTFNfR3p1XzBEQzNZOER4dTZzVHJkZ1FGdWwtUjJRbjFBZjhyYnRISGthTF94WXY1aUdKQU9sUVdPc3BWUkQ4RmpBQXBOaVRpSWRy?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Nippon Rent-A-Car (app)（news report）</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>41 people, revised to 55</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Some systems stopped; whether data leaked under investigation</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 →</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Yagura / Security NEXT / ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/ / https://www.security-next.com/190761 / https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ウェアの被害報告件数が過去最多に ～ 警察庁 サイバー警察局便り 警察庁</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.25 Fri 8:00 ランサムウェアの被害報告件数が過去最多に ～ 警察庁 サイバー警察局便り 警察庁は9月10日、サイバー警察局便りR8Vol.15「「サイバー空間の脅威情勢」が公表されました 」を公開した。</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>川崎市施設のサイトに不正アクセス - サイト更新時に判明</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190242</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>女性向け情報サイトの管理画面に不正アクセス - ハルメクHD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190247</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>株式会社Eストアーによる「「ショップサーブ」に不正アクセス</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>コラム リーク・東郷 2026.9.25 Fri 8:10 今日もどこかで情報漏えい 第52回「2026年8月の情報漏えい」約一割で逮捕・懲戒・行政指導 8 月に最も件数換算の被害規模が大きかったのは、株式会社Eストアーによる「「ショップサーブ」に不正アクセス、不正なプログラムを実行し購入者情報を外部に送信」の 8,853,839 件であった。</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>大興印刷</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.25 Fri 8:05 カルビーのプロ野球チップス関連サービス「PhotoGoods」で個人情報漏えいの可能性 カルビー株式会社は9月17日、同社業務提携先での個人情報等の漏えいの可能性について発表した。</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>株式会社ApplyNowは9月9日</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.25 Fri 8:05 ApplyNow 提供の採用管理プラットフォームに不正アクセス、マイナンバー含む個人データが漏えいした可能性 株式会社ApplyNowは9月9日、同社が提供する採用管理プラットフォーム「Interview Cloud」「ApplyNow」「ApplyNow Sign」への不正アクセスによる顧客および応募者の個人データが漏えいした可能性について発表した。</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Smaregi EC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Customer environments of four client companies; no card data held</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Exploitation of an administrator-login vulnerability.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 →</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Yagura / ScanNetSecurity / Security NEXT</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>3</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/ / https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://www.security-next.com/190842</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>警察庁、2026年上半期のサイバー脅威情勢を公表 ランサムウェア被害123件で半期過去最多 - JAPANSecuritySummit Update</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE11SWJBcFY3MHN1dnZSalhvT1NTY3Y3SUQ3cTRKUGxFeVBFQTd5NGxQYldjcTNEbklzV3ZHQjJnbzloMF9RWS1OZHJwMF84UjFDdTlHT0xfQlFfdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.24 Thu 8:00 ISC BIND に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月18日、ISC BINDにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>非常勤講師が外部SNSサービス「hyocom」を利用 関西学院大学</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.24 Thu 8:05 関西学院大学で学生の個人情報が閲覧可能な状態に、非常勤講師が外部SNSサービス「hyocom」を利用 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>株式会社は9月1日</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.24 Thu 8:05 「paperlogic」に不正アクセス、現時点で情報の閲覧や外部への持ち出しが行われた痕跡は見つからず ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>About 22.18M rows; transfer outside confirmed. Company says conversion to a population count is difficult</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Unauthorized access to an email account.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ryomo Systems（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ransomware group SafePay published stolen data.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>426 accounts</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>理工学部教職員がフィッシング被害、不審メールが送信 - 日大</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190198</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>業界動向 ScanNetSecurity 2026.9.18 Fri 8:00 xxx.soumu.go.jp などのサブドメインも拒否に ～ 総務省を装うフィッシングメール対策強化 総務省は9月11日、同省を装ったなりすましメールへの対策強化について発表した。</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>不正アクセスでサイト改ざん、内部に個人情報 - コンサル会社</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189792</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ランサムウェア、暗号化前にバックアップ破壊 「Living off the Land」が72％増、Halcyon調査 - JAPANSecuritySummit Update</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1xcHlJQ3NScXQzTFdrdHkxOHI2T1U3ZXlGUVV1NWpvMVdTX1NyZWFZR3FpdEo0V3VXb3QyeUNaOG9ZdEhuS2NxVXRGWmFiUEo1alJEa2FvNGJxQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.18 Fri 8:00 Android アプリ「【保護者専用】まなびポケット」にアクセス制限不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月15日、Androidアプリ「【保護者専用】まなびポケット」におけるアクセス制限不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>株式会社繋は8月27日</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.18 Fri 8:05 サーバ上にバックドア等の不正プログラムを設置 ～ 繋が運営するコーポレートサイトに不正アクセス 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>26.9.18 Fri 8:05 ウェブ画面設定誤りが原因「オペラ銀河鉄道</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.18 Fri 8:05 ウェブ画面設定誤りが原因「オペラ銀河鉄道の夜」合唱申込フォーム入力の個人情報が閲覧可能に 公益財団法人名古屋市文化振興事業団は8月28日、瑞穂文化小劇場での個人情報漏えいについて発表した。</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Bellcadia (montbell global site)（ news report ）</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Up to 15 people</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>従業員アカウントが侵害、なりすましメールが送信 - ホテル運営会社</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189987</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>千葉銀行子会社サイトに不正アクセス 顧客情報漏洩の可能性 - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAzQXdsOHpVVXRERzRWLS1pTDRYdEx5X2VURmduRVhDYlUwR2tiSHBvX3p5QWtfSHhoaGNOZTRYeEEtbk9jWUp3LUFsRDZuYlBFa1BnRkduWXJRNmZQVW9SX2MwNVhjSFV4M2ZPYw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>株式会社は9月10日</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 さくらインターネットが不正アクセス調査結果を発表「さくらのレンタルサーバ」全サーバ再構築など再発防止策を掲げる さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学が契約しているレンタルサーバでのWebサイト改ざん 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>「秘密情報流出」急上昇でトレンド入り、ネット「氷山の一角」「今までも日本では多くの技術を外国に」 - スポニチ Sponichi Annex</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQeUpuanlYamNuN2hYYjFRZzhZVTdhYTV6V1ZRemktMTJFSmpwWnN5b19MaG9wd3ktT1NUeUwtem9abnpjUXRKMGk2UjBmd2VIUHV0SHNOVTFLcDVnSWlkaDlaWGY2emJRdnNFSDIxajZZLUY0aFgyM2JjT3BvWTZRWkRCS3ZycGppR1p5NWp3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Osaka City (recorded interview system)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>106 people</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>— (some pages defaced; no personal-data leak confirmed)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Website accessed. Measures applied against the causal vulnerability.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>9 people</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Vulnerability exploitation.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Calbee (baseball-chip cards)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Credit-card data possibly affected</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190377</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>株式会社のプレスリリース - PR TIMES</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ランサムウェアは、暗号化より先にバックアップを消す | Halcyon Japan株式会社のプレスリリース - PR TIMES</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBSbC1lV3Ewa2syR1FCYnhZTlFxcHNHSGY1YkwxZTBMODFkT3NTRkpfUkE3QjJrUVEyNllrRTNZRHdkSi1mRHpKOEo3SlpNMjhDaHZXYjI4Wlo1R3hLcXpYM0NKX21oTXlGblE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.16 Wed 8:00 a-blog cms にパストラバーサルの脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月11日、a-blog cmsにおけるパストラバーサルの脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189866</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>株式会社は8月27日</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.16 Wed 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 つるみ観光株式会社は8月27日、4月10日に公表した同社が運営するホテル白菊が利用する宿泊予約・販売管理システムへの不正アクセスの可能性について、調査結果を発表した。</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Attacker claims about 4TB acquired</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Unauthorized access to EC site.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>About 23.62M user-data records, confirmed leak, including about 18.01M anonymous users. Separately about 490M image-metadata records; Sep 25 second report adds about 174M deleted-image metadata records</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SmartScope / Yagura / ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>3</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/ / https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）は9月8日</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.15 Tue 8:00 IPA「経営者のためのランサムウェア対策ハンドブック」公開 ～ 脅威に立ち向かうには経営者の関与が不可欠 独立行政法人情報処理推進機構（IPA）は9月8日、「ランサムウェア被害から学ぶ教訓集～経営者のためのランサムウェア対策ハンドブック～」を公開した。</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>予約サイトなどで侵害、影響など調査中 - 審美歯科チェーン</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189665</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>株式会社RBW JAPANは9月3日</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.15 Tue 8:05 MAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」に不正アクセス 株式会社RBW JAPANは9月3日、同社が運営するMAMAMOO JAPAN OFFICIAL FANCLUB「MOOMOO JAPAN」への不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ）</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>7,716,811 records; confirmed exfiltration</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>About 440,000 accounts, confirmed acquisition, including former members; actual population expected to be smaller</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>26,489 records possibly affected</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Unauthorized access to cloud storage.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネット</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 →</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/ / https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/ / https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.14 Mon 8:00 不正アクセスや報告遅れを中心に民間 98 件へ指導 ～ 個人情報保護委員会が第367回会合を開催 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189985</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>プルデンシャル生命、1570人の顧客情報漏洩 元営業社員が紛失 - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBzdVVabF9ZbmZEemdxcEFOTzl6SGVDOGFEZlBvdEZGSEt5bUtHcmhxZkRRWUdOdmNVNU1VaVpiVEhDWDBkS2dmdUh6dG1UNnhhU2dCM2NjRzJqWVRLYjlySEZWVnNQeXkzVU5LaQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>株式会社のプレスリリース - PR TIMES</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>チェック・ポイント・リサーチ、2026年8月の主要なサイバー脅威を発表 ランサムウェア攻撃が前年比でほぼ2倍に増加、生成AIによるデータ漏えいリスクが企業の重要課題に | チェック・ポイント・ソフトウェア・テクノロジーズ株式会社のプレスリリース - PR TIMES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1rZG9ud0o1dkVMM3dDRmVkbnBSejZ2aEJBeV9hMlFhdGMxVDRDQzJ1MWFIOFZlRDNHTHo1VlRCZW1GTW9hRFVJNnVnVXBiNG8wSFV1WHJLUFg1OVZkQUhwall1OFlrTFJwQnc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.14 Mon 8:00 SHIRASAGI に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月10日、SHIRASAGIにおける複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>株式会社TRUNKは9月1日</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.14 Mon 8:05 TRUNK 従業員のメールアカウントに不正アクセス、不審メール送信も確認 ホテル企画運営を行う株式会社TRUNKは9月1日、同社従業員のメールアカウントへの不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Ransomware group INC Ransom claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Up to 73,185 records</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>日本WAF市場、2035年に約18.8億ドル規模へ成長か 高度化するサイバー攻撃とクラウド化が需要を牽引 - サイバーセキュリティメディア</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTE5Ob1l6WloxWmQ2QnFvQnpJTThXcFl2Smx5RlRrODlMLXl6UTNjVDN0VGNWUzdMbDdWX3c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>株式会社は9月3日</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>政府共通の業務実施環境「GSS」に不正アクセス - VPN機器の脆弱性を悪用</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Security NEXT / Yagura / ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190208 / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/ / https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>政府システムに不正アクセス、職員ら情報24万件漏洩か デジタル庁 - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE45eWd6V1lyMWxFbElHYVhUUXRWb0R4ek5Jc0xPUlhDWEs0eEFpYUJuX05kdW1lakJYSVhzcXBkb2h5Y3RPSjUwaWY0ZGt5elBaNEVIdGc5MFNOcHkwZDlFWVV3SG16eWJGSWFrZg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ランサムウエア被害最多 攻防激化で体制整備急ぐ 手口高度化「特効薬なし」【表層深層】 - 静岡新聞DIGITAL</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5WMTdWdEpfV01XcU8yVTk3dTJCUXQxTTlfbEJfTVpqanpiWGRNZnNSWTJVVW9qWlNwMTVLaXZxQ0tVd2VOSEZNaWFLUEMwdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ネクストリード、ランサムウェア被害増加受け「Microsoft 365攻撃兆候診断」を中堅中小企業に無償提供 - サイバーセキュリティメディア</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTFBYdzBhUjQ2dnQ3NEVOb2hDQ0txUmVqRVZ6OEpfcEdWdTlHbHZxUGl1dUxXMGJBNV9rTFE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.11 Fri 8:00 baserCMS用プラグイン「BurgerEditor」に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月9日、baserCMS用プラグイン「BurgerEditor」における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188880</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>株式会社は8月25日</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.11 Fri 8:05 「hololive OFFICIAL CARD GAME」公式サイトに不正アクセス、CMSで脆弱性が公表されたことを受け調査し発覚 カバー株式会社は8月25日、「hololive OFFICIAL CARD GAME」公式サイトヘの不正アクセスの可能性について発表した。</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>合計17,668件の迷惑メールを送信 立教大学</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.11 Fri 8:00 立教大学利用のGoogeアカウントに不正アクセス、合計17,668件の迷惑メールを送信 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>「東京外環プロジェクト」サイトで侵害のおそれ - 公開を一時停止</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190203</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>About 246,000 records; possible leak</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5,784 records for Yoshinoya/Hanamaru (Sep 30 disclosure). ApplyNow disclosed effects on three services Sep 11</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026/09/16 映像制作の円谷プロダクション（東京都渋谷区）、直営店「ULTRA MART」の購入抽選システムが不正アクセスで改ざん — 当選していた133人が「落選」表示に 続報を注視中 中程度 株式会社円谷プロダクション（東京都渋谷区／映像制作）とmogily株式会社は2026年9月11日、直営店「ULTRA MART」がLINEアプリ上で実施した購入抽選に使うデジタル整理券システム「mogily」の管理システムが2026年9月9日から10日にかけて外部から不正アクセスを受け、本来「当選」だった133人の当落データが「落選」に書き換えられていたと公表。個人情報の漏えいは確認されておらず、対象者の状態はすべて「当選」に復旧済み。 →</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Yagura / Security NEXT / ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>3</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315 / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>身代金要求「ランサムウェア」被害、上半期１２３件で過去最多…サイバー攻撃の「予兆」は前年同期比５割増 - 読売新聞</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE92YlF6MkFFS1l1YTZWN0l3R2lDVWNNR2M5Nk9zZ3BkOE44d1BOQzlFZThjdW1nRzRrMDE3MWxXUWExczFhdnFJQWJNSzVLZW5sYV9Dckd0SGw2V0pLcU1vOWw4c2ViZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190132</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>システムがランサム被害、一部業務を停止 - インキメーカー</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189674</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NetSecurity 2026.9.10 Thu 8:05 東京科学大学</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 東京科学大学の情報基盤に不正アクセス、個人情報が漏えいした可能性 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>株式会社（NEXCO東日本）は9月4日</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 NEXCO東日本の東京外環プロジェクトホームページで不正アクセス疑い 東日本高速道路株式会社（NEXCO東日本）は9月4日、東京外環プロジェクトホームページの一時公開停止について発表した。</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>「美容医療プラットフォーム Unni（カンナムオンニ）」個人情報漏えい事案に関するお詫びと漏洩項目精査のご報告 - PR TIMES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE55QmF3NU5PVm0yZ192MUlHb2ZTaUxpTEZTT1JtanQzdzJuWHl0VVl2a3JnUlVtemZVUDhkV2VvR0lWVE5ISmFFU1BqWTZMN2ZBTjdvcjRYMU4wb2lZWjFIcVlIN3VnejNSdkE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>50 suspicious emails</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Email takeover via phishing.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189902</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>学生の複数アカウントに不正アクセス、スパム踏み台に - 立教大</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190050</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>セミナー・イベント ScanNetSecurity 2026.9.9 Wed 8:00 「フィッシング対策セミナー2026」11 / 19 開催 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>株式会社は8月19日</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.9 Wed 8:05 DAIKO NEXT LINK のメールアカウントに不正アクセス、二次被害と不正送信の拡大防止のためメールシステムを一時的に停止 DAIKO NEXT LINK株式会社は8月19日、同社メールシステムへの不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>17,668 spam emails</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Unauthorized access to six Google accounts.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Malware infection on a work PC.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.8 Tue 8:00 サイバー攻撃の「被害経験なし」企業は約 6 割へ減少 ～ 東商2026年アンケート調査 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>異なる手法による別の不正アクセスが判明「ニッポンレンタカーアプリ」</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>九州電子</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ムラウチドットコムに不正アクセス、7,716,811件の個人情報が漏えい</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>マルウェアの挙動をリアルタイム監視するOSSを公開 - JPCERT/CC</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/177455</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>三井不動産</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>グループのシステムに不正アクセス、個人情報流出の可能性 - 三井不動産</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189789</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>株式会社は8月20日</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.8 Tue 8:05 さくらインターネットへの不正アクセス、案内ページを公開 さくらインターネット株式会社は8月20日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについての案内ページを公開した。最新のニュースリリース、FAQの他、必要な案内を随時掲載している。</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>「SonicWall SMA 100」にアップデート - 既知マルウェアの除去機能を追加</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/174925</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>「Catalyst SD-WAN Manager」にゼロデイ脆弱性 - 更新や侵害調査を</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190883</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TheRegister The Register誌特約記事 2026.9.8 Tue 8:20 AI がランサムウェア攻撃全工程を実行、被害企業に 80 ページにわたる“セキュリティ監査報告書”まで提出 「攻撃者は戦術面での実行を AI エージェントに委ね、エージェントは監視・評価・行動・再計画のサイクルをリアルタイムで繰り返し、攻撃の各段階の"継ぎ目"で（人間による判断なら必ず発生する）遅れをなくすことで、侵入工程全体を一貫して高速化した」</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>国家公務員共済組合連合会</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>KKR京都くに荘のメールサーバに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>アンビションDX</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>社内ファイルサーバが侵害、情報流出が判明 - アンビションDX</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188534</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>企業化するランサムウェア集団、防御側が取るべきリスク戦略とは - Forbes JAPAN</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Google News</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1uOFAyT0VlNVJGTGNISFRVbVhfb1FYckNYSFl4ckVBbEpqVERmZ1NTTVM1UEVsWXl1b292eGdWbVdwZzcyYlJtT1NfbkdtSmxOdTRmdlJxQ0hTZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセン</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.9.7 Mon 8:00 PALLET CONTROL 製品にアクセス制御不備の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>株式会社T&amp;K TOKAは8月28日</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 T&amp;K TOKAにランサムウェア攻撃、一部の業務を停止 株式会社T&amp;K TOKAは8月28日、同社システムへの不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>canNetSecurity 2026.9.7 Mon 8:05 01銀行</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 01銀行のシステムに不正アクセス、最大100社の情報が漏えい 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>まんだらけ</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>「まんだらけ」サーバに不正侵入、情報流出か - 通販やオークションは再開</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189663</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
+  <autoFilter ref="A1:I240"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4496,7 +9835,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 ～ 2026-10-06</t>
+          <t>2026-09-07 ～ 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4507,7 +9846,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -4518,7 +9857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Security NEXT / Yagura / ScanNetSecurity / SmartScope</t>
+          <t>Security NEXT / Yagura / ScanNetSecurity / SmartScope / Google News</t>
         </is>
       </c>
     </row>
@@ -4542,7 +9881,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06T01:08:24.868160+00:00</t>
+          <t>2026-10-07T00:20:27.134003+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:29:35.977709+00:00</t>
+          <t>2026-10-07T00:31:33.000593+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -551,50 +551,54 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56404.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ニモカ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>日経BP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Da…</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>メールアドレス, クレジットカード情報, 認証情報, 会員情報</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -602,41 +606,59 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>マイクロソフト365</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>焼肉きんぐ、大和証券、日経新聞…麻生幾氏が警告するサイバー攻撃とマイナンバー - zakⅡ</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Mana…</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -649,41 +671,54 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5 / https://news.google.com/rss/articles/CBMijAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMtIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>焼肉きんぐ1078万件流出、タイムズカー、大和証券も…AIが変えた「サイバー攻撃の経済学」、ターゲットは普通の会社 【生成AI事件簿】AIによって攻撃コストと必要技能が低下、これまで割に合わなかった中小企業が標的になる時代に - JBpress</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Confer…</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1078万</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -691,46 +726,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE10RWhfeVpscm1XX19semJVbldGOFVzXzMzQ21aOXp4eUUzZklXUkVNVkQzSFh0LXY2NXI5UXRjaFNUM21neWlTWmI4eDQ2Qmc4VDdxVlJB?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>国家公務員共済組合連合会</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー…</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55万</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -738,46 +786,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>シンカ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>カイクラサービス紹介サイト</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Managemen…</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>56万</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -785,12 +846,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56404.html</t>
         </is>
       </c>
     </row>
@@ -802,18 +863,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>ニモカ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
+          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -821,7 +882,16 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -837,7 +907,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -849,29 +919,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>日本交通</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
+          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Su…</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -879,12 +962,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
         </is>
       </c>
     </row>
@@ -896,42 +979,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Microsoft 365</t>
-        </is>
-      </c>
+          <t>旭化成</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 【セキュリティ ニュース】従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 同社によれば、従業員が使っていた「Microsoft 365」のアカウントが不正アクセスを受けたもの。第三者が従業員アカウントへ不正にログインしたと見られ、送信先のメールアドレスや氏名のほか、一部メールの内容が流出した可能性がある。 また2026年9月30日には、社内や複数従業員とやりとりがあった取材先などに対し、約9000件の「なりすましメール」が送信さ…</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>55万</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -939,12 +1009,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189987 / https://www.security-next.com/190198 / https://www.security-next.com/190319 / https://www.security-next.com/190791 / https://www.security-next.com/191072</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -956,42 +1026,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>旭化成</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 【セキュリティ ニュース】委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 同社によれば、インターネット経由の問い合わせについて管理を委託しているスカラコミュニケーションズが侵害を受けたもの。 2026年10月2日20時半ごろから、翌3日8時ごろにかけてサーバが侵害され、大和証券の顧客情報が取得された形跡が確認されたとして、同月3日にスカラコミュニケーションズから報告を受けたという。 流出した可能性があるのは、インターネット経由で問い合わせを行った顧客約11万人。氏名、メールアドレス、口座番号などが含まれる。さらに個人が特定できる情報を…</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 顧客情報, 会員情報</t>
-        </is>
-      </c>
+          <t>56万</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -999,12 +1056,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132 / https://www.security-next.com/189665 / https://www.security-next.com/189866 / https://www.security-next.com/191070 / https://www.security-next.com/191068</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1016,28 +1073,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ミスターマックス</t>
+          <t>日経BP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
+          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>173万</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1056,7 +1108,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1120,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>シチズン時計</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
+          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1084,12 +1136,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>10万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1103,12 +1150,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1167,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Microsoft 365</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
+          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 【セキュリティ ニュース】従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 同社によれば、従業員が使っていた「Microsoft 365」のアカウントが不正アクセスを受けたもの。第三者が従業員アカウントへ不正にログインしたと見られ、送信先のメールアドレスや氏名のほか、一部メールの内容が流出した可能性がある。 また2026年9月30日には、社内や複数従業員とやりとりがあった取材先などに対し、約9000件の「なりすましメール」が送信さ…</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1150,7 +1215,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/191072</t>
         </is>
       </c>
     </row>
@@ -1162,24 +1227,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ）</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>焼肉きんぐ</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
+          <t>委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 【セキュリティ ニュース】委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 同社によれば、インターネット経由の問い合わせについて管理を委託しているスカラコミュニケーションズが侵害を受けたもの。 2026年10月2日20時半ごろから、翌3日8時ごろにかけてサーバが侵害され、大和証券の顧客情報が取得された形跡が確認されたとして、同月3日にスカラコミュニケーションズから報告を受けたという。 流出した可能性があるのは、インターネット経由で問い合わせを行った顧客約11万人。氏名、メールアドレス、口座番号などが含まれる。さらに個人が特定できる情報を…</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1187,12 +1270,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190132 / https://www.security-next.com/189665 / https://www.security-next.com/191068</t>
         </is>
       </c>
     </row>
@@ -1204,13 +1287,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>ミスターマックス</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
+          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1225,7 +1308,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>95万</t>
+          <t>173万</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1244,7 +1327,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1256,24 +1339,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+          <t>シチズン時計</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
+          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10万</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1281,39 +1374,39 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
+          <t>信濃毎日新聞</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>洛西進学教室</t>
+          <t>信濃毎日新聞デジタル</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 【セキュリティ ニュース】複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 同社によれば、プロモーションサイト「洛西進学教室」と「進学館」が不正アクセスを受けたもの。2026年8月24日に判明した。 講師採用応募者やサイト管理者の個人情報が、被害を受けたサーバ内に保存されていた。情報が外部へ持ち出された痕跡は確認されていないとしているが、第三者によって参照された可能性がある。 対象となるのは、洛西…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品…</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1323,17 +1416,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7,368</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 会員情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1346,50 +1439,54 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190961</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>ベネフィット・ワン</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ベネワン・プラットフォーム</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J …</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1000万</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>氏名, 生年月日, クレジットカード情報</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1402,54 +1499,58 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>大興印刷</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PhotoGoods</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management…</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1000万</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>会員情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity / Security NEXT</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1458,41 +1559,54 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>大起水産</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>大起水産公式アプリ</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
+          <t>アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 【セキュリティ ニュース】アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が侵害され、顧客の個人情報が流出した可能性があることを明らかにした。アプリは平常どおり利用できるとしている。 同社によれば、大起水産公式アプリが侵害されたもの。2026年9月15日に確認した。問題の発覚を受けて対策を講じるとともに監視体制を強化した。 10月5日の時点で、外部における個人情報の流通や不正利用などは確認されていないが、流出した可能性があるという。対象となるのは、2024年11月1日から2026年9月15日までに、同アプリに登録した17万4933人。退会者も対象…</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1500,51 +1614,41 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
+          <t>https://www.security-next.com/191070</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>9000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1557,30 +1661,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>Yaomasa（ news report ）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1591,7 +1690,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1599,30 +1698,30 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大和証券</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
+          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1637,7 +1736,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22万</t>
+          <t>95万</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1656,30 +1755,30 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
+          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1698,46 +1797,36 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>4933</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1750,7 +1839,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -1762,24 +1851,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>洛西進学教室</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
+          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 【セキュリティ ニュース】複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 同社によれば、プロモーションサイト「洛西進学教室」と「進学館」が不正アクセスを受けたもの。2026年8月24日に判明した。 講師採用応募者やサイト管理者の個人情報が、被害を受けたサーバ内に保存されていた。情報が外部へ持ち出された痕跡は確認されていないとしているが、第三者によって参照された可能性がある。 対象となるのは、洛西…</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 会員情報</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1792,7 +1899,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190961</t>
         </is>
       </c>
     </row>
@@ -1804,24 +1911,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline）</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1829,12 +1950,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -1846,24 +1967,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline）</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
+          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1871,12 +2006,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1888,24 +2023,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ）</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>365</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1913,12 +2053,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
         </is>
       </c>
     </row>
@@ -1930,24 +2070,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
+          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -1960,7 +2110,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
         </is>
       </c>
     </row>
@@ -1972,13 +2122,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline）</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
+          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1989,7 +2144,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -1997,12 +2152,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2014,24 +2169,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
+          <t>大和証券</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>22万</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2044,7 +2209,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2056,24 +2221,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>原田産業</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ビールの縁側</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk M…</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2086,7 +2269,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
@@ -2098,24 +2281,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ）</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2128,7 +2311,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2140,24 +2323,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline）</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4933</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2170,7 +2363,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2182,42 +2375,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>White Essence（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/06 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者のほぼ全員が対象 続報を注視中 深刻 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者の…</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8,963</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>氏名, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2230,36 +2405,36 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>The Japan Times（tracker headline）</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
+          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2272,41 +2447,36 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>Safer Internet Association（tracker headline）</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
+          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>9000</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2319,36 +2489,36 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>Osaka Metropolitan University（ news report ）</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
+          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2361,41 +2531,36 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2408,25 +2573,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ）</t>
+          <t>JOGMEC（tracker headline）</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2457,43 +2622,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>12万</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>従業員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2506,36 +2657,36 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2548,25 +2699,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline）</t>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2597,18 +2748,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline）</t>
+          <t>777CON-PASS（tracker headline）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2639,37 +2790,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>返金</t>
+          <t>焼肉きんぐ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/04 アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 続報を注視中 重大 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。 → アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 | インシデント速報 by …</t>
+          <t>2026/10/06 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者のほぼ全員が対象 続報を注視中 深刻 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者の…</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>8,963</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
+          <t>氏名, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2687,54 +2843,36 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>スマートクラブ</t>
-        </is>
-      </c>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 【セキュリティ ニュース】荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 同社によれば、2026年9月30日に、同社サイトの荷物問い合わせサービスへの第三者による侵害を確認したもの。調査の結果、顧客の個人情報が流出した可能性があることが判明した。 流出の可能性があるのは、同社が預かった荷物の送り主と届け先の氏名または会社名、担当者名、住所、電話番号などで、9月30日以前の約100日間の累計データが含まれる。 そのほか、同社と運賃契約している顧客の氏名または会社名、担当者名、住所、…</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2742,40 +2880,40 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534 / https://www.security-next.com/189789 / https://www.security-next.com/190208 / https://www.security-next.com/189792 / https://www.security-next.com/190247 / https://www.security-next.com/190242 / https://www.security-next.com/190798 / https://www.security-next.com/190952</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ジャパンタイムズ</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2794,35 +2932,30 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>12万</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2841,35 +2974,35 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
+          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>175</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2888,46 +3021,36 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -2940,25 +3063,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2968,10 +3091,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>従業員情報</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2987,30 +3119,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3018,11 +3145,7 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3038,45 +3161,36 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>MoonStar（tracker headline）</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3089,45 +3203,36 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>Abahouse（tracker headline）</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3140,36 +3245,49 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>アバハウスインターナショナル</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>返金</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+          <t>2026/10/04 アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 続報を注視中 重大 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。 → アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 | インシデント速報 by …</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3182,7 +3300,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3194,24 +3312,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>スマートクラブ</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 【セキュリティ ニュース】荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 同社によれば、2026年9月30日に、同社サイトの荷物問い合わせサービスへの第三者による侵害を確認したもの。調査の結果、顧客の個人情報が流出した可能性があることが判明した。 流出の可能性があるのは、同社が預かった荷物の送り主と届け先の氏名または会社名、担当者名、住所、電話番号などで、9月30日以前の約100日間の累計データが含まれる。 そのほか、同社と運賃契約している顧客の氏名または会社名、担当者名、住所、…</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3224,7 +3360,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
@@ -3236,24 +3372,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ）</t>
+          <t>ジャパンタイムズ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3266,7 +3407,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3278,24 +3419,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline）</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>12万</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3308,7 +3454,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3320,24 +3466,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>175</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3350,7 +3501,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3362,24 +3513,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3392,25 +3553,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
+          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3420,7 +3581,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3439,25 +3600,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3470,7 +3631,11 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>氏名, 住所</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3481,59 +3646,50 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Chrome 155</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大 【セキュリティ ニュース】事務用NASがランサム被害、通常業務は再開 - 佐賀大（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 事務用NASがランサム被害、通常業務は再開 - 佐賀大 佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 同大によれば、2026年9月24日、事務部門で利用するネットワーク対応ストレージ（NAS）において、ランサムウェアが原因と見られる被害が発生したことを確認したという。 同大では被害の拡大を防ぐため、問題の機器をネットワークから遮断。事務で利用する端末の利用を停止した。 警察へ相談するとともに侵害を受けた経路や被害範囲の調査を実施。感染が疑われたサーバについては復旧し、同月27日に事務用端末の利用を再開。翌28日か…</t>
+          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>会員情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3541,39 +3697,35 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674 / https://www.security-next.com/190761 / https://www.security-next.com/190835 / https://www.security-next.com/190842</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>大興印刷</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>8つの壁</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC | ScanNetSecurity 2026.10.07（水） HOME…</t>
+          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3581,19 +3733,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3606,34 +3753,34 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PhotoGoods</t>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>グッズ作成サービス、クレカ情報含む個人情報流出の可能性 【セキュリティ ニュース】グッズ作成サービス、クレカ情報含む個人情報流出の可能性（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ グッズ作成サービス、クレカ情報含む個人情報流出の可能性 写真からオリジナルグッズを作成するサービス「PhotoGoods」が不正アクセスを受け、個人情報が流出した可能性があることがわかった。 同サービスを運営する大興印刷によれば、システムの脆弱性やファイルアップロード機能を悪用され、第三者による不正アクセスを受けたもの。 2026年9月11日に同サービス内で不審なプログラムが読み込まれているとの連絡を受け、調査を実施したところ判明した。2026年8月6日から、決済画面に入力されたクレジットカード情報を不正に取得するプログラムが設置されていたという。 サービス利用者の氏名、住所、電話番号、メールアドレス、変換処理されたパス…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit …</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3643,17 +3790,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3666,50 +3813,54 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190511</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>日本郵便</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mogily</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 - ScanNetSecurity</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 当選を落選に書き換え ～ デジタル整理券システム「mogily」に不正アクセス mogily株式会社は9月11日、同社が提供するデジタル整理券システム「mogily」への不正アクセスについて発表した。 当選を落選に書き換え ～ デジタル整理券システム「mogily」に不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference S…</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3717,88 +3868,119 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>郵便局アプリ</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / …</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
+          <t>https://www.security-next.com/188534 / https://www.security-next.com/189789 / https://www.security-next.com/189792 / https://www.security-next.com/190247 / https://www.security-next.com/190242 / https://www.security-next.com/190734 / https://www.security-next.com/190798 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eplus（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>セイコーマートアプリ</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>eplus（tracker headline） — Unauthorized access.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conf…</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -3811,25 +3993,25 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline）</t>
+          <t>Toyobo MC（tracker headline）</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3860,18 +4042,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ）</t>
+          <t>Three educational institutions（tracker headline）</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3902,18 +4084,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline）</t>
+          <t>Kodansha BECK（ news report ）</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3944,18 +4126,18 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline）</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3986,18 +4168,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4028,18 +4210,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ）</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4070,18 +4252,18 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4110,36 +4292,41 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4147,41 +4334,55 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chrome 155</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
+          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大 【セキュリティ ニュース】事務用NASがランサム被害、通常業務は再開 - 佐賀大（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 事務用NASがランサム被害、通常業務は再開 - 佐賀大 佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 同大によれば、2026年9月24日、事務部門で利用するネットワーク対応ストレージ（NAS）において、ランサムウェアが原因と見られる被害が発生したことを確認したという。 同大では被害の拡大を防ぐため、問題の機器をネットワークから遮断。事務で利用する端末の利用を停止した。 警察へ相談するとともに侵害を受けた経路や被害範囲の調査を実施。感染が疑われたサーバについては復旧し、同月27日に事務用端末の利用を再開。翌28日か…</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4189,41 +4390,59 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189674 / https://www.security-next.com/190842</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>8つの壁</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline） — Unauthorized access.</t>
+          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC | ScanNetSecurity 2026.10.07（水） HOME…</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4236,97 +4455,118 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ULTRA MART</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Sec…</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura / Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315 / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>クロネコ代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 「クロネコ代金後払いサービス」に不正アクセス ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 「クロネコ代金後払いサービス」に不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / 業界動向 新製品 サービス 業界…</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4335,25 +4575,30 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
+          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline）</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+          <t>「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 - ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4361,10 +4606,19 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4372,41 +4626,46 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline） — Ransomware.</t>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -4419,25 +4678,25 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ）</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4468,18 +4727,18 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline）</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4510,18 +4769,18 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4552,47 +4811,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>スマチケ</t>
-        </is>
-      </c>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 → チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 | インシデント速報 by ヤグラ コンテンツにスキップ インシデン…</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>確認されず</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>1,463</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 口座情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -4605,50 +4846,36 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>郵便局アプリ</t>
-        </is>
-      </c>
+          <t>Lashinbang（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中 【セキュリティ ニュース】日本郵便のサーバに不正アクセスか - 詳細は調査中（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 日本郵便のサーバに不正アクセスか - 詳細は調査中 日本郵便は、国際郵便物の取り扱いに関するサーバが、外部からサイバー攻撃を受けた可能性があることを明らかにした。 同社によれば、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが外部から攻撃を受けた可能性があることが、2026年9月25日に判明したもの。原因や影響範囲について調査している。 同社では、同サービスの受け付けを一時的に停止。サービス再開については、あらためてウェブサイトで通知するとしている。 （Security NEXT - 2026/09/28 ） ツイート 関連リンク 日本郵便 PR 関連記事 「郵便局アプリ」で個人情報流出 - 緊急メンテを実施 グッズ…</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -4661,54 +4888,36 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190734</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>山東聖泉</t>
-        </is>
-      </c>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品…</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -4716,30 +4925,30 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report）</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4770,29 +4979,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report）</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -4805,36 +5019,54 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 京王電鉄にランサムウェア攻撃 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / 業界動向 新製品 サービス 業界動向 市場規模 セキュリティとお金 コンテン…</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 従業員情報</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4847,49 +5079,36 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>情報が持ち出されたか</t>
-        </is>
-      </c>
+          <t>VOISING（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 → 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 …</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4902,25 +5121,25 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline）</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4951,42 +5170,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>事務情報システムにおけるランサムウェア被害の発生について</t>
-        </is>
-      </c>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 → 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク…</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>メールアドレス, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4999,36 +5205,46 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5041,36 +5257,41 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
+          <t>セイコーマート</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
+          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5078,41 +5299,59 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>メトポ</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
+          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 【セキュリティ ニュース】「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 同社によれば、同サービスで利用するサーバが第三者によって侵害されたことが判明したもの。 サーバ内には、同サービス会員の登録メールアドレス約5万9000件が保存されており、流出したおそれがある。これらメールアドレスは、メール送信が不能となったことから、同社で配信を停止しているものだという。 同社は、侵害を受けたと見られる部分を特定し、対策を講じた。引き続き原因や影響の範囲など詳細について調査を進めている。 同社では…</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5120,30 +5359,30 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190050 / https://www.security-next.com/190791</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+          <t>Toyobo Textile（tracker headline）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5174,18 +5413,18 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ）</t>
+          <t>Saga University（tracker headline）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+          <t>Saga University（tracker headline） — Ransomware.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5216,18 +5455,18 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline）</t>
+          <t>QUO Card（ news report ）</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5258,18 +5497,18 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
+          <t>International House of Japan (library)（tracker headline）</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5300,18 +5539,18 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5342,29 +5581,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>スマチケ</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 → チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 | インシデント速報 by ヤグラ コンテンツにスキップ インシデン…</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>確認されず</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1,463</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, 口座情報</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -5377,34 +5634,34 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>セイコーマート</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chrome 155</t>
+          <t>タイムズカー</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 【セキュリティ ニュース】ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 同社によれば、2026年9月10日、通信販売で利用しているシステムが侵害された疑いがあることを確認。同月11日に事態を公表し、対応を進めている。 その後の調査で、通信販売の顧客対応に利用するシステム内に保存されていた顧客との通話音声データや関連情報が、第三者に取得された可能性があることがわかった。 さらに同社が利用する顧客管理システムも侵害され、情報を窃取された可能性があるという。 同社では、個人情報保護委員会へ報告す…</t>
+          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 【セキュリティ ニュース】教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 同大によれば、2026年8月7日に教員5人のメールアカウントが第三者によって侵害されたもの。同月29日に検知した。 フィッシング攻撃などにより、認証情報が窃取され、アカウントが乗っ取られたことが原因とみられる。 アカウントを不正に利用され、1333件の迷惑メールが送信されたほか、一部アカウントでは、第三者がメールデータにアクセスした痕跡が確認された。大規模なデータの抽出や持ち出しなどは確認されていないものの、一部のデータへアクセ…</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5414,12 +5671,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>認証情報, 会員情報</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5437,36 +5694,54 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189663 / https://www.security-next.com/190883 / https://www.security-next.com/174925 / https://www.security-next.com/177455 / https://www.security-next.com/190050 / https://www.security-next.com/190203 / https://www.security-next.com/188880 / https://www.security-next.com/189985 / https://www.security-next.com/190377</t>
+          <t>https://www.security-next.com/190203 / https://www.security-next.com/189987 / https://www.security-next.com/190198 / https://www.security-next.com/190319</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Chrome 155</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 【セキュリティ ニュース】ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 同社によれば、同社グループのサーバがランサムウェアによる攻撃を受けたもので、9月26日未明に確認した。 同社では被害拡大を防ぐため、ネットワークを遮断。警察へ通報するとともに、外部協力のもと、原因や攻撃経路について調査を進めている。 また事業に関する機密情報や顧客情報などが流出した可能性も含め、影響範囲など被害状況を調べている。 （Security NEXT - 2026/09/28 ） ツイ…</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -5479,96 +5754,114 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190761</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Helpfeel</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Gyazo</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Managemen…</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gyazo</t>
+          <t>山東聖泉</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/09/19 株式会社Helpfeel、画像共有サービス「Gyazo」に不正アクセス — ユーザー関連データ約2,362万件と画像メタデータ約4.9億件が流出、第二報で削除済み画像のメタデータ約1.74億件の流出も判明 続報を注視中 深刻 株式会社Helpfeel（京都府京都市／AIナレッジデータプラットフォームの開発・運用）は2026年9月16日、画像共有サービス「Gyazo」の画像アップロードサーバの脆弱性を悪用され、第三者にシステム上で任意のコマンドを実行されたと公表した。ユーザー関連データ約2,362万件と画像に関するメタデータ約4.9億件が外部に流出しており、漏えいした情報にはメールアドレス、パスワードのハッシュ値、ログインセッションID、非公開画像のパスフレーズのハッシュ値が含まれる。画像ファイルそのものの持ち出しは確認されていないが、画像URLを構成する情報が取得されたため、非公開画像が閲覧された可能性について調査が続いている。2026年9月25日の第二報では、主に2023年2月以前にユーザーが削除した画像に関するメタデータ約1.74億件の外部流出が新たに確認され…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品…</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>362万</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>氏名, メールアドレス, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -5576,90 +5869,72 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>当選</t>
-        </is>
-      </c>
+          <t>Tokyo Metro (Metpo)（news report）</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に 【セキュリティ ニュース】円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に 円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 同社によれば、同店舗では購入の抽選に、mogilyが提供するLINEアプリのデジタル整理券システム「mogily」を利用しているが、当落結果を改ざんされる被害が発生したもの。 対象となるのは、2026年9月9日から同月10日までの「M78ウルトラマン ふわふわお座りぬいぐるみ」に関する抽選枠。「当選」となった顧客133人のステータスが「落選」に変更されたという。 当選者の特定は完了して…</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yagura / Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ）</t>
+          <t>Nippon Rent-A-Car (app)（news report）</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5690,18 +5965,18 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ）</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5732,29 +6007,42 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>情報が持ち出されたか</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 → 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 …</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -5767,54 +6055,36 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>本社の従業員</t>
-        </is>
-      </c>
+          <t>Smaregi EC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/09/17 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。 → 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← インシデント一覧に戻る 小田原エンジニアリング、ドイツ子会社出向者のメール…</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -5827,34 +6097,34 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>murauchi.com</t>
+          <t>事務情報システムにおけるランサムウェア被害の発生について</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 → 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← イン…</t>
+          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 → 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク…</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5862,14 +6132,9 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>6,811</t>
-        </is>
-      </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
+          <t>メールアドレス, 認証情報</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5887,36 +6152,54 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA C…</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -5924,30 +6207,30 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5978,18 +6261,18 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6020,18 +6303,18 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+          <t>Ryomo Systems（tracker headline）</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6062,47 +6345,29 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>GSS</t>
-        </is>
-      </c>
+          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/09/14 デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 続報を注視中 重大 デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。 → デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ …</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6115,25 +6380,25 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline）</t>
+          <t>Bellcadia (montbell global site)（ news report ）</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6164,47 +6429,29 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Chrome 155</t>
-        </is>
-      </c>
+          <t>Osaka City (recorded interview system)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区 【セキュリティ ニュース】施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区 東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 同区によれば、2026年8月22日、大田区民プラザの職員がパソコンでインターネットを利用中、サポート詐欺の被害に遭ったという。 警告画面が表示され、表示された連絡先に電話して指示に従いパソコンを操作したところ、パソコンを操作できない状況に陥った。その後、ネットワークから端末を隔離したが、それまでの間、第三者によってアクセスされた。 問題の端末には、同施設の職員や利用者556人の氏名などが…</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6217,25 +6464,25 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline）</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6266,18 +6513,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline）</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6308,18 +6555,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline）</t>
+          <t>Calbee (baseball-chip cards)（tracker headline）</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6347,8 +6594,1094 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Chrome 155</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 【セキュリティ ニュース】ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 同社によれば、2026年9月10日、通信販売で利用しているシステムが侵害された疑いがあることを確認。同月11日に事態を公表し、対応を進めている。 その後の調査で、通信販売の顧客対応に利用するシステム内に保存されていた顧客との通話音声データや関連情報が、第三者に取得された可能性があることがわかった。 さらに同社が利用する顧客管理システムも侵害され、情報を窃取された可能性があるという。 同社では、個人情報保護委員会へ報告す…</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189663 / https://www.security-next.com/190377</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>第一生命</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CINRA JOB</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス 【セキュリティ ニュース】クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 同サービスを運営するCINRAによれば2026年8月18日、認証情報が第三者に取得され、クラウド環境にある同サービスのシステムが不正アクセスを受けたことを確認した。 取得された認証情報を用いることで、会員情報を保管するデータベースやバックアップにアクセスすることが可能だった。第三者による会員情報の閲覧、取得などは確認されていないものの、流出の可能性がある。 対象となるのは、退会者も含む会員…</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 認証情報, 会員情報</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189866</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ）</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>本社の従業員</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026/09/17 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。 → 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← インシデント一覧に戻る 小田原エンジニアリング、ドイツ子会社出向者のメール…</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>murauchi.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 → 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← イン…</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6,811</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>マルウェアに感染しており、除去作業が必要</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 【セキュリティ ニュース】生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 同県によれば、2026年9月4日、生徒寮の管理人がインターネットで防災気象情報を収集していたところ、サポート詐欺の被害に遭ったもの。 「マルウェアに感染しており、除去作業が必要」などとだます端末上に表示された偽の警告画面を信じ、記載のあった電話番号に連絡。相手の指示に従って操作したことから、パソコンが遠隔操作される状況に陥った。 電話を切った後、見慣れないウイルス対策ソフトが起動していることを不…</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189902 / https://www.security-next.com/189985</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミ…</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>サポート詐欺</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 【セキュリティ ニュース】サポート詐欺で約4000ファイル削除 - サカイHD子会社（1ページ目 / 全2ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 同社によれば、2026年8月7日、従業員が業務用パソコンでAIツールに関するウェブサイトを検索し、閲覧していたところ、警告画面が表示され、記載先へ連絡するように誘導されたという。相手先がサポートセンターであると信じて従業員が案内に従ったところ、遠隔操作ツールがパソコンにインストールされた。 同従業員が異常を認識してシステム担当者へ…</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190883 / https://www.security-next.com/174925 / https://www.security-next.com/177455 / https://www.security-next.com/188880</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GSS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026/09/14 デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 続報を注視中 重大 デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。 → デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ …</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Security NEXT / Yagura</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190208 / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>この脆弱性は〇〇社の△△が報告した</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 REVISIO 役職員が使用する PC がマルウェア感染、ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 REVISIO 役職員が使用する PC がマルウェア感染、ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Manage…</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L125"/>
+  <autoFilter ref="A1:L147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6393,7 +7726,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
@@ -6428,7 +7761,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:31:33.000593+00:00</t>
+          <t>2026-10-07T00:33:30.747902+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 異なる手法による別の不正アクセスが判明「ニッポンレンタカーアプリ」 ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 異なる手法による別の不正アクセスが判明「ニッポンレンタカーアプリ」 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 異なる手法による別の不正アクセスが判明「ニッポンレンタカーアプリ」 ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利…</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -568,17 +568,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
+          <t>マイページ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Da…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは9月30日に、同社従業員のメールアカウントに不正アクセスがあり、メール送受信先の一部の個人情報が漏えいした可能性が判明したというもの。当該従業員は、日本経済新聞社社員のメールアドレスで届いたフィッシングメールから、認証情報を入手されている。 漏えいした可能性があるのは、26件の個人情報（個人名、メールアドレス）。 同社では、個人情報漏えいが疑われるメールアドレス先の対象者に個別にメールで連絡を行っている。 同社では不正アクセスの発覚後に、当該アカウントへの接続を遮断している。 同社では引き続き、個人情報の安全を守るために最善を尽くすとのこと。 なお、株式会社日本経済新聞社は10月4日に、約9,000件のなりすましメール…</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Mana…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 これは同社社員が使用していた「マイクロソフト365」のアカウントに第三者が不正にログインし、約9,000件のなりすましメールが送信されたというもの。社内の他複数の社員とやりとりがあった取材先などに対し、悪性サイトに誘導する内容のメールが9月30日送信されている。 同社では、送信先のメールアドレスや氏名の他、一部メールの内容が漏えいしたとみており、侵害を受けた範囲や漏えいした個人情報の件数を調査している。 同社では、なりすましメールの送信先に個別に連絡し、当該メールの削除を依頼している。 同社では、セキュリティ対策をさらに強化して情報…</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Confer…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 同社台湾子会社のMOST社では3月21日未明に、メールサーバでのウイルス感染を確認し、その後の調査でランサムウェアによる攻撃を受けたことが判明したため、被害状況と影響範囲の詳細について調査を行っていた。 九州電子ではMOST社でランサムウェア感染が確認された旨の報告を受け、初動対応としてMOST社とのネットワーク接続を遮断し、外部専門機関と連携のうえ、詳細な調査と安全確認を実施している。 九州電子で調査した結果、MOST社から九州電子への感染拡大を示す痕跡、外部からの不正アクセスや情報漏えいにつながる通信の痕跡は確認されなかった。 九州電子では予防的措置として、…</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
         </is>
       </c>
     </row>
@@ -743,22 +743,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>国家公務員共済組合連合会</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
+          <t>さとこはいつも</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 これは8月31日に、当該従業員のメールアカウントで第三者からの不正アクセスの痕跡を確認したというもの。調査の結果、2026年3月27日から8月31日までの間、当該アカウントに第三者が継続的にアクセスし、メールを閲覧していたことが判明している。 漏えいした可能性があるのは、当該従業員1名と取引先担当者との間で送受信されたメールの内容が対象で、2026年3月27日から8月31日までの時点で…</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Managemen…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 同社では8月24日に、「カイクラサービス紹介サイト」（ https://kaiwa.cloud/ ）で複数の不正プログラムの設置を検知し、社内調査による分析の結果、不正プログラムのうち1件は、当該サイトが設置されているサーバからの情報取得を技術的に可能にするものと判明したため、リスク拡大を回避し、調査を行うため、当該サイトおよび同一サーバで運用していた下記3サイトを含め、アクセスを一時停止するとともに、外部の専門機関に依頼し、ログ解析等を通じた精査を開始していた。 コーポレートサイト：https://www.thinca.co.jp カイクラサー…</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -858,43 +858,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ニモカ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>国家公務員共済組合連合会</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 KKR京都くに荘のメールサーバに不正アクセス 国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 同会では8月25日に、KKR京都くに荘のメールサーバへの不正アクセスに伴う個人情報漏えいの可能性について公表していたが、その後、メールシステム運用事業者及び外部専門事業者による詳細な調査を実施した結果、第三者からの当該メールアカウントのメールボックスへのアクセスやメールの閲覧を示す記録は確認されず、現時点で、顧客の個人情報が漏えいした事実は確認されなかったという。 同会では、メールシステムのセキュリティ対策の強化を図るとともに、顧客の個人情報の適切な管理に努め、再発防止に取り組むとのこと。 実行犯が示唆したダークウェブでの情報公開は確認されず ～ ワシントンホテルにランサムウェア攻撃 2026.9.25 Fri 8:05 ホテル白菊が利用する…</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -902,12 +906,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html</t>
         </is>
       </c>
     </row>
@@ -919,42 +923,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
-        </is>
-      </c>
+          <t>ニモカ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Su…</t>
+          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>氏名, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -962,12 +962,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -979,29 +979,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AI トークン乗っ取り</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
+          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している 4月、あるソフトウェアアーキテクトが AI プロバイダーからの請求書を開き、二度見しました。 彼が承認した覚えのない利用に対して、25,000 ドルが請求 されていたのです。別の組織の請求額は、 詐欺が発見され抑止されるまでに100万ドル近く に達しました。犯罪者が AI アカウントの制御を獲得し、盗んだアクセス権を転売して利益を得るために「AI トークン乗っ取り」のような新しい手口に転じる中、このような事例は増加傾向にあります。 AI への需要は急上昇しており、誰もが最も能力の高いフロンティアモデルへのアクセスを求めています。しかし、請求が届き、ユーザーが上昇するトークンコストに直面するにつれ、AI へのアクセス料を支払うのではなく盗むという動機が、 AI のコスト 上昇とまさに並行して…</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>55万</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1014,7 +1027,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1045,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
+          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1042,7 +1055,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>56万</t>
+          <t>55万</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1061,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1073,23 +1086,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日経BP</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>56万</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1108,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1120,23 +1133,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>日経BP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
+          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1155,7 +1168,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
         </is>
       </c>
     </row>
@@ -1167,42 +1180,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Microsoft 365</t>
-        </is>
-      </c>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 【セキュリティ ニュース】従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 同社によれば、従業員が使っていた「Microsoft 365」のアカウントが不正アクセスを受けたもの。第三者が従業員アカウントへ不正にログインしたと見られ、送信先のメールアドレスや氏名のほか、一部メールの内容が流出した可能性がある。 また2026年9月30日には、社内や複数従業員とやりとりがあった取材先などに対し、約9000件の「なりすましメール」が送信さ…</t>
+          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191072</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1227,39 +1227,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>焼肉きんぐ</t>
+          <t>Microsoft 365</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 【セキュリティ ニュース】委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 同社によれば、インターネット経由の問い合わせについて管理を委託しているスカラコミュニケーションズが侵害を受けたもの。 2026年10月2日20時半ごろから、翌3日8時ごろにかけてサーバが侵害され、大和証券の顧客情報が取得された形跡が確認されたとして、同月3日にスカラコミュニケーションズから報告を受けたという。 流出した可能性があるのは、インターネット経由で問い合わせを行った顧客約11万人。氏名、メールアドレス、口座番号などが含まれる。さらに個人が特定できる情報を…</t>
+          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 顧客情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Security NEXT</t>
@@ -1270,12 +1261,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132 / https://www.security-next.com/189665 / https://www.security-next.com/191068</t>
+          <t>https://www.security-next.com/191072</t>
         </is>
       </c>
     </row>
@@ -1287,13 +1278,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ミスターマックス</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>問い合わせ顧客の情報が流出か - 大和証券 大和証券</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>問い合わせ顧客の情報が流出か - 大和証券 大和証券は</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
+          <t>委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1303,18 +1298,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>173万</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1327,7 +1317,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
+          <t>https://www.security-next.com/191068</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1329,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>シチズン時計</t>
+          <t>ミスターマックス</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
+          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1355,12 +1345,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10万</t>
+          <t>173万</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1374,12 +1364,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1391,22 +1381,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>信濃毎日新聞</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>信濃毎日新聞デジタル</t>
+          <t>Japan Vulnerability Notes（JVN）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品…</t>
+          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.6 Tue 8:00 Apache HTTP Server 2.4 に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 The Apache Software Foundationでは、Apache HTTP Server 2.4系における複数の脆弱性に対応したApache HTTP Server 2.4.69を現地時間10月1日に公開している。 JVNでは、影響を受けるシステム、想定される影…</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1416,12 +1406,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7,368</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1434,12 +1424,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1441,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ベネフィット・ワン</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ベネワン・プラットフォーム</t>
-        </is>
-      </c>
+          <t>シチズン時計</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J …</t>
+          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1476,17 +1462,13 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>氏名, 生年月日, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>10万</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1499,7 +1481,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
         </is>
       </c>
     </row>
@@ -1511,22 +1493,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>信濃毎日新聞</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PhotoGoods</t>
+          <t>信濃毎日新聞デジタル</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 これは9月7日に、「信濃毎日新聞デジタル」の信毎ポイント交換システムへの外部からの不正アクセスが判明したというもので、一時的に一部の履歴データが消去される事象が発生していた。 同社で調査した結果、現時点で個人情報の流出は確認されていないという。 同社では、該当システムに修正措置を講じ、データの復旧も完了している。また、顧客が保有しているポイント数への影響はない。 同社では今後、より一層の安全管理とセキュリティ強化に努めるとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員…</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1536,30 +1518,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7,368</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ScanNetSecurity / Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1553,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>ベネフィット・ワン</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>大起水産公式アプリ</t>
+          <t>ベネワン・プラットフォーム</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 【セキュリティ ニュース】アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が侵害され、顧客の個人情報が流出した可能性があることを明らかにした。アプリは平常どおり利用できるとしている。 同社によれば、大起水産公式アプリが侵害されたもの。2026年9月15日に確認した。問題の発覚を受けて対策を講じるとともに監視体制を強化した。 10月5日の時点で、外部における個人情報の流通や不正利用などは確認されていないが、流出した可能性があるという。対象となるのは、2024年11月1日から2026年9月15日までに、同アプリに登録した17万4933人。退会者も対象…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 これは「ベネワン・プラットフォーム」のアンケート機能にて、担当者がアンケート結果をダウンロードした際、本来アクセスできない他企業・団体の従業員の個人情報の一部が表示される状態となっていたというもの。同社サービスを利用している企業・団体の担当者1社1名から7月30日に連絡があり、発覚した。 対象となるのは2,322企業・団体の13,460名の個人情報（社員・職員番号、氏名、性別、生年月日、企業・団体名、所属/役職、入…</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1596,17 +1578,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 顧客情報, 会員情報</t>
+          <t>氏名, 生年月日, クレジットカード情報</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1619,7 +1601,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191070</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
         </is>
       </c>
     </row>
@@ -1631,37 +1613,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>大興印刷</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PhotoGoods</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 これは9月11日に、「PhotoGoods」内に不審な外部プログラムが読み込まれているとの連絡があり、システム管理会社による調査を行った結果、決済画面等に入力されたクレジットカード情報などを不正に取得する機能を持つプログラムの設置を確認したというもの。あわせてシステム上の脆弱性およびファイルアップロード機能の悪用による第三者からの不正アクセスも確認している。 「PhotoGoods」を利用した顧客下記の情報が漏えいした可能性がある。なお、クレジットカ…</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity / Security NEXT</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
         </is>
       </c>
     </row>
@@ -1673,24 +1673,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ）</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>大起水産</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>大起水産公式アプリ</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
+          <t>アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が不正アクセスを受け、顧客の個人情報が流出した可能性があることを明らかにした。アプリは通常通り利用できる。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1703,7 +1716,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/191070</t>
         </is>
       </c>
     </row>
@@ -1715,34 +1728,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>95万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1755,7 +1758,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -1767,13 +1770,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>Yaomasa（ news report ）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
+          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1784,7 +1787,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1797,7 +1800,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -1809,24 +1812,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
+          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>95万</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1839,54 +1852,36 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>洛西進学教室</t>
-        </is>
-      </c>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 【セキュリティ ニュース】複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 同社によれば、プロモーションサイト「洛西進学教室」と「進学館」が不正アクセスを受けたもの。2026年8月24日に判明した。 講師採用応募者やサイト管理者の個人情報が、被害を受けたサーバ内に保存されていた。情報が外部へ持ち出された痕跡は確認されていないとしているが、第三者によって参照された可能性がある。 対象となるのは、洛西…</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1899,50 +1894,36 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190961</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1950,30 +1931,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>i-ask</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+          <t>2026/10/06 FAQ・問い合わせ管理システム「i-ask」を提供するスカラコミュニケーションズ（東京都渋谷区）、管理サイトへの不正ログインで最大5社・延べ71万3,126件の問い合わせ情報が漏えいのおそれ 情報収集中 重大 株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ（東京都渋谷区／FAQ・問い合わせ管理システム「i-ask」を提供）のサーバが不正アクセスを受け、同システムを導入していた最大5社・延べ最大713,126件の問い合わせ情報が漏えいした可能性があると公表した。第三者が2026年10月2日20時33分頃から10月3日8時1分頃にかけて「i-ask」の管理サイトへ不正にログインし、サーバに不正なプログラムを設置していた。スカラコミュニケーションズは10月3日朝にアクセスを遮断し、同日中に利用企業へ報告している。利用企業の一部は個別に対象件数を公表しているが、全5社の内訳は明らかにされていない。公表時点で二次被害は確認されていない。 株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ…</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1983,22 +1968,18 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>会員情報</t>
-        </is>
-      </c>
+          <t>3,126</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2006,12 +1987,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-scala-communications-i-ask-breach/</t>
         </is>
       </c>
     </row>
@@ -2023,29 +2004,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
+          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>365</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2053,12 +2038,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
+          <t>https://www.security-next.com/190961</t>
         </is>
       </c>
     </row>
@@ -2070,31 +2055,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
+          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2105,12 +2094,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -2122,13 +2111,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
+          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2138,10 +2127,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2157,7 +2155,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2169,18 +2167,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>大和証券</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2190,7 +2183,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22万</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2204,12 +2197,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
         </is>
       </c>
     </row>
@@ -2221,42 +2214,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>原田産業</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ビールの縁側</t>
-        </is>
-      </c>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk M…</t>
+          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2269,7 +2254,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
         </is>
       </c>
     </row>
@@ -2281,18 +2266,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
+          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2306,12 +2296,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2323,13 +2313,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>大和証券</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2339,12 +2329,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>22万</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2363,7 +2353,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2375,24 +2365,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 池上通信機にサイバー攻撃、サーバ内の一部ファイルが暗号化 池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:…</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2400,12 +2408,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
         </is>
       </c>
     </row>
@@ -2417,24 +2425,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wp2shell</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 東産業 公式サイトにwp2shell を悪用した不正アクセス 株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPre…</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,950,165</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2442,12 +2468,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
         </is>
       </c>
     </row>
@@ -2459,24 +2485,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>アカウント乗っ取り</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 日本大学の計 5 名の教員アカウントに不正アクセス、スパムメール送信の踏み台に 日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日に、第三者が同学の計5名の教員アカウントに不正アクセスし、当該アカウントをスパムメール送信の踏み台として利用していたことを8月29日に確認したというもの。当該アカウントから学内外に1,333件の不審メールが送信されたことを確認している。 調査の結果、当該アカウント内のデータに対する大規模な抽出や持ち出し等の痕跡は確認されていないが、一部のデータへアクセスされた可能性はあるという。 同学では、連絡先が特定可能な対象者に順次、個別にメール等で連絡を行っている。 同学では、悪意ある第三者がフィッシングメール等の手段で認証情報（ID・パスワード）を窃取し、アカウントを乗っ取ったことが原因と推測している。 同学では検知後に、当該アカウントの利用を一時停止（或いは無…</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2489,7 +2533,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
         </is>
       </c>
     </row>
@@ -2501,24 +2545,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ）</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>一万三千尺物語</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 あいの風とやま鉄道 観光列車の座席管理システムに不正アクセス あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 これは9月8日朝に、同社社員が座席管理システムにアクセスしたところ、複数の予約がキャンセルされていた他、当該システムから正規の手順で行われていない予約を確認したため、全ての新規予約の受付を停止するとともに調査を行った結果、9月2日に最初の不正アクセスがあり、以降、9月8日までに複数回の不正アクセスを確認したというもの。 漏えいした可能性があるのは、これまでに観光列車「一万三千尺物語」に乗車した顧客または今後の乗車予約をしていた顧客 計1,409名の個人情報（氏名、住所、電話番号、メールアドレス）。 同社では対象の顧客に9月12日付で、文書「個人情報の漏えいのおそれがあ…</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,409</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 従業員情報</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2531,7 +2593,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html</t>
         </is>
       </c>
     </row>
@@ -2543,24 +2605,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 「ドズル社ストア」で不正なページに誘導、カード情報を入力した場合はカード会社への連絡を呼びかけ 株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 これは9月11日午後4時頃に、「ドズル社ストア」で商品購入手続きの際、正規の決済ページではない不正な外部ページへ誘導される事象が発生したというもの。不正なページには、主に下記のような特徴があり、不正なページで行われた支払いは、「ドズル社ストア」での注文として受け付けられていない。 ・ページ左上に「Checkout」と表示され、ドズル社ストアの名称・ロゴが表示されない ・英語で表示され、配送先の国・地域に「United States」があらかじめ選択されている ・実際の商品価格と大きく異なる高額な金額が表示される 同社によると、発生推定期間中（9月11日午後3時頃～午後5時50分）に購入…</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2568,12 +2648,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html</t>
         </is>
       </c>
     </row>
@@ -2585,24 +2665,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>原田産業</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ビールの縁側</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレ…</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2610,12 +2708,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
@@ -2627,24 +2725,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2657,7 +2755,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2669,24 +2767,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4933</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2699,7 +2807,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2711,13 +2819,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ）</t>
+          <t>White Essence（ disclosure ）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2753,13 +2861,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline）</t>
+          <t>The Japan Times（tracker headline）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2795,42 +2903,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>Safer Internet Association（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/06 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者のほぼ全員が対象 続報を注視中 深刻 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者の…</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>8,963</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>氏名, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2843,36 +2933,36 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>Osaka Metropolitan University（ news report ）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
+          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2885,41 +2975,36 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>9000</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -2932,36 +3017,36 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>JOGMEC（tracker headline）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
+          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -2974,41 +3059,36 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3021,25 +3101,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ）</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3070,43 +3150,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>12万</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>従業員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3119,36 +3185,36 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>777CON-PASS（tracker headline）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3161,36 +3227,54 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>焼肉きんぐ</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+          <t>2026/10/06 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者のほぼ全員が対象 続報を注視中 深刻 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。 → 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5…</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>8,963</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3203,36 +3287,36 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline）</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3245,49 +3329,41 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>返金</t>
-        </is>
-      </c>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/04 アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 続報を注視中 重大 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。 → アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 | インシデント速報 by …</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3300,54 +3376,36 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>佐川急便</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>スマートクラブ</t>
-        </is>
-      </c>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 【セキュリティ ニュース】荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 同社によれば、2026年9月30日に、同社サイトの荷物問い合わせサービスへの第三者による侵害を確認したもの。調査の結果、顧客の個人情報が流出した可能性があることが判明した。 流出の可能性があるのは、同社が預かった荷物の送り主と届け先の氏名または会社名、担当者名、住所、電話番号などで、9月30日以前の約100日間の累計データが含まれる。 そのほか、同社と運賃契約している顧客の氏名または会社名、担当者名、住所、…</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3360,25 +3418,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190952</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ジャパンタイムズ</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3388,7 +3446,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3407,41 +3465,36 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>12万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3454,25 +3507,30 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3482,10 +3540,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>従業員情報</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3501,40 +3563,30 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3553,41 +3605,36 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>MoonStar（tracker headline）</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3600,45 +3647,36 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>Abahouse（tracker headline）</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3651,25 +3689,29 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>アバハウスインターナショナル</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>返金</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
+          <t>2026/10/04 アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 続報を注視中 重大 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。 → 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情…</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3679,17 +3721,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>氏名, 住所</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3702,7 +3744,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3714,13 +3756,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>問い合わせサービスがサイバー攻撃を受け</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
+          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3733,14 +3779,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3753,7 +3795,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
+          <t>https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
@@ -3765,42 +3807,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
-        </is>
-      </c>
+          <t>ジャパンタイムズ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit …</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3813,7 +3842,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3825,42 +3854,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>mogily</t>
-        </is>
-      </c>
+          <t>第一生命</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 当選を落選に書き換え ～ デジタル整理券システム「mogily」に不正アクセス mogily株式会社は9月11日、同社が提供するデジタル整理券システム「mogily」への不正アクセスについて発表した。 当選を落選に書き換え ～ デジタル整理券システム「mogily」に不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference S…</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3873,7 +3889,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3885,55 +3901,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>日本郵便</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>郵便局アプリ</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / …</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Security NEXT / ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534 / https://www.security-next.com/189789 / https://www.security-next.com/189792 / https://www.security-next.com/190247 / https://www.security-next.com/190242 / https://www.security-next.com/190734 / https://www.security-next.com/190798 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3945,42 +3948,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>セイコーマートアプリ</t>
-        </is>
-      </c>
+          <t>日本エネルギー経済研究所</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conf…</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 会員情報</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -3993,7 +3988,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4005,24 +4000,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline）</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4047,24 +4047,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline）</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>氏名, 住所</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4077,7 +4086,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4089,24 +4098,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ）</t>
+          <t>ヤマト運輸</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>氏名, 住所</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4119,7 +4137,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4131,24 +4149,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline）</t>
+          <t>ヤマト運輸</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4161,7 +4188,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4173,24 +4200,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>さくらのレンタルサーバ</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本トレクスの情報システムに不正アクセス、一部業務が停止 日本トレクス株式会社は9月11日、同社情報システムへの不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56377;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本トレクス株式会社は9月11日、同社情報システムへの不正アクセスについて発表した。 これは9月8日に、同社が管理する情報システムへの第三者からの不正アクセスを確認したというもの。 さくらインターネットが不正アクセス調査結果を発表「さくらのレンタルサーバ」全サーバ再構築など再発防止策を掲げる 2026.9.1…</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4198,12 +4243,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html</t>
         </is>
       </c>
     </row>
@@ -4215,24 +4260,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>日本エネルギー経済研究所</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicros…</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4245,41 +4308,54 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>イープラス</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 払戻し申請を行った顧客1,463件の個人情報が漏えい ～ イープラスに不正アクセス 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正…</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,463</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4292,41 +4368,54 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>郵便局アプリ</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実…</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4334,39 +4423,39 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
+          <t>セイコーマート</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chrome 155</t>
+          <t>セイコーマートアプリ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大 【セキュリティ ニュース】事務用NASがランサム被害、通常業務は再開 - 佐賀大（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 事務用NASがランサム被害、通常業務は再開 - 佐賀大 佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 同大によれば、2026年9月24日、事務部門で利用するネットワーク対応ストレージ（NAS）において、ランサムウェアが原因と見られる被害が発生したことを確認したという。 同大では被害の拡大を防ぐため、問題の機器をネットワークから遮断。事務で利用する端末の利用を停止した。 警察へ相談するとともに侵害を受けた経路や被害範囲の調査を実施。感染が疑われたサーバについては復旧し、同月27日に事務用端末の利用を再開。翌28日か…</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした…</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4376,13 +4465,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4390,59 +4483,41 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674 / https://www.security-next.com/190842</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>8つの壁</t>
-        </is>
-      </c>
+          <t>Toyobo MC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC | ScanNetSecurity 2026.10.07（水） HOME…</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4455,150 +4530,109 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ULTRA MART</t>
-        </is>
-      </c>
+          <t>Three educational institutions（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Sec…</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yagura / Security NEXT / ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315 / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>クロネコ代金後払いサービス</t>
-        </is>
-      </c>
+          <t>Kodansha BECK（ news report ）</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 「クロネコ代金後払いサービス」に不正アクセス ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 「クロネコ代金後払いサービス」に不正アクセス | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / 業界動向 新製品 サービス 業界…</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Security NEXT / ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 - ScanNetSecurity</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4606,19 +4640,10 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4626,46 +4651,41 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -4678,25 +4698,25 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>eplus（tracker headline）</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>eplus（tracker headline） — Unauthorized access.</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4732,24 +4752,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -4762,7 +4787,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
@@ -4774,24 +4799,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -4799,12 +4829,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4816,13 +4846,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>システムで</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大 佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4833,7 +4872,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -4846,7 +4885,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190842</t>
         </is>
       </c>
     </row>
@@ -4858,24 +4897,42 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>8つの壁</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。 EDR やファイアウォール、クラウドサービスなど、多様な領域から届くアラートを横断して相関分析しなければ、インシデントの全体像と因果関係は見えてこない。しかし、毎秒生まれる大量のログと、異常を知らせるアラートはときに SOC 担当者の手に余る。 10 月 21 日…</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -4888,7 +4945,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
         </is>
       </c>
     </row>
@@ -4900,37 +4957,55 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ULTRA MART</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56356;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 これは9月9日から9月10日の抽選枠で販売を実施した、「ULTRA MART」での「M78ウルトラマン ふわふわお…</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
         </is>
       </c>
     </row>
@@ -4942,44 +5017,62 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ）</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>クロネコ代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 「クロネコ代金後払いサービス」に不正アクセス ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8…</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4990,7 +5083,7 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+          <t>「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 - ScanNetSecurity</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5000,10 +5093,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -5014,59 +5116,46 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 京王電鉄にランサムウェア攻撃 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品･サービス / 業界動向 新製品 サービス 業界動向 市場規模 セキュリティとお金 コンテン…</t>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 従業員情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5079,25 +5168,25 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ）</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5128,18 +5217,18 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5170,18 +5259,18 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline）</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline） — Unauthorized access.</t>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5212,39 +5301,29 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>41</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5257,41 +5336,36 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
+          <t>Lashinbang（tracker headline）</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5299,59 +5373,41 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>日本郵便</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>メトポ</t>
-        </is>
-      </c>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 【セキュリティ ニュース】「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 同社によれば、同サービスで利用するサーバが第三者によって侵害されたことが判明したもの。 サーバ内には、同サービス会員の登録メールアドレス約5万9000件が保存されており、流出したおそれがある。これらメールアドレスは、メール送信が不能となったことから、同社で配信を停止しているものだという。 同社は、侵害を受けたと見られる部分を特定し、対策を講じた。引き続き原因や影響の範囲など詳細について調査を進めている。 同社では…</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5359,30 +5415,30 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190050 / https://www.security-next.com/190791</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline）</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5413,29 +5469,34 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline）</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline） — Ransomware.</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5448,36 +5509,54 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ）</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ランサムウェア被害拡大中</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+          <t>脅威動向 ScanNetSecurity 2026.9.30 Wed 8:00 ランサムウェア被害件数が過去最多の123件に、警察庁が対策情報を紹介 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア…</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5485,41 +5564,59 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>サイバー攻撃共同対処訓練</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+          <t>業界動向 ScanNetSecurity 2026.9.30 Wed 8:00 山口東京理科大チームが優勝 ～ 県警ら主催「サイバー攻撃共同対処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 …</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5532,36 +5629,54 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>お問合せフォーム</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支…</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 従業員情報</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5574,54 +5689,36 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>スマチケ</t>
-        </is>
-      </c>
+          <t>VOISING（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 → チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 | インシデント速報 by ヤグラ コンテンツにスキップ インシデン…</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>確認されず</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>1,463</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 口座情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -5634,54 +5731,36 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>タイムズカー</t>
-        </is>
-      </c>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 【セキュリティ ニュース】教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 同大によれば、2026年8月7日に教員5人のメールアカウントが第三者によって侵害されたもの。同月29日に検知した。 フィッシング攻撃などにより、認証情報が窃取され、アカウントが乗っ取られたことが原因とみられる。 アカウントを不正に利用され、1333件の迷惑メールが送信されたほか、一部アカウントでは、第三者がメールデータにアクセスした痕跡が確認された。大規模なデータの抽出や持ち出しなどは確認されていないものの、一部のデータへアクセ…</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5689,59 +5768,41 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203 / https://www.security-next.com/189987 / https://www.security-next.com/190198 / https://www.security-next.com/190319</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Chrome 155</t>
-        </is>
-      </c>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 【セキュリティ ニュース】ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 同社によれば、同社グループのサーバがランサムウェアによる攻撃を受けたもので、9月26日未明に確認した。 同社では被害拡大を防ぐため、ネットワークを遮断。警察へ通報するとともに、外部協力のもと、原因や攻撃経路について調査を進めている。 また事業に関する機密情報や顧客情報などが流出した可能性も含め、影響範囲など被害状況を調べている。 （Security NEXT - 2026/09/28 ） ツイ…</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -5754,34 +5815,34 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190761</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gyazo</t>
+          <t>WaterPlum</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Managemen…</t>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁が注意喚起する「WaterPlum」の手口 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書…</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5796,52 +5857,52 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yagura / ScanNetSecurity</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>旭化成</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>山東聖泉</t>
+          <t>サイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA Conference Security Days 新技術 / 新製品…</t>
+          <t>モンベルのグローバルサイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5849,19 +5910,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -5869,41 +5921,51 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
+          <t>https://www.security-next.com/190798</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report）</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -5916,36 +5978,54 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report）</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Helpfeel</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>モンベル・グローバルサイト</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。…</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -5958,36 +6038,41 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
+          <t>セイコーマート</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -5995,39 +6080,39 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>情報が持ち出されたか</t>
+          <t>メトポ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 → 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 …</t>
+          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6035,14 +6120,10 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6055,25 +6136,25 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
+          <t>https://www.security-next.com/190791</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline）</t>
+          <t>Toyobo Textile（tracker headline）</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6104,42 +6185,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>事務情報システムにおけるランサムウェア被害の発生について</t>
-        </is>
-      </c>
+          <t>Saga University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 → 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク…</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Saga University（tracker headline） — Ransomware.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>メールアドレス, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6152,54 +6220,36 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
-        </is>
-      </c>
+          <t>QUO Card（ news report ）</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Management Summit RSA C…</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6207,30 +6257,30 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+          <t>International House of Japan (library)（tracker headline）</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6261,18 +6311,18 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6303,29 +6353,47 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>スマチケ</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
+          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 → 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月3…</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1,463</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, 口座情報</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6338,36 +6406,54 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+          <t>脅威動向 ScanNetSecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大、金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのUR…</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6380,25 +6466,34 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>サーバに不正アクセスか - 詳細は調査中 日本郵便は</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中 日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6409,7 +6504,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6422,36 +6517,50 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190734</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>スパムの踏み台に - 日大 日本大学</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
+          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6464,25 +6573,34 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190319</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>システムに影響 - 京王電鉄 京王電鉄は</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
+          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6493,7 +6611,7 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6506,78 +6624,114 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190761</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>Helpfeel</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gyazo</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆…</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>旭化成</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>山東聖泉</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記…</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6590,54 +6744,36 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Chrome 155</t>
-        </is>
-      </c>
+          <t>Tokyo Metro (Metpo)（news report）</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 【セキュリティ ニュース】ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 同社によれば、2026年9月10日、通信販売で利用しているシステムが侵害された疑いがあることを確認。同月11日に事態を公表し、対応を進めている。 その後の調査で、通信販売の顧客対応に利用するシステム内に保存されていた顧客との通話音声データや関連情報が、第三者に取得された可能性があることがわかった。 さらに同社が利用する顧客管理システムも侵害され、情報を窃取された可能性があるという。 同社では、個人情報保護委員会へ報告す…</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -6645,59 +6781,41 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189663 / https://www.security-next.com/190377</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>第一生命</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>CINRA JOB</t>
-        </is>
-      </c>
+          <t>Nippon Rent-A-Car (app)（news report）</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス 【セキュリティ ニュース】クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 同サービスを運営するCINRAによれば2026年8月18日、認証情報が第三者に取得され、クラウド環境にある同サービスのシステムが不正アクセスを受けたことを確認した。 取得された認証情報を用いることで、会員情報を保管するデータベースやバックアップにアクセスすることが可能だった。第三者による会員情報の閲覧、取得などは確認されていないものの、流出の可能性がある。 対象となるのは、退会者も含む会員…</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -6710,25 +6828,25 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189866</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline）</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6759,29 +6877,42 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>サーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 → 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソ…</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -6794,36 +6925,45 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ）</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+          <t>川崎市施設のサイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は、かわさき新産業創造センターのウェブサイトが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -6836,25 +6976,34 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190242</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>クセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングス</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>HALMEK up</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+          <t>女性向け情報サイトの管理画面に不正アクセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングスは、ウェブサイト「HALMEK up」の管理画面が不正アクセスを受けたことを明らかにした。詳細について調査を行っている。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6865,7 +7014,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -6878,36 +7027,54 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190247</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026年8月の情報漏えい</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+          <t>コラム リーク・東郷 2026.9.25 Fri 8:10 今日もどこかで情報漏えい 第52回「2026年8月の情報漏えい」約一割で逮捕・懲戒・行政指導 8 月に最も件数換算の被害規模が大きかったのは、株式会社Eストアーによる「「ショップサーブ」に不正アクセス、不正なプログラムを実行し購入者情報を外部に送信」の 8,853,839 件であった。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知…</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>8,853,839</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -6920,54 +7087,36 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>本社の従業員</t>
-        </is>
-      </c>
+          <t>Smaregi EC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/09/17 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。 → 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← インシデント一覧に戻る 小田原エンジニアリング、ドイツ子会社出向者のメール…</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -6980,34 +7129,34 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>murauchi.com</t>
+          <t>システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 → 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ 一覧 カテゴリ 検索 Ctrl K キャンセル 業種・種別で探す テーマの選択 ダーク ライト 自動 ← イン…</t>
+          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 → 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員…</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7015,14 +7164,9 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>6,811</t>
-        </is>
-      </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
+          <t>認証情報</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7040,34 +7184,34 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>マルウェアに感染しており、除去作業が必要</t>
+          <t>政府の信用を大きく傷つける深刻な問題</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 【セキュリティ ニュース】生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県（1ページ目 / 全1ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ 生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 同県によれば、2026年9月4日、生徒寮の管理人がインターネットで防災気象情報を収集していたところ、サポート詐欺の被害に遭ったもの。 「マルウェアに感染しており、除去作業が必要」などとだます端末上に表示された偽の警告画面を信じ、記載のあった電話番号に連絡。相手の指示に従って操作したことから、パソコンが遠隔操作される状況に陥った。 電話を切った後、見慣れないウイルス対策ソフトが起動していることを不…</t>
+          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証…</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7077,17 +7221,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7100,25 +7244,25 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902 / https://www.security-next.com/189985</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7149,18 +7293,18 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7191,47 +7335,29 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
-        </is>
-      </c>
+          <t>Ryomo Systems（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミ…</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7239,59 +7365,41 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>サポート詐欺</t>
-        </is>
-      </c>
+          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 【セキュリティ ニュース】サポート詐欺で約4000ファイル削除 - サカイHD子会社（1ページ目 / 全2ページ）：Security NEXT Security NEXTでは、最新の情報セキュリティに関するニュースを日刊でお届けしています。 ニュース 政府・業界動向 脆弱性 製品・サービス コラム 過去記事 メルマガ サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 同社によれば、2026年8月7日、従業員が業務用パソコンでAIツールに関するウェブサイトを検索し、閲覧していたところ、警告画面が表示され、記載先へ連絡するように誘導されたという。相手先がサポートセンターであると信じて従業員が案内に従ったところ、遠隔操作ツールがパソコンにインストールされた。 同従業員が異常を認識してシステム担当者へ…</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7299,30 +7407,39 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190883 / https://www.security-next.com/174925 / https://www.security-next.com/177455 / https://www.security-next.com/188880</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>不審メールが送信 - 日大 日本大学</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>メールが送信 - 日大 日本大学は</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>理工学部教職員がフィッシング被害、不審メールが送信 - 日大 日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7333,7 +7450,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -7346,25 +7463,34 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190198</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>サイト改ざん</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>不正アクセスでサイト改ざん、内部に個人情報 - コンサル会社 コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7375,7 +7501,7 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -7388,94 +7514,76 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189792</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>GSS</t>
-        </is>
-      </c>
+          <t>Bellcadia (montbell global site)（ news report ）</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/09/14 デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 続報を注視中 重大 デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。 → デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 | インシデント速報 by ヤグラ コンテンツにスキップ インシデント速報 by ヤグラ …</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Security NEXT / Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190208 / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>この脆弱性は〇〇社の△△が報告した</t>
+          <t>メールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 REVISIO 役職員が使用する PC がマルウェア感染、ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 REVISIO 役職員が使用する PC がマルウェア感染、ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず | ScanNetSecurity 2026.10.07（水） HOME 新着記事 Scan PREMIUM 会員限定記事 Scan PREMIUM とは ? ～ なぜセキュリティ情報は面白くないのか インシデント 情報漏えい 不正アクセス 設定ミス メール誤送信 ランサムウェア Web改ざん 脆弱性 / 脅威 脆弱性 JVN IPA JPCERT/CC NISC 警察庁 JC3 CISA 調査レポート / 白書 調査報告書 JNSA ISOG-J OWASP 講演 / セミナー Black Hat Gartner Security ＆ Risk Manage…</t>
+          <t>従業員アカウントが侵害、なりすましメールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7483,19 +7591,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -7503,41 +7602,59 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
+          <t>https://www.security-next.com/189987</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>コープやまぐちLINEミニアプリ</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 データベース内の全てのデータを削除 ～「コープやまぐちLINEミニアプリ」に不正アクセス 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」…</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -7545,30 +7662,30 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline）</t>
+          <t>Osaka City (recorded interview system)（tracker headline）</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7599,18 +7716,18 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline）</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7641,18 +7758,18 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline）</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7680,8 +7797,1868 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Calbee (baseball-chip cards)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>システムが侵害され</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190377</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CINRA JOB</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189866</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>当選</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に 円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190315</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ホワイトエッセンス</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>予約サイトなどで侵害、影響など調査中 - 審美歯科チェーン 審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189665</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026/09/17 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。 → 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信…</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 → 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステム…</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>6,811</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>第367回 個人情報保護委員会</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.14 Mon 8:00 不正アクセスや報告遅れを中心に民間 98 件へ指導 ～ 個人情報保護委員会が第367回会合を開催 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機…</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189985</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出…</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングス</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188880</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>東京外環プロジェクト</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>「東京外環プロジェクト」サイトで侵害のおそれ - 公開を一時停止 国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190203</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>GSS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026/09/14 デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 続報を注視中 重大 デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。 → デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,0…</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Security NEXT / Yagura</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>2</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190208 / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングス</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190132</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>システムがランサム被害</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>システムがランサム被害、一部業務を停止 - インキメーカー 印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189674</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区 東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189902</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>スパム踏み台に - 立教大 立教大学</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Googleアカウント</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>学生の複数アカウントに不正アクセス、スパム踏み台に - 立教大 立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190050</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>フィッシング対策セミナー2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>セミナー・イベント ScanNetSecurity 2026.9.9 Wed 8:00 「フィッシング対策セミナー2026」11 / 19 開催 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6…</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>被害経験なし</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.8 Tue 8:00 サイバー攻撃の「被害経験なし」企業は約 6 割へ減少 ～ 東商2026年アンケート調査 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定され…</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>13,156</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>YAMAGoya</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>マルウェアの挙動をリアルタイム監視するOSSを公開 - JPCERT/CC JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/177455</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>システムに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>グループのシステムに不正アクセス、個人情報流出の可能性 - 三井不動産 三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189789</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SonicWall SMA 100</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>「SonicWall SMA 100」にアップデート - 既知マルウェアの除去機能を追加 SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/174925</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Catalyst SD-WAN Manager</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>「Catalyst SD-WAN Manager」にゼロデイ脆弱性 - 更新や侵害調査を Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190883</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>サーバが侵害</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>社内ファイルサーバが侵害、情報流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188534</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>まんだらけ</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>「まんだらけ」サーバに不正侵入、情報流出か - 通販やオークションは再開 コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189663</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L147"/>
+  <autoFilter ref="A1:L185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7726,7 +9703,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>146</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -7761,7 +9738,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:33:30.747902+00:00</t>
+          <t>2026-10-07T00:34:51.004749+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:34:51.004749+00:00</t>
+          <t>2026-10-07T00:36:07.523379+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,12 +513,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 異なる手法による別の不正アクセスが判明「ニッポンレンタカーアプリ」 ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利…</t>
+          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス、26件の個人情報が漏えいした可能性 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは9月30日に、同社従業員のメールアカウントに不正アクセスがあり、メール送受信先の一部の個人情報が漏えいした可能性が判明したというもの。当該従業員は、日本経済新聞社社員のメールアドレスで届いたフィッシングメールから、認証情報を入手されている。 漏えいした可能性があるのは、26件の個人情報（個人名、メールアドレス）。 同社では、個人情報漏えいが疑われるメールアドレス先の対象者に個別にメールで連絡を行っている。 同社では不正アクセスの発覚後に、当該アカウントへの接続を遮断している。 同社では引き続き、個人情報の安全を守るために最善を尽くすとのこと。 なお、株式会社日本経済新聞社は10月4日に、約9,000件のなりすましメール…</t>
+          <t>株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは9月30日に、同社従業員のメールアカウントに不正アクセスがあり、メール送受信先の一部の個人情報が漏えいした可能性が判明したというもの。当該従業員は、日本経済新聞社社員のメールアドレスで届いたフィッシングメールから、認証情報を入手されている。 漏えいした可能性があるのは、26件の個人情報（個人名、メールアドレス）。 同社では、個人情報漏えいが疑われるメールアドレス先の対象者に個別にメールで連絡を行っている。 同社では不正アクセスの発覚後に、当該アカウントへの接続を遮断している。 同社では引き続き、個人情報の安全を守るために最善を尽くすとのこと。 なお、株式会社日本経済新聞社は10月4日に、約9,000件のなりすましメールが送信された旨を公表している。 Fujisan.co.jp「マイページ」への不正ログイン、日経BP の雑誌書籍等の購入者も対象に 2025.7.14 Mon 8:05 日経BP従業員メールアカウントに不正アクセス、33名の個人情報流出の可能性 2024.6.14 Fri 8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 日本経済新聞社社員の「マイクロソフト365」のアカウントにサイバー攻撃、悪性サイトに誘導するメールを送信 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 これは同社社員が使用していた「マイクロソフト365」のアカウントに第三者が不正にログインし、約9,000件のなりすましメールが送信されたというもの。社内の他複数の社員とやりとりがあった取材先などに対し、悪性サイトに誘導する内容のメールが9月30日送信されている。 同社では、送信先のメールアドレスや氏名の他、一部メールの内容が漏えいしたとみており、侵害を受けた範囲や漏えいした個人情報の件数を調査している。 同社では、なりすましメールの送信先に個別に連絡し、当該メールの削除を依頼している。 同社では、セキュリティ対策をさらに強化して情報…</t>
+          <t>株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 これは同社社員が使用していた「マイクロソフト365」のアカウントに第三者が不正にログインし、約9,000件のなりすましメールが送信されたというもの。社内の他複数の社員とやりとりがあった取材先などに対し、悪性サイトに誘導する内容のメールが9月30日送信されている。 同社では、送信先のメールアドレスや氏名の他、一部メールの内容が漏えいしたとみており、侵害を受けた範囲や漏えいした個人情報の件数を調査している。 同社では、なりすましメールの送信先に個別に連絡し、当該メールの削除を依頼している。 同社では、セキュリティ対策をさらに強化して情報管理を徹底するとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃、事業運営に必要なシステム環境の復旧を完了 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 同社台湾子会社のMOST社では3月21日未明に、メールサーバでのウイルス感染を確認し、その後の調査でランサムウェアによる攻撃を受けたことが判明したため、被害状況と影響範囲の詳細について調査を行っていた。 九州電子ではMOST社でランサムウェア感染が確認された旨の報告を受け、初動対応としてMOST社とのネットワーク接続を遮断し、外部専門機関と連携のうえ、詳細な調査と安全確認を実施している。 九州電子で調査した結果、MOST社から九州電子への感染拡大を示す痕跡、外部からの不正アクセスや情報漏えいにつながる通信の痕跡は確認されなかった。 九州電子では予防的措置として、…</t>
+          <t>九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 同社台湾子会社のMOST社では3月21日未明に、メールサーバでのウイルス感染を確認し、その後の調査でランサムウェアによる攻撃を受けたことが判明したため、被害状況と影響範囲の詳細について調査を行っていた。 九州電子ではMOST社でランサムウェア感染が確認された旨の報告を受け、初動対応としてMOST社とのネットワーク接続を遮断し、外部専門機関と連携のうえ、詳細な調査と安全確認を実施している。 九州電子で調査した結果、MOST社から九州電子への感染拡大を示す痕跡、外部からの不正アクセスや情報漏えいにつながる通信の痕跡は確認されなかった。 九州電子では予防的措置として、端末単位での隔離対応、エンドポイントセキュリティ対策の強化、認証管理およびパスワード運用の見直しなどを実施し、システム全体の安全性をあらためて確認している。 MOST社では影響調査と復旧作業を進めた結果、事業運営に必要なシステム環境の復旧を完了しており、現在は安全性を確認している。またMOST社でも、セキ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 これは8月31日に、当該従業員のメールアカウントで第三者からの不正アクセスの痕跡を確認したというもの。調査の結果、2026年3月27日から8月31日までの間、当該アカウントに第三者が継続的にアクセスし、メールを閲覧していたことが判明している。 漏えいした可能性があるのは、当該従業員1名と取引先担当者との間で送受信されたメールの内容が対象で、2026年3月27日から8月31日までの時点で…</t>
+          <t>株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 これは8月31日に、当該従業員のメールアカウントで第三者からの不正アクセスの痕跡を確認したというもの。調査の結果、2026年3月27日から8月31日までの間、当該アカウントに第三者が継続的にアクセスし、メールを閲覧していたことが判明している。 漏えいした可能性があるのは、当該従業員1名と取引先担当者との間で送受信されたメールの内容が対象で、2026年3月27日から8月31日までの時点でメールボックス内に保存されていた過去のメールも閲覧の対象となる。現時点で閲覧を確認できているのは約3,500通で、最も古いもので2018年に送受信されたメールが含まれる。 同社によると、不正アクセスを行った第三者が同社従業員になりすまし、取引先宛てに入金を指示するメールを送信していたことが判明している。当該第三者は正規のやり取りを閲覧していたとみられ、一部の取引先で金銭的な被害が生じている。 同社では当該</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 「カイクラサービス紹介サイト」に複数の不正プログラム、サーバ内のデータを外部に送信した形跡は確認されず 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 同社では8月24日に、「カイクラサービス紹介サイト」（ https://kaiwa.cloud/ ）で複数の不正プログラムの設置を検知し、社内調査による分析の結果、不正プログラムのうち1件は、当該サイトが設置されているサーバからの情報取得を技術的に可能にするものと判明したため、リスク拡大を回避し、調査を行うため、当該サイトおよび同一サーバで運用していた下記3サイトを含め、アクセスを一時停止するとともに、外部の専門機関に依頼し、ログ解析等を通じた精査を開始していた。 コーポレートサイト：https://www.thinca.co.jp カイクラサー…</t>
+          <t>株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 同社では8月24日に、「カイクラサービス紹介サイト」（ https://kaiwa.cloud/ ）で複数の不正プログラムの設置を検知し、社内調査による分析の結果、不正プログラムのうち1件は、当該サイトが設置されているサーバからの情報取得を技術的に可能にするものと判明したため、リスク拡大を回避し、調査を行うため、当該サイトおよび同一サーバで運用していた下記3サイトを含め、アクセスを一時停止するとともに、外部の専門機関に依頼し、ログ解析等を通じた精査を開始していた。 コーポレートサイト：https://www.thinca.co.jp カイクラサービス紹介サイト：https://kaiwa.cloud/ カイクラ.mag：https://kaiwa.cloud/media/ Car Connect：https://carconnect.jp/ 外部専門調査機関による調査の結果、検出された不正プログラムが実行され、サーバ内のデータを外部に送信した形跡は確認されなかった</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.7 Wed 8:05 KKR京都くに荘のメールサーバに不正アクセス 国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 同会では8月25日に、KKR京都くに荘のメールサーバへの不正アクセスに伴う個人情報漏えいの可能性について公表していたが、その後、メールシステム運用事業者及び外部専門事業者による詳細な調査を実施した結果、第三者からの当該メールアカウントのメールボックスへのアクセスやメールの閲覧を示す記録は確認されず、現時点で、顧客の個人情報が漏えいした事実は確認されなかったという。 同会では、メールシステムのセキュリティ対策の強化を図るとともに、顧客の個人情報の適切な管理に努め、再発防止に取り組むとのこと。 実行犯が示唆したダークウェブでの情報公開は確認されず ～ ワシントンホテルにランサムウェア攻撃 2026.9.25 Fri 8:05 ホテル白菊が利用する…</t>
+          <t>国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 同会では8月25日に、KKR京都くに荘のメールサーバへの不正アクセスに伴う個人情報漏えいの可能性について公表していたが、その後、メールシステム運用事業者及び外部専門事業者による詳細な調査を実施した結果、第三者からの当該メールアカウントのメールボックスへのアクセスやメールの閲覧を示す記録は確認されず、現時点で、顧客の個人情報が漏えいした事実は確認されなかったという。 同会では、メールシステムのセキュリティ対策の強化を図るとともに、顧客の個人情報の適切な管理に努め、再発防止に取り組むとのこと。 実行犯が示唆したダークウェブでの情報公開は確認されず ～ ワシントンホテルにランサムウェア攻撃 2026.9.25 Fri 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 2026.9.16 Wed 8:05 Booking.com経由でホテルグランバッハ京都セレクトを予約した顧客にフィッシングサイト誘導メッセージ、注意を呼びかけ 2026.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>脅威動向 Okta, Inc. 2026.10.6 Tue 8:15 Okta Blog 第20回 AIアカウント乗っ取りと偽登録の仕組み ～ Oktaが明かすアンダーグラウンドAI経済 AI 需要の高まりは、AI アカウント乗っ取りや無料特典の悪用で得たアクセス権を転売する違法市場を生み出している 4月、あるソフトウェアアーキテクトが AI プロバイダーからの請求書を開き、二度見しました。 彼が承認した覚えのない利用に対して、25,000 ドルが請求 されていたのです。別の組織の請求額は、 詐欺が発見され抑止されるまでに100万ドル近く に達しました。犯罪者が AI アカウントの制御を獲得し、盗んだアクセス権を転売して利益を得るために「AI トークン乗っ取り」のような新しい手口に転じる中、このような事例は増加傾向にあります。 AI への需要は急上昇しており、誰もが最も能力の高いフロンティアモデルへのアクセスを求めています。しかし、請求が届き、ユーザーが上昇するトークンコストに直面するにつれ、AI へのアクセス料を支払うのではなく盗むという動機が、 AI のコスト 上昇とまさに並行して…</t>
+          <t>4月、あるソフトウェアアーキテクトが AI プロバイダーからの請求書を開き、二度見しました。 彼が承認した覚えのない利用に対して、25,000 ドルが請求 されていたのです。別の組織の請求額は、 詐欺が発見され抑止されるまでに100万ドル近く に達しました。犯罪者が AI アカウントの制御を獲得し、盗んだアクセス権を転売して利益を得るために「AI トークン乗っ取り」のような新しい手口に転じる中、このような事例は増加傾向にあります。 AI への需要は急上昇しており、誰もが最も能力の高いフロンティアモデルへのアクセスを求めています。しかし、請求が届き、ユーザーが上昇するトークンコストに直面するにつれ、AI へのアクセス料を支払うのではなく盗むという動機が、 AI のコスト 上昇とまさに並行して高まっています。 この摩擦が、急成長する違法市場を生み出しました。脅威アクターが介入し、標準的なサブスクリプション価格から時には 70%～ 90% オフという大幅な割引で AI アクセスを提供しています。しかし、彼らは一体どのようにそれを行っているのでしょうか？ Okta 脅威インテリジェンスチームは</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>従業員アカウントに不正アクセス、取材先に大量なりすましメール - 日経 日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 ：Security NEXT</t>
+          <t>日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>委託先で侵害、問い合わせ顧客の情報が流出か - 大和証券 大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>セキュリティホール・脆弱性 ScanNetSecurity 2026.10.6 Tue 8:00 Apache HTTP Server 2.4 に複数の脆弱性 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 The Apache Software Foundationでは、Apache HTTP Server 2.4系における複数の脆弱性に対応したApache HTTP Server 2.4.69を現地時間10月1日に公開している。 JVNでは、影響を受けるシステム、想定される影…</t>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 The Apache Software Foundationでは、Apache HTTP Server 2.4系における複数の脆弱性に対応したApache HTTP Server 2.4.69を現地時間10月1日に公開している。 JVNでは、影響を受けるシステム、想定される影響、対策方法についてはApache HTTP Serverのアドバイザリを参照するよう案内している。 Fixed in Apache HTTP Server 2.4.69 https://httpd.apache.org/security/vulnerabilities_24.html#2.4.69 Apache HTTP Server 2.4 に複数の脆弱性 2026.6.11 Thu 8:00 Apache HTTP Server 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
         </is>
       </c>
     </row>
@@ -1493,22 +1493,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>信濃毎日新聞</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>信濃毎日新聞デジタル</t>
+          <t>さくらのレンタルサーバ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「信濃毎日新聞デジタル」に不正アクセス、一時的に一部の履歴データが消去 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 これは9月7日に、「信濃毎日新聞デジタル」の信毎ポイント交換システムへの外部からの不正アクセスが判明したというもので、一時的に一部の履歴データが消去される事象が発生していた。 同社で調査した結果、現時点で個人情報の流出は確認されていないという。 同社では、該当システムに修正措置を講じ、データの復旧も完了している。また、顧客が保有しているポイント数への影響はない。 同社では今後、より一層の安全管理とセキュリティ強化に努めるとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員…</t>
+          <t>株式会社ムラウチドットコムは9月15日、7月24日に公表した同社が運用する一部システムへの不正アクセスについて、第二報を発表した。 同社では7月15日未明に、社内システムで障害が発生し、翌7月16日の復旧作業中に第三者からの不正アクセスの痕跡を確認したため、システム保全として外部アクセスを遮断し、外部の情報セキュリティ専門会社によるフォレンジック調査を実施し、侵入経路や影響範囲の特定を進めていた。 調査結果によると、同社が管理するWebシステムの一部に存在していた脆弱性を悪用されたことを起点とした不正アクセスがあり、その後、複数のシステムへの不正アクセスが判明している。また、同社が保有する顧客の個人情報の一部が外部に持ち出されたことを確認している。 不正アクセスによる漏えいが確認されたのは7,716,811件の個人情報（氏名、住所、電話番号、メールアドレス、生年月日、性別）。 同社では9月15日から、対象となる顧客に個別に通知メールの送信を開始している。 同社では、システムへのアクセス権限および認証情報の管理方法の見直し、サーバ・ネットワークの監視および不正アクセスの検知体制の強化等に</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7,368</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
         </is>
       </c>
     </row>
@@ -1553,22 +1553,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ベネフィット・ワン</t>
+          <t>信濃毎日新聞</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ベネワン・プラットフォーム</t>
+          <t>信濃毎日新聞デジタル</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「ベネワン・プラットフォーム」のアンケート機能で他企業・団体の個人情報がダウンロード可能に、不具合を認知するも解消作業が適切に実施されず 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 これは「ベネワン・プラットフォーム」のアンケート機能にて、担当者がアンケート結果をダウンロードした際、本来アクセスできない他企業・団体の従業員の個人情報の一部が表示される状態となっていたというもの。同社サービスを利用している企業・団体の担当者1社1名から7月30日に連絡があり、発覚した。 対象となるのは2,322企業・団体の13,460名の個人情報（社員・職員番号、氏名、性別、生年月日、企業・団体名、所属/役職、入…</t>
+          <t>信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 これは9月7日に、「信濃毎日新聞デジタル」の信毎ポイント交換システムへの外部からの不正アクセスが判明したというもので、一時的に一部の履歴データが消去される事象が発生していた。 同社で調査した結果、現時点で個人情報の流出は確認されていないという。 同社では、該当システムに修正措置を講じ、データの復旧も完了している。また、顧客が保有しているポイント数への影響はない。 同社では今後、より一層の安全管理とセキュリティ強化に努めるとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 3 日間で約 2 万件の ID でログイン「毎日新聞デジタル</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,368</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>氏名, 生年月日, クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1613,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>ベネフィット・ワン</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PhotoGoods</t>
+          <t>ベネワン・プラットフォーム</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.6 Tue 8:05 「PhotoGoods」に不正アクセス、カード情報が漏えいした可能性 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 これは9月11日に、「PhotoGoods」内に不審な外部プログラムが読み込まれているとの連絡があり、システム管理会社による調査を行った結果、決済画面等に入力されたクレジットカード情報などを不正に取得する機能を持つプログラムの設置を確認したというもの。あわせてシステム上の脆弱性およびファイルアップロード機能の悪用による第三者からの不正アクセスも確認している。 「PhotoGoods」を利用した顧客下記の情報が漏えいした可能性がある。なお、クレジットカ…</t>
+          <t>株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 これは「ベネワン・プラットフォーム」のアンケート機能にて、担当者がアンケート結果をダウンロードした際、本来アクセスできない他企業・団体の従業員の個人情報の一部が表示される状態となっていたというもの。同社サービスを利用している企業・団体の担当者1社1名から7月30日に連絡があり、発覚した。 対象となるのは2,322企業・団体の13,460名の個人情報（社員・職員番号、氏名、性別、生年月日、企業・団体名、所属/役職、入退社情報）.。 同社では当該データについて、利用企業・団体の担当者に連絡し、第三者への転送、複製その他の提供は行われておらず、同社への連絡後にデータを削除したことを確認している。 同社で調査した結果、2025年6月に行ったシステム改修により発生していた、アンケート結果ダウンロード機能におけるプログラムの条件設定不備が原因と確認している。また、2025年10月に行った社内調査で本不具合を認知していたものの、</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1643,25 +1643,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+          <t>氏名, 生年月日, クレジットカード情報</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ScanNetSecurity / Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html / https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
         </is>
       </c>
     </row>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>大興印刷</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>大起水産公式アプリ</t>
+          <t>PhotoGoods</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>アプリシステムが侵害、顧客情報流出の可能性 - 回転ずしチェーン 回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が不正アクセスを受け、顧客の個人情報が流出した可能性があることを明らかにした。アプリは通常通り利用できる。 ：Security NEXT</t>
+          <t>大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 これは9月11日に、「PhotoGoods」内に不審な外部プログラムが読み込まれているとの連絡があり、システム管理会社による調査を行った結果、決済画面等に入力されたクレジットカード情報などを不正に取得する機能を持つプログラムの設置を確認したというもの。あわせてシステム上の脆弱性およびファイルアップロード機能の悪用による第三者からの不正アクセスも確認している。 「PhotoGoods」を利用した顧客下記の情報が漏えいした可能性がある。なお、クレジットカード情報については、不正プログラムが稼働していた2026年8月6日から9月11日までの期間に、「PhotoGoods」の決済画面にカード情報を入力した顧客が対象となる。 ・クレジットカード情報（カード番号、有効期限、セキュリティコード） ・個人情報（氏名、住所、電話番号、メールアドレス） ・会員パスワードに関する情報（元のパスワードを直接読み取ることがで</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1696,27 +1696,32 @@
           <t>可能性あり</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191070</t>
+          <t>https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
         </is>
       </c>
     </row>
@@ -1728,24 +1733,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>大起水産</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>大起水産公式アプリ</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
+          <t>回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が不正アクセスを受け、顧客の個人情報が流出した可能性があることを明らかにした。アプリは通常通り利用できる。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1758,7 +1776,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/191070</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1788,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ）</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
+          <t>nimoca (Nimoca Co., usage-history inquiry service)（ disclosure ） — Third-party unauthorized access (attack on a public web service) to the usage-history inquiry service, from about 00:00 on Oct 4 until the service was stopped at 17:40. Found after a customer reported an unfamiliar email at about 09:00 on Oct 4. Cause and scope under investigation. No public release or misuse of the leaked data confirmed.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1812,34 +1830,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>Yaomasa（ news report ）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Yaomasa（ news report ） — Ransomware group AiLock listed the company on its leak site and claimed data publication; listing dated Sep 30.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>95万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1852,7 +1860,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1878,22 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
+          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>95万</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1894,7 +1912,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1906,13 +1924,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
+          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1923,7 +1941,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1936,7 +1954,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1948,38 +1966,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>i-ask</t>
-        </is>
-      </c>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/06 FAQ・問い合わせ管理システム「i-ask」を提供するスカラコミュニケーションズ（東京都渋谷区）、管理サイトへの不正ログインで最大5社・延べ71万3,126件の問い合わせ情報が漏えいのおそれ 情報収集中 重大 株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ（東京都渋谷区／FAQ・問い合わせ管理システム「i-ask」を提供）のサーバが不正アクセスを受け、同システムを導入していた最大5社・延べ最大713,126件の問い合わせ情報が漏えいした可能性があると公表した。第三者が2026年10月2日20時33分頃から10月3日8時1分頃にかけて「i-ask」の管理サイトへ不正にログインし、サーバに不正なプログラムを設置していた。スカラコミュニケーションズは10月3日朝にアクセスを遮断し、同日中に利用企業へ報告している。利用企業の一部は個別に対象件数を公表しているが、全5社の内訳は明らかにされていない。公表時点で二次被害は確認されていない。 株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ…</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>3,126</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1992,14 +1996,14 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-scala-communications-i-ask-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2009,12 +2013,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス</t>
+          <t>i-ask</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>複数サイトに不正アクセス、プラグイン脆弱性が標的に - ベネッセグループ会社 ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ（東京都渋谷区／FAQ・問い合わせ管理システム「i-ask」を提供）のサーバが不正アクセスを受け、同システムを導入していた最大5社・延べ最大713,126件の問い合わせ情報が漏えいした可能性があると公表した。第三者が2026年10月2日20時33分頃から10月3日8時1分頃にかけて「i-ask」の管理サイトへ不正にログインし、サーバに不正なプログラムを設置していた。スカラコミュニケーションズは10月3日朝にアクセスを遮断し、同日中に利用企業へ報告している。利用企業の一部は個別に対象件数を公表しているが、全5社の内訳は明らかにされていない。公表時点で二次被害は確認されていない。</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2025,12 +2029,17 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>713,126</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2043,7 +2052,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190961</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-scala-communications-i-ask-breach/</t>
         </is>
       </c>
     </row>
@@ -2055,13 +2064,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
+          <t>ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2071,22 +2084,13 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2094,12 +2098,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5 / https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
+          <t>https://www.security-next.com/190961</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2121,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2130,16 +2134,7 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>会員情報</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2150,12 +2145,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -2167,13 +2162,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
+          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2183,10 +2183,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2202,7 +2206,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2220,22 +2224,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2249,12 +2248,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
         </is>
       </c>
     </row>
@@ -2266,23 +2265,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
+          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2296,12 +2300,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
         </is>
       </c>
     </row>
@@ -2313,13 +2317,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大和証券</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
+          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2329,12 +2333,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>22万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2348,12 +2347,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2365,42 +2364,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ドズル社ストア</t>
-        </is>
-      </c>
+          <t>大和証券</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 池上通信機にサイバー攻撃、サーバ内の一部ファイルが暗号化 池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:…</t>
+          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>22万</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2408,12 +2399,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2425,22 +2416,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>wp2shell</t>
+          <t>WEB 発注システム</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 東産業 公式サイトにwp2shell を悪用した不正アクセス 株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPre…</t>
+          <t>池上通信機株式会社は9月24日、同社に対するサイバー攻撃の可能性について発表した。 これは9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、直ちに調査を開始したというもの。 同社では現在、社内関係部門および外部専門機関と連携し、事実関係や影響範囲および情報漏えいの範囲について調査を進めるとともに、被害拡大防止のために必要な措置を講じている。 同社では現時点で、サイバー攻撃の有無を含む詳細な事実関係および情報漏えいの範囲について確認中とのこと。 鳥取県環境放射線モニタリングシステムにランサムウェア攻撃、副サーバは被害受けず放射線モニタリングに影響なし 2026.9.16 Wed 8:05 サンメッセが利用する購買発注システム「WEB 発注システム」へサイバー攻撃 2026.9.14 Mon 8:05 メディア4u の SMS 送信システムにサイバー攻撃、連携していたブロードリーフの「.cシリーズ」「.NSシリーズ」にも影響 2026.8.26 Wed 8:10 ADサーバ上のデータが外部へ転送されたと判断 ～ 精電舎電子工業にランサムウェア攻撃 2026.8.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2450,12 +2441,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1,950,165</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2473,7 +2464,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
         </is>
       </c>
     </row>
@@ -2485,22 +2476,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>アカウント乗っ取り</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 日本大学の計 5 名の教員アカウントに不正アクセス、スパムメール送信の踏み台に 日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日に、第三者が同学の計5名の教員アカウントに不正アクセスし、当該アカウントをスパムメール送信の踏み台として利用していたことを8月29日に確認したというもの。当該アカウントから学内外に1,333件の不審メールが送信されたことを確認している。 調査の結果、当該アカウント内のデータに対する大規模な抽出や持ち出し等の痕跡は確認されていないが、一部のデータへアクセスされた可能性はあるという。 同学では、連絡先が特定可能な対象者に順次、個別にメール等で連絡を行っている。 同学では、悪意ある第三者がフィッシングメール等の手段で認証情報（ID・パスワード）を窃取し、アカウントを乗っ取ったことが原因と推測している。 同学では検知後に、当該アカウントの利用を一時停止（或いは無…</t>
+          <t>池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:05 教育ソフトウェアの休眠中のレンタルサーバにランサムウェア攻撃、暗号化被害と不正アクセスの痕跡を確認 2026.9.8 Tue 8:05 サンコーテクノのベトナム子会社にランサムウェア攻撃、サーバ及びパソコン内の各種ファイルの暗号化を</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2510,12 +2501,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2528,12 +2519,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
         </is>
       </c>
     </row>
@@ -2545,22 +2536,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>一万三千尺物語</t>
+          <t>wp2shell</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 あいの風とやま鉄道 観光列車の座席管理システムに不正アクセス あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 これは9月8日朝に、同社社員が座席管理システムにアクセスしたところ、複数の予約がキャンセルされていた他、当該システムから正規の手順で行われていない予約を確認したため、全ての新規予約の受付を停止するとともに調査を行った結果、9月2日に最初の不正アクセスがあり、以降、9月8日までに複数回の不正アクセスを確認したというもの。 漏えいした可能性があるのは、これまでに観光列車「一万三千尺物語」に乗車した顧客または今後の乗車予約をしていた顧客 計1,409名の個人情報（氏名、住所、電話番号、メールアドレス）。 同社では対象の顧客に9月12日付で、文書「個人情報の漏えいのおそれがあ…</t>
+          <t xml:space="preserve">株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri 8:00 WordPress の深刻度「緊急」脆弱性「wp2shell 」の概要と対応指針 ～ GMO Flatt Security </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2570,12 +2561,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1,409</t>
+          <t>1,950,165</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 従業員情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2588,12 +2579,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
         </is>
       </c>
     </row>
@@ -2605,22 +2596,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>原田産業</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ビールの縁側</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 「ドズル社ストア」で不正なページに誘導、カード情報を入力した場合はカード会社への連絡を呼びかけ 株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 これは9月11日午後4時頃に、「ドズル社ストア」で商品購入手続きの際、正規の決済ページではない不正な外部ページへ誘導される事象が発生したというもの。不正なページには、主に下記のような特徴があり、不正なページで行われた支払いは、「ドズル社ストア」での注文として受け付けられていない。 ・ページ左上に「Checkout」と表示され、ドズル社ストアの名称・ロゴが表示されない ・英語で表示され、配送先の国・地域に「United States」があらかじめ選択されている ・実際の商品価格と大きく異なる高額な金額が表示される 同社によると、発生推定期間中（9月11日午後3時頃～午後5時50分）に購入…</t>
+          <t>原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレジットカード情報を含む情報が漏えいした可能性のある顧客は9名。対象となる情報には、氏名、電話番号、メールアドレス、性別、生年月日、住所、クレジットカード情報（番号、名義人、有効期限、セキュリティコード）が含まれる。なお、決済を完了した顧客は4名、決済を完了せずに注文手続を終了した顧客は5名。 同社では対象となる9名に個別にメールで連絡を行っている。 同社では現在</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2630,12 +2621,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2648,12 +2639,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
@@ -2665,22 +2656,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>原田産業</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ビールの縁側</t>
-        </is>
-      </c>
+          <t>アバハウスインターナショナル</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 ECサイト「ビールの縁側」に不正アクセス、9 名のカード情報が漏えいした可能性 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレ…</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2688,19 +2670,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2708,12 +2681,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2725,18 +2698,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
+          <t>『焼肉きんぐ』1000万件超の情報漏洩 なぜ今、飲食店アプリが狙われるのか？ #エキスパートトピ（山路力也） - エキスパート - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1000万</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2755,7 +2733,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2767,13 +2745,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+          <t>「焼肉きんぐ」、顧客情報漏洩 不正アクセスで1000万件超 - 日本経済新聞</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2783,15 +2761,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2807,7 +2789,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2819,24 +2801,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ）</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4933</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2849,7 +2841,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2861,13 +2853,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline）</t>
+          <t>White Essence（ disclosure ）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2903,13 +2895,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline）</t>
+          <t>The Japan Times（tracker headline）</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
+          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2945,13 +2937,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ）</t>
+          <t>Safer Internet Association（tracker headline）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2987,13 +2979,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
+          <t>Osaka Metropolitan University（ news report ）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
+          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3029,13 +3021,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline）</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3071,13 +3063,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
+          <t>JOGMEC（tracker headline）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3113,13 +3105,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3155,13 +3147,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ）</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3197,13 +3189,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline）</t>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3239,42 +3231,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>777CON-PASS（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/06 焼肉チェーンを運営する物語コーポレーション（愛知県豊橋市）、「焼肉きんぐ」公式アプリの会員管理システムに不正アクセス — 1,078万8,963件が漏えい、登録者のほぼ全員が対象 続報を注視中 深刻 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。 → 株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5…</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>8,963</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3287,25 +3261,34 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>焼肉きんぐ</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
+          <t>株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3313,10 +3296,19 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8,963</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3329,7 +3321,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3347,17 +3339,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>9000</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3376,7 +3363,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3381,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -3418,7 +3410,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3430,23 +3422,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3465,7 +3452,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3477,24 +3464,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ）</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3507,50 +3499,36 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>12万</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>従業員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3563,7 +3541,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -3575,13 +3553,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3589,7 +3572,16 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>従業員情報</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3605,7 +3597,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
@@ -3617,24 +3609,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline）</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3647,7 +3639,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3659,13 +3651,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline）</t>
+          <t>MoonStar（tracker headline）</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3701,37 +3693,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>返金</t>
-        </is>
-      </c>
+          <t>Abahouse（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/10/04 アパレルのアバハウスインターナショナル、会員・EC受注データベースに不正アクセス — 全顧客に影響の可能性、実際の注文内容と一致する「返金」詐欺メールも確認 続報を注視中 重大 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。 → 株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情…</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3744,29 +3723,29 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>問い合わせサービスがサイバー攻撃を受け</t>
+          <t>返金</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>荷物問合サービスが侵害、個人情報流出の可能性 - 佐川急便 佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
+          <t>株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3779,10 +3758,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3795,7 +3778,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190952</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3807,13 +3790,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ジャパンタイムズ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>問い合わせサービスがサイバー攻撃を受け</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+          <t>佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3823,13 +3810,13 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3842,7 +3829,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
+          <t>https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
@@ -3854,23 +3841,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>ジャパンタイムズ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>12万</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3889,7 +3876,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3901,13 +3888,13 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3917,7 +3904,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>12万</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3936,7 +3923,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3948,18 +3935,13 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3969,7 +3951,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3988,7 +3970,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4000,13 +3982,13 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4016,7 +3998,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -4035,7 +4022,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4040,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
+          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4063,14 +4050,10 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -4086,7 +4069,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4098,13 +4081,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4137,7 +4120,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4138,7 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
+          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4165,12 +4148,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4188,7 +4171,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4200,22 +4183,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>さくらのレンタルサーバ</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本トレクスの情報システムに不正アクセス、一部業務が停止 日本トレクス株式会社は9月11日、同社情報システムへの不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56377;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本トレクス株式会社は9月11日、同社情報システムへの不正アクセスについて発表した。 これは9月8日に、同社が管理する情報システムへの第三者からの不正アクセスを確認したというもの。 さくらインターネットが不正アクセス調査結果を発表「さくらのレンタルサーバ」全サーバ再構築など再発防止策を掲げる 2026.9.1…</t>
+          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4223,19 +4202,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4243,12 +4217,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4244,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃、所員6名のMicrosoft 365 アカウントに不正アクセス 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicros…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicrosoft 365 アカウントに不正アクセスがあり、メール及びファイルの閲覧による外部への情報漏えいの可能性、ファイルのダウンロードによる外部への情報漏えいが判明したというもの。 富山県立大学の Microsoft 365 学生アカウントから大量の迷惑メール送信 2026.7.23 Thu 8:05 TE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4330,12 +4304,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 払戻し申請を行った顧客1,463件の個人情報が漏えい ～ イープラスに不正アクセス 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正アクセスがあり、同システム内に保管していた払戻しを実施するための情報に含まれていた顧客の個人情報の漏えいが判明したというもの。 一部顧客の情報が閲覧・編集・削除可能に ～ リセールサイト「RELIEF Ticket」 2025.7.3 Thu 8:05 CNプレイガイドへの不正アクセス、キョードー東京と</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4345,7 +4319,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1,463</t>
+          <t>236,323</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4380,22 +4354,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>郵便局アプリ</t>
+          <t>mogily</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56375;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); mogily株式会社は9月11日、同社が提供するデジタル整理券システム「mogily」への不正アクセスについて発表した。 これは9月9日から9月10日にかけて、同社の「mogily」の管理システムに外部から不正アクセスがあり、一部顧客の抽選結果（当落ステータス）が第三者に改ざんされたというもの。本来「当選」であった顧客のステータスが「落選」に書き換えられたという。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィッシング詐欺等によるものとみられる不正アクセス・不</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4423,12 +4397,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html</t>
         </is>
       </c>
     </row>
@@ -4440,22 +4414,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>セイコーマートアプリ</t>
+          <t>郵便局アプリ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.2 Fri 8:05 「セイコーマートアプリ」に不正アクセス、約57万アカウントの会員情報が漏えいした可能性 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実施した結果、ゆうIDおよび郵便局アプリに関連する顧客情報が不正に取得されたことが判明している。 日本郵便 調査請求 Web受付サービスに不正アクセス、一時的に受付を停止 2026.9.30 Wed 8:05 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4465,30 +4439,30 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
         </is>
       </c>
     </row>
@@ -4500,24 +4474,42 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>セイコーマートアプリ</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした可能性が9月28日午後5時過ぎに判明したというもの。9月24日午後10時から11時の間に、不正にクラブカードの退会処理が行われたアカウントが1件あり発覚した。 「コープやまぐちLINEミニアプリ」に不正アクセス、データベースに保存されていた内容を精査し漏えいの可能性がある情報を確定 2026.9.24 T</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4530,7 +4522,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
         </is>
       </c>
     </row>
@@ -4542,13 +4534,13 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline）</t>
+          <t>Toyobo MC（tracker headline）</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4584,13 +4576,13 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ）</t>
+          <t>Three educational institutions（tracker headline）</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4626,13 +4618,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline）</t>
+          <t>Kodansha BECK（ news report ）</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4668,13 +4660,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline）</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4710,13 +4702,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4747,34 +4739,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -4787,7 +4774,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4792,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4829,12 +4816,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
@@ -4846,33 +4833,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>システムで</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>事務用NASがランサム被害、通常業務は再開 - 佐賀大 佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -4880,12 +4863,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190842</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4897,17 +4880,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>8つの壁</t>
+          <t>システムで</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.10.1 Thu 8:15 人材不足に打ち勝つセキュリティ運用とは ～ DNP との対談で明かされる効果、テクマトリックスが Palo Alto Networks の Cortex XSIAM で提案する次世代 SOC PR サイバー攻撃の高度化・巧妙化に伴い、SOCには膨大なアラートが押し寄せるようになった。複数のセキュリティ製品から上がる情報を人手で分析し、対応するには限界がある。そこで注目されているのが、AIと自動化によるセキュリティ運用だ。 では、AIと自動化を実際の現場に組み込むと、セキュリティ運用はどう変わるのか。約4万5,000台のデバイスを運用する大日本印刷（DNP）が直面した「8つの壁」と、その乗り越え方から、AI時代のSOC運用の可能性に迫る。 EDR やファイアウォール、クラウドサービスなど、多様な領域から届くアラートを横断して相関分析しなければ、インシデントの全体像と因果関係は見えてこない。しかし、毎秒生まれる大量のログと、異常を知らせるアラートはときに SOC 担当者の手に余る。 10 月 21 日…</t>
+          <t>佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4917,22 +4900,13 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -4945,7 +4919,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
+          <t>https://www.security-next.com/190842</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4941,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 当選が落選に「ULTRA MART」チケット抽選システムに不正アクセス 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56356;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 これは9月9日から9月10日の抽選枠で販売を実施した、「ULTRA MART」での「M78ウルトラマン ふわふわお…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56356;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 これは9月9日から9月10日の抽選枠で販売を実施した、「ULTRA MART」での「M78ウルトラマン ふわふわお座りぬいぐるみ」購入抽選システム（mogily）に対する第三者からの不正アクセスの影響で、一部の抽選結果データに不整合が発生し、「当選」した一部顧客が「落選」表示に変更されたというもの。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fr</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4992,20 +4966,20 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yagura / ScanNetSecurity</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
         </is>
       </c>
     </row>
@@ -5017,22 +4991,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>クロネコ代金後払いサービス</t>
+          <t>オズモール</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.10.1 Thu 8:05 「クロネコ代金後払いサービス」に不正アクセス ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56359;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); スターツ出版株式会社は9月27日、同社運営のウェブサイト「オズモール」への不正アクセスについて発表した。 これは9月26日に、「オズモール」への海外からの大量の不正アクセスを同社システム部門が検知したため、調査した結果、顧客の個人情報が閲覧された可能性が判明したというもの。 不正プログラム設置 ～ 東京大学大学院医学系研究科公共健康医学専攻ウェブサイトに不正アクセス 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 2026.9.29 Tue 8:05 「スマ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5042,7 +5016,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5052,20 +5026,20 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Security NEXT / ScanNetSecurity</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190835 / https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
         </is>
       </c>
     </row>
@@ -5077,13 +5051,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>日本郵便</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーアプリ</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>「郵便局アプリ」に不正アクセス、顧客情報を不正に取得 - ScanNetSecurity</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56358;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ニッポンレンタカーサービス株式会社は9月26日、同社が運営する「ニッポンレンタカーアプリ」への不正アクセスについて発表した。 これは「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認したというもの。 カーシェアサービス「RIDENOW」に登録された運転免許証画像が漏えいした可能性 2024.3.25 Mon 8:05 名鉄協商にランサムウェア攻撃、カーシェア「カリテコ」の顧客情報が漏えいした可能性 2026.8.26 Wed 8:10 日本テレネットにランサムウェア型サイバー攻撃、大和リ</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5093,22 +5071,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>クレジットカード情報, 顧客情報, 会員情報</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5116,12 +5094,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5 / https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
         </is>
       </c>
     </row>
@@ -5133,13 +5111,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>クロネコ代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8:05 刑事告訴検討 ～ ヤマト運輸の元従業員が取引先企業に関する情報の一部を不正に持ち出し 2 社に流出 2025.10.20 Mon 8:05 シンガポールヤマト運輸に不正アクセス、個人情報の不正持ち出しが判明 2024.11.18 M</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5149,13 +5131,22 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5168,7 +5159,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
         </is>
       </c>
     </row>
@@ -5180,24 +5171,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>eplus（tracker headline）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>eplus（tracker headline） — Unauthorized access.</t>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5210,7 +5206,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5218,13 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline）</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5264,13 +5260,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ）</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5306,13 +5302,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline）</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5348,13 +5344,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline）</t>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5390,13 +5386,13 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+          <t>Lashinbang（tracker headline）</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5432,13 +5428,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ）</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5469,34 +5465,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5509,7 +5500,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -5521,42 +5512,38 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>ランサムウェア被害拡大中</t>
-        </is>
-      </c>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.30 Wed 8:00 ランサムウェア被害件数が過去最多の123件に、警察庁が対策情報を紹介 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア…</t>
+          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5569,7 +5556,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5581,42 +5568,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>サイバー攻撃共同対処訓練</t>
-        </is>
-      </c>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.30 Wed 8:00 山口東京理科大チームが優勝 ～ 県警ら主催「サイバー攻撃共同対処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 …</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5629,7 +5603,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5641,17 +5615,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>お問合せフォーム</t>
+          <t>ランサムウェア被害拡大中</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支…</t>
+          <t>警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア被害から学ぶ教訓集」～ 経営者のためのランサムウェア対策ハンドブック ～ https://www.ipa.go.jp/security/todokede/crack-virus/ransomware_lessons_learned.html 個人</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5666,12 +5640,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 従業員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5684,12 +5658,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
         </is>
       </c>
     </row>
@@ -5701,24 +5675,42 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>サイバー攻撃共同対処訓練</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+          <t xml:space="preserve">山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 また、同訓練では、サイバー攻撃への対処の速さやサービスの継続性などをポイント化して競うチーム対抗形式のコンテストが実施され、同学数理情報科学科2年生（長尾柚葉氏、清水海凜氏、奥田陸斗氏、松岡俊汰氏）のチームが優勝している。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 </t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -5731,7 +5723,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
         </is>
       </c>
     </row>
@@ -5743,24 +5735,42 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>誤った配達をしないように</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56344;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵便株式会社は9月25日、同社の国際郵便物の調査請求Web受付サービスへの不正アクセスについて発表した。 これは9月25日午後3時頃に、調査請求Web受付サービスで使用しているサーバに対し、外部から不正アクセスの可能性が発覚したというもの。 同社では現在、同サービスについて一時的に受付を停止している。 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配達資料を撮影 2025.1.28 Tue 8:05 保有ドメインへ不正アクセス、迷惑メール送信の踏み台に（日本郵便） 2020.2.18 Tue 10:00 弓削郵便局で居住者情報を記載</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>29,116</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5768,12 +5778,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html</t>
         </is>
       </c>
     </row>
@@ -5785,24 +5795,42 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56341;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。 鎌倉市児童発達支援センターあおぞら園では6月に個人情報の誤送付事案が発生し、2025年3月にも同様の事案が判明したため、同市では6月23日付で指定管理者の社会福祉法人県央福祉会に対し、令和3（2021）年度以降の指定管理期間における管理業務の総点検と総合的な再発防止策の報告を指示している。 指定管理者から7月31日付で提出された総点検結果によると、5年間の指定管理期間を通じて、13件の個人情報管理</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>氏名, 住所, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -5810,39 +5838,39 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WaterPlum</t>
+          <t>お問合せフォーム</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁が注意喚起する「WaterPlum」の手口 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支障はない。 「西武 旅するレストラン 『52 席の至福』」予約サイトで予約関連情報の一部が漏えい 2026.9.24 Thu 8:05 駅放送設備から意図しない音声が送出 ～ 西鉄福岡（天神）駅と薬院駅 2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5852,12 +5880,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>978</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 従業員情報</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5875,29 +5903,29 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造</t>
+          <t>HALMEK up</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>モンベルのグローバルサイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56343;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。 これは社員1名のID・パスワードが窃取されたことが原因で、「HALMEK up」管理画面への不正アクセスの発生を9月9日に確認したというもの。 同社では不正アクセス確認後に、管理画面へのサイトアクセスに必要なパスワードの変更を実施するとともに、外部専門家の協力のもと調査を開始している。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィ</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5910,10 +5938,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -5921,30 +5958,34 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190798</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+          <t>ヤマト運輸は、「クロネコ代金後払いサービス」が第三者により侵害されたことを明らかにした。宅配サービスの提供には影響はないとしている。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5954,18 +5995,13 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>41</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -5978,54 +6014,36 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+          <t>https://www.security-next.com/190835</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>モンベル・グローバルサイト</t>
-        </is>
-      </c>
+          <t>VOISING（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。…</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6038,41 +6056,36 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6080,50 +6093,41 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>メトポ</t>
-        </is>
-      </c>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>「メトポ」のサーバで侵害、一部会員のメアド流出か - 東京メトロ 東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6136,7 +6140,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190791</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -6148,24 +6152,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>WaterPlum</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+          <t>警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書によると、北朝鮮サイバー攻撃グループ「WaterPlum」は、警戒心の薄い求職者のコンピュータネットワークに密かに侵入し、機密情報の収集や暗号資産を盗み出すことを主な目的として、日本、米国、欧州及びその他の国々を標的としてサイバー攻撃を行っている。 警察庁とFBIでは、「WaterPlum」と一部の北朝鮮IT労働者が、北朝鮮朝鮮労働党（WPK）中央委員会軍需工業部313総局</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6173,12 +6195,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
         </is>
       </c>
     </row>
@@ -6190,24 +6212,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline） — Ransomware.</t>
+          <t>アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6220,7 +6251,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190798</t>
         </is>
       </c>
     </row>
@@ -6232,24 +6263,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ）</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6262,7 +6303,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6274,24 +6315,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>あいこんナビ</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56325;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 愛知県は9月22日、同県が管理・運営する出会いサポートポータルサイト「あいこんナビ」での個人情報の誤掲載について発表した。 これは「あいこんナビ」のイベント情報にて、イベント主催団体が保有する、イベントに直接関係のない非公開情報が誤掲載され、氏名、年齢等の個人情報が読み取れる状態になっていたというもの。9月20日午後2時30分頃に一般の人から連絡があり、発覚した。 埼玉県「公文書検索・閲覧システム」で不開示情報を誤掲載 2024.6.3 Mon 8:05 県実施ユーチューバートークイベントで申込者の個人情報が閲覧可能に 2023.11.8 We</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>5,261</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6304,7 +6363,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
         </is>
       </c>
     </row>
@@ -6316,24 +6375,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>個別お打合せのご提案</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56330;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 選挙ドットコムを運営するイチニ株式会社は9月10日、メール誤送信によるメールアドレス漏えいについて発表した。 これは9月6日に、同社から送信した「個別お打合せのご提案」と題するメールについて、「BCC」等で送信すべき送信先メールアドレスを「宛先」で送信したことで、当該メールの受信者以外の他の顧客のメールアドレスが表示される状況となったというもの。 公益財団法人 九州先端科学技術研究所でメール誤送信、見積書を自治体 ML 宛に送信 2026.9.15 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 202</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6346,7 +6423,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html</t>
         </is>
       </c>
     </row>
@@ -6358,17 +6435,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>イープラス</t>
+          <t>Helpfeel</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>スマチケ</t>
+          <t>モンベル・グローバルサイト</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/09/30 チケット販売のイープラス（東京都渋谷区）、電子チケット「スマチケ」の払戻し管理システムに不正アクセス — 払戻し申請者1,463件が漏えい、うち751件に振込先口座情報 続報を注視中 中程度 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。 → 株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月3…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。 REXTにランサムウェア攻撃、流出した可能性のある情報の一部がインターネット上に掲載 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6378,22 +6455,22 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1,463</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>氏名, メールアドレス, 口座情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6406,14 +6483,14 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6423,17 +6500,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ワンストップジョブサイトくまもと</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>脅威動向 ScanNetSecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大、金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのUR…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56326;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 熊本県は9月9日、同県が運営する「ワンストップジョブサイトくまもと」への不正アクセスについて発表した。 これは「ワンストップジョブサイトくまもと」に外部から不正アクセスがあり、一部内容が改ざんされたというもの。当該サイトの利用登録画面で会員規約の同意ボタンをクリックすると、「ウイルスが検出された」等の偽の警告で不安を煽り、有料アプリのインストールへ誘導する「フェイクアラート（偽の警告広告）」が表示される状態となっていたという。 熊本県「白塗り」PDF 公開 ～ 他自治体の黒塗り PDF 案件報道で確認したところ発覚 2025.10.30 Thu</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6443,12 +6520,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29,451</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6466,29 +6543,25 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>サーバに不正アクセスか - 詳細は調査中 日本郵便は</t>
-        </is>
-      </c>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>日本郵便のサーバに不正アクセスか - 詳細は調査中 日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6498,13 +6571,13 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6512,49 +6585,44 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190734</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>スパムの踏み台に - 日大 日本大学</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
+          <t>メトポ</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>教員5人のアカウントに不正アクセス、スパムの踏み台に - 日大 日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
+          <t>東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -6573,34 +6641,25 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190319</t>
+          <t>https://www.security-next.com/190791</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>システムに影響 - 京王電鉄 京王電鉄は</t>
-        </is>
-      </c>
+          <t>Toyobo Textile（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ランサム被害、一部グループ会社の営業システムに影響 - 京王電鉄 京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6611,7 +6670,7 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6624,114 +6683,78 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190761</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Gyazo</t>
-        </is>
-      </c>
+          <t>Saga University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆…</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Saga University（tracker headline） — Ransomware.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Yagura / ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>山東聖泉</t>
-        </is>
-      </c>
+          <t>QUO Card（ news report ）</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.28 Mon 8:05 旭化成の元従業員が不正競争防止法違反で逮捕、機密情報持ち出し中国企業「山東聖泉」へ流出 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記…</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6744,25 +6767,25 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report）</t>
+          <t>International House of Japan (library)（tracker headline）</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6793,18 +6816,18 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report）</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6835,29 +6858,47 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>スマチケ</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+          <t>株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1,463</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>氏名, メールアドレス, 口座情報</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -6870,49 +6911,54 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>サーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/09/29 京王電鉄、グループのサーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響、鉄道運行に支障なし 情報収集中 中程度 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。 → 京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソ…</t>
+          <t>金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのURLをブックマーク登録しておき、ブックマークからアクセスする。 3.インターネット取引サービスを利用する際は、各証券会社が提供しているセキュリティ強化機能（ログイン時・取引実行時・出金時の多要素認証や通知サービス）を有効にして、不審な取引に注意する。 4.パスワードの使いまわしを</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -6925,14 +6971,14 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6942,12 +6988,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は</t>
+          <t>サーバに不正アクセスか - 詳細は調査中 日本郵便は</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>川崎市施設のサイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は、かわさき新産業創造センターのウェブサイトが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6957,7 +7003,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6976,39 +7022,44 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190242</t>
+          <t>https://www.security-next.com/190734</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>クセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングス</t>
+          <t>スパムの踏み台に - 日大 日本大学</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HALMEK up</t>
+          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>女性向け情報サイトの管理画面に不正アクセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングスは、ウェブサイト「HALMEK up」の管理画面が不正アクセスを受けたことを明らかにした。詳細について調査を行っている。 ：Security NEXT</t>
+          <t>日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -7027,29 +7078,29 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190247</t>
+          <t>https://www.security-next.com/190319</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026年8月の情報漏えい</t>
+          <t>システムに影響 - 京王電鉄 京王電鉄は</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>コラム リーク・東郷 2026.9.25 Fri 8:10 今日もどこかで情報漏えい 第52回「2026年8月の情報漏えい」約一割で逮捕・懲戒・行政指導 8 月に最も件数換算の被害規模が大きかったのは、株式会社Eストアーによる「「ショップサーブ」に不正アクセス、不正なプログラムを実行し購入者情報を外部に送信」の 8,853,839 件であった。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知…</t>
+          <t>京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7059,22 +7110,13 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>8,853,839</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -7087,76 +7129,94 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
+          <t>https://www.security-next.com/190761</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>Helpfeel</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Gyazo</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆弱性を悪用し、第三者が同社のシステム上で任意のコマンドを実行する不正アクセスがあり、同社では同日夜に不正な挙動を検知し、調査および対応を開始していた。 「はいチーズ！フォト」に不正アクセス、漏えい件数の公表は顧客の保護と二次被害防止の観点から差し控える 2026.8.20 Thu 8:05 「はいチーズ！フォト」への不正アクセス、漏</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性</t>
+          <t>山東聖泉</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/10/01 佐賀大学、事務情報システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性、事務用端末約500台を3日間停止 続報を注視中 重大 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。 → 国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記録を対象家庭に匿名で郵送、市職員 生活福祉課 主幹 50歳 逮捕 2026.9.16 Wed 8:05 個人情報を無断で持ち出し 不正競争防止法違反容疑で逮捕 2026.7.31 Fri 8:05 器物損壊罪等で逮捕された津田塾大学元職員、個人情</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7164,14 +7224,19 @@
           <t>可能性あり</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7184,54 +7249,36 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>政府の信用を大きく傷つける深刻な問題</t>
-        </is>
-      </c>
+          <t>Tokyo Metro (Metpo)（news report）</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>業界動向 ScanNetSecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正アクセス、政府が自民党に説明 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証…</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7239,30 +7286,30 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+          <t>Nippon Rent-A-Car (app)（news report）</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7293,18 +7340,18 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7335,29 +7382,42 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>京王電鉄</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>サーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
+          <t>京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7370,36 +7430,45 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+          <t>神奈川県川崎市は、かわさき新産業創造センターのウェブサイトが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7412,34 +7481,34 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190242</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>不審メールが送信 - 日大 日本大学</t>
+          <t>クセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングス</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>メールが送信 - 日大 日本大学は</t>
+          <t>HALMEK up</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>理工学部教職員がフィッシング被害、不審メールが送信 - 日大 日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
+          <t>50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングスは、ウェブサイト「HALMEK up」の管理画面が不正アクセスを受けたことを明らかにした。詳細について調査を行っている。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7463,29 +7532,29 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190198</t>
+          <t>https://www.security-next.com/190247</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>サイト改ざん</t>
+          <t>2026年8月の情報漏えい</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>不正アクセスでサイト改ざん、内部に個人情報 - コンサル会社 コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知らないところで漏えい事件は起き続けている。 頼まれもしないのに月ごとの情報漏えいの動向を勝手にウォッチしている、虫の音ならぬ虫の息のような本連載、今月も一寸の虫のようにひっそりと掲載である。 ●インシデント原因内訳 さて、先月 2026 年 8 月に本誌が取り上げた事故・インシデント記事は 2026 年 7 月の 84 本から 42 本増となる全</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7495,13 +7564,22 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -7514,36 +7592,54 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189792</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>大興印刷</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PhotoGoods</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56305;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); カルビー株式会社は9月17日、同社業務提携先での個人情報等の漏えいの可能性について発表した。 これは同社の「プロ野球チップス」をモチーフとしたオリジナルカードなどを注文できるサービス「PhotoGoods」にて、顧客の個人情報等が漏えいした可能性が判明したというもの。当該サービス運営する業務提携先の大興印刷株式会社では、状況の確認と詳細の調査を進めている。 今日もどこかで情報漏えい 第3回「クレジットカード情報漏えい顛末記」 2022.8.3 Wed 8:10 いまでやが管理する注文情報が外部流出した可能性、フィッシングサイト上でカード情報を入</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -7556,45 +7652,36 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>メールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは</t>
-        </is>
-      </c>
+          <t>Smaregi EC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>従業員アカウントが侵害、なりすましメールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -7607,34 +7694,34 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189987</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>コープやまぐちLINEミニアプリ</t>
+          <t>システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>インシデント・情報漏えい ScanNetSecurity 2026.9.17 Thu 8:05 データベース内の全てのデータを削除 ～「コープやまぐちLINEミニアプリ」に不正アクセス 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」…</t>
+          <t>国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7642,19 +7729,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>認証情報</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -7662,41 +7744,59 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>政府の信用を大きく傷つける深刻な問題</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
+          <t>自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証するセキュリティモデル）を」と求め、VPNで「ゼロトラスト」が働く境界の手前の領域も含めた防御の再構築を促している。 VPNの脆弱性を利用 ～ デジタル庁が運用するガバメントソリューションサービス（GSS）に不正アクセス、約24.6万件の個人情報が漏えいした可能性 2026.9.14 Mon 8:05 「ガバメントソリ</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -7704,41 +7804,59 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>hyocom</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56290;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。 これは同学の非常勤講師が授業運営に際し、同学と無関係の外部SNSサービス「hyocom」を利用し、学生の個人情報を公開した上、公開範囲の管理を適切に行っていなかったことから、個人情報が外部から閲覧可能な状態となっていたというもの。外部から公益通報受付窓口に寄せられた情報提供を受けて、2026年7月に発覚している。 誤ってフィッシングサイトにアクセス、学生や卒業生ら1,466人分の個人情報の</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1,466</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -7751,36 +7869,54 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>アカウント乗っ取り</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56285;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東証プライム上場企業の株式会社トレジャー・ファクトリーは8月28日、同社連結子会社である株式会社カインドオルへの不正アクセスについて発表した。 これは8月22日に、カインドオルがECサイトで利用しているECプラットフォームのスタッフアカウントに第三者から不正アクセスがあり、8月23日に当該アカウントのメールアドレスが変更され、同日、顧客情報の一括エクスポートが2回実行されたことを確認したというもの。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 3,177件の不審</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>3,177</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -7788,41 +7924,59 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>生命のにぎわい調査団</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56289;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 千葉県は9月1日、同県が運営する生物多様性センターのホームページへの不正アクセスについて発表した。 これは8月27日午前9時頃に、生物多様性センターホームページ（ https://www.bdcchiba.jp/ ） 内の「生命のにぎわい調査団」ページに不正アクセスがあった可能性があるので、アクセスログを確認して欲しい旨の連絡が千葉県警からあり、同日午前10時頃に同センター職員がアクセスログを確認したところ、8月27日午前1時1分と午前1時9分に不正アクセスがあり、本来存在しない画面（通常ではリンクしないページ）が差し込まれていることを確認した</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -7835,29 +7989,29 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>システムが侵害され</t>
+          <t>paperlogic</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ロート製薬の不正アクセス、顧客との通話音声データが流出の可能性 ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56287;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。 これは8月27日に、同社が利用するクラウドサーバに対し、第三者からの不正アクセスおよび通常とは異なる動作を検知したというもの まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7870,10 +8024,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1,801,499</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -7881,54 +8044,41 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190377</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>CINRA JOB</t>
-        </is>
-      </c>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」に不正アクセス クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -7941,25 +8091,25 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189866</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline）</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7990,18 +8140,18 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+          <t>Ryomo Systems（tracker headline）</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8032,27 +8182,18 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>当選</t>
-        </is>
-      </c>
+          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>円谷プロの購入抽選に不正アクセス - 「当選」が「落選」に 円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8063,7 +8204,7 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -8076,34 +8217,34 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190315</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>不審メールが送信 - 日大 日本大学</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ホワイトエッセンス</t>
+          <t>メールが送信 - 日大 日本大学は</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>予約サイトなどで侵害、影響など調査中 - 審美歯科チェーン 審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
+          <t>日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8127,36 +8268,54 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189665</t>
+          <t>https://www.security-next.com/190198</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ）</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>令和8年版情報通信白書</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+          <t>総務省は9月11日、同省を装ったなりすましメールへの対策強化について発表した。 近年、行政機関を装ったなりすましメールによるフィッシング詐欺や不正サイトへの誘導などが発生しており、同省では今回の対策で、総務省を装うなりすましメールの抑止を図る。 同省では以前から、総務省ルートドメインになりすましたメールアドレス（@soumu.go.jp）からの不正なメールの受信を拒否する仕組みを導入していたが、9月1日からはサブドメインになりすましたメールアドレス（@xxx.soumu.go.jp）からのメールの受信を拒否する仕組みも導入し、対策を強化する。 同省によると、本対応で総務省から送信する正規のメールの受信方法に変更はないが、メール転送サービスや自動転送を利用している等、転送の仕組みによっては認証に失敗し、総務省からのメールが受信できなくなる可能性があるとのこと。 ダークネット観測パケット数が過去最高を更新、10年前から10倍に増大 ～ 総務省「令和8年版情報通信白書」 2026.9.8 Tue 8:00 KDDI の ISP 事業者向けメールシステムに不正アクセス、総務省が行政指導 202</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8164,30 +8323,39 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>サイト改ざん</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+          <t>コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8198,7 +8366,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8211,36 +8379,54 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189792</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>原田産業</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ビールの縁側</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56270;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社カインドオルは8月28日、同社が運営するECサイトで利用しているECプラットフォームのスタッフアカウントへの不正アクセスについて発表した。 これは8月24日に、同社が通常業務として注文情報の出力を行った際に、ECプラットフォームのスタッフアカウントに登録されているメールアドレスが同社で使用していないものに変更されていることを確認したため、ECプラットフォームの運営会社に調査を依頼したところ、当該スタッフアカウントに第三者から不正アクセスが行われた後、8月23日に顧客情報の一括エクスポートが2回行われていたことが判明したというもの。 EC</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -8253,29 +8439,29 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
+          <t>捜査に必要と求められ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/09/17 小田原エンジニアリング、ドイツ子会社出向者のメールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。 → 株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56269;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社安藤・間（安藤ハザマ）は8月31日、名刺情報の外部流出について発表した。 これは8月16日から8月23日にかけて、同社社員が警察官を名乗る者から、交友関係の捜査に必要であるとして名刺情報を提出するよう求められ、当該社員は8月17日に同社の名刺管理システムに保管していた名刺情報をダウンロードの上、相手方にメールで提出したというもの。 名刺管理システムへ不正アクセス、サービス運営会社からの連絡で発覚 2023.5.9 Tue 8:05 名刺管理システムへの不正アクセス ～ 当の名刺管理システム会社名乗り電話とメールでIDパスワード詐取 20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8285,18 +8471,22 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8309,14 +8499,14 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8326,37 +8516,37 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
+          <t>交通安全施設損壊事案報告書</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/07/24 通販のムラウチドットコム（東京都八王子市）、不正アクセスで771万6,811件の個人情報漏えいを確認 — Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。 → 株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステム…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56275;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 長野県警察は9月7日、塩尻警察署交通課での個人情報の所在不明について発表した。 これは塩尻警察署交通課が、令和3（2021）年度中に交通事故や自然災害等で交通安全施設の損壊等が発生した際に作成した「交通安全施設損壊事案報告書」「交通安全施設修繕執行伺」「交通安全施設修理結果表」「道路標識標示工事監督等指示書」、交通安全施設への意見・要望が寄せられた際に作成した「信号機BOX」が所在不明となったというもの。 12 名の個人情報記載した「交通切符等引継簿」紛失 ～ 釧路方面弟子屈警察署 2026.5.12 Tue 8:05 拾得物として届けられ回収</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6,811</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8369,14 +8559,14 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8386,17 +8576,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>第367回 個人情報保護委員会</t>
+          <t>大オークション大会</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.14 Mon 8:00 不正アクセスや報告遅れを中心に民間 98 件へ指導 ～ 個人情報保護委員会が第367回会合を開催 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56274;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社マネジメントサービスセンターは8月25日、同社ホームページへの不正アクセスについて発表した。 これは7月に、同社ホームページへの第三者からの不正アクセスおよびホームページ改ざんを確認したというもの。 まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの一部が改ざんされる被害 2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8406,12 +8596,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>1,801,499</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8429,40 +8619,54 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>生徒寮でサポート詐欺、入寮者の個人情報が流出か - 宮崎県 宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56271;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。 これは6月29日に、当該サイトで異常を確認したため公開を停止し、調査および証拠保全等の対応を開始し、その後、外部専門機関による調査を行った結果、管理者権限を持つアカウントが第三者によって不正に作成され、サーバ上にバックドア等の不正プログラムが設置されていたことが判明したというもの。 人気の無料ソフト公式サイトを侵害、Linux 標的としたバックドア 3 年間拡散 2023.10.17 Tue 8:00 無料提</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1,668</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8475,25 +8679,25 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189985</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
+          <t>Bellcadia (montbell global site)（ news report ）</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8524,29 +8728,38 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>メールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -8559,34 +8772,34 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189987</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+          <t>洛西進学教室</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>新製品・新サービス ScanNetSecurity 2026.9.11 Fri 8:00 「ネット de 診断 AIホワイトハッカー侵入テスト」提供開始、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出…</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56256;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アップは9月4日、同社が運営するプロモーションサイト「洛西進学教室」及び「進学館」への不正アクセスについて発表した。 これは8月24日に、当該サイトが利用していた外部ソフトウェア（プラグイン）の脆弱性を悪用した不正アクセスがあり、サーバ内に不正なプログラムが設置されたことが判明したというもの。当該サーバ内に保管されていた採用応募者の個人情報及び社内サイト管理者の個人情報が閲覧された可能性があるという。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 VOISI</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8596,7 +8809,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>17,559</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8614,45 +8827,59 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングス</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>コープやまぐちLINEミニアプリ</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」のデータベースに第三者から不正アクセスがあり、データベース内の全てのデータが削除される事象が発生したというもの。 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 メール配信システム「める配くん」の一部サーバに不正アクセス、配信先情報の一部が外部に取得されていた事実を確認</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -8665,45 +8892,54 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188880</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>東京外環プロジェクト</t>
+          <t>東海大学山中湖セミナーハウス</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>「東京外環プロジェクト」サイトで侵害のおそれ - 公開を一時停止 国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56253;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。 これは同学が契約しているレンタルサーバで発生したセキュリティインシデントに伴い、当該サーバ上で開設していた複数のWebサイトで公開を停止したというもの。 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 福岡大学の委託先ノストラムに不正アクセス、攻撃者のサイト上に窃取したデータを公開する旨の告知 2026.7.27 Mon 8:05 日本大学の学生・卒業生</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -8716,25 +8952,25 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
+          <t>Osaka City (recorded interview system)（tracker headline）</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8765,18 +9001,18 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8807,98 +9043,71 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>GSS</t>
-        </is>
-      </c>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026/09/14 デジタル庁、政府共通の業務実施環境「GSS」がVPN機器の脆弱性を悪用した不正アクセスで職員等 約24.6万件の個人情報漏えいのおそれ — 5月侵入・6月検知・9月公表 続報を注視中 重大 デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。 → デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,0…</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Security NEXT / Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190208 / https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングス</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ecurity NEXT</t>
-        </is>
-      </c>
+          <t>Calbee (baseball-chip cards)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -8911,14 +9120,14 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8928,22 +9137,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>システムがランサム被害</t>
+          <t>システムが侵害され</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>システムがランサム被害、一部業務を停止 - インキメーカー 印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+          <t>ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -8962,36 +9171,49 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674</t>
+          <t>https://www.security-next.com/190377</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CINRA JOB</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9004,40 +9226,54 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189866</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>白塗り</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>施設職員がサポート詐欺被害、PC内部に個人情報 - 大田区 東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56244;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 鳥取県は9月3日、モニタリングポストの放射線量率等の測定データを収集・監視する鳥取県環境放射線モニタリングシステムへのサイバー攻撃について発表した。 これは鳥取県環境放射線モニタリングシステムで、庁内に設置していた主監視局（主サーバ）へのランサムウェア攻撃を判明したというもの。同サーバ内の電子ファイルが暗号化され、主監視局に障害が発生しシステム停止している。 「白塗り」に気付けなかったのは決裁を紙文書でやっていたから ～ 消防防災航空センターホームページで個人情報が閲覧可能に 2024.5.30 Thu 8:05 食パラダイス鳥取県公式インスタ</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9050,29 +9286,29 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>スパム踏み台に - 立教大 立教大学</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Googleアカウント</t>
+          <t>先輩就職先情報リスト</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>学生の複数アカウントに不正アクセス、スパム踏み台に - 立教大 立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56245;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 大阪高等裁判所は9月4日、同裁判所での特定の事件に係るMicrosoft Teamsのチーム作成の誤りについて発表した。 これは8月27日午前10時40分頃に、大阪高等裁判所民事部で、Microsoft Teamsを利用して特定の事件に係るチームを作成する際に、誤って本来登録するメンバー以外のメンバー（裁判所外部ユーザー約3,500アカウント、裁判所職員ユーザーが約2,500アカウント）を登録したというもの。同日午後0時20分頃に、外部からの問い合わせで発覚したという。 最高裁判所 メール誤送信 2024.6.13 Thu 8:05 最高裁で修</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9082,13 +9318,22 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>住所, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9101,54 +9346,36 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190050</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>フィッシング対策セミナー2026</t>
-        </is>
-      </c>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>セミナー・イベント ScanNetSecurity 2026.9.9 Wed 8:00 「フィッシング対策セミナー2026」11 / 19 開催 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6…</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9161,25 +9388,25 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline）</t>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9210,89 +9437,94 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>当選</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+          <t>円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / Security NEXT</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>被害経験なし</t>
+          <t>ホワイトエッセンス</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>調査・ホワイトペーパー ScanNetSecurity 2026.9.8 Tue 8:00 サイバー攻撃の「被害経験なし」企業は約 6 割へ減少 ～ 東商2026年アンケート調査 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定され…</t>
+          <t>審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>13,156</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -9305,45 +9537,54 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+          <t>https://www.security-next.com/189665</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>YAMAGoya</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>マルウェアの挙動をリアルタイム監視するOSSを公開 - JPCERT/CC JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56230;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 静岡県長泉町は8月25日、8月20日付けで行った職員の懲戒処分について発表した。 これは同町の教育委員会 主査（57歳・女性）が、同町が管理すべき大量の廃棄対象の公文書等を無断で自宅に持ち帰って保管していたほか、同町のコピー機等を使用して上記文書の裏面に私的目的のため大量の小説のコピーを行っていたこと、通勤手段の変更に係る届出を長期間怠っていたことに対し、地方公務員としての信用を著しく失墜させるものであると判断し、免職の処分を行ったというもの。 停職1ヶ月 ～ 市職員が飲食店関係者に関する市税等の情報を口外 2026.8.6 Thu 8:05 </t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -9351,39 +9592,39 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/177455</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>システムに不正アクセス</t>
+          <t>注文書フォーム</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>グループのシステムに不正アクセス、個人情報流出の可能性 - 三井不動産 三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56233;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 福岡市の外郭団体である公益財団法人九州先端科学技術研究所は9月8日、メール誤送信による情報漏えいについて発表した。 これは9月3日午後3時44分に、同研究所が提供しているビッグデータ&amp;オープンデータ・イニシアティブ九州（BODIK）のホームページ保守等のサービスにて、自治体からの依頼を受けて作成した見積書をメール送信する際、誤って同サービスの利用自治体のメーリングリストを設定したことで、同リスト登録の全339の行政機関（アドレス数342件）に送信されたというもの。同日午後3時50分に発覚している。 取引先に送付した「注文書フォーム」エクセルファ</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9391,10 +9632,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J180" t="n">
@@ -9407,34 +9657,25 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189789</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>SonicWall SMA 100</t>
-        </is>
-      </c>
+          <t>Murauchi.com（ news report ）</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>「SonicWall SMA 100」にアップデート - 既知マルウェアの除去機能を追加 SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9445,7 +9686,7 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -9458,34 +9699,25 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/174925</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Catalyst SD-WAN Manager</t>
-        </is>
-      </c>
+          <t>LEAN BODY（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>「Catalyst SD-WAN Manager」にゼロデイ脆弱性 - 更新や侵害調査を Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9496,7 +9728,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -9509,25 +9741,25 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190883</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline）</t>
+          <t>Fuso Dentsu（tracker headline）</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -9558,38 +9790,43 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>サーバが侵害</t>
+          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>社内ファイルサーバが侵害、情報流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+          <t>株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -9602,63 +9839,1887 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>6,811</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>第367回 個人情報保護委員会</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機関等が43件であった。 民間事業者に対しては、不正アクセスを原因とする漏えい等事案を中心に、安全管理措置の不備等について指導を行っており、外部からの不正アクセス等の防止の不備（21件）、アクセス者の識別と認証の不備（14件）、委託先に対する監督の不備（12件）、情報システムの使用に伴う漏えい等の防止の不備（3件）の他、</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>6,101</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189985</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56219;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); WEVERSE JAPAN株式会社は9月6日、一部顧客の個人情報流出について発表した。 これは9月3日に、韓国インターネット振興院（KISA）より外部の報告者からWeverseサービスのセキュリティ脆弱性に関する指摘があった旨の連絡があり、社内点検を実施した結果、一部顧客の個人情報が流出した事実を確認したというもの。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 ソディックの</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>17,559</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>GSS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>デジタル庁は、同庁が運用する「ガバメントソリューションサービス（GSS）」が不正アクセスを受けたことを明らかにした。機器の脆弱性を突かれて侵入され、保守運用アカウントが侵害されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190208</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングス</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188880</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>カリテコ</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>アカウント乗っ取り</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>東京外環プロジェクト</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190203</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>GSS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Yagura</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングス</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190132</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>システムがランサム被害</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189674</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>東海大学山中湖セミナーハウス</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3,177</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189902</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>スパム踏み台に - 立教大 立教大学</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Googleアカウント</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190050</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>フィッシング対策セミナー2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6039/eCrv5d/M?S=nepdq0lcl0k オンライン参加（Webex） https://antiphishingjp.webex.com/weblink/register/r80bc37361931544860d6329aee56afaf 申</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>スマイルサーバ</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56173;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社東邦通信システムズは8月19日、同社がサービス提供に利用している外部ホスティングサーバ環境への不正アクセスについて発表した。 これは7月31日頃から、第三者による不審な接続元から同社が利用するサーバ管理アカウントへの不正アクセスが断続的に行われ、一部のメールアカウントで設定情報が書き換えられる事態を確認したというもの。 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 「スマイルサーバ」で不正アクセスの痕跡、復旧までに長期間を要する見込み 2026.8</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1,360,563</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>被害経験なし</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定されるため、一社単独ではなく、他企業・官民連携による対策が必要と感じる。」、「取引先がランサムウェア攻撃を受け、商品の出荷が停止となる影響が生じた。」などが寄せられている。 「富士山噴火による影響の懸念・事業継続への影響」について尋ねたところ、富士山噴火（広域降灰）による影響を懸念する企業が</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>13,156</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーアプリ</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>YAMAGoya</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/177455</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>システムに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189789</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SonicWall SMA 100</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/174925</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Catalyst SD-WAN Manager</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190883</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>サーバが侵害</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188534</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Japan Vulnerability Notes（JVN）</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。GMOサイバーセキュリティ byイエラエ株式会社の黒須宏道氏と上田将嗣氏が報告を行っている。影響を受けるシステムは以下の通り。 PALLET CONTROL Ver. 6.3 パッチ 5 およびそれ以前 PalletControl 10 Update 8 およびそれ以前 PalletControl クラウド（PalletControl 10 Update 8）およびそれ以前 JALデジタル株式会社が提供するPALLET CONTROL製品には、バックグラウンドで動作し一定の機能を提供するサービスプログラムが複数含まれているが、サービスプログラムとの通信に適切なアクセス権限が設定されておらず、管理者権限を持たない一般ユーザによりアクセスが可能となる脆弱性（CVE-2026-81302）が存在する。 想定される影響と</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
         <is>
           <t>企業・組織名要確認</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>まんだらけ</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>「まんだらけ」サーバに不正侵入、情報流出か - 通販やオークションは再開 コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
         <is>
           <t>不正アクセス</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr">
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
         <is>
           <t>Security NEXT</t>
         </is>
       </c>
-      <c r="J185" t="n">
-        <v>1</v>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
         <is>
           <t>https://www.security-next.com/189663</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L185"/>
+  <autoFilter ref="A1:L220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9703,7 +11764,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>184</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
@@ -9738,7 +11799,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:36:07.523379+00:00</t>
+          <t>2026-10-07T00:37:39.428337+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L220"/>
+  <dimension ref="A1:L232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>マイページ</t>
+          <t>ecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>さとこはいつも</t>
+          <t>ecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.10.7 Wed 8:05 KKR京都くに荘のメールサーバに不正アクセス 国家</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>氏名, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+          <t>氏名, 電話番号, メールアドレス, 認証情報</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Microsoft 365</t>
+          <t>メール - 日経</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>問い合わせ顧客の情報が流出か - 大和証券 大和証券</t>
+          <t>大和証券</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>問い合わせ顧客の情報が流出か - 大和証券 大和証券は</t>
+          <t>問い合わせ顧客の情報が流出か - 大和証券</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>さくらのレンタルサーバ</t>
+          <t>ecurity 2026.10.6 Tue 8:05 ムラウチドットコムに不正アクセス</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>大起水産公式アプリ</t>
+          <t>アプリシステムが侵害</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WEB 発注システム</t>
+          <t>ecurity 2026.10.5 Mon 8:05 池上通信機にサイバー攻撃</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>池上通信機株式会社は9月24日、同社に対するサイバー攻撃の可能性について発表した。 これは9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、直ちに調査を開始したというもの。 同社では現在、社内関係部門および外部専門機関と連携し、事実関係や影響範囲および情報漏えいの範囲について調査を進めるとともに、被害拡大防止のために必要な措置を講じている。 同社では現時点で、サイバー攻撃の有無を含む詳細な事実関係および情報漏えいの範囲について確認中とのこと。 鳥取県環境放射線モニタリングシステムにランサムウェア攻撃、副サーバは被害受けず放射線モニタリングに影響なし 2026.9.16 Wed 8:05 サンメッセが利用する購買発注システム「WEB 発注システム」へサイバー攻撃 2026.9.14 Mon 8:05 メディア4u の SMS 送信システムにサイバー攻撃、連携していたブロードリーフの「.cシリーズ」「.NSシリーズ」にも影響 2026.8.26 Wed 8:10 ADサーバ上のデータが外部へ転送されたと判断 ～ 精電舎電子工業にランサムウェア攻撃 2026.8.</t>
+          <t>池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:05 教育ソフトウェアの休眠中のレンタルサーバにランサムウェア攻撃、暗号化被害と不正アクセスの痕跡を確認 2026.9.8 Tue 8:05 サンコーテクノのベトナム子会社にランサムウェア攻撃、サーバ及びパソコン内の各種ファイルの暗号化を</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
         </is>
       </c>
     </row>
@@ -2476,22 +2476,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.10.5 Mon 8:05 東産業 公式サイトにwp2shell を悪用した不</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:05 教育ソフトウェアの休眠中のレンタルサーバにランサムウェア攻撃、暗号化被害と不正アクセスの痕跡を確認 2026.9.8 Tue 8:05 サンコーテクノのベトナム子会社にランサムウェア攻撃、サーバ及びパソコン内の各種ファイルの暗号化を</t>
+          <t xml:space="preserve">株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri 8:00 WordPress の深刻度「緊急」脆弱性「wp2shell 」の概要と対応指針 ～ GMO Flatt Security </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>1,950,165</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
         </is>
       </c>
     </row>
@@ -2536,22 +2536,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>ト・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 日本大学</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>wp2shell</t>
+          <t>ecurity 2026.10.5 Mon 8:05 日本大学の計 5 名の教員アカウントに不正アクセス</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri 8:00 WordPress の深刻度「緊急」脆弱性「wp2shell 」の概要と対応指針 ～ GMO Flatt Security </t>
+          <t>日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日に、第三者が同学の計5名の教員アカウントに不正アクセスし、当該アカウントをスパムメール送信の踏み台として利用していたことを8月29日に確認したというもの。当該アカウントから学内外に1,333件の不審メールが送信されたことを確認している。 調査の結果、当該アカウント内のデータに対する大規模な抽出や持ち出し等の痕跡は確認されていないが、一部のデータへアクセスされた可能性はあるという。 同学では、連絡先が特定可能な対象者に順次、個別にメール等で連絡を行っている。 同学では、悪意ある第三者がフィッシングメール等の手段で認証情報（ID・パスワード）を窃取し、アカウントを乗っ取ったことが原因と推測している。 同学では検知後に、当該アカウントの利用を一時停止（或いは無効化）し、不正アクセスを遮断している。 同学では、多要素認証（MFA）の導入推進、アカウントの管理適正化及び情報セキュリティ教育の再徹底を行い、再発防止に取り組むとのこと。 日本大学理工学部教職員のアカウントに対し巧妙に偽装されたフィッシングメール、</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1,950,165</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
         </is>
       </c>
     </row>
@@ -2596,17 +2596,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>原田産業</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ビールの縁側</t>
+          <t>一万三千尺物語</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレジットカード情報を含む情報が漏えいした可能性のある顧客は9名。対象となる情報には、氏名、電話番号、メールアドレス、性別、生年月日、住所、クレジットカード情報（番号、名義人、有効期限、セキュリティコード）が含まれる。なお、決済を完了した顧客は4名、決済を完了せずに注文手続を終了した顧客は5名。 同社では対象となる9名に個別にメールで連絡を行っている。 同社では現在</t>
+          <t>あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 これは9月8日朝に、同社社員が座席管理システムにアクセスしたところ、複数の予約がキャンセルされていた他、当該システムから正規の手順で行われていない予約を確認したため、全ての新規予約の受付を停止するとともに調査を行った結果、9月2日に最初の不正アクセスがあり、以降、9月8日までに複数回の不正アクセスを確認したというもの。 漏えいした可能性があるのは、これまでに観光列車「一万三千尺物語」に乗車した顧客または今後の乗車予約をしていた顧客 計1,409名の個人情報（氏名、住所、電話番号、メールアドレス）。 同社では対象の顧客に9月12日付で、文書「個人情報の漏えいのおそれがある事象に関するお詫びとお知らせ」を郵送している。 同社では、外部からの不正アクセスが判明したことから、その拡大を防ぐため、ネットによる新規予約の受付停止を継続している。 同社では今後、調査結果を踏まえてシステム全体のセキュリティ対策の強化などに努めるとのこと。 駅放送設備から意図しない音声が</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 従業員情報</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html</t>
         </is>
       </c>
     </row>
@@ -2656,13 +2656,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
+          <t>株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 これは9月11日午後4時頃に、「ドズル社ストア」で商品購入手続きの際、正規の決済ページではない不正な外部ページへ誘導される事象が発生したというもの。不正なページには、主に下記のような特徴があり、不正なページで行われた支払いは、「ドズル社ストア」での注文として受け付けられていない。 ・ページ左上に「Checkout」と表示され、ドズル社ストアの名称・ロゴが表示されない ・英語で表示され、配送先の国・地域に「United States」があらかじめ選択されている ・実際の商品価格と大きく異なる高額な金額が表示される 同社によると、発生推定期間中（9月11日午後3時頃～午後5時50分）に購入手続きをおこなったにもかかわらず、同ストアからの注文確認メールが届いていない場合は、不正なページで決済が行われた可能性があるという。 同社では、発生推定期間中に上記の特徴を持つページでクレジットカード情報を入力した場合、利用のカード会社に連絡のうえで、不正利用の有無の確認や、カードの利用停止・再発行</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2670,10 +2679,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2681,12 +2699,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2716,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>原田産業</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ビールの縁側</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>『焼肉きんぐ』1000万件超の情報漏洩 なぜ今、飲食店アプリが狙われるのか？ #エキスパートトピ（山路力也） - エキスパート - Yahoo!ニュース</t>
+          <t>原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレジットカード情報を含む情報が漏えいした可能性のある顧客は9名。対象となる情報には、氏名、電話番号、メールアドレス、性別、生年月日、住所、クレジットカード情報（番号、名義人、有効期限、セキュリティコード）が含まれる。なお、決済を完了した顧客は4名、決済を完了せずに注文手続を終了した顧客は5名。 同社では対象となる9名に個別にメールで連絡を行っている。 同社では現在</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2733,7 +2764,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
@@ -2745,35 +2776,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>「焼肉きんぐ」、顧客情報漏洩 不正アクセスで1000万件超 - 日本経済新聞</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2789,7 +2806,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2801,28 +2818,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>『焼肉きんぐ』1000万件超の情報漏洩 なぜ今、飲食店アプリが狙われるのか？ #エキスパートトピ（山路力也） - エキスパート - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1000万</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2841,7 +2853,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2853,24 +2865,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ）</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
+          <t>「焼肉きんぐ」、顧客情報漏洩 不正アクセスで1000万件超 - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2883,7 +2909,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2895,24 +2921,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline）</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>4933</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2925,7 +2961,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2937,13 +2973,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline）</t>
+          <t>White Essence（ disclosure ）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
+          <t>White Essence（ disclosure ） — A booking-site program vulnerability led to access to core systems. Access confirmed Aug 5; systems stopped and notice issued Aug 12.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2979,13 +3015,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ）</t>
+          <t>The Japan Times（tracker headline）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
+          <t>The Japan Times（tracker headline） — Unauthorized access; ransomware group Eclipse claimed responsibility.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3021,13 +3057,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
+          <t>Safer Internet Association（tracker headline）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
+          <t>Safer Internet Association（tracker headline） — Unauthorized access to a server used by the association.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3063,13 +3099,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline）</t>
+          <t>Osaka Metropolitan University（ news report ）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
+          <t>Osaka Metropolitan University（ news report ） — University-disclosed ransomware; virtualization platform accessed. Entry point and attacker not stated. Temporary notice site used while official site was down.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3105,13 +3141,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
+          <t>Monogatari Corporation (Yakiniku King app)（ disclosure ） — Cause and how access became possible under investigation. Unauthorized access confirmed Oct 2; leak confirmed Oct 3.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3147,13 +3183,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
+          <t>JOGMEC（tracker headline）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
+          <t>JOGMEC（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3189,13 +3225,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ）</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+          <t>GMO Research &amp; AI (infoQ)（ disclosure ） — Site software vulnerability exploited. Access from Oct 2; confirmed on the morning of Oct 3 after a member inquiry, and service stopped.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3231,13 +3267,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline）</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3273,42 +3309,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>8,963</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3321,36 +3339,36 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>777CON-PASS（tracker headline）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3363,25 +3381,34 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>焼肉きんぐ</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
+          <t>株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3391,13 +3418,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>8,963</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3410,7 +3441,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3459,7 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3452,7 +3483,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
@@ -3464,23 +3495,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3499,7 +3530,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3511,24 +3542,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ）</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3541,25 +3572,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
+          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3569,19 +3600,10 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>12万</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>従業員情報</t>
-        </is>
-      </c>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3597,36 +3619,36 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3639,7 +3661,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -3651,24 +3673,38 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline）</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>従業員情報</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3681,7 +3717,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
@@ -3693,24 +3729,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline）</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3723,7 +3759,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3735,37 +3771,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>返金</t>
-        </is>
-      </c>
+          <t>MoonStar（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3778,45 +3801,36 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>佐川急便</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>問い合わせサービスがサイバー攻撃を受け</t>
-        </is>
-      </c>
+          <t>Abahouse（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3829,25 +3843,29 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190952</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ジャパンタイムズ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>アバハウスインターナショナル</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>返金</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+          <t>株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3857,13 +3875,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3876,7 +3898,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3888,29 +3910,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>第一生命</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>問い合わせサービスがサイバー攻撃を受け</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+          <t>佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>12万</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -3923,7 +3949,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
+          <t>https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
@@ -3935,23 +3961,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>ジャパンタイムズ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>175</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3970,7 +3996,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3982,18 +4008,13 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4003,7 +4024,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12万</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -4022,7 +4043,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4034,23 +4055,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>175</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -4069,7 +4090,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4081,13 +4102,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4100,11 +4121,12 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -4120,7 +4142,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4132,13 +4154,13 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
+          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4148,14 +4170,10 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -4171,7 +4189,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4183,13 +4201,13 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4199,12 +4217,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4222,7 +4240,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4234,42 +4252,33 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ドズル社ストア</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicrosoft 365 アカウントに不正アクセスがあり、メール及びファイルの閲覧による外部への情報漏えいの可能性、ファイルのダウンロードによる外部への情報漏えいが判明したというもの。 富山県立大学の Microsoft 365 学生アカウントから大量の迷惑メール送信 2026.7.23 Thu 8:05 TE</t>
+          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4282,7 +4291,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4294,17 +4303,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>イープラス</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正アクセスがあり、同システム内に保管していた払戻しを実施するための情報に含まれていた顧客の個人情報の漏えいが判明したというもの。 一部顧客の情報が閲覧・編集・削除可能に ～ リセールサイト「RELIEF Ticket」 2025.7.3 Thu 8:05 CNプレイガイドへの不正アクセス、キョードー東京と</t>
+          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4317,19 +4322,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>236,323</t>
-        </is>
-      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4354,22 +4354,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mogily</t>
+          <t>ecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56375;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); mogily株式会社は9月11日、同社が提供するデジタル整理券システム「mogily」への不正アクセスについて発表した。 これは9月9日から9月10日にかけて、同社の「mogily」の管理システムに外部から不正アクセスがあり、一部顧客の抽選結果（当落ステータス）が第三者に改ざんされたというもの。本来「当選」であった顧客のステータスが「落選」に書き換えられたという。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィッシング詐欺等によるものとみられる不正アクセス・不</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicrosoft 365 アカウントに不正アクセスがあり、メール及びファイルの閲覧による外部への情報漏えいの可能性、ファイルのダウンロードによる外部への情報漏えいが判明したというもの。 富山県立大学の Microsoft 365 学生アカウントから大量の迷惑メール送信 2026.7.23 Thu 8:05 TE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
         </is>
       </c>
     </row>
@@ -4414,17 +4414,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>イープラス</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>郵便局アプリ</t>
+          <t>イープラス</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実施した結果、ゆうIDおよび郵便局アプリに関連する顧客情報が不正に取得されたことが判明している。 日本郵便 調査請求 Web受付サービスに不正アクセス、一時的に受付を停止 2026.9.30 Wed 8:05 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正アクセスがあり、同システム内に保管していた払戻しを実施するための情報に含まれていた顧客の個人情報の漏えいが判明したというもの。 一部顧客の情報が閲覧・編集・削除可能に ～ リセールサイト「RELIEF Ticket」 2025.7.3 Thu 8:05 CNプレイガイドへの不正アクセス、キョードー東京と</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4439,30 +4439,30 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>236,323</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>メールアドレス, クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Google News / ScanNetSecurity</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html</t>
         </is>
       </c>
     </row>
@@ -4474,22 +4474,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>セイコーマートアプリ</t>
+          <t>郵便局アプリ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした可能性が9月28日午後5時過ぎに判明したというもの。9月24日午後10時から11時の間に、不正にクラブカードの退会処理が行われたアカウントが1件あり発覚した。 「コープやまぐちLINEミニアプリ」に不正アクセス、データベースに保存されていた内容を精査し漏えいの可能性がある情報を確定 2026.9.24 T</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実施した結果、ゆうIDおよび郵便局アプリに関連する顧客情報が不正に取得されたことが判明している。 日本郵便 調査請求 Web受付サービスに不正アクセス、一時的に受付を停止 2026.9.30 Wed 8:05 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4499,30 +4499,30 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
         </is>
       </c>
     </row>
@@ -4534,24 +4534,42 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>セイコーマートアプリ</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした可能性が9月28日午後5時過ぎに判明したというもの。9月24日午後10時から11時の間に、不正にクラブカードの退会処理が行われたアカウントが1件あり発覚した。 「コープやまぐちLINEミニアプリ」に不正アクセス、データベースに保存されていた内容を精査し漏えいの可能性がある情報を確定 2026.9.24 T</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4564,7 +4582,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
         </is>
       </c>
     </row>
@@ -4576,13 +4594,13 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline）</t>
+          <t>Toyobo MC（tracker headline）</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4618,13 +4636,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ）</t>
+          <t>Three educational institutions（tracker headline）</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4660,13 +4678,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline）</t>
+          <t>Kodansha BECK（ news report ）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4702,13 +4720,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline）</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4744,13 +4762,13 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4781,34 +4799,29 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -4821,7 +4834,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4852,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4863,12 +4876,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
@@ -4880,33 +4893,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>システムで</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -4914,12 +4923,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190842</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4931,42 +4940,33 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ULTRA MART</t>
+          <t>システムで</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56356;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 これは9月9日から9月10日の抽選枠で販売を実施した、「ULTRA MART」での「M78ウルトラマン ふわふわお座りぬいぐるみ」購入抽選システム（mogily）に対する第三者からの不正アクセスの影響で、一部の抽選結果データに不整合が発生し、「当選」した一部顧客が「落選」表示に変更されたというもの。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fr</t>
+          <t>佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+          <t>https://www.security-next.com/190842</t>
         </is>
       </c>
     </row>
@@ -4991,17 +4991,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>円谷プロダクション</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>オズモール</t>
+          <t>ULTRA MART</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56359;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); スターツ出版株式会社は9月27日、同社運営のウェブサイト「オズモール」への不正アクセスについて発表した。 これは9月26日に、「オズモール」への海外からの大量の不正アクセスを同社システム部門が検知したため、調査した結果、顧客の個人情報が閲覧された可能性が判明したというもの。 不正プログラム設置 ～ 東京大学大学院医学系研究科公共健康医学専攻ウェブサイトに不正アクセス 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 2026.9.29 Tue 8:05 「スマ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56356;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社円谷プロダクションは9月11日、同社が運営する「ULTRA MART」チケット抽選システムへの不正アクセスについて発表した。 これは9月9日から9月10日の抽選枠で販売を実施した、「ULTRA MART」での「M78ウルトラマン ふわふわお座りぬいぐるみ」購入抽選システム（mogily）に対する第三者からの不正アクセスの影響で、一部の抽選結果データに不整合が発生し、「当選」した一部顧客が「落選」表示に変更されたというもの。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fr</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
         </is>
       </c>
     </row>
@@ -5051,17 +5051,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーアプリ</t>
+          <t>オズモール</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56358;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ニッポンレンタカーサービス株式会社は9月26日、同社が運営する「ニッポンレンタカーアプリ」への不正アクセスについて発表した。 これは「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認したというもの。 カーシェアサービス「RIDENOW」に登録された運転免許証画像が漏えいした可能性 2024.3.25 Mon 8:05 名鉄協商にランサムウェア攻撃、カーシェア「カリテコ」の顧客情報が漏えいした可能性 2026.8.26 Wed 8:10 日本テレネットにランサムウェア型サイバー攻撃、大和リ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56359;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); スターツ出版株式会社は9月27日、同社運営のウェブサイト「オズモール」への不正アクセスについて発表した。 これは9月26日に、「オズモール」への海外からの大量の不正アクセスを同社システム部門が検知したため、調査した結果、顧客の個人情報が閲覧された可能性が判明したというもの。 不正プログラム設置 ～ 東京大学大学院医学系研究科公共健康医学専攻ウェブサイトに不正アクセス 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 2026.9.29 Tue 8:05 「スマ</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
         </is>
       </c>
     </row>
@@ -5111,17 +5111,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>クロネコ代金後払いサービス</t>
+          <t>ニッポンレンタカーアプリ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8:05 刑事告訴検討 ～ ヤマト運輸の元従業員が取引先企業に関する情報の一部を不正に持ち出し 2 社に流出 2025.10.20 Mon 8:05 シンガポールヤマト運輸に不正アクセス、個人情報の不正持ち出しが判明 2024.11.18 M</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56358;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ニッポンレンタカーサービス株式会社は9月26日、同社が運営する「ニッポンレンタカーアプリ」への不正アクセスについて発表した。 これは「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認したというもの。 カーシェアサービス「RIDENOW」に登録された運転免許証画像が漏えいした可能性 2024.3.25 Mon 8:05 名鉄協商にランサムウェア攻撃、カーシェア「カリテコ」の顧客情報が漏えいした可能性 2026.8.26 Wed 8:10 日本テレネットにランサムウェア型サイバー攻撃、大和リ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 顧客情報, 会員情報</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
         </is>
       </c>
     </row>
@@ -5171,13 +5171,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>クロネコ代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8:05 刑事告訴検討 ～ ヤマト運輸の元従業員が取引先企業に関する情報の一部を不正に持ち出し 2 社に流出 2025.10.20 Mon 8:05 シンガポールヤマト運輸に不正アクセス、個人情報の不正持ち出しが判明 2024.11.18 M</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5187,13 +5191,22 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5206,7 +5219,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
         </is>
       </c>
     </row>
@@ -5218,24 +5231,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eplus（tracker headline）</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>eplus（tracker headline） — Unauthorized access.</t>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5248,7 +5266,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5260,13 +5278,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline）</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5302,13 +5320,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ）</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5344,13 +5362,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline）</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5386,13 +5404,13 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline）</t>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5428,13 +5446,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+          <t>Lashinbang（tracker headline）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5470,13 +5488,13 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ）</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5507,43 +5525,29 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5551,12 +5555,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5578,7 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5587,7 +5591,16 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -5598,12 +5611,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5615,42 +5628,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ランサムウェア被害拡大中</t>
-        </is>
-      </c>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア被害から学ぶ教訓集」～ 経営者のためのランサムウェア対策ハンドブック ～ https://www.ipa.go.jp/security/todokede/crack-virus/ransomware_lessons_learned.html 個人</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5675,17 +5675,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>警察庁が対策情報を紹介 警察庁</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>サイバー攻撃共同対処訓練</t>
+          <t>ランサムウェア被害拡大中</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 また、同訓練では、サイバー攻撃への対処の速さやサービスの継続性などをポイント化して競うチーム対抗形式のコンテストが実施され、同学数理情報科学科2年生（長尾柚葉氏、清水海凜氏、奥田陸斗氏、松岡俊汰氏）のチームが優勝している。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 </t>
+          <t>警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア被害から学ぶ教訓集」～ 経営者のためのランサムウェア対策ハンドブック ～ https://www.ipa.go.jp/security/todokede/crack-virus/ransomware_lessons_learned.html 個人</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
         </is>
       </c>
     </row>
@@ -5735,22 +5735,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>誤った配達をしないように</t>
+          <t>サイバー攻撃共同対処訓練</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56344;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵便株式会社は9月25日、同社の国際郵便物の調査請求Web受付サービスへの不正アクセスについて発表した。 これは9月25日午後3時頃に、調査請求Web受付サービスで使用しているサーバに対し、外部から不正アクセスの可能性が発覚したというもの。 同社では現在、同サービスについて一時的に受付を停止している。 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配達資料を撮影 2025.1.28 Tue 8:05 保有ドメインへ不正アクセス、迷惑メール送信の踏み台に（日本郵便） 2020.2.18 Tue 10:00 弓削郵便局で居住者情報を記載</t>
+          <t xml:space="preserve">山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 また、同訓練では、サイバー攻撃への対処の速さやサービスの継続性などをポイント化して競うチーム対抗形式のコンテストが実施され、同学数理情報科学科2年生（長尾柚葉氏、清水海凜氏、奥田陸斗氏、松岡俊汰氏）のチームが優勝している。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>29,116</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.9.30 Wed 8:05 日本郵便 調査請求 Web受付サービスに不正アクセ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56341;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。 鎌倉市児童発達支援センターあおぞら園では6月に個人情報の誤送付事案が発生し、2025年3月にも同様の事案が判明したため、同市では6月23日付で指定管理者の社会福祉法人県央福祉会に対し、令和3（2021）年度以降の指定管理期間における管理業務の総点検と総合的な再発防止策の報告を指示している。 指定管理者から7月31日付で提出された総点検結果によると、5年間の指定管理期間を通じて、13件の個人情報管理</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56344;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵便株式会社は9月25日、同社の国際郵便物の調査請求Web受付サービスへの不正アクセスについて発表した。 これは9月25日午後3時頃に、調査請求Web受付サービスで使用しているサーバに対し、外部から不正アクセスの可能性が発覚したというもの。 同社では現在、同サービスについて一時的に受付を停止している。 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配達資料を撮影 2025.1.28 Tue 8:05 保有ドメインへ不正アクセス、迷惑メール送信の踏み台に（日本郵便） 2020.2.18 Tue 10:00 弓削郵便局で居住者情報を記載</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29,116</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>氏名, 住所, クレジットカード情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html</t>
         </is>
       </c>
     </row>
@@ -5855,22 +5855,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>お問合せフォーム</t>
+          <t>ecurity 2026.9.30 Wed 8:05 保育上の不適切な対応も確認 ～ 鎌倉市児童発達支援</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支障はない。 「西武 旅するレストラン 『52 席の至福』」予約サイトで予約関連情報の一部が漏えい 2026.9.24 Thu 8:05 駅放送設備から意図しない音声が送出 ～ 西鉄福岡（天神）駅と薬院駅 2026</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56341;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。 鎌倉市児童発達支援センターあおぞら園では6月に個人情報の誤送付事案が発生し、2025年3月にも同様の事案が判明したため、同市では6月23日付で指定管理者の社会福祉法人県央福祉会に対し、令和3（2021）年度以降の指定管理期間における管理業務の総点検と総合的な再発防止策の報告を指示している。 指定管理者から7月31日付で提出された総点検結果によると、5年間の指定管理期間を通じて、13件の個人情報管理</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 従業員情報</t>
+          <t>氏名, 住所, クレジットカード情報</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html</t>
         </is>
       </c>
     </row>
@@ -5915,22 +5915,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HALMEK up</t>
+          <t>ecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56343;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。 これは社員1名のID・パスワードが窃取されたことが原因で、「HALMEK up」管理画面への不正アクセスの発生を9月9日に確認したというもの。 同社では不正アクセス確認後に、管理画面へのサイトアクセスに必要なパスワードの変更を実施するとともに、外部専門家の協力のもと調査を開始している。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支障はない。 「西武 旅するレストラン 『52 席の至福』」予約サイトで予約関連情報の一部が漏えい 2026.9.24 Thu 8:05 駅放送設備から意図しない音声が送出 ～ 西鉄福岡（天神）駅と薬院駅 2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>978</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+          <t>クレジットカード情報, 従業員情報</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5975,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>5 ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングス</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>代金後払いサービス</t>
+          <t>HALMEK up</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ヤマト運輸は、「クロネコ代金後払いサービス」が第三者により侵害されたことを明らかにした。宅配サービスの提供には影響はないとしている。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56343;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。 これは社員1名のID・パスワードが窃取されたことが原因で、「HALMEK up」管理画面への不正アクセスの発生を9月9日に確認したというもの。 同社では不正アクセス確認後に、管理画面へのサイトアクセスに必要なパスワードの変更を実施するとともに、外部専門家の協力のもと調査を開始している。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィ</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5995,13 +5995,22 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6014,7 +6023,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190835</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
         </is>
       </c>
     </row>
@@ -6026,13 +6035,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
+          <t>ヤマト運輸は、「クロネコ代金後払いサービス」が第三者により侵害されたことを明らかにした。宅配サービスの提供には影響はないとしている。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6043,7 +6061,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6056,7 +6074,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190835</t>
         </is>
       </c>
     </row>
@@ -6068,13 +6086,13 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
+          <t>VOISING（ disclosure ）</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
+          <t>VOISING（ disclosure ） — Vulnerability in a BI tool; failure to apply a known vulnerability fix in time identified as the direct cause. Product/CVE not disclosed.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6110,13 +6128,13 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline）</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline）</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline） — Unauthorized access.</t>
+          <t>Japan Post Holdings / Japan Post (Post Office app / Yu-ID)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6147,47 +6165,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>WaterPlum</t>
-        </is>
-      </c>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書によると、北朝鮮サイバー攻撃グループ「WaterPlum」は、警戒心の薄い求職者のコンピュータネットワークに密かに侵入し、機密情報の収集や暗号資産を盗み出すことを主な目的として、日本、米国、欧州及びその他の国々を標的としてサイバー攻撃を行っている。 警察庁とFBIでは、「WaterPlum」と一部の北朝鮮IT労働者が、北朝鮮朝鮮労働党（WPK）中央委員会軍需工業部313総局</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -6212,22 +6212,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>6.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス - 個人情報流出の可能性 アウトドア用品の製造</t>
+          <t>WaterPlum</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書によると、北朝鮮サイバー攻撃グループ「WaterPlum」は、警戒心の薄い求職者のコンピュータネットワークに密かに侵入し、機密情報の収集や暗号資産を盗み出すことを主な目的として、日本、米国、欧州及びその他の国々を標的としてサイバー攻撃を行っている。 警察庁とFBIでは、「WaterPlum」と一部の北朝鮮IT労働者が、北朝鮮朝鮮労働党（WPK）中央委員会軍需工業部313総局</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6235,10 +6235,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6251,7 +6260,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190798</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
         </is>
       </c>
     </row>
@@ -6263,13 +6272,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス - 個人情報流出の可能性</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+          <t>アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6279,18 +6292,13 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>41</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6303,7 +6311,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+          <t>https://www.security-next.com/190798</t>
         </is>
       </c>
     </row>
@@ -6315,42 +6323,34 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>あいこんナビ</t>
-        </is>
-      </c>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56325;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 愛知県は9月22日、同県が管理・運営する出会いサポートポータルサイト「あいこんナビ」での個人情報の誤掲載について発表した。 これは「あいこんナビ」のイベント情報にて、イベント主催団体が保有する、イベントに直接関係のない非公開情報が誤掲載され、氏名、年齢等の個人情報が読み取れる状態になっていたというもの。9月20日午後2時30分頃に一般の人から連絡があり、発覚した。 埼玉県「公文書検索・閲覧システム」で不開示情報を誤掲載 2024.6.3 Mon 8:05 県実施ユーチューバートークイベントで申込者の個人情報が閲覧可能に 2023.11.8 We</t>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5,261</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>個別お打合せのご提案</t>
+          <t>あいこんナビ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56330;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 選挙ドットコムを運営するイチニ株式会社は9月10日、メール誤送信によるメールアドレス漏えいについて発表した。 これは9月6日に、同社から送信した「個別お打合せのご提案」と題するメールについて、「BCC」等で送信すべき送信先メールアドレスを「宛先」で送信したことで、当該メールの受信者以外の他の顧客のメールアドレスが表示される状況となったというもの。 公益財団法人 九州先端科学技術研究所でメール誤送信、見積書を自治体 ML 宛に送信 2026.9.15 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 202</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56325;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 愛知県は9月22日、同県が管理・運営する出会いサポートポータルサイト「あいこんナビ」での個人情報の誤掲載について発表した。 これは「あいこんナビ」のイベント情報にて、イベント主催団体が保有する、イベントに直接関係のない非公開情報が誤掲載され、氏名、年齢等の個人情報が読み取れる状態になっていたというもの。9月20日午後2時30分頃に一般の人から連絡があり、発覚した。 埼玉県「公文書検索・閲覧システム」で不開示情報を誤掲載 2024.6.3 Mon 8:05 県実施ユーチューバートークイベントで申込者の個人情報が閲覧可能に 2023.11.8 We</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>5,261</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報</t>
+          <t>氏名, クレジットカード情報</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
         </is>
       </c>
     </row>
@@ -6435,22 +6435,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>モンベル・グローバルサイト</t>
+          <t>個別お打合せのご提案</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。 REXTにランサムウェア攻撃、流出した可能性のある情報の一部がインターネット上に掲載 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56330;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 選挙ドットコムを運営するイチニ株式会社は9月10日、メール誤送信によるメールアドレス漏えいについて発表した。 これは9月6日に、同社から送信した「個別お打合せのご提案」と題するメールについて、「BCC」等で送信すべき送信先メールアドレスを「宛先」で送信したことで、当該メールの受信者以外の他の顧客のメールアドレスが表示される状況となったというもの。 公益財団法人 九州先端科学技術研究所でメール誤送信、見積書を自治体 ML 宛に送信 2026.9.15 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 202</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>メールアドレス, クレジットカード情報</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html</t>
         </is>
       </c>
     </row>
@@ -6495,17 +6495,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>Helpfeel</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ワンストップジョブサイトくまもと</t>
+          <t>モンベル・グローバルサイト</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56326;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 熊本県は9月9日、同県が運営する「ワンストップジョブサイトくまもと」への不正アクセスについて発表した。 これは「ワンストップジョブサイトくまもと」に外部から不正アクセスがあり、一部内容が改ざんされたというもの。当該サイトの利用登録画面で会員規約の同意ボタンをクリックすると、「ウイルスが検出された」等の偽の警告で不安を煽り、有料アプリのインストールへ誘導する「フェイクアラート（偽の警告広告）」が表示される状態となっていたという。 熊本県「白塗り」PDF 公開 ～ 他自治体の黒塗り PDF 案件報道で確認したところ発覚 2025.10.30 Thu</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。 REXTにランサムウェア攻撃、流出した可能性のある情報の一部がインターネット上に掲載 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29,451</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
         </is>
       </c>
     </row>
@@ -6555,13 +6555,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ワンストップジョブサイトくまもと</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56326;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 熊本県は9月9日、同県が運営する「ワンストップジョブサイトくまもと」への不正アクセスについて発表した。 これは「ワンストップジョブサイトくまもと」に外部から不正アクセスがあり、一部内容が改ざんされたというもの。当該サイトの利用登録画面で会員規約の同意ボタンをクリックすると、「ウイルスが検出された」等の偽の警告で不安を煽り、有料アプリのインストールへ誘導する「フェイクアラート（偽の警告広告）」が表示される状態となっていたという。 熊本県「白塗り」PDF 公開 ～ 他自治体の黒塗り PDF 案件報道で確認したところ発覚 2025.10.30 Thu</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6571,13 +6575,22 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>29,451</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6585,12 +6598,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html</t>
         </is>
       </c>
     </row>
@@ -6602,17 +6615,13 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>メトポ</t>
-        </is>
-      </c>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
+          <t>【画像】「お前もか」セイコーマート、不正アクセスで情報漏洩を発表「日本企業どうしたの」「心配でなりません」 - ライブドアニュース</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6628,7 +6637,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6636,12 +6645,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190791</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE83bkF1UGJ0VlF4cENva3k1alE5WVFNT0J2RlRKMFViOFlXbld1THlPZ0J4V21uYTRLaTZrSGNSVnhIQkptMnFWTGJROXpoUjVoc2RUQmoyTE5OQWxoUWc?oc=5 / https://news.google.com/rss/articles/CBMiWkFVX3lxTE9Qa2NUWlltV2V6YkdwM3hMR2RTRFhSZE8weEdKNHlSMVhqRlZtMkNHVTdIMG5qemRlSXpTWndtVUJFUUhmcEtYbVlrVllBa1VpMWdqLUlRRktXUQ?oc=5 / https://news.google.com/rss/articles/CBMiYkFVX3lxTE51V3ZwaVh1dWNNVDJMd1VTdl92UHQwSUdVVkN6YTUtV1Z0T2N1SmEzUHVjcm1WQ0sxM3UzcWpMZGh6LXMxOGgxYkJpUFZBTnF4ZzJVbl91OWxacEdDNDBPeVJn?oc=5 / https://news.google.com/rss/articles/CBMifEFVX3lxTE1CRnZRTG52QlNESndNS25oUERHVHVYcFZ1RlpmZTRJVm5kakNXVnRWUzRuLVRFQmNDZTdGbHFhRktwVnE2RDRUYjBmNjZnSVlvV0hvaDNlTW96Q3BsMl9jSHlUdHlLRnVoZl9JTUgzTWlYYk1JdGJrR1B5TFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6653,24 +6662,33 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>メトポ</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+          <t>東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6683,7 +6701,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190791</t>
         </is>
       </c>
     </row>
@@ -6695,13 +6713,13 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline）</t>
+          <t>Toyobo Textile（tracker headline）</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline） — Ransomware.</t>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6737,13 +6755,13 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ）</t>
+          <t>Saga University（tracker headline）</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+          <t>Saga University（tracker headline） — Ransomware.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6779,13 +6797,13 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline）</t>
+          <t>QUO Card（ news report ）</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6821,13 +6839,13 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+          <t>International House of Japan (library)（tracker headline）</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6863,42 +6881,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>スマチケ</t>
-        </is>
-      </c>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>1,463</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 口座情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -6911,29 +6911,29 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>イープラス</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>スマチケ</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのURLをブックマーク登録しておき、ブックマークからアクセスする。 3.インターネット取引サービスを利用する際は、各証券会社が提供しているセキュリティ強化機能（ログイン時・取引実行時・出金時の多要素認証や通知サービス）を有効にして、不審な取引に注意する。 4.パスワードの使いまわしを</t>
+          <t>株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6943,22 +6943,22 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1,463</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+          <t>氏名, メールアドレス, 口座情報</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
         </is>
       </c>
     </row>
@@ -6983,17 +6983,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>サーバに不正アクセスか - 詳細は調査中 日本郵便は</t>
+          <t>ecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのURLをブックマーク登録しておき、ブックマークからアクセスする。 3.インターネット取引サービスを利用する際は、各証券会社が提供しているセキュリティ強化機能（ログイン時・取引実行時・出金時の多要素認証や通知サービス）を有効にして、不審な取引に注意する。 4.パスワードの使いまわしを</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7003,13 +7003,22 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7022,7 +7031,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190734</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
         </is>
       </c>
     </row>
@@ -7034,32 +7043,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>スパムの踏み台に - 日大 日本大学</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
+          <t>サーバに不正アクセスか - 詳細は調査中</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
+          <t>日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -7078,7 +7082,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190319</t>
+          <t>https://www.security-next.com/190734</t>
         </is>
       </c>
     </row>
@@ -7090,27 +7094,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>日本大学</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>システムに影響 - 京王電鉄 京王電鉄は</t>
+          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
+          <t>日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -7129,7 +7138,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190761</t>
+          <t>https://www.security-next.com/190319</t>
         </is>
       </c>
     </row>
@@ -7141,55 +7150,46 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Gyazo</t>
+          <t>システムに影響 - 京王電鉄</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆弱性を悪用し、第三者が同社のシステム上で任意のコマンドを実行する不正アクセスがあり、同社では同日夜に不正な挙動を検知し、調査および対応を開始していた。 「はいチーズ！フォト」に不正アクセス、漏えい件数の公表は顧客の保護と二次被害防止の観点から差し控える 2026.8.20 Thu 8:05 「はいチーズ！フォト」への不正アクセス、漏</t>
+          <t>京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yagura / ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+          <t>https://www.security-next.com/190761</t>
         </is>
       </c>
     </row>
@@ -7201,22 +7201,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>旭化成</t>
+          <t>Helpfeel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>山東聖泉</t>
+          <t>Gyazo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記録を対象家庭に匿名で郵送、市職員 生活福祉課 主幹 50歳 逮捕 2026.9.16 Wed 8:05 個人情報を無断で持ち出し 不正競争防止法違反容疑で逮捕 2026.7.31 Fri 8:05 器物損壊罪等で逮捕された津田塾大学元職員、個人情</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆弱性を悪用し、第三者が同社のシステム上で任意のコマンドを実行する不正アクセスがあり、同社では同日夜に不正な挙動を検知し、調査および対応を開始していた。 「はいチーズ！フォト」に不正アクセス、漏えい件数の公表は顧客の保護と二次被害防止の観点から差し控える 2026.8.20 Thu 8:05 「はいチーズ！フォト」への不正アクセス、漏</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7231,54 +7231,72 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>メールアドレス, クレジットカード情報</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report）</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>旭化成</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>山東聖泉</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記録を対象家庭に匿名で郵送、市職員 生活福祉課 主幹 50歳 逮捕 2026.9.16 Wed 8:05 個人情報を無断で持ち出し 不正競争防止法違反容疑で逮捕 2026.7.31 Fri 8:05 器物損壊罪等で逮捕された津田塾大学元職員、個人情</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7291,36 +7309,54 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report）</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.28 Mon 8:05 PCデポのメールドメインの認証情報を不正利用</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56316;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ピーシーデポコーポレーションは9月11日、メールドメインの認証情報の不正利用による不審メールの送信について発表した。 これは同社が提供しているメールドメインの認証情報が第三者に不正利用され、同社の正規メール送信環境からフィッシングメールが不正に送信されたというもの。送信元には、同社が提供しているメールドメイン（＠ozzio.jp）が使用されたことを確認している。 日本大学理工学部教職員のアカウントに対し巧妙に偽装されたフィッシングメール、多数の不審メールを送信 2026.9.15 Tue 8:05 TRUNK 従業員のメールアカウントに</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>3,177</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7328,41 +7364,59 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56316.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56312;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 遠州夢咲農業協同組合（JA遠州夢咲）は9月9日、不正アクセスによるホームページの一時閉鎖について発表した。 これは8月24日に、同組合のホームページに不正アクセスがあり、プログラム改ざんが行われたため、ホームページの更新が不可能な状況となったというもの。同組合では現在、念のためにホームページを一時閉鎖している。 農林中央金庫が個人データ 3,176 件を誤提供、改修テストで本番データ混入 2026.7.14 Tue 8:05 懲戒解雇 情報漏えいと着服で ～ JA鹿児島県信連 元職員 2025.4.10 Thu 8:05 元職員による持ち出しの</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>3,176</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7375,49 +7429,36 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56312.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>サーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響</t>
-        </is>
-      </c>
+          <t>Tokyo Metro (Metpo)（news report）</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Tokyo Metro (Metpo)（news report） — Unauthorized access; cause under investigation.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7430,45 +7471,36 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>サイトに不正アクセス - サイト更新時に判明 神奈川県川崎市は</t>
-        </is>
-      </c>
+          <t>Nippon Rent-A-Car (app)（news report）</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>神奈川県川崎市は、かわさき新産業創造センターのウェブサイトが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nippon Rent-A-Car (app)（news report） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7481,34 +7513,25 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190242</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>クセス - ハルメクHD 50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングス</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>HALMEK up</t>
-        </is>
-      </c>
+          <t>Keio Plaza Hotel / Keio Group（ news report ）</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングスは、ウェブサイト「HALMEK up」の管理画面が不正アクセスを受けたことを明らかにした。詳細について調査を行っている。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Keio Plaza Hotel / Keio Group（ news report ） — Ransomware system outage, separately disclosed by Keio Plaza Hotel and Keio Group.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7519,7 +7542,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -7532,54 +7555,49 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190247</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026年8月の情報漏えい</t>
+          <t>サーバがランサムウェア攻撃を受けシステム障害 — 京王ストアの決済や京王プレッソインの予約受付に影響</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知らないところで漏えい事件は起き続けている。 頼まれもしないのに月ごとの情報漏えいの動向を勝手にウォッチしている、虫の音ならぬ虫の息のような本連載、今月も一寸の虫のようにひっそりと掲載である。 ●インシデント原因内訳 さて、先月 2026 年 8 月に本誌が取り上げた事故・インシデント記事は 2026 年 7 月の 84 本から 42 本増となる全</t>
+          <t>京王電鉄株式会社（東京都多摩市／鉄道事業を中核に流通・不動産・レジャーサービスを展開する京王グループの中核会社）は2026年9月26日、同社グループのサーバがランサムウェアによる攻撃を受け、システム障害が発生していると公表した。京王ストアの一部店舗でクレジットカードや電子マネーの決済ができなくなり、京王プレッソインは新規予約の受付を当面停止、京王プラザホテルも自社サーバへの攻撃を確認したと公表している。鉄道の運行に支障はなく、情報漏えいの事実は公表時点で確認されていないとして調査が続いている。</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>97</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -7592,7 +7610,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-29-keio-group-ransomware/</t>
         </is>
       </c>
     </row>
@@ -7604,22 +7622,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>8:00 ランサムウェアの被害報告件数が過去最多に ～ 警察庁 サイバー警察局便り 警察庁</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PhotoGoods</t>
+          <t>「サイバー空間の脅威情勢</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56305;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); カルビー株式会社は9月17日、同社業務提携先での個人情報等の漏えいの可能性について発表した。 これは同社の「プロ野球チップス」をモチーフとしたオリジナルカードなどを注文できるサービス「PhotoGoods」にて、顧客の個人情報等が漏えいした可能性が判明したというもの。当該サービス運営する業務提携先の大興印刷株式会社では、状況の確認と詳細の調査を進めている。 今日もどこかで情報漏えい 第3回「クレジットカード情報漏えい顛末記」 2022.8.3 Wed 8:10 いまでやが管理する注文情報が外部流出した可能性、フィッシングサイト上でカード情報を入</t>
+          <t>警察庁は9月10日、サイバー警察局便りR8Vol.15「「サイバー空間の脅威情勢」が公表されました 」を公開した。 同便りでは、同庁が9月10日に「令和8年上半期におけるサイバー空間をめぐる脅威の情勢等について」を公表したことを取り上げ、同資料によると令和8（2026）年上半期におけるランサムウェアの被害報告件数が123件で、半期の件数としては、統計を取り始めた令和2（2020）年下半期以降、最多となっていることを紹介している。 令和8年上半期におけるサイバー空間をめぐる脅威の情勢等について https://www.npa.go.jp/publications/statistics/cybersecurity/data/R8kami/R08_kami_cyber_jousei.pdf 同庁では、諸外国と連携して注意喚起するとともに、都道府県警察で体制強化を進めている。 警察庁が DMARC を郵便局に例えて紹介「Quarantine」「Reject」への移行促す 2026.9.8 Tue 8:00 警察庁「パスワードだけの認証はもう限界です」パスキー導入検討を呼びかけ 2026.9.7</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7629,12 +7647,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7652,7 +7670,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56296.html</t>
         </is>
       </c>
     </row>
@@ -7664,24 +7682,33 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス - サイト更新時に判明</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
+          <t>神奈川県川崎市は、かわさき新産業創造センターのウェブサイトが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -7694,7 +7721,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190242</t>
         </is>
       </c>
     </row>
@@ -7706,37 +7733,33 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
+          <t>50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングス</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性</t>
+          <t>サイトの管理画面に不正アクセス - ハルメクHD</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。</t>
+          <t>50代以上の女性向け情報誌の発行や通信販売事業を展開するハルメクホールディングスは、ウェブサイト「HALMEK up」の管理画面が不正アクセスを受けたことを明らかにした。詳細について調査を行っている。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -7749,29 +7772,29 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
+          <t>https://www.security-next.com/190247</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>政府の信用を大きく傷つける深刻な問題</t>
+          <t>2026年8月の情報漏えい</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証するセキュリティモデル）を」と求め、VPNで「ゼロトラスト」が働く境界の手前の領域も含めた防御の再構築を促している。 VPNの脆弱性を利用 ～ デジタル庁が運用するガバメントソリューションサービス（GSS）に不正アクセス、約24.6万件の個人情報が漏えいした可能性 2026.9.14 Mon 8:05 「ガバメントソリ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知らないところで漏えい事件は起き続けている。 頼まれもしないのに月ごとの情報漏えいの動向を勝手にウォッチしている、虫の音ならぬ虫の息のような本連載、今月も一寸の虫のようにひっそりと掲載である。 ●インシデント原因内訳 さて、先月 2026 年 8 月に本誌が取り上げた事故・インシデント記事は 2026 年 7 月の 84 本から 42 本増となる全</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7786,12 +7809,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7804,19 +7827,19 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7826,17 +7849,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>hyocom</t>
+          <t>ecurity 2026.9.25 Fri 8:05 京都パープルサンガでメール誤送信</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56290;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。 これは同学の非常勤講師が授業運営に際し、同学と無関係の外部SNSサービス「hyocom」を利用し、学生の個人情報を公開した上、公開範囲の管理を適切に行っていなかったことから、個人情報が外部から閲覧可能な状態となっていたというもの。外部から公益通報受付窓口に寄せられた情報提供を受けて、2026年7月に発覚している。 誤ってフィッシングサイトにアクセス、学生や卒業生ら1,466人分の個人情報の</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56301;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社京都パープルサンガは9月8日、ファンクラブ会員情報の誤送信による個人情報漏えいについて発表した。 これは9月2日午前11時15分に、同社の担当者が取引先企業の担当者へメールを送信した際、誤ってファンクラブ会員情報が記載されたファイルを添付したというもの。メールを受信した11名のうち2名がファイルを開封したことを確認している。 京都サンガF.C.公式サイトで未発表の試合情報が漏えい 2022.2.8 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 2026.7.16 Thu 8:05 フィルタを解</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7846,12 +7869,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>1,466</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7864,34 +7887,34 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>大興印刷</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>アカウント乗っ取り</t>
+          <t>PhotoGoods</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56285;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東証プライム上場企業の株式会社トレジャー・ファクトリーは8月28日、同社連結子会社である株式会社カインドオルへの不正アクセスについて発表した。 これは8月22日に、カインドオルがECサイトで利用しているECプラットフォームのスタッフアカウントに第三者から不正アクセスがあり、8月23日に当該アカウントのメールアドレスが変更され、同日、顧客情報の一括エクスポートが2回実行されたことを確認したというもの。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 3,177件の不審</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56305;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); カルビー株式会社は9月17日、同社業務提携先での個人情報等の漏えいの可能性について発表した。 これは同社の「プロ野球チップス」をモチーフとしたオリジナルカードなどを注文できるサービス「PhotoGoods」にて、顧客の個人情報等が漏えいした可能性が判明したというもの。当該サービス運営する業務提携先の大興印刷株式会社では、状況の確認と詳細の調査を進めている。 今日もどこかで情報漏えい 第3回「クレジットカード情報漏えい顛末記」 2022.8.3 Wed 8:10 いまでやが管理する注文情報が外部流出した可能性、フィッシングサイト上でカード情報を入</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7906,12 +7929,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3,177</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7924,59 +7947,41 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56285.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56305.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>生命のにぎわい調査団</t>
-        </is>
-      </c>
+          <t>Smaregi EC（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56289;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 千葉県は9月1日、同県が運営する生物多様性センターのホームページへの不正アクセスについて発表した。 これは8月27日午前9時頃に、生物多様性センターホームページ（ https://www.bdcchiba.jp/ ） 内の「生命のにぎわい調査団」ページに不正アクセスがあった可能性があるので、アクセスログを確認して欲しい旨の連絡が千葉県警からあり、同日午前10時頃に同センター職員がアクセスログを確認したところ、8月27日午前1時1分と午前1時9分に不正アクセスがあり、本来存在しない画面（通常ではリンクしないページ）が差し込まれていることを確認した</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Smaregi EC（tracker headline） — Exploitation of an administrator-login vulnerability.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -7989,34 +7994,34 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>paperlogic</t>
+          <t>システムのNASがランサムウェア被害 — 教職員・学生のID・パスワードが流出した可能性</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56287;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。 これは8月27日に、同社が利用するクラウドサーバに対し、第三者からの不正アクセスおよび通常とは異なる動作を検知したというもの まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの</t>
+          <t>国立大学法人佐賀大学（佐賀市本庄町）は2026年9月25日、事務情報システムの一部でランサムウェアによる被害が発生したと公表した。事務部門が利用するNAS内のファイルが暗号化され、大学は該当NASをネットワークから隔離したうえで事務用端末約500台の利用を停止した。9月28日には、学内システムへのログインに使う教職員・学生のユーザー認証情報が流出した恐れがあると公表し、全教職員・学生にパスワードの変更を指示している。認証情報が使用された被害は確認されておらず、感染経路は公表されていない。</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8024,19 +8029,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>1,801,499</t>
-        </is>
-      </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>認証情報</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-01-saga-university-nas-ransomware/</t>
         </is>
       </c>
     </row>
@@ -8061,24 +8061,42 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>デジタル庁</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
+          <t>自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証するセキュリティモデル）を」と求め、VPNで「ゼロトラスト」が働く境界の手前の領域も含めた防御の再構築を促している。 VPNの脆弱性を利用 ～ デジタル庁が運用するガバメントソリューションサービス（GSS）に不正アクセス、約24.6万件の個人情報が漏えいした可能性 2026.9.14 Mon 8:05 「ガバメントソリ</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8086,41 +8104,59 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>非常勤講師が外部SNSサービス「hyocom」を利用 関西学院大学</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>hyocom</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56290;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。 これは同学の非常勤講師が授業運営に際し、同学と無関係の外部SNSサービス「hyocom」を利用し、学生の個人情報を公開した上、公開範囲の管理を適切に行っていなかったことから、個人情報が外部から閲覧可能な状態となっていたというもの。外部から公益通報受付窓口に寄せられた情報提供を受けて、2026年7月に発覚している。 誤ってフィッシングサイトにアクセス、学生や卒業生ら1,466人分の個人情報の</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1,466</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8133,36 +8169,54 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>生命のにぎわい調査団</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56289;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 千葉県は9月1日、同県が運営する生物多様性センターのホームページへの不正アクセスについて発表した。 これは8月27日午前9時頃に、生物多様性センターホームページ（ https://www.bdcchiba.jp/ ） 内の「生命のにぎわい調査団」ページに不正アクセスがあった可能性があるので、アクセスログを確認して欲しい旨の連絡が千葉県警からあり、同日午前10時頃に同センター職員がアクセスログを確認したところ、8月27日午前1時1分と午前1時9分に不正アクセスがあり、本来存在しない画面（通常ではリンクしないページ）が差し込まれていることを確認した</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -8175,36 +8229,54 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56289.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>topia</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56286;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アンビリアルは8月31日、同社が運営するバーチャル音楽ライブ配信アプリ「topia」の配信音声への不正アクセスについて発表した。 「topia」では8月17日のプライベート配信において、音声サーバへの不正アクセスが1件発生したことを確認しており、音声サーバの提供元であるAgora社と原因および対策について協議、実装を進めていた。 ホワイトエッセンスの予約サイトおよび基幹システムに不正アクセス、Webサイト・アプリ等からの予約等を一時停止 2026.9.1 Tue 8:05 「東京アプリ」の運営に係るコールセンター業務で1名の個人情報漏え</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -8217,45 +8289,54 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56286.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>不審メールが送信 - 日大 日本大学</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>メールが送信 - 日大 日本大学は</t>
+          <t>paperlogic</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56287;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ペーパーロジック株式会社は9月1日、同社サービス「paperlogic」への不正アクセスについて発表した。 これは8月27日に、同社が利用するクラウドサーバに対し、第三者からの不正アクセスおよび通常とは異なる動作を検知したというもの まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1,801,499</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8263,59 +8344,41 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190198</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>令和8年版情報通信白書</t>
-        </is>
-      </c>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>総務省は9月11日、同省を装ったなりすましメールへの対策強化について発表した。 近年、行政機関を装ったなりすましメールによるフィッシング詐欺や不正サイトへの誘導などが発生しており、同省では今回の対策で、総務省を装うなりすましメールの抑止を図る。 同省では以前から、総務省ルートドメインになりすましたメールアドレス（@soumu.go.jp）からの不正なメールの受信を拒否する仕組みを導入していたが、9月1日からはサブドメインになりすましたメールアドレス（@xxx.soumu.go.jp）からのメールの受信を拒否する仕組みも導入し、対策を強化する。 同省によると、本対応で総務省から送信する正規のメールの受信方法に変更はないが、メール転送サービスや自動転送を利用している等、転送の仕組みによっては認証に失敗し、総務省からのメールが受信できなくなる可能性があるとのこと。 ダークネット観測パケット数が過去最高を更新、10年前から10倍に増大 ～ 総務省「令和8年版情報通信白書」 2026.9.8 Tue 8:00 KDDI の ISP 事業者向けメールシステムに不正アクセス、総務省が行政指導 202</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>EPARK Relax &amp; Esthe (PeakManager)（ disclosure ） — Unauthorized access to its PeakManager booking/customer platform. Route/method withheld to avoid inducing similar attacks.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8323,39 +8386,30 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>サイト改ざん</t>
-        </is>
-      </c>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Taikisha (Malaysian subsidiary)（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8366,7 +8420,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8379,54 +8433,36 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189792</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>原田産業</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>ビールの縁側</t>
-        </is>
-      </c>
+          <t>Ryomo Systems（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56270;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社カインドオルは8月28日、同社が運営するECサイトで利用しているECプラットフォームのスタッフアカウントへの不正アクセスについて発表した。 これは8月24日に、同社が通常業務として注文情報の出力を行った際に、ECプラットフォームのスタッフアカウントに登録されているメールアドレスが同社で使用していないものに変更されていることを確認したため、ECプラットフォームの運営会社に調査を依頼したところ、当該スタッフアカウントに第三者から不正アクセスが行われた後、8月23日に顧客情報の一括エクスポートが2回行われていたことが判明したというもの。 EC</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Ryomo Systems（tracker headline） — Ransomware group SafePay published stolen data.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報, 認証情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -8439,54 +8475,36 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>捜査に必要と求められ</t>
-        </is>
-      </c>
+          <t>GMO Internet (ConoHa WING)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56269;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社安藤・間（安藤ハザマ）は8月31日、名刺情報の外部流出について発表した。 これは8月16日から8月23日にかけて、同社社員が警察官を名乗る者から、交友関係の捜査に必要であるとして名刺情報を提出するよう求められ、当該社員は8月17日に同社の名刺管理システムに保管していた名刺情報をダウンロードの上、相手方にメールで提出したというもの。 名刺管理システムへ不正アクセス、サービス運営会社からの連絡で発覚 2023.5.9 Tue 8:05 名刺管理システムへの不正アクセス ～ 当の名刺管理システム会社名乗り電話とメールでIDパスワード詐取 20</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>GMO Internet (ConoHa WING)（tracker headline） — Unauthorized access and malicious-program installation on a hosting machine; intrusion from Sep 3.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8499,7 +8517,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -8511,42 +8529,33 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>日本大学</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>交通安全施設損壊事案報告書</t>
+          <t>メールが送信 - 日大</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56275;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 長野県警察は9月7日、塩尻警察署交通課での個人情報の所在不明について発表した。 これは塩尻警察署交通課が、令和3（2021）年度中に交通事故や自然災害等で交通安全施設の損壊等が発生した際に作成した「交通安全施設損壊事案報告書」「交通安全施設修繕執行伺」「交通安全施設修理結果表」「道路標識標示工事監督等指示書」、交通安全施設への意見・要望が寄せられた際に作成した「信号機BOX」が所在不明となったというもの。 12 名の個人情報記載した「交通切符等引継簿」紛失 ～ 釧路方面弟子屈警察署 2026.5.12 Tue 8:05 拾得物として届けられ回収</t>
+          <t>日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8559,7 +8568,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html</t>
+          <t>https://www.security-next.com/190198</t>
         </is>
       </c>
     </row>
@@ -8571,17 +8580,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>大オークション大会</t>
+          <t>サイト改ざん</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56274;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社マネジメントサービスセンターは8月25日、同社ホームページへの不正アクセスについて発表した。 これは7月に、同社ホームページへの第三者からの不正アクセスおよびホームページ改ざんを確認したというもの。 まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの一部が改ざんされる被害 2</t>
+          <t>コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8591,22 +8600,13 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>1,801,499</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html</t>
+          <t>https://www.security-next.com/189792</t>
         </is>
       </c>
     </row>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>原田産業</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.9.18 Fri 8:05 顧客情報の一括エクスポートを確認 ～ カインドオル</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56271;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。 これは6月29日に、当該サイトで異常を確認したため公開を停止し、調査および証拠保全等の対応を開始し、その後、外部専門機関による調査を行った結果、管理者権限を持つアカウントが第三者によって不正に作成され、サーバ上にバックドア等の不正プログラムが設置されていたことが判明したというもの。 人気の無料ソフト公式サイトを侵害、Linux 標的としたバックドア 3 年間拡散 2023.10.17 Tue 8:00 無料提</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56270;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社カインドオルは8月28日、同社が運営するECサイトで利用しているECプラットフォームのスタッフアカウントへの不正アクセスについて発表した。 これは8月24日に、同社が通常業務として注文情報の出力を行った際に、ECプラットフォームのスタッフアカウントに登録されているメールアドレスが同社で使用していないものに変更されていることを確認したため、ECプラットフォームの運営会社に調査を依頼したところ、当該スタッフアカウントに第三者から不正アクセスが行われた後、8月23日に顧客情報の一括エクスポートが2回行われていたことが判明したというもの。 EC</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1,668</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>メールアドレス, クレジットカード情報, 認証情報, 顧客情報</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
         </is>
       </c>
     </row>
@@ -8691,24 +8691,42 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>捜査に必要と求められ</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56269;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社安藤・間（安藤ハザマ）は8月31日、名刺情報の外部流出について発表した。 これは8月16日から8月23日にかけて、同社社員が警察官を名乗る者から、交友関係の捜査に必要であるとして名刺情報を提出するよう求められ、当該社員は8月17日に同社の名刺管理システムに保管していた名刺情報をダウンロードの上、相手方にメールで提出したというもの。 名刺管理システムへ不正アクセス、サービス運営会社からの連絡で発覚 2023.5.9 Tue 8:05 名刺管理システムへの不正アクセス ～ 当の名刺管理システム会社名乗り電話とメールでIDパスワード詐取 20</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8721,34 +8739,34 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>メールが送信 - ホテル運営会社 ホテルの運営を手がけるTRUNKは</t>
+          <t>交通安全施設損壊事案報告書</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56275;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 長野県警察は9月7日、塩尻警察署交通課での個人情報の所在不明について発表した。 これは塩尻警察署交通課が、令和3（2021）年度中に交通事故や自然災害等で交通安全施設の損壊等が発生した際に作成した「交通安全施設損壊事案報告書」「交通安全施設修繕執行伺」「交通安全施設修理結果表」「道路標識標示工事監督等指示書」、交通安全施設への意見・要望が寄せられた際に作成した「信号機BOX」が所在不明となったというもの。 12 名の個人情報記載した「交通切符等引継簿」紛失 ～ 釧路方面弟子屈警察署 2026.5.12 Tue 8:05 拾得物として届けられ回収</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8756,10 +8774,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -8772,14 +8799,14 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189987</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8789,12 +8816,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>洛西進学教室</t>
+          <t>ecurity 2026.9.18 Fri 8:05 マネジメントサービスセンターのホームページに不正ア</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56256;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アップは9月4日、同社が運営するプロモーションサイト「洛西進学教室」及び「進学館」への不正アクセスについて発表した。 これは8月24日に、当該サイトが利用していた外部ソフトウェア（プラグイン）の脆弱性を悪用した不正アクセスがあり、サーバ内に不正なプログラムが設置されたことが判明したというもの。当該サーバ内に保管されていた採用応募者の個人情報及び社内サイト管理者の個人情報が閲覧された可能性があるという。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 VOISI</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56274;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社マネジメントサービスセンターは8月25日、同社ホームページへの不正アクセスについて発表した。 これは7月に、同社ホームページへの第三者からの不正アクセスおよびホームページ改ざんを確認したというもの。 まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの一部が改ざんされる被害 2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8809,12 +8836,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>17,559</t>
+          <t>1,801,499</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8827,39 +8854,39 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>ecurity 2026.9.18 Fri 8:05 ウェブ画面設定誤りが原因「オペラ銀河鉄道</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>コープやまぐちLINEミニアプリ</t>
+          <t>オペラ銀河鉄道の夜</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」のデータベースに第三者から不正アクセスがあり、データベース内の全てのデータが削除される事象が発生したというもの。 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 メール配信システム「める配くん」の一部サーバに不正アクセス、配信先情報の一部が外部に取得されていた事実を確認</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56272;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 公益財団法人名古屋市文化振興事業団は8月28日、瑞穂文化小劇場での個人情報漏えいについて発表した。 これは管理者側のウェブ画面設定誤りが原因で、申込フォーム画面で申込者の個人情報含む申込情報が閲覧可能な状態となっていたというもの。 公益財団法人日産財団Webサイトに不正アクセス、情報が外部から閲覧され得る状態にあったことが判明 2026.9.1 Tue 8:05 手順書に管理者権限を有するアカウント情報を誤記載 ～ 東芝テックの「ShopCraft」で他のユーザーの情報が閲覧可能に 2026.8.24 Mon 8:05 オンデマンド学習サイト「</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8892,54 +8919,36 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56272.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>東海大学山中湖セミナーハウス</t>
-        </is>
-      </c>
+          <t>Bellcadia (montbell global site)（ news report ）</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56253;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。 これは同学が契約しているレンタルサーバで発生したセキュリティインシデントに伴い、当該サーバ上で開設していた複数のWebサイトで公開を停止したというもの。 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 福岡大学の委託先ノストラムに不正アクセス、攻撃者のサイト上に窃取したデータを公開する旨の告知 2026.7.27 Mon 8:05 日本大学の学生・卒業生</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Bellcadia (montbell global site)（ news report ） — Unauthorized access to overseas-facing site, detected Sep 11. Identified vulnerability fixed.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -8952,7 +8961,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -8964,24 +8973,33 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>メールが送信 - ホテル運営会社</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
+          <t>ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -8994,7 +9012,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189987</t>
         </is>
       </c>
     </row>
@@ -9006,24 +9024,42 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>同区の指定管理者である公益財団法人大田区文化振興協会</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.17 Thu 8:05 表示された連絡先に電話 指示に従いパソコン操作 ～</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56257;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東京都大田区は9月4日、同区の指定管理者である公益財団法人大田区文化振興協会が管理運営する大田区民プラザでの情報漏えいの可能性について発表した。 これは8月22日午前11時15分頃に、施設職員が施設配備パソコン端末でインターネットを閲覧中に画面に警告が表示されたため、表示された連絡先に電話し指示に従いパソコンを操作したところ、端末を操作できなくなり、その後、当該端末をネットワークから隔離したが、その間、当該端末に不正アクセスされたことから、個人情報を含む情報漏えいの可能性があというもの。 エスケーアイマネージメントへのサポート詐欺、Lansco</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9036,7 +9072,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html</t>
         </is>
       </c>
     </row>
@@ -9048,24 +9084,42 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>洛西進学教室</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56256;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アップは9月4日、同社が運営するプロモーションサイト「洛西進学教室」及び「進学館」への不正アクセスについて発表した。 これは8月24日に、当該サイトが利用していた外部ソフトウェア（プラグイン）の脆弱性を悪用した不正アクセスがあり、サーバ内に不正なプログラムが設置されたことが判明したというもの。当該サーバ内に保管されていた採用応募者の個人情報及び社内サイト管理者の個人情報が閲覧された可能性があるという。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 VOISI</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>17,559</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9078,7 +9132,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html</t>
         </is>
       </c>
     </row>
@@ -9090,24 +9144,42 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>コープやまぐちLINEミニアプリ</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」のデータベースに第三者から不正アクセスがあり、データベース内の全てのデータが削除される事象が発生したというもの。 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 メール配信システム「める配くん」の一部サーバに不正アクセス、配信先情報の一部が外部に取得されていた事実を確認</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9120,29 +9192,29 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>システムが侵害され</t>
+          <t>さくらのレンタルサーバ</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56259;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。 同社では8月9日に、同社のレンタルサーバサービス「さくらのレンタルサーバ」のメンテナンス用サーバで異常を検知し、事実確認および影響範囲を調査した結果、下記の事象を確認していた。 さくらインターネットへの不正アクセス、案内ページを公開 2026.9.8 Tue 8:05 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 </t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9155,10 +9227,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1,360,563</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9166,39 +9247,39 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190377</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>tSecurity 2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CINRA JOB</t>
+          <t>ecurity 2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学が契約している</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56253;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。 これは同学が契約しているレンタルサーバで発生したセキュリティインシデントに伴い、当該サーバ上で開設していた複数のWebサイトで公開を停止したというもの。 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 福岡大学の委託先ノストラムに不正アクセス、攻撃者のサイト上に窃取したデータを公開する旨の告知 2026.7.27 Mon 8:05 日本大学の学生・卒業生</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9206,14 +9287,19 @@
           <t>可能性あり</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9226,54 +9312,36 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189866</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>白塗り</t>
-        </is>
-      </c>
+          <t>Osaka City (recorded interview system)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56244;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 鳥取県は9月3日、モニタリングポストの放射線量率等の測定データを収集・監視する鳥取県環境放射線モニタリングシステムへのサイバー攻撃について発表した。 これは鳥取県環境放射線モニタリングシステムで、庁内に設置していた主監視局（主サーバ）へのランサムウェア攻撃を判明したというもの。同サーバ内の電子ファイルが暗号化され、主監視局に障害が発生しシステム停止している。 「白塗り」に気付けなかったのは決裁を紙文書でやっていたから ～ 消防防災航空センターホームページで個人情報が閲覧可能に 2024.5.30 Thu 8:05 食パラダイス鳥取県公式インスタ</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>Osaka City (recorded interview system)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9286,54 +9354,36 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>先輩就職先情報リスト</t>
-        </is>
-      </c>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ）</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56245;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 大阪高等裁判所は9月4日、同裁判所での特定の事件に係るMicrosoft Teamsのチーム作成の誤りについて発表した。 これは8月27日午前10時40分頃に、大阪高等裁判所民事部で、Microsoft Teamsを利用して特定の事件に係るチームを作成する際に、誤って本来登録するメンバー以外のメンバー（裁判所外部ユーザー約3,500アカウント、裁判所職員ユーザーが約2,500アカウント）を登録したというもの。同日午後0時20分頃に、外部からの問い合わせで発覚したという。 最高裁判所 メール誤送信 2024.6.13 Thu 8:05 最高裁で修</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Minami Nihon Joho Shori Center (minc)（ news report ） — Website accessed. Measures applied against the causal vulnerability.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>住所, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9346,25 +9396,25 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline）</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline）</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+          <t>Harada Corporation (Beer no Engawa)（tracker headline） — Vulnerability exploitation.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9395,18 +9445,18 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+          <t>Calbee (baseball-chip cards)（tracker headline）</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+          <t>Calbee (baseball-chip cards)（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9437,22 +9487,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>当選</t>
+          <t>システムが侵害され</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
+          <t>ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9462,38 +9512,33 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>133</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Yagura / Security NEXT</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315</t>
+          <t>https://www.security-next.com/190377</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9503,12 +9548,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ホワイトエッセンス</t>
+          <t>CINRA JOB</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9518,10 +9563,14 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>Security NEXT</t>
@@ -9537,34 +9586,34 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189665</t>
+          <t>https://www.security-next.com/189866</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ecurity 2026.9.16 Wed 8:05 鳥取県環境放射線モニタリングシステムにランサムウェ</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56230;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 静岡県長泉町は8月25日、8月20日付けで行った職員の懲戒処分について発表した。 これは同町の教育委員会 主査（57歳・女性）が、同町が管理すべき大量の廃棄対象の公文書等を無断で自宅に持ち帰って保管していたほか、同町のコピー機等を使用して上記文書の裏面に私的目的のため大量の小説のコピーを行っていたこと、通勤手段の変更に係る届出を長期間怠っていたことに対し、地方公務員としての信用を著しく失墜させるものであると判断し、免職の処分を行ったというもの。 停職1ヶ月 ～ 市職員が飲食店関係者に関する市税等の情報を口外 2026.8.6 Thu 8:05 </t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56244;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 鳥取県は9月3日、モニタリングポストの放射線量率等の測定データを収集・監視する鳥取県環境放射線モニタリングシステムへのサイバー攻撃について発表した。 これは鳥取県環境放射線モニタリングシステムで、庁内に設置していた主監視局（主サーバ）へのランサムウェア攻撃を判明したというもの。同サーバ内の電子ファイルが暗号化され、主監視局に障害が発生しシステム停止している。 「白塗り」に気付けなかったのは決裁を紙文書でやっていたから ～ 消防防災航空センターホームページで個人情報が閲覧可能に 2024.5.30 Thu 8:05 食パラダイス鳥取県公式インスタ</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9574,12 +9623,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, クレジットカード情報</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -9592,19 +9641,19 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9614,12 +9663,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>注文書フォーム</t>
+          <t>ecurity 2026.9.16 Wed 8:05 大阪高等裁判所で特定の事件に係る Microsof</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56233;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 福岡市の外郭団体である公益財団法人九州先端科学技術研究所は9月8日、メール誤送信による情報漏えいについて発表した。 これは9月3日午後3時44分に、同研究所が提供しているビッグデータ&amp;オープンデータ・イニシアティブ九州（BODIK）のホームページ保守等のサービスにて、自治体からの依頼を受けて作成した見積書をメール送信する際、誤って同サービスの利用自治体のメーリングリストを設定したことで、同リスト登録の全339の行政機関（アドレス数342件）に送信されたというもの。同日午後3時50分に発覚している。 取引先に送付した「注文書フォーム」エクセルファ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56245;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 大阪高等裁判所は9月4日、同裁判所での特定の事件に係るMicrosoft Teamsのチーム作成の誤りについて発表した。 これは8月27日午前10時40分頃に、大阪高等裁判所民事部で、Microsoft Teamsを利用して特定の事件に係るチームを作成する際に、誤って本来登録するメンバー以外のメンバー（裁判所外部ユーザー約3,500アカウント、裁判所職員ユーザーが約2,500アカウント）を登録したというもの。同日午後0時20分頃に、外部からの問い合わせで発覚したという。 最高裁判所 メール誤送信 2024.6.13 Thu 8:05 最高裁で修</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9634,12 +9683,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>住所, クレジットカード情報</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9657,25 +9706,25 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56245.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ）</t>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9706,18 +9755,18 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ）</t>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9753,37 +9802,51 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>円谷プロダクション</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>当選</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+          <t>円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>不明</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura / Security NEXT</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315</t>
         </is>
       </c>
     </row>
@@ -9800,33 +9863,28 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
+          <t>予約サイトなどで侵害</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。</t>
+          <t>審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -9839,7 +9897,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+          <t>https://www.security-next.com/189665</t>
         </is>
       </c>
     </row>
@@ -9851,42 +9909,42 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
+          <t>ecurity 2026.9.15 Tue 8:05 町職員（57歳・女性）が廃棄対象の公文書等を持ち帰</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56230;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 静岡県長泉町は8月25日、8月20日付けで行った職員の懲戒処分について発表した。 これは同町の教育委員会 主査（57歳・女性）が、同町が管理すべき大量の廃棄対象の公文書等を無断で自宅に持ち帰って保管していたほか、同町のコピー機等を使用して上記文書の裏面に私的目的のため大量の小説のコピーを行っていたこと、通勤手段の変更に係る届出を長期間怠っていたことに対し、地方公務員としての信用を著しく失墜させるものであると判断し、免職の処分を行ったというもの。 停職1ヶ月 ～ 市職員が飲食店関係者に関する市税等の情報を口外 2026.8.6 Thu 8:05 </t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>6,811</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -9894,19 +9952,19 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56221.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56230.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9916,17 +9974,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>第367回 個人情報保護委員会</t>
+          <t>ecurity 2026.9.15 Tue 8:05 日本大学理工学部教職員のアカウントに対し巧妙に偽装</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機関等が43件であった。 民間事業者に対しては、不正アクセスを原因とする漏えい等事案を中心に、安全管理措置の不備等について指導を行っており、外部からの不正アクセス等の防止の不備（21件）、アクセス者の識別と認証の不備（14件）、委託先に対する監督の不備（12件）、情報システムの使用に伴う漏えい等の防止の不備（3件）の他、</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56234;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本大学理工学部は9月8日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日午後11時40分頃に、同学部の教職員1名のメールアカウントが外部からのフィッシング攻撃で第三者に不正利用され、多数の不審メールが外部に送信されたというもの。当該教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」が原因という。 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri 8:05 日本大学の学生・卒業生 9 名のアカウントに不</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -9936,7 +9994,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>6,101</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9959,40 +10017,54 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56234.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>ecurity 2026.9.15 Tue 8:05 公益財団法人 九州先端科学技術研究所でメール誤送信</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56233;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 福岡市の外郭団体である公益財団法人九州先端科学技術研究所は9月8日、メール誤送信による情報漏えいについて発表した。 これは9月3日午後3時44分に、同研究所が提供しているビッグデータ&amp;オープンデータ・イニシアティブ九州（BODIK）のホームページ保守等のサービスにて、自治体からの依頼を受けて作成した見積書をメール送信する際、誤って同サービスの利用自治体のメーリングリストを設定したことで、同リスト登録の全339の行政機関（アドレス数342件）に送信されたというもの。同日午後3時50分に発覚している。 取引先に送付した「注文書フォーム」エクセルファ</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -10005,54 +10077,36 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189985</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/15/56233.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>日本交通</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>ドズル社ストア</t>
-        </is>
-      </c>
+          <t>Murauchi.com（ news report ）</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56219;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); WEVERSE JAPAN株式会社は9月6日、一部顧客の個人情報流出について発表した。 これは9月3日に、韓国インターネット振興院（KISA）より外部の報告者からWeverseサービスのセキュリティ脆弱性に関する指摘があった旨の連絡があり、社内点検を実施した結果、一部顧客の個人情報が流出した事実を確認したというもの。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 ソディックの</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>17,559</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -10065,25 +10119,25 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
+          <t>LEAN BODY（ disclosure ）</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10114,18 +10168,18 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
+          <t>Fuso Dentsu（tracker headline）</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10156,47 +10210,43 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
+          <t>株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -10209,29 +10259,29 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>デジタル庁は、同庁が運用する「ガバメントソリューションサービス（GSS）」が不正アクセスを受けたことを明らかにした。機器の脆弱性を突かれて侵入され、保守運用アカウントが侵害されたという。 ：Security NEXT</t>
+          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10241,13 +10291,22 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>6,811</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -10260,40 +10319,54 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190208</t>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>サポート詐欺で約4000ファイル削除 - サカイHD子会社 サカイホールディングス</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>第367回 個人情報保護委員会</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+          <t>個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機関等が43件であった。 民間事業者に対しては、不正アクセスを原因とする漏えい等事案を中心に、安全管理措置の不備等について指導を行っており、外部からの不正アクセス等の防止の不備（21件）、アクセス者の識別と認証の不備（14件）、委託先に対する監督の不備（12件）、情報システムの使用に伴う漏えい等の防止の不備（3件）の他、</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>6,101</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -10306,54 +10379,40 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188880</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>カリテコ</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -10366,14 +10425,14 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
+          <t>https://www.security-next.com/189985</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10383,17 +10442,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ドズル社ストア</t>
+          <t>ファンくる</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56222;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ファンくるは8月25日、8月24日に公表した同社が運営する「ファンくる」への不正ログインについて、第二報を発表した。 同社では、同社システム内への外部からのリスト型攻撃とみられる不正ログインを検知したため、二次被害の防止と安全確保のため「ファンくる」のサービスを一時停止していた。 全会員のパスワードを一新 ～「ミドルの転職」へのリスト型攻撃で不正ログイン 2,503 件 2026.6.15 Mon 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 ポイント不正利用 444 件</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10403,12 +10462,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2,503</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>氏名, クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -10426,29 +10485,29 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>アカウント乗っ取り</t>
+          <t>ecurity 2026.9.14 Mon 8:05 Weverseサービスにセキュリティ脆弱性</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56219;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); WEVERSE JAPAN株式会社は9月6日、一部顧客の個人情報流出について発表した。 これは9月3日に、韓国インターネット振興院（KISA）より外部の報告者からWeverseサービスのセキュリティ脆弱性に関する指摘があった旨の連絡があり、社内点検を実施した結果、一部顧客の個人情報が流出した事実を確認したというもの。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 ソディックの</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10463,7 +10522,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17,559</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -10486,34 +10545,25 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>東京外環プロジェクト</t>
-        </is>
-      </c>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10524,7 +10574,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -10537,25 +10587,25 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
+          <t>Five Foxes（tracker headline）</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10591,24 +10641,42 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
+        </is>
+      </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -10621,7 +10689,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
         </is>
       </c>
     </row>
@@ -10643,32 +10711,23 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
+          <t>デジタル庁は、同庁が運用する「ガバメントソリューションサービス（GSS）」が不正アクセスを受けたことを明らかにした。機器の脆弱性を突かれて侵入され、保守運用アカウントが侵害されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -10681,19 +10740,19 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://www.security-next.com/190208</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>採用管理プラットフォームに不正アクセス - きちりHD子会社 飲食店の経営を手がけるきちりホールディングス</t>
+          <t>サカイホールディングス</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -10703,17 +10762,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -10732,29 +10786,29 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132</t>
+          <t>https://www.security-next.com/188880</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>システムがランサム被害</t>
+          <t>ecurity 2026.9.11 Fri 8:05 日本スウェージロックFST にランサムウェア攻撃</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10764,13 +10818,22 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -10783,14 +10846,14 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10800,17 +10863,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>東海大学山中湖セミナーハウス</t>
+          <t>ecurity 2026.9.11 Fri 8:05 いまでやが管理する注文情報が外部流出した可能性</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -10820,12 +10883,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>3,177</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10838,41 +10901,59 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
+          <t>合計17,668件の迷惑メールを送信 立教大学</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.11 Fri 8:00 立教大学利用のGoogeアカウントに不正アクセス</t>
+        </is>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -10885,14 +10966,14 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10902,12 +10983,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>東京外環プロジェクト</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
+          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -10931,34 +11017,25 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902</t>
+          <t>https://www.security-next.com/190203</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>スパム踏み台に - 立教大 立教大学</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Googleアカウント</t>
-        </is>
-      </c>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -10969,7 +11046,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -10982,54 +11059,36 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190050</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>フィッシング対策セミナー2026</t>
-        </is>
-      </c>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6039/eCrv5d/M?S=nepdq0lcl0k オンライン参加（Webex） https://antiphishingjp.webex.com/weblink/register/r80bc37361931544860d6329aee56afaf 申</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -11042,29 +11101,29 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>スマイルサーバ</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56173;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社東邦通信システムズは8月19日、同社がサービス提供に利用している外部ホスティングサーバ環境への不正アクセスについて発表した。 これは7月31日頃から、第三者による不審な接続元から同社が利用するサーバ管理アカウントへの不正アクセスが断続的に行われ、一部のメールアカウントで設定情報が書き換えられる事態を確認したというもの。 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 「スマイルサーバ」で不正アクセスの痕跡、復旧までに長期間を要する見込み 2026.8</t>
+          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11079,17 +11138,17 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>1,360,563</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -11102,36 +11161,45 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
+          <t>飲食店の経営を手がけるきちりホールディングス</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -11144,25 +11212,34 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190132</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>システムがランサム被害</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11173,7 +11250,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -11186,14 +11263,14 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189674</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11203,17 +11280,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>被害経験なし</t>
+          <t>ecurity 2026.9.10 Thu 8:05 耳鼻咽喉科の廃棄予定の問診票を裏紙使用し患者に交付</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定されるため、一社単独ではなく、他企業・官民連携による対策が必要と感じる。」、「取引先がランサムウェア攻撃を受け、商品の出荷が停止となる影響が生じた。」などが寄せられている。 「富士山噴火による影響の懸念・事業継続への影響」について尋ねたところ、富士山噴火（広域降灰）による影響を懸念する企業が</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56186;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般社団法人グランファミリア 海老名こじろう耳鼻咽喉科は8月19日、個人情報を含む書類の不適切な取り扱いについて発表した。 同院では、保管期間を経過し廃棄予定であった過去の問診票について、本来は適切に廃棄すべきところ、その一部を印刷用紙の裏紙として使用し、その後、当該用紙の一部がプリンタ内に残ったまま通常業務に移行したことで、患者に渡す資料の裏面に、別の患者の問診票の内容が記載された状態で交付したという。 気付いた生徒が撮影拡散、生徒39名の成績一覧表を裏紙として利用 2024.2.1 Thu 8:05 大学元職員が裏紙利用のため資料持ち出し </t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11223,7 +11300,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>13,156</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -11241,34 +11318,34 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
+          <t>情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 東京科学大学</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーアプリ</t>
+          <t>ecurity 2026.9.10 Thu 8:05 東京科学大学の情報基盤に不正アクセス</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11283,12 +11360,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3,177</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11306,29 +11383,29 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>YAMAGoya</t>
+          <t>ecurity 2026.9.10 Thu 8:05 REVISIO 役職員が使用する PC がマルウェ</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56189;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 これは3月20日に、同社役職員が使用するPCでマルウェア感染および不審な挙動が確認されたため、当該PCをネットワークから遮断し、各種アカウントを停止した上で、外部専門会社によるフォレンジック調査を行ったところ、外部からのリモート接続やサーバへの不正アクセスは確認されなかったものの、当該PC内部のローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できないとの報告があったというもの。 PC端末がマルウェア感染しアカウントの認証情報が窃取、海外から継続的な不正</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11338,13 +11415,22 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -11352,50 +11438,41 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/177455</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>システムに不正アクセス</t>
-        </is>
-      </c>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -11408,14 +11485,14 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189789</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11425,17 +11502,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SonicWall SMA 100</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -11459,34 +11531,34 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/174925</t>
+          <t>https://www.security-next.com/189902</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>立教大学</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Catalyst SD-WAN Manager</t>
+          <t>Googleアカウント</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
+          <t>立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11510,36 +11582,54 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190883</t>
+          <t>https://www.security-next.com/190050</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>フィッシング対策セミナー2026</t>
+        </is>
+      </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+          <t>フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6039/eCrv5d/M?S=nepdq0lcl0k オンライン参加（Webex） https://antiphishingjp.webex.com/weblink/register/r80bc37361931544860d6329aee56afaf 申</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J217" t="n">
@@ -11552,45 +11642,54 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>流出が判明 - アンビションDX マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>サーバが侵害</t>
+          <t>ecurity 2026.9.9 Wed 8:05 東邦通信システムズが利用する外部ホスティングサーバに</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56173;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社東邦通信システムズは8月19日、同社がサービス提供に利用している外部ホスティングサーバ環境への不正アクセスについて発表した。 これは7月31日頃から、第三者による不審な接続元から同社が利用するサーバ管理アカウントへの不正アクセスが断続的に行われ、一部のメールアカウントで設定情報が書き換えられる事態を確認したというもの。 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 「スマイルサーバ」で不正アクセスの痕跡、復旧までに長期間を要する見込み 2026.8</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>1,360,563</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -11603,54 +11702,36 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56173.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Japan Vulnerability Notes（JVN）</t>
-        </is>
-      </c>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。GMOサイバーセキュリティ byイエラエ株式会社の黒須宏道氏と上田将嗣氏が報告を行っている。影響を受けるシステムは以下の通り。 PALLET CONTROL Ver. 6.3 パッチ 5 およびそれ以前 PalletControl 10 Update 8 およびそれ以前 PalletControl クラウド（PalletControl 10 Update 8）およびそれ以前 JALデジタル株式会社が提供するPALLET CONTROL製品には、バックグラウンドで動作し一定の機能を提供するサービスプログラムが複数含まれているが、サービスプログラムとの通信に適切なアクセス権限が設定されておらず、管理者権限を持たない一般ユーザによりアクセスが可能となる脆弱性（CVE-2026-81302）が存在する。 想定される影響と</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -11663,63 +11744,702 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>まんだらけ</t>
-        </is>
-      </c>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>被害経験なし</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定されるため、一社単独ではなく、他企業・官民連携による対策が必要と感じる。」、「取引先がランサムウェア攻撃を受け、商品の出荷が停止となる影響が生じた。」などが寄せられている。 「富士山噴火による影響の懸念・事業継続への影響」について尋ねたところ、富士山噴火（広域降灰）による影響を懸念する企業が</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>13,156</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーアプリ</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>YAMAGoya</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
           <t>Security NEXT</t>
         </is>
       </c>
-      <c r="J220" t="n">
-        <v>1</v>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/177455</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>システムに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/189789</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SonicWall SMA 100</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/174925</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Catalyst SD-WAN Manager</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/190883</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>SmartScope</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>サーバが侵害</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>https://www.security-next.com/188534</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Japan Vulnerability Notes（JVN）</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。GMOサイバーセキュリティ byイエラエ株式会社の黒須宏道氏と上田将嗣氏が報告を行っている。影響を受けるシステムは以下の通り。 PALLET CONTROL Ver. 6.3 パッチ 5 およびそれ以前 PalletControl 10 Update 8 およびそれ以前 PalletControl クラウド（PalletControl 10 Update 8）およびそれ以前 JALデジタル株式会社が提供するPALLET CONTROL製品には、バックグラウンドで動作し一定の機能を提供するサービスプログラムが複数含まれているが、サービスプログラムとの通信に適切なアクセス権限が設定されておらず、管理者権限を持たない一般ユーザによりアクセスが可能となる脆弱性（CVE-2026-81302）が存在する。 想定される影響と</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.7 Mon 8:05 資格情報の不正利用でシステム閲覧被害 ～ 三井不動産</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56140;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 三井不動産株式会社は9月1日、同社グループが利用する一部のシステムへの不正アクセスによる情報漏えいの可能性について発表した。 これは8月28日に、同社が利用する一部のシステムへの不正アクセスを確認したため調査したところ、同社が利用する一部のシステムに係る資格情報が不正に利用され、第三者から情報の一部を閲覧された可能性を確認したというもの。 青山財産ネットワークス グループ会社にランサムウェア攻撃、日本資産総研と日東不動産以外での影響は確認されず 2026.8.21 Fri 8:05 名鉄協商へのランサムウェア攻撃、中電不動産の顧客情報 約4,0</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 01銀行</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ecurity 2026.9.7 Mon 8:05 01銀行のシステムに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56142;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。 これは8月17日に、同行のシステムへの不正アクセスを検知し、調査した結果、顧客情報の漏えいが発生した事実を確認したというもの。 阿波銀行への不正アクセス、原因はテスト環境の「管理不備」と発表 関係役員らの処分も 2026.6.8 Mon 8:05 事態を重く受け止め「第65回 博多どんたく港まつり」への参加自粛 ～ 西日本シティ銀行 2026.5.12 Tue 8:05 メットライフ生命保険のサーバで不正に取得保管 ～ きらぼし銀行の顧客 95 名の保険契約情報が漏え</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>まんだらけ</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Security NEXT</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
         <is>
           <t>https://www.security-next.com/189663</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L220"/>
+  <autoFilter ref="A1:L232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11764,7 +12484,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
@@ -11799,7 +12519,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:37:39.428337+00:00</t>
+          <t>2026-10-07T00:39:16.369760+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L232"/>
+  <dimension ref="A1:L234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,22 +563,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日経BP</t>
+          <t>ニッポンレンタカーサービス</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ecurity 2026.10.7 Wed 8:05 日経BP従業員のメールアカウントに不正アクセス</t>
+          <t>ニッポンレンタカーアプリ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは9月30日に、同社従業員のメールアカウントに不正アクセスがあり、メール送受信先の一部の個人情報が漏えいした可能性が判明したというもの。当該従業員は、日本経済新聞社社員のメールアドレスで届いたフィッシングメールから、認証情報を入手されている。 漏えいした可能性があるのは、26件の個人情報（個人名、メールアドレス）。 同社では、個人情報漏えいが疑われるメールアドレス先の対象者に個別にメールで連絡を行っている。 同社では不正アクセスの発覚後に、当該アカウントへの接続を遮断している。 同社では引き続き、個人情報の安全を守るために最善を尽くすとのこと。 なお、株式会社日本経済新聞社は10月4日に、約9,000件のなりすましメールが送信された旨を公表している。 Fujisan.co.jp「マイページ」への不正ログイン、日経BP の雑誌書籍等の購入者も対象に 2025.7.14 Mon 8:05 日経BP従業員メールアカウントに不正アクセス、33名の個人情報流出の可能性 2024.6.14 Fri 8</t>
+          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報, 認証情報, 会員情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
         </is>
       </c>
     </row>
@@ -623,17 +623,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>日経BP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>マイクロソフト365</t>
+          <t>メールアカウントに不正アクセス</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 これは同社社員が使用していた「マイクロソフト365」のアカウントに第三者が不正にログインし、約9,000件のなりすましメールが送信されたというもの。社内の他複数の社員とやりとりがあった取材先などに対し、悪性サイトに誘導する内容のメールが9月30日送信されている。 同社では、送信先のメールアドレスや氏名の他、一部メールの内容が漏えいしたとみており、侵害を受けた範囲や漏えいした個人情報の件数を調査している。 同社では、なりすましメールの送信先に個別に連絡し、当該メールの削除を依頼している。 同社では、セキュリティ対策をさらに強化して情報管理を徹底するとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05</t>
+          <t>株式会社日経BPは10月4日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは9月30日に、同社従業員のメールアカウントに不正アクセスがあり、メール送受信先の一部の個人情報が漏えいした可能性が判明したというもの。当該従業員は、日本経済新聞社社員のメールアドレスで届いたフィッシングメールから、認証情報を入手されている。 漏えいした可能性があるのは、26件の個人情報（個人名、メールアドレス）。 同社では、個人情報漏えいが疑われるメールアドレス先の対象者に個別にメールで連絡を行っている。 同社では不正アクセスの発覚後に、当該アカウントへの接続を遮断している。 同社では引き続き、個人情報の安全を守るために最善を尽くすとのこと。 なお、株式会社日本経済新聞社は10月4日に、約9,000件のなりすましメールが送信された旨を公表している。 Fujisan.co.jp「マイページ」への不正ログイン、日経BP の雑誌書籍等の購入者も対象に 2025.7.14 Mon 8:05 日経BP従業員メールアカウントに不正アクセス、33名の個人情報流出の可能性 2024.6.14 Fri 8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>氏名, メールアドレス, クレジットカード情報</t>
+          <t>メールアドレス, クレジットカード情報, 認証情報, 会員情報</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56402.html</t>
         </is>
       </c>
     </row>
@@ -683,22 +683,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ecurity 2026.10.7 Wed 8:05 九州電子 台湾子会社にランサムウェア攻撃</t>
+          <t>マイクロソフト365</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 同社台湾子会社のMOST社では3月21日未明に、メールサーバでのウイルス感染を確認し、その後の調査でランサムウェアによる攻撃を受けたことが判明したため、被害状況と影響範囲の詳細について調査を行っていた。 九州電子ではMOST社でランサムウェア感染が確認された旨の報告を受け、初動対応としてMOST社とのネットワーク接続を遮断し、外部専門機関と連携のうえ、詳細な調査と安全確認を実施している。 九州電子で調査した結果、MOST社から九州電子への感染拡大を示す痕跡、外部からの不正アクセスや情報漏えいにつながる通信の痕跡は確認されなかった。 九州電子では予防的措置として、端末単位での隔離対応、エンドポイントセキュリティ対策の強化、認証管理およびパスワード運用の見直しなどを実施し、システム全体の安全性をあらためて確認している。 MOST社では影響調査と復旧作業を進めた結果、事業運営に必要なシステム環境の復旧を完了しており、現在は安全性を確認している。またMOST社でも、セキ</t>
+          <t>株式会社日本経済新聞社は10月4日、同社社員が使用していた「マイクロソフト365」のアカウントへのサイバー攻撃について発表した。 これは同社社員が使用していた「マイクロソフト365」のアカウントに第三者が不正にログインし、約9,000件のなりすましメールが送信されたというもの。社内の他複数の社員とやりとりがあった取材先などに対し、悪性サイトに誘導する内容のメールが9月30日送信されている。 同社では、送信先のメールアドレスや氏名の他、一部メールの内容が漏えいしたとみており、侵害を受けた範囲や漏えいした個人情報の件数を調査している。 同社では、なりすましメールの送信先に個別に連絡し、当該メールの削除を依頼している。 同社では、セキュリティ対策をさらに強化して情報管理を徹底するとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>氏名, メールアドレス, クレジットカード情報</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56401.html</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ecurity 2026.10.7 Wed 8:05 なりすましメールで取引先に金銭的な被害も ～ 小田</t>
+          <t>システム環境の復旧を完了 九州電子株式会社は9月15日</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 これは8月31日に、当該従業員のメールアカウントで第三者からの不正アクセスの痕跡を確認したというもの。調査の結果、2026年3月27日から8月31日までの間、当該アカウントに第三者が継続的にアクセスし、メールを閲覧していたことが判明している。 漏えいした可能性があるのは、当該従業員1名と取引先担当者との間で送受信されたメールの内容が対象で、2026年3月27日から8月31日までの時点でメールボックス内に保存されていた過去のメールも閲覧の対象となる。現時点で閲覧を確認できているのは約3,500通で、最も古いもので2018年に送受信されたメールが含まれる。 同社によると、不正アクセスを行った第三者が同社従業員になりすまし、取引先宛てに入金を指示するメールを送信していたことが判明している。当該第三者は正規のやり取りを閲覧していたとみられ、一部の取引先で金銭的な被害が生じている。 同社では当該</t>
+          <t>九州電子株式会社は9月15日、3月23日に公表した同社台湾子会社での情報セキュリティインシデントについて、最終報を発表した。 同社台湾子会社のMOST社では3月21日未明に、メールサーバでのウイルス感染を確認し、その後の調査でランサムウェアによる攻撃を受けたことが判明したため、被害状況と影響範囲の詳細について調査を行っていた。 九州電子ではMOST社でランサムウェア感染が確認された旨の報告を受け、初動対応としてMOST社とのネットワーク接続を遮断し、外部専門機関と連携のうえ、詳細な調査と安全確認を実施している。 九州電子で調査した結果、MOST社から九州電子への感染拡大を示す痕跡、外部からの不正アクセスや情報漏えいにつながる通信の痕跡は確認されなかった。 九州電子では予防的措置として、端末単位での隔離対応、エンドポイントセキュリティ対策の強化、認証管理およびパスワード運用の見直しなどを実施し、システム全体の安全性をあらためて確認している。 MOST社では影響調査と復旧作業を進めた結果、事業運営に必要なシステム環境の復旧を完了しており、現在は安全性を確認している。またMOST社でも、セキ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56141.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56160.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56158.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56171.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56220.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56229.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56300.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56299.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56315.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56363.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56385.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56405.html</t>
         </is>
       </c>
     </row>
@@ -803,22 +803,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>シンカ</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>カイクラサービス紹介サイト</t>
+          <t>メールで取引先に金銭的な被害も ～ 小田原エンジニアリング従業員のメールアカウントに不正アクセス 株式会社</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 同社では8月24日に、「カイクラサービス紹介サイト」（ https://kaiwa.cloud/ ）で複数の不正プログラムの設置を検知し、社内調査による分析の結果、不正プログラムのうち1件は、当該サイトが設置されているサーバからの情報取得を技術的に可能にするものと判明したため、リスク拡大を回避し、調査を行うため、当該サイトおよび同一サーバで運用していた下記3サイトを含め、アクセスを一時停止するとともに、外部の専門機関に依頼し、ログ解析等を通じた精査を開始していた。 コーポレートサイト：https://www.thinca.co.jp カイクラサービス紹介サイト：https://kaiwa.cloud/ カイクラ.mag：https://kaiwa.cloud/media/ Car Connect：https://carconnect.jp/ 外部専門調査機関による調査の結果、検出された不正プログラムが実行され、サーバ内のデータを外部に送信した形跡は確認されなかった</t>
+          <t>株式会社小田原エンジニアリングは9月15日、子会社であるOdawara Automation Deutschland GmbHに出向していた同社従業員のメールアカウントへの不正アクセスについて発表した。 これは8月31日に、当該従業員のメールアカウントで第三者からの不正アクセスの痕跡を確認したというもの。調査の結果、2026年3月27日から8月31日までの間、当該アカウントに第三者が継続的にアクセスし、メールを閲覧していたことが判明している。 漏えいした可能性があるのは、当該従業員1名と取引先担当者との間で送受信されたメールの内容が対象で、2026年3月27日から8月31日までの時点でメールボックス内に保存されていた過去のメールも閲覧の対象となる。現時点で閲覧を確認できているのは約3,500通で、最も古いもので2018年に送受信されたメールが含まれる。 同社によると、不正アクセスを行った第三者が同社従業員になりすまし、取引先宛てに入金を指示するメールを送信していたことが判明している。当該第三者は正規のやり取りを閲覧していたとみられ、一部の取引先で金銭的な被害が生じている。 同社では当該</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56404.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56205.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56400.html</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>国家公務員共済組合連合会</t>
+          <t>シンカ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ecurity 2026.10.7 Wed 8:05 KKR京都くに荘のメールサーバに不正アクセス 国家</t>
+          <t>カイクラサービス紹介サイト</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 同会では8月25日に、KKR京都くに荘のメールサーバへの不正アクセスに伴う個人情報漏えいの可能性について公表していたが、その後、メールシステム運用事業者及び外部専門事業者による詳細な調査を実施した結果、第三者からの当該メールアカウントのメールボックスへのアクセスやメールの閲覧を示す記録は確認されず、現時点で、顧客の個人情報が漏えいした事実は確認されなかったという。 同会では、メールシステムのセキュリティ対策の強化を図るとともに、顧客の個人情報の適切な管理に努め、再発防止に取り組むとのこと。 実行犯が示唆したダークウェブでの情報公開は確認されず ～ ワシントンホテルにランサムウェア攻撃 2026.9.25 Fri 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 2026.9.16 Wed 8:05 Booking.com経由でホテルグランバッハ京都セレクトを予約した顧客にフィッシングサイト誘導メッセージ、注意を呼びかけ 2026.6</t>
+          <t>株式会社シンカは9月17日、8月28日に公表した同社運営のサービス紹介サイトへの不正アクセスについて、調査結果を発表した。 同社では8月24日に、「カイクラサービス紹介サイト」（ https://kaiwa.cloud/ ）で複数の不正プログラムの設置を検知し、社内調査による分析の結果、不正プログラムのうち1件は、当該サイトが設置されているサーバからの情報取得を技術的に可能にするものと判明したため、リスク拡大を回避し、調査を行うため、当該サイトおよび同一サーバで運用していた下記3サイトを含め、アクセスを一時停止するとともに、外部の専門機関に依頼し、ログ解析等を通じた精査を開始していた。 コーポレートサイト：https://www.thinca.co.jp カイクラサービス紹介サイト：https://kaiwa.cloud/ カイクラ.mag：https://kaiwa.cloud/media/ Car Connect：https://carconnect.jp/ 外部専門調査機関による調査の結果、検出された不正プログラムが実行され、サーバ内のデータを外部に送信した形跡は確認されなかった</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -911,25 +911,29 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56288.html / https://scan.netsecurity.ne.jp/article/2026/10/07/56404.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ニモカ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>国家公務員共済組合連合会</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>メールサーバに不正アクセス 国家公務員共済組合連合会は9月16日</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
+          <t>国家公務員共済組合連合会は9月16日、KKR京都くに荘のメールサーバへの不正アクセスについて発表した。 同会では8月25日に、KKR京都くに荘のメールサーバへの不正アクセスに伴う個人情報漏えいの可能性について公表していたが、その後、メールシステム運用事業者及び外部専門事業者による詳細な調査を実施した結果、第三者からの当該メールアカウントのメールボックスへのアクセスやメールの閲覧を示す記録は確認されず、現時点で、顧客の個人情報が漏えいした事実は確認されなかったという。 同会では、メールシステムのセキュリティ対策の強化を図るとともに、顧客の個人情報の適切な管理に努め、再発防止に取り組むとのこと。 実行犯が示唆したダークウェブでの情報公開は確認されず ～ ワシントンホテルにランサムウェア攻撃 2026.9.25 Fri 8:05 ホテル白菊が利用する宿泊予約・販売管理システムに不正アクセス、フィッシングメール送信を確認 2026.9.16 Wed 8:05 Booking.com経由でホテルグランバッハ京都セレクトを予約した顧客にフィッシングサイト誘導メッセージ、注意を呼びかけ 2026.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -939,22 +943,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -962,12 +966,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56406.html</t>
         </is>
       </c>
     </row>
@@ -979,42 +983,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AI トークン乗っ取り</t>
-        </is>
-      </c>
+          <t>ニモカ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4月、あるソフトウェアアーキテクトが AI プロバイダーからの請求書を開き、二度見しました。 彼が承認した覚えのない利用に対して、25,000 ドルが請求 されていたのです。別の組織の請求額は、 詐欺が発見され抑止されるまでに100万ドル近く に達しました。犯罪者が AI アカウントの制御を獲得し、盗んだアクセス権を転売して利益を得るために「AI トークン乗っ取り」のような新しい手口に転じる中、このような事例は増加傾向にあります。 AI への需要は急上昇しており、誰もが最も能力の高いフロンティアモデルへのアクセスを求めています。しかし、請求が届き、ユーザーが上昇するトークンコストに直面するにつれ、AI へのアクセス料を支払うのではなく盗むという動機が、 AI のコスト 上昇とまさに並行して高まっています。 この摩擦が、急成長する違法市場を生み出しました。脅威アクターが介入し、標準的なサブスクリプション価格から時には 70%～ 90% オフという大幅な割引で AI アクセスを提供しています。しかし、彼らは一体どのようにそれを行っているのでしょうか？ Okta 脅威インテリジェンスチームは</t>
+          <t>西鉄系のニモカ、不正アクセスで約500件の顧客情報流出 - 日本経済新聞</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>氏名, 電話番号, メールアドレス, 認証情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBFVXhLcklFc0thaTBzY1RfNUx6bGVkWGdhZ0xKY0dDZ2tFYVVUOVFVX245UEFNZGo1YjZOV2RaNGRwekkwRmM5OE9MUWdsMEgzTjFxRmpjTWREZ3VDSFY4aWk2QnhZbnhBaklCYQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1039,29 +1039,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>旭化成</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AI トークン乗っ取り</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
+          <t>4月、あるソフトウェアアーキテクトが AI プロバイダーからの請求書を開き、二度見しました。 彼が承認した覚えのない利用に対して、25,000 ドルが請求 されていたのです。別の組織の請求額は、 詐欺が発見され抑止されるまでに100万ドル近く に達しました。犯罪者が AI アカウントの制御を獲得し、盗んだアクセス権を転売して利益を得るために「AI トークン乗っ取り」のような新しい手口に転じる中、このような事例は増加傾向にあります。 AI への需要は急上昇しており、誰もが最も能力の高いフロンティアモデルへのアクセスを求めています。しかし、請求が届き、ユーザーが上昇するトークンコストに直面するにつれ、AI へのアクセス料を支払うのではなく盗むという動機が、 AI のコスト 上昇とまさに並行して高まっています。 この摩擦が、急成長する違法市場を生み出しました。脅威アクターが介入し、標準的なサブスクリプション価格から時には 70%～ 90% オフという大幅な割引で AI アクセスを提供しています。しかし、彼らは一体どのようにそれを行っているのでしょうか？ Okta 脅威インテリジェンスチームは</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>55万</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, 認証情報</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1074,7 +1087,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56396.html</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1105,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
+          <t>旭化成系、最大55万人の情報漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1102,7 +1115,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>56万</t>
+          <t>55万</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1121,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2dhS3FkTW9td2xNcU1nbXpPSTBMV2ZFOVpTa2t0QjlSV1hkeFZKS21kcjltNnQwV0N4WmZHLW14TGpIZVJvT0VQRlZKMy1JSGxOSDB5aTVlbzhuUFYtUHlDRVlOQk9uQUxmU2pqUk5lVG9lNEpXR3l1VFB6WV9yWWV0SFhVaXdHZXJYcXBKeWxVdHfSAZMBQVVfeXFMTVdnYUtxZE1vbXdsTXFNZ216T0kwTFdmRTlaU2trdEI5UldYZHhWSkttZHI5bTZ0MFdDeFpmRy1teExqSGVSb09FUEZWSjMtSUhsTkgweWk1ZW84blBWLVB5Q0VZTkJPbkFMZlNqalJOZVRvZTRKV0d5dVRQellfcllldEhYVWl3R2VyWHFwSnlsVXR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1133,23 +1146,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日経BP</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>旭化成系、医療従事者向けサイトで情報漏洩か 最大約56万人 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>56万</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1168,7 +1181,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5tVXhMYWxuZ2QtYi1oYXAwWElUWGpIa2toamZFUy1oVW8wSFd1WHQ1Um1FNlAzeVZBRjE1S0VvOXNJNkJSUW1MYVVUeUhHUVozSEtBYjFlVGF6SHppRlpTRU9oN1JoNUpyUVotdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1180,23 +1193,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>日経BP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
+          <t>日経BP、メールアカウントへの不正アクセスにより個人情報漏えいの疑い。日経新聞社への攻撃が影響 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1215,7 +1228,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNZjNrWnZFd3NoSmxsZ19EYUtuZGJCS2EzMU54MVFsUzlXSm5qbDZhNktlM2dSWWhySHcyeWRmc2xLTGJpczJoUG9QMDNfR19FN21mRHNPcEZfcFVnOTJiU2MzRW5QTjEyNklTbmNuWHBBN0JZVzNJZ1IyMGpmaUlkblpvVmRfdzNzZFpuUFdqbWvSAZABQVVfeXFMTWYza1p2RXdzaEpsbGdfRGFLbmRiQkthMzFOeDFRbFM5V0puamw2YTZLZTNnUllockh3MnlkZnNsS0xiaXMyaFBvUDAzX0dfRTdtZkRzT3BGX3BVZzkyYlNjM0VuUE4xMjZJU25jblhwQTdCWVczSWdSMjBqZmlJZG5ab1ZkX3czc2RablBXam1r?oc=5</t>
         </is>
       </c>
     </row>
@@ -1227,22 +1240,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>メール - 日経</t>
-        </is>
-      </c>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 ：Security NEXT</t>
+          <t>日本交通、電話配車と陣痛タクシーWeb登録を10月6日再開へ-不正アクセスから約3カ月 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1253,7 +1262,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1266,7 +1275,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191072</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPT2ZNdldPSUlMWWNiclFETGtGcEZwcXI5dXpXUlpoMXJmWHVvVTVVV1ZFMHB4UnFJVXdmeEhqSlljcUNONS10WXVybWF4aktEMThtYnZiUkdnMThUaU5EQmhGcDRjbnNOUG5YTzYxVlozektQbHJQdm5Ra2dTNlRQeGN6ckd5LUdvXzdHR0xBVmZtejZxWEpvT1h3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1278,27 +1287,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>大和証券</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>問い合わせ顧客の情報が流出か - 大和証券</t>
+          <t>メール - 日経</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>日本経済新聞社は、従業員が利用していた「Microsoft 365」のアカウントがサイバー攻撃を受けたことを明らかにした。大量のなりすましメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1317,7 +1326,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191068</t>
+          <t>https://www.security-next.com/191072</t>
         </is>
       </c>
     </row>
@@ -1329,13 +1338,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ミスターマックス</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>大和証券</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>問い合わせ顧客の情報が流出か - 大和証券</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
+          <t>大和証券は、同社に問い合わせを行った顧客の個人情報が外部に流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1345,18 +1358,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>173万</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1369,7 +1377,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
+          <t>https://www.security-next.com/191068</t>
         </is>
       </c>
     </row>
@@ -1386,17 +1394,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan Vulnerability Notes（JVN）</t>
+          <t>システムへの不正アクセスについて</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 The Apache Software Foundationでは、Apache HTTP Server 2.4系における複数の脆弱性に対応したApache HTTP Server 2.4.69を現地時間10月1日に公開している。 JVNでは、影響を受けるシステム、想定される影響、対策方法についてはApache HTTP Serverのアドバイザリを参照するよう案内している。 Fixed in Apache HTTP Server 2.4.69 https://httpd.apache.org/security/vulnerabilities_24.html#2.4.69 Apache HTTP Server 2.4 に複数の脆弱性 2026.6.11 Thu 8:00 Apache HTTP Server 2</t>
+          <t>株式会社ムラウチドットコムは9月15日、7月24日に公表した同社が運用する一部システムへの不正アクセスについて、第二報を発表した。 同社では7月15日未明に、社内システムで障害が発生し、翌7月16日の復旧作業中に第三者からの不正アクセスの痕跡を確認したため、システム保全として外部アクセスを遮断し、外部の情報セキュリティ専門会社によるフォレンジック調査を実施し、侵入経路や影響範囲の特定を進めていた。 調査結果によると、同社が管理するWebシステムの一部に存在していた脆弱性を悪用されたことを起点とした不正アクセスがあり、その後、複数のシステムへの不正アクセスが判明している。また、同社が保有する顧客の個人情報の一部が外部に持ち出されたことを確認している。 不正アクセスによる漏えいが確認されたのは7,716,811件の個人情報（氏名、住所、電話番号、メールアドレス、生年月日、性別）。 同社では9月15日から、対象となる顧客に個別に通知メールの送信を開始している。 同社では、システムへのアクセス権限および認証情報の管理方法の見直し、サーバ・ネットワークの監視および不正アクセスの検知体制の強化等に</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1411,7 +1419,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1429,7 +1437,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56145.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56155.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html</t>
         </is>
       </c>
     </row>
@@ -1441,13 +1449,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>シチズン時計</t>
+          <t>ミスターマックス</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
+          <t>ミスターマックスのアプリ MrMax アプリとオンラインストアへ不正アクセスによるサイバー攻撃-最大約173万件の個人情報漏洩 - 合同会社ロケットボーイズ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1457,12 +1465,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10万</t>
+          <t>173万</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1476,12 +1484,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOOEhaMmt3NW1GYWhvSlpQUEF4R1c0aXg4cGJtZ0E4Y3dHMzF3T1J5NUkxYVkwbC1Cc0VtbGQwcGNTMUJEZ3I5eC11bzFZekEyNjlVUGJudmFMN3JncGFPellNV0tsb3NWS1BiNzVBSXdCajlSbDJiYUxhTnQ0cHdGNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1501,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ecurity 2026.10.6 Tue 8:05 ムラウチドットコムに不正アクセス</t>
-        </is>
-      </c>
+          <t>シチズン時計</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>株式会社ムラウチドットコムは9月15日、7月24日に公表した同社が運用する一部システムへの不正アクセスについて、第二報を発表した。 同社では7月15日未明に、社内システムで障害が発生し、翌7月16日の復旧作業中に第三者からの不正アクセスの痕跡を確認したため、システム保全として外部アクセスを遮断し、外部の情報セキュリティ専門会社によるフォレンジック調査を実施し、侵入経路や影響範囲の特定を進めていた。 調査結果によると、同社が管理するWebシステムの一部に存在していた脆弱性を悪用されたことを起点とした不正アクセスがあり、その後、複数のシステムへの不正アクセスが判明している。また、同社が保有する顧客の個人情報の一部が外部に持ち出されたことを確認している。 不正アクセスによる漏えいが確認されたのは7,716,811件の個人情報（氏名、住所、電話番号、メールアドレス、生年月日、性別）。 同社では9月15日から、対象となる顧客に個別に通知メールの送信を開始している。 同社では、システムへのアクセス権限および認証情報の管理方法の見直し、サーバ・ネットワークの監視および不正アクセスの検知体制の強化等に</t>
+          <t>シチズン時計、委託先システムへの不正アクセスにより約10万人の個人情報漏えいの可能性 - 東京報道新聞</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1518,17 +1522,13 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>10万</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56391.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56152.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56232.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56243.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56255.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56292.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56293.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56304.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56303.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56331.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56333.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56329.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56342.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56357.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56360.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56371.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56374.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56375.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56377.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56382.html</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqSjZaUkdrNWdFY0JmcmFmbkgyczNtNjhLUm9BWmUwSFpmeFNQc1RBNG5CMVkwVFQ4aHRMS2VtWmczMFlKMTFFOW9adzFqUmFHbUNyMHdSSWZXajlQYlE2VVZUTDFMUXVwckpDRldIONIBdEFVX3lxTFBWLWR2YmUxMXdaLWpOZThrXzNpNFR0OHE5Mk54TV85a2RnQUotVXNLNXFwck5nTnAxU0RPdXp1TzYtM0Q4YmJfUWxmQTNOZnE2MDAteG1BMndPMHdkS252dXBPWVRmMzB6NlNDQ3B1Y0tQQWZW?oc=5 / https://news.google.com/rss/articles/CBMiU0FVX3lxTE9NTmI2bm5FYUR2ZUZzcUhlb3FkT1VRWmtBb01IbUhsbjk5dnUzOHFWOTZEUVRSUVpIcnFITnU5YVFxRE1zc2JaTWhVaC1kUTJIOEtv?oc=5</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>信濃毎日新聞</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>信濃毎日新聞デジタル</t>
+          <t>アプリシステムが侵害</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 これは9月7日に、「信濃毎日新聞デジタル」の信毎ポイント交換システムへの外部からの不正アクセスが判明したというもので、一時的に一部の履歴データが消去される事象が発生していた。 同社で調査した結果、現時点で個人情報の流出は確認されていないという。 同社では、該当システムに修正措置を講じ、データの復旧も完了している。また、顧客が保有しているポイント数への影響はない。 同社では今後、より一層の安全管理とセキュリティ強化に努めるとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 3 日間で約 2 万件の ID でログイン「毎日新聞デジタル</t>
+          <t>回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が不正アクセスを受け、顧客の個人情報が流出した可能性があることを明らかにした。アプリは通常通り利用できる。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1576,19 +1576,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>7,368</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1601,7 +1596,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
+          <t>https://www.security-next.com/191070</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1608,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ベネフィット・ワン</t>
+          <t>信濃毎日新聞</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ベネワン・プラットフォーム</t>
+          <t>信濃毎日新聞デジタル</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 これは「ベネワン・プラットフォーム」のアンケート機能にて、担当者がアンケート結果をダウンロードした際、本来アクセスできない他企業・団体の従業員の個人情報の一部が表示される状態となっていたというもの。同社サービスを利用している企業・団体の担当者1社1名から7月30日に連絡があり、発覚した。 対象となるのは2,322企業・団体の13,460名の個人情報（社員・職員番号、氏名、性別、生年月日、企業・団体名、所属/役職、入退社情報）.。 同社では当該データについて、利用企業・団体の担当者に連絡し、第三者への転送、複製その他の提供は行われておらず、同社への連絡後にデータを削除したことを確認している。 同社で調査した結果、2025年6月に行ったシステム改修により発生していた、アンケート結果ダウンロード機能におけるプログラムの条件設定不備が原因と確認している。また、2025年10月に行った社内調査で本不具合を認知していたものの、</t>
+          <t>信濃毎日新聞株式会社は9月28日、「信濃毎日新聞デジタル」への不正アクセスについて発表した。 これは9月7日に、「信濃毎日新聞デジタル」の信毎ポイント交換システムへの外部からの不正アクセスが判明したというもので、一時的に一部の履歴データが消去される事象が発生していた。 同社で調査した結果、現時点で個人情報の流出は確認されていないという。 同社では、該当システムに修正措置を講じ、データの復旧も完了している。また、顧客が保有しているポイント数への影響はない。 同社では今後、より一層の安全管理とセキュリティ強化に努めるとのこと。 日経アメリカ社で不正ログイン被害、取引先へのなりすましメール送信で発覚 2026.5.14 Thu 8:05 取材に関する情報漏えいは確認されず ～ 日本経済新聞社が利用する「Slack」に不正ログイン、社員や取引先など 1 万 7,368 人分の情報が流出した可能性 2025.11.7 Fri 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 3 日間で約 2 万件の ID でログイン「毎日新聞デジタル</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1638,12 +1633,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,368</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>氏名, 生年月日, クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56393.html</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1668,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>大興印刷</t>
+          <t>ベネフィット・ワン</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PhotoGoods</t>
+          <t>ベネワン・プラットフォーム</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 これは9月11日に、「PhotoGoods」内に不審な外部プログラムが読み込まれているとの連絡があり、システム管理会社による調査を行った結果、決済画面等に入力されたクレジットカード情報などを不正に取得する機能を持つプログラムの設置を確認したというもの。あわせてシステム上の脆弱性およびファイルアップロード機能の悪用による第三者からの不正アクセスも確認している。 「PhotoGoods」を利用した顧客下記の情報が漏えいした可能性がある。なお、クレジットカード情報については、不正プログラムが稼働していた2026年8月6日から9月11日までの期間に、「PhotoGoods」の決済画面にカード情報を入力した顧客が対象となる。 ・クレジットカード情報（カード番号、有効期限、セキュリティコード） ・個人情報（氏名、住所、電話番号、メールアドレス） ・会員パスワードに関する情報（元のパスワードを直接読み取ることがで</t>
+          <t>株式会社ベネフィット・ワンは9月30日、同社が提供する福利厚生サービスの企業・団体の担当者向けの機能である「ベネワン・プラットフォーム」での個人情報漏えいについて発表した。 これは「ベネワン・プラットフォーム」のアンケート機能にて、担当者がアンケート結果をダウンロードした際、本来アクセスできない他企業・団体の従業員の個人情報の一部が表示される状態となっていたというもの。同社サービスを利用している企業・団体の担当者1社1名から7月30日に連絡があり、発覚した。 対象となるのは2,322企業・団体の13,460名の個人情報（社員・職員番号、氏名、性別、生年月日、企業・団体名、所属/役職、入退社情報）.。 同社では当該データについて、利用企業・団体の担当者に連絡し、第三者への転送、複製その他の提供は行われておらず、同社への連絡後にデータを削除したことを確認している。 同社で調査した結果、2025年6月に行ったシステム改修により発生していた、アンケート結果ダウンロード機能におけるプログラムの条件設定不備が原因と確認している。また、2025年10月に行った社内調査で本不具合を認知していたものの、</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1703,25 +1698,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
+          <t>氏名, 生年月日, クレジットカード情報</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Security NEXT / ScanNetSecurity</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/06/56394.html</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1728,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大起水産</t>
+          <t>大興印刷</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>アプリシステムが侵害</t>
+          <t>PhotoGoods</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>回転ずしチェーンなどを展開する大起水産は、「大起水産公式アプリ」が不正アクセスを受け、顧客の個人情報が流出した可能性があることを明らかにした。アプリは通常通り利用できる。 ：Security NEXT</t>
+          <t>大興印刷株式会社は9月16日、同社が運営するインターネットサービス「PhotoGoods（photo-goods.com）」への不正アクセスによる個人情報等漏えいの可能性について発表した。 これは9月11日に、「PhotoGoods」内に不審な外部プログラムが読み込まれているとの連絡があり、システム管理会社による調査を行った結果、決済画面等に入力されたクレジットカード情報などを不正に取得する機能を持つプログラムの設置を確認したというもの。あわせてシステム上の脆弱性およびファイルアップロード機能の悪用による第三者からの不正アクセスも確認している。 「PhotoGoods」を利用した顧客下記の情報が漏えいした可能性がある。なお、クレジットカード情報については、不正プログラムが稼働していた2026年8月6日から9月11日までの期間に、「PhotoGoods」の決済画面にカード情報を入力した顧客が対象となる。 ・クレジットカード情報（カード番号、有効期限、セキュリティコード） ・個人情報（氏名、住所、電話番号、メールアドレス） ・会員パスワードに関する情報（元のパスワードを直接読み取ることがで</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1756,27 +1751,32 @@
           <t>可能性あり</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>顧客情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/191070</t>
+          <t>https://www.security-next.com/190511 / https://scan.netsecurity.ne.jp/article/2026/10/06/56392.html</t>
         </is>
       </c>
     </row>
@@ -1872,34 +1872,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Japan Vulnerability Notes（JVN）</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は10月2日、Apache HTTP Server 2.4における複数の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。 The Apache Software Foundationでは、Apache HTTP Server 2.4系における複数の脆弱性に対応したApache HTTP Server 2.4.69を現地時間10月1日に公開している。 JVNでは、影響を受けるシステム、想定される影響、対策方法についてはApache HTTP Serverのアドバイザリを参照するよう案内している。 Fixed in Apache HTTP Server 2.4.69 https://httpd.apache.org/security/vulnerabilities_24.html#2.4.69 Apache HTTP Server 2.4 に複数の脆弱性 2026.6.11 Thu 8:00 Apache HTTP Server 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>95万</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1907,12 +1915,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56135.html / https://scan.netsecurity.ne.jp/article/2026/09/09/56170.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56188.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56202.html / https://scan.netsecurity.ne.jp/article/2026/09/11/56204.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56215.html / https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56240.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56242.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56254.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56267.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56264.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56268.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56265.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56278.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56276.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56277.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56291.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56302.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56309.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56310.html / https://scan.netsecurity.ne.jp/article/2026/09/28/56314.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56322.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56327.html / https://scan.netsecurity.ne.jp/article/2026/09/29/56328.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56355.html / https://scan.netsecurity.ne.jp/article/2026/10/01/56364.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56367.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56366.html / https://scan.netsecurity.ne.jp/article/2026/10/02/56369.html / https://scan.netsecurity.ne.jp/article/2026/10/06/56388.html</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1938,22 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
+          <t>GMO系に不正アクセス、個人情報95万人分漏洩 ポイント不正利用も - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>95万</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1954,7 +1972,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaTW1ldnRrSnNzVE1weWdfa3NFT0c3U0hka21QSWlPcUdGN1ZxblV3Ynh3VG1WamZWelFUeDFTeDJuLThXdkhYMG1zRkp3UGc1bzRUa3ZiVEVfR0JjMnN2blhRZWpBRWtzbVM1cA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1966,13 +1984,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
+          <t>GMO、焼肉きんぐ、大和証券…サイバー攻撃止まらず 麻生幾氏が重大警告 - zakⅡ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1983,7 +2001,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1996,7 +2014,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE02NmRabnlReVpyMzJsLVRoX2o0U29FWXhLZXJnWUNhdDdHNTRjNFRlLTdUOFlEd3dVZGZsYlhLZnAxbnpmZkh6dXJKTGM4aTVrZEtaV2UtVFprZWlhNFdYTnRDQWN2SnNHcy1KVm4zdmFYTkY1YnZkMNIBjAFBVV95cUxQTkV5SjBVUXVHVHJieUZXUlJDRlpsMzFkc3gtQmJjSjhxYUFfaGtMeG1qVFFkV1lfQTlyU0plVU1veE5GQU5vajdYVTZ2SHBXdGlGQ2ZhdVdYNVE3d0U5UHRsWUhhODNUbnlDSlJYZzNhNzhRSklMMnF1bDRPRWRkbVI0WGRMcDF5M1IzMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2008,38 +2026,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>i-ask</t>
-        </is>
-      </c>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ（東京都渋谷区／FAQ・問い合わせ管理システム「i-ask」を提供）のサーバが不正アクセスを受け、同システムを導入していた最大5社・延べ最大713,126件の問い合わせ情報が漏えいした可能性があると公表した。第三者が2026年10月2日20時33分頃から10月3日8時1分頃にかけて「i-ask」の管理サイトへ不正にログインし、サーバに不正なプログラムを設置していた。スカラコミュニケーションズは10月3日朝にアクセスを遮断し、同日中に利用企業へ報告している。利用企業の一部は個別に対象件数を公表しているが、全5社の内訳は明らかにされていない。公表時点で二次被害は確認されていない。</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Citizen Watch (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of contractor Scala Communications, provider of the inquiry-form system, from about 20:33 on Oct 2 to about 08:01 on Oct 3. No unauthorized access to Citizen's own systems confirmed. Citizen's notice does not state the entry route (Scala says an unauthorized login to the i-ask admin site).</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>713,126</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2052,14 +2056,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-scala-communications-i-ask-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2069,12 +2073,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス</t>
+          <t>i-ask</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>株式会社スカラ（東証）は2026年10月6日、連結子会社の株式会社スカラコミュニケーションズ（東京都渋谷区／FAQ・問い合わせ管理システム「i-ask」を提供）のサーバが不正アクセスを受け、同システムを導入していた最大5社・延べ最大713,126件の問い合わせ情報が漏えいした可能性があると公表した。第三者が2026年10月2日20時33分頃から10月3日8時1分頃にかけて「i-ask」の管理サイトへ不正にログインし、サーバに不正なプログラムを設置していた。スカラコミュニケーションズは10月3日朝にアクセスを遮断し、同日中に利用企業へ報告している。利用企業の一部は個別に対象件数を公表しているが、全5社の内訳は明らかにされていない。公表時点で二次被害は確認されていない。</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2085,12 +2089,17 @@
       <c r="F31" t="inlineStr">
         <is>
           <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>713,126</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2103,7 +2112,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190961</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-scala-communications-i-ask-breach/</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2124,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>サイトに不正アクセス</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
+          <t>ベネッセコーポレーションのグループ会社で総合教育サービスを提供するアップは、運営する2サイトが不正アクセスを受け、採用応募者などの個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2131,13 +2144,13 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2150,7 +2163,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
+          <t>https://www.security-next.com/190961</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2181,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+          <t>物語コーポレーション[3097]：当社『焼肉きんぐ』公式アプリ会員管理システムへの第三者からの不正アクセスによる個人情報漏えいに関するお知らせ 2026年10月5日(適時開示) ：日経会社情報DIGITAL - 日本経済新聞</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2181,16 +2194,7 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>会員情報</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2201,12 +2205,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1kMmdvc2RJa2FJaUVycUdwVlNvcnVKcGFLNXYzeU8wNFJ5dnBKcnhnX3BtZTVxLWllekdzZDk0b2JRbEhLd2ZHUHZINVh0V3E4eW9rM2RpTVcyVndFTWp0Y2hVT3l4Q2dLR3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -2218,13 +2222,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
+          <t>焼肉きんぐ、ほぼ全会員の個人情報1000万件超が流出 第三者の不正アクセスで - ｄメニューニュース</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2234,10 +2243,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>1000万</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2253,7 +2266,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xedIBgAFBVV95cUxQc3RlVWY5RFJETVMxUmFjRUxoUUtsZ3NQa0RiZ2VTT18tcjIxZHZ6M0xXT1pKcFJOZVVxQVBMQktrd3Utby03MzVxYXEzMVVaZ19DNnIzaVlZNDlhcVhseUZmcktNMUMyWWZhOG9LaWtYTENnc3k1eGc4MEZOUW1xeQ?oc=5 / https://news.google.com/rss/articles/CBMiggFBVV95cUxPODFrNThTbE1YcTh2bkxWMXpOaUJqMjJDTm9uZml6bzZVeVBDVkdmOWwxM0ZxaERMcjhDSFBRWjc2X29iVkRuTFBwX2dfTWw1MldFNkRRcXlnSlhCblAxY1dQd3FSQVRiQlQzbFpnTzhGRUx6cGN6WkRyZGtfWmpkVmxB0gGCAUFVX3lxTE84MWs1OFNsTVhxOHZuTFYxek5pQmoyMkNOb25maXpvNlV5UENWR2Y5bDEzRnFoRExyOENIUFFaNzZfb2JWRG5MUHBfZ19NbDUyV0U2RFFxeWdKWEJuUDFjV1B3cVJBVGJCVDNsWmdPOEZFTHpwY3paRHJka19aamRWbEE?oc=5 / https://news.google.com/rss/articles/CBMihwFBVV95cUxOS3FkRjF3UEJwcHFSejA1SHEtUWd3bjRfNHVBTlRKZ1VSYlVMYjZrT0hHZzRBbkJGM1h0X0tIbFMwSUh1aElTSkViWVQ4Z1FlVjVrZzJCMUpZcjZCYy1CYm1Rd1AySGpDclgwclpKTUtMQjByXy1EOV9GQl9fVDg5c0M3UHhuNWvSAYcBQVVfeXFMTktxZEYxd1BCcHBxUnowNUhxLVFnd240XzR1QU5USmdVUmJVTGI2a09IR2c0QW5CRjNYdF9LSGxTMElIdWhJU0pFYllUOGdRZVY1a2cyQjFKWXI2QmMtQmJtUXdQMkhqQ3JYMHJaSk1LTEIwcl8tRDlfRkJfX1Q4OXNDN1B4bjVr?oc=5 / https://news.google.com/rss/articles/CBMisAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRtIBsAFBVV95cUxQcUc4aFRUdEdWUUlqbkZSbm9ISWY3bnBuM1h5MGVXanhjc1VJRVQtV2xRdk53R2ZTSWxXREpBOFBJeGZ2N1NYbEJkSjV6TWpHdUdWWUU4TzhOU1M2d2NrWXQtTF80SHJsT3gzVmRBcFFJbXVaZk5SVmNEZmFSbVBEQkVfTVN6eFRnSFh4Vmt5NmZia1dhMUNydFNoYW55dDFESy1DN3Zpc05hNmpOX2JjRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2265,34 +2278,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>佐賀大学</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>サーバ内の一部ファイルが暗号化 池上通信機株式会社は9月30日</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
+          <t>池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:05 教育ソフトウェアの休眠中のレンタルサーバにランサムウェア攻撃、暗号化被害と不正アクセスの痕跡を確認 2026.9.8 Tue 8:05 サンコーテクノのベトナム子会社にランサムウェア攻撃、サーバ及びパソコン内の各種ファイルの暗号化を</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2300,12 +2321,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
         </is>
       </c>
     </row>
@@ -2317,13 +2338,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>日本交通</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>公式サイトにwp2shell を悪用した不正アクセス 株式会社東産業は9月14日</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
+          <t xml:space="preserve">株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri 8:00 WordPress の深刻度「緊急」脆弱性「wp2shell 」の概要と対応指針 ～ GMO Flatt Security </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2333,13 +2358,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,950,165</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2352,7 +2386,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
         </is>
       </c>
     </row>
@@ -2364,18 +2398,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大和証券</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日経新聞社、Microsoft 365アカウントの情報漏えいと、Google Workspaceからの情報漏えい疑いを発表 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2385,7 +2414,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22万</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -2399,12 +2428,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9IMzJ4WTV6cXJZbjZUTmFqSHJTQUsxbVByMGo3R2FGWDVsbW5PVlRrRFEyYUNoMXZCaUN5WHBEeVBvUTAteWxDbkhLZi1aVHE5eXhzYWVLWVdmbURTUGgtOFdGNHVCbzVndDlV?oc=5 / https://news.google.com/rss/articles/CBMiX0FVX3lxTFBJR3RNbG9BOC1GNTNBQnM0N1VYYWQ3RHBBUHI5UHRXSE5leHNmUGZFVHQ2ZnZwY29KS0JCN0t4TmUxTWNUUDlaWFZmakZucFdyWWphZ1pvbUJkMUVZaHFj?oc=5</t>
         </is>
       </c>
     </row>
@@ -2416,42 +2445,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ecurity 2026.10.5 Mon 8:05 池上通信機にサイバー攻撃</t>
-        </is>
-      </c>
+          <t>日本経済新聞社</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>池上通信機株式会社は9月30日、同社に対するサイバー攻撃について、続報を発表した。 同社では9月21日に、外部から同社に対するサイバー攻撃の可能性について情報提供があり、調査を開始した旨を9月24日に公表していた。 同社では、同社の一部サーバで外部からの不正アクセスが疑われる痕跡を確認するとともに、当該サーバ内の一部ファイルが暗号化されていることを確認している。また同社では、外部から提供のあった情報を確認したところ、その一部に同社の資料とみられる情報が含まれていることを把握している。 同社では、被害拡大の防止と安全性確保を最優先とし、社内ネットワークを切断した状態を継続しており、外部専門機関の協力のもと、原因および影響範囲の特定に向けた調査を進めている。 佐賀大学のNASにランサムウェア攻撃、ファイルが暗号化される被害 2026.9.30 Wed 8:05 教育ソフトウェアの休眠中のレンタルサーバにランサムウェア攻撃、暗号化被害と不正アクセスの痕跡を確認 2026.9.8 Tue 8:05 サンコーテクノのベトナム子会社にランサムウェア攻撃、サーバ及びパソコン内の各種ファイルの暗号化を</t>
+          <t>日本経済新聞社、社員のメールアカウントに不正アクセス なりすましメール9000件送信 - 千葉テレビ放送株式会社</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2459,12 +2480,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56346.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56384.html</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WSXlUMGNRZ1UxLTBfSHdmd0d6OFNVWGlhcGpkdWV0QnNVeDh5VnhCbFhnQnpEcGloNVFHbmFLYkZxMmtFeGpNSzdyZkh3Q2x6bTRkZWd6WldNVkhDbzdr?oc=5</t>
         </is>
       </c>
     </row>
@@ -2476,22 +2497,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GMO</t>
+          <t>日本大学</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ecurity 2026.10.5 Mon 8:05 東産業 公式サイトにwp2shell を悪用した不</t>
+          <t>メール送信の踏み台に 日本大学は9月14日</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">株式会社東産業は9月14日、同社公式サイトへの不正アクセスについて発表した。 これは同社公式サイトに対し、WordPressの脆弱性を悪用した第三者からの不正アクセス確認したというもの。当該脆弱性（CVE-2026-60137、CVE-2026-63030：wp2shell）については、IPAから7月22日に注意喚起が公表されている。 同社ではすでに、当該サイト脆弱性への対策を実施済みで、不正アクセスの発生時期や影響範囲について、調査を行っている。 なお、不正アクセスの対象となる情報は、問い合わせフォームを通じて取得した顧客情報のみ。 同社では今後、情報セキュリティ対策および管理体制の強化に努めるとのこと。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri 8:00 WordPress の深刻度「緊急」脆弱性「wp2shell 」の概要と対応指針 ～ GMO Flatt Security </t>
+          <t>日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日に、第三者が同学の計5名の教員アカウントに不正アクセスし、当該アカウントをスパムメール送信の踏み台として利用していたことを8月29日に確認したというもの。当該アカウントから学内外に1,333件の不審メールが送信されたことを確認している。 調査の結果、当該アカウント内のデータに対する大規模な抽出や持ち出し等の痕跡は確認されていないが、一部のデータへアクセスされた可能性はあるという。 同学では、連絡先が特定可能な対象者に順次、個別にメール等で連絡を行っている。 同学では、悪意ある第三者がフィッシングメール等の手段で認証情報（ID・パスワード）を窃取し、アカウントを乗っ取ったことが原因と推測している。 同学では検知後に、当該アカウントの利用を一時停止（或いは無効化）し、不正アクセスを遮断している。 同学では、多要素認証（MFA）の導入推進、アカウントの管理適正化及び情報セキュリティ教育の再徹底を行い、再発防止に取り組むとのこと。 日本大学理工学部教職員のアカウントに対し巧妙に偽装されたフィッシングメール、</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2501,21 +2522,21 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1,950,165</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2524,7 +2545,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56381.html</t>
+          <t>https://www.security-next.com/190319 / https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
         </is>
       </c>
     </row>
@@ -2536,42 +2557,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ト・情報漏えい ScanNetSecurity 2026.10.5 Mon 8:05 日本大学</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ecurity 2026.10.5 Mon 8:05 日本大学の計 5 名の教員アカウントに不正アクセス</t>
-        </is>
-      </c>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>日本大学は9月14日、不正アクセスによる迷惑メール発信について発表した。 これは8月7日に、第三者が同学の計5名の教員アカウントに不正アクセスし、当該アカウントをスパムメール送信の踏み台として利用していたことを8月29日に確認したというもの。当該アカウントから学内外に1,333件の不審メールが送信されたことを確認している。 調査の結果、当該アカウント内のデータに対する大規模な抽出や持ち出し等の痕跡は確認されていないが、一部のデータへアクセスされた可能性はあるという。 同学では、連絡先が特定可能な対象者に順次、個別にメール等で連絡を行っている。 同学では、悪意ある第三者がフィッシングメール等の手段で認証情報（ID・パスワード）を窃取し、アカウントを乗っ取ったことが原因と推測している。 同学では検知後に、当該アカウントの利用を一時停止（或いは無効化）し、不正アクセスを遮断している。 同学では、多要素認証（MFA）の導入推進、アカウントの管理適正化及び情報セキュリティ教育の再徹底を行い、再発防止に取り組むとのこと。 日本大学理工学部教職員のアカウントに対し巧妙に偽装されたフィッシングメール、</t>
+          <t>日本交通、不正アクセスで停止していた「電話でタクシー配車」再開へ 約3カ月ぶり - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2579,12 +2587,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56380.html</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1PMWhRMUdibHJxUUg3MUE0MzQxell5RHZpV21lUjZieG1zZkNHX0t1c2xZdFhGNmFhT3NNMzZETUxxWG8xLVB6Y2ozRTB4SjAxT3dTMFdrMlp5NXlGZzVUTzltcUp2dGZ5WWRVdkd1SndQZw?oc=5 / https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNNIBmwFBVV95cUxNTFBsakhRYWV2YUNEY0V2NTBHVGZjSUt5QS11LTZJano4bTZ3UHVfVmxEX19vWFkyd2NycklTbzBPSVZuZ1Z5VzR0VFR2OFhTMFBtVnB2MnpKdVZBY0l3Wm1kWXpLR3FpT0s3MVBpWmU1NTNpVk85V0ZTYmxKZDZDSE5GanlzWEpLS3hpMVlKaVl2UXdXYzIySEZUNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2596,17 +2604,13 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>一万三千尺物語</t>
-        </is>
-      </c>
+          <t>大和証券</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 これは9月8日朝に、同社社員が座席管理システムにアクセスしたところ、複数の予約がキャンセルされていた他、当該システムから正規の手順で行われていない予約を確認したため、全ての新規予約の受付を停止するとともに調査を行った結果、9月2日に最初の不正アクセスがあり、以降、9月8日までに複数回の不正アクセスを確認したというもの。 漏えいした可能性があるのは、これまでに観光列車「一万三千尺物語」に乗車した顧客または今後の乗車予約をしていた顧客 計1,409名の個人情報（氏名、住所、電話番号、メールアドレス）。 同社では対象の顧客に9月12日付で、文書「個人情報の漏えいのおそれがある事象に関するお詫びとお知らせ」を郵送している。 同社では、外部からの不正アクセスが判明したことから、その拡大を防ぐため、ネットによる新規予約の受付停止を継続している。 同社では今後、調査結果を踏まえてシステム全体のセキュリティ対策の強化などに努めるとのこと。 駅放送設備から意図しない音声が</t>
+          <t>大和証券に不正アクセス、22万件漏えいか - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2616,22 +2620,18 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1,409</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 従業員情報</t>
-        </is>
-      </c>
+          <t>22万</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPSE85Vmc4eVp5N2JjaDRZZ0toVURTcUlyLXVxTEJzWno0c05TQ0NOZFFLZmlQamdOUVNuT2Rkajl0N3hRZU9IMFJXTXZKQW1mSGlFWHF4TFlsWGpTeE10R0dFYmxZeXhRSFVrVi1tWGVqS3hCTWNUTzZ1TzNGc3E4RURheDA2LUxNc2NaZVN2ZDg4RHPSAZMBQVVfeXFMT0hPOVZnOHlaeTdiY2g0WWdLaFVEU3FJci11cUxCc1p6NHNOU0NDTmRRS2ZpUGpnTlFTbk9kZGo5dDd4UWVPSDBSV012SkFtZkhpRVhxeExZbFhqU3hNdEdHRWJsWXl4UUhVa1YtbVhlakt4Qk1jVE82dU8zRnNxOEVEYXgwNi1MTXNjWmVTdmQ4OERz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2656,22 +2656,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ドズル社ストア</t>
-        </is>
-      </c>
+          <t>アバハウスインターナショナル</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 これは9月11日午後4時頃に、「ドズル社ストア」で商品購入手続きの際、正規の決済ページではない不正な外部ページへ誘導される事象が発生したというもの。不正なページには、主に下記のような特徴があり、不正なページで行われた支払いは、「ドズル社ストア」での注文として受け付けられていない。 ・ページ左上に「Checkout」と表示され、ドズル社ストアの名称・ロゴが表示されない ・英語で表示され、配送先の国・地域に「United States」があらかじめ選択されている ・実際の商品価格と大きく異なる高額な金額が表示される 同社によると、発生推定期間中（9月11日午後3時頃～午後5時50分）に購入手続きをおこなったにもかかわらず、同ストアからの注文確認メールが届いていない場合は、不正なページで決済が行われた可能性があるという。 同社では、発生推定期間中に上記の特徴を持つページでクレジットカード情報を入力した場合、利用のカード会社に連絡のうえで、不正利用の有無の確認や、カードの利用停止・再発行</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>フィッシング</t>
+          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2679,19 +2670,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2699,12 +2681,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2716,17 +2698,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>原田産業</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ビールの縁側</t>
+          <t>一万三千尺物語</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレジットカード情報を含む情報が漏えいした可能性のある顧客は9名。対象となる情報には、氏名、電話番号、メールアドレス、性別、生年月日、住所、クレジットカード情報（番号、名義人、有効期限、セキュリティコード）が含まれる。なお、決済を完了した顧客は4名、決済を完了せずに注文手続を終了した顧客は5名。 同社では対象となる9名に個別にメールで連絡を行っている。 同社では現在</t>
+          <t>あいの風とやま鉄道株式会社は9月15日、同社が運営する観光列車「一万三千尺物語」の座席管理システムへの不正アクセスについて発表した。 これは9月8日朝に、同社社員が座席管理システムにアクセスしたところ、複数の予約がキャンセルされていた他、当該システムから正規の手順で行われていない予約を確認したため、全ての新規予約の受付を停止するとともに調査を行った結果、9月2日に最初の不正アクセスがあり、以降、9月8日までに複数回の不正アクセスを確認したというもの。 漏えいした可能性があるのは、これまでに観光列車「一万三千尺物語」に乗車した顧客または今後の乗車予約をしていた顧客 計1,409名の個人情報（氏名、住所、電話番号、メールアドレス）。 同社では対象の顧客に9月12日付で、文書「個人情報の漏えいのおそれがある事象に関するお詫びとお知らせ」を郵送している。 同社では、外部からの不正アクセスが判明したことから、その拡大を防ぐため、ネットによる新規予約の受付停止を継続している。 同社では今後、調査結果を踏まえてシステム全体のセキュリティ対策の強化などに努めるとのこと。 駅放送設備から意図しない音声が</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2741,12 +2723,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, クレジットカード情報, 従業員情報</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2764,7 +2746,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56383.html</t>
         </is>
       </c>
     </row>
@@ -2776,18 +2758,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>物語コーポレーション</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>アバハウス、会員・受注情報漏えいの可能性 注文内容と一致する不審な返金案内メールを確認 - ｄメニューニュース</t>
+          <t>『焼肉きんぐ』1000万件超の情報漏洩 なぜ今、飲食店アプリが狙われるのか？ #エキスパートトピ（山路力也） - エキスパート - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1000万</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2806,7 +2793,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONUZPeWw1eUdIMElEMkNMd0poV2lHajFIY2FLbEU1VFBSNjVGb2k2ejhWeG9Kc1hhdGtTNDAtTmdzbkdkQWw4MDNiUDRNdEh5OFZWdDkzN2d2RXdzbGl2d0dLZU93NFU5Z1l1aHFCZ2FoRlMwQWs5NmRKUTZFdGdMTUhoS1TSAYQBQVVfeXFMTjVGT3lsNXlHSDBJRDJDTHdKaFdpR2oxSGNhS2xFNVRQUjY1Rm9pNno4VnhvSnNYYXRrUzQwLU5nc25HZEFsODAzYlA0TXRIeThWVnQ5MzdndkV3c2xpdndHS2VPdzRVOWdZdWhxQmdhaEZTMEFrOTZkSlE2RXRnTE1IaEtU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2811,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>『焼肉きんぐ』1000万件超の情報漏洩 なぜ今、飲食店アプリが狙われるのか？ #エキスパートトピ（山路力也） - エキスパート - Yahoo!ニュース</t>
+          <t>「焼肉きんぐ」、顧客情報漏洩 不正アクセスで1000万件超 - 日本経済新聞</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2837,7 +2829,11 @@
           <t>1000万</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>顧客情報</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2853,7 +2849,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZ3BXc0hsQzFqdExLZlpwQU5PcGpYOVFYYnAxVDNTUmZzTjE5MC1UR1BhcnoycS12amQ2Y0o0cHBYdVZadUNWdmZUWGMxRGtJZldzQnVpbktyMGpJZzBxOFBWNjB6LVhrNWc0MGd1SEVzdnh4LTU5Mi05Z2RZTVdlTzRTVkVlcHBZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2865,13 +2861,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
+          <t>大起水産</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>「焼肉きんぐ」、顧客情報漏洩 不正アクセスで1000万件超 - 日本経済新聞</t>
+          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2881,19 +2877,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1000万</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -2909,7 +2901,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1jRFdhTkNYYXF2SnFlT3dlSUtla0RHRFE0MTcxc1hvN3VOdi1RMlpBZ1FnVFMwR1VlUnZUZnJsOEY1cGQ2dDIzM2h4WjJOTnhMZ2RYVGE3Q1pWT2EzSmdOdThUMDF4YkRla2d2WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2921,18 +2913,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大起水産</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>「大起水産公式アプリ」に不正アクセス 17万4933人の個人情報漏えいのおそれ 現時点で不正利用は確認されず - ｄメニューニュース</t>
+          <t>株式会社ドズルは9月12日、同社が運営する「ドズル社ストア」における不正なページへの誘導について発表した。 これは9月11日午後4時頃に、「ドズル社ストア」で商品購入手続きの際、正規の決済ページではない不正な外部ページへ誘導される事象が発生したというもの。不正なページには、主に下記のような特徴があり、不正なページで行われた支払いは、「ドズル社ストア」での注文として受け付けられていない。 ・ページ左上に「Checkout」と表示され、ドズル社ストアの名称・ロゴが表示されない ・英語で表示され、配送先の国・地域に「United States」があらかじめ選択されている ・実際の商品価格と大きく異なる高額な金額が表示される 同社によると、発生推定期間中（9月11日午後3時頃～午後5時50分）に購入手続きをおこなったにもかかわらず、同ストアからの注文確認メールが届いていない場合は、不正なページで決済が行われた可能性があるという。 同社では、発生推定期間中に上記の特徴を持つページでクレジットカード情報を入力した場合、利用のカード会社に連絡のうえで、不正利用の有無の確認や、カードの利用停止・再発行</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2942,13 +2938,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13V0pxazkwVWZMWlhxTVpmT2wtZk13eFgwd0QxZFBtdmlTcFJwNHU3ejlwNk5OdklENlRGTEdUeml6MnQ3b3dFZnNEckdWSjFPbG9TMWp0QWhPN3pRbEtVTHBtR2ZuMEJFeUF3OFV2cms3YjdrdzN2SmZZanJIRjjSAX9BVV95cUxNd1dKcWs5MFVmTFpYcU1aZk9sLWZNd3hYMHdEMWRQbXZpU3BScDR1N3o5cDZOTnZJRDZURkxHVHppejJ0N293RWZzRHJHVkoxT2xvUzFqdEFoTzd6UWxLVUxwbUdmbjBCRXlBdzhVdnJrN2I3a3czdkpmWWpySEY4?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56154.html / https://scan.netsecurity.ne.jp/article/2026/09/15/56231.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56247.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56273.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56262.html / https://scan.netsecurity.ne.jp/article/2026/10/05/56386.html</t>
         </is>
       </c>
     </row>
@@ -3267,24 +3267,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>原田産業</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ビールの縁側</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
+          <t>原田産業株式会社は9月14日、8月18日に公表した同社が運営するECサイト「ビールの縁側」（ https://beer-engawa.jp/ ）への不正アクセスについて、続報を発表した。 同社では、同社運営の「ビールの縁側」に不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が判明しており、外部専門機関の協力のもとで事実関係の確認と影響範囲の調査を進めていた。 実施調査によると、当該サイトで使用していたシステムの一部に存在した脆弱性が悪用された結果、管理者権限が不正に取得され、不正なプログラムが稼働していた可能性が判明している。 不正プログラムの稼働期間は2026年8月11日午後7時9分から8月14日午後4時57分で、クレジットカード情報を含む情報が漏えいした可能性のある顧客は9名。対象となる情報には、氏名、電話番号、メールアドレス、性別、生年月日、住所、クレジットカード情報（番号、名義人、有効期限、セキュリティコード）が含まれる。なお、決済を完了した顧客は4名、決済を完了せずに注文手続を終了した顧客は5名。 同社では対象となる9名に個別にメールで連絡を行っている。 同社では現在</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3297,7 +3315,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/05/56379.html</t>
         </is>
       </c>
     </row>
@@ -3309,13 +3327,13 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ）</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ）</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
+          <t>Daiwa Securities (contractor Scala Communications)（ disclosure ） — Unauthorized access to the server of inquiry-management service provider Scala Communications, from about 20:33 on Oct 2 to about 08:01 on Oct 3 according to Daiwa's notice. Scala's notice reports that a third party logged in without authorization to the i-ask admin site and installed a malicious program on its server. How the login credentials were obtained is not stated. No unauthorized access to Daiwa's systems confirmed.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3351,13 +3369,13 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline）</t>
+          <t>Daiki Suisan (official app)（ disclosure ）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
+          <t>Daiki Suisan (official app)（ disclosure ） — Third-party unauthorized access; route not stated. Confirmed Sep 15. Passwords on a separate server were out of scope.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3393,42 +3411,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>物語コーポレーション</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>焼肉きんぐ</t>
-        </is>
-      </c>
+          <t>777CON-PASS（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>777CON-PASS（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>8,963</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3441,25 +3441,34 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日本経済新聞社</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>物語コーポレーション</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>焼肉きんぐ</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
+          <t>株式会社物語コーポレーション（愛知県豊橋市西岩田／「焼肉きんぐ」「丸源ラーメン」等を展開する外食チェーン。東証プライム・証券コード3097）は2026年10月5日、「焼肉きんぐ」公式アプリの会員管理システムが第三者による不正アクセスを受け、会員情報1,078万8,963件が漏えいしたと公表した。アプリの登録者数1,080万8,784件のほぼ全員にあたる。漏えいしたのは会員番号、氏名（アプリ登録名）、メールアドレス、電話番号で、ログインパスワードや決済情報、店舗利用履歴などは対象外としている。10月2日に不正アクセスを検知して通信遮断などの防御措置を実施し、翌3日に漏えいを確認した。侵入経路や原因は調査中。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3467,10 +3476,19 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8,963</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>氏名, 電話番号, メールアドレス, 認証情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3483,7 +3501,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-06-yakiniku-king-app-member-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3501,17 +3519,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
+          <t>日経新聞サイバー攻撃で情報漏えいか なりすましメールが送信 | NHKニュース | サイバー攻撃、IT・ネット、企業・経営 - NHKニュース</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>9000</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3530,7 +3543,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFB1SnV5ay1RdWRIRXlaRGhlYWtUZXdsZGFtYUJBRTNBa2ZVUWlFNS1TU043eEpzcHdOWkdacjhsNEdrVURGNjFLQWQtc1VqX256R1hGYU1TRVBBcWEwRXRj?oc=5</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3561,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
+          <t>日経新聞にサイバー攻撃 社員になりすましたメール約9000件が送信される 個人情報の流出数など調査 - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>9000</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3572,7 +3590,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xSWJHdVdZX0VETVNfTFpXSXJ3aHhwcktuSFBGdVRoeEZKdmlnSmhUWWhJTjJORjJGV2s1M2J2RDBqUjZfMTN6V0Vaa3BkOXRrOVk1S1R3c1lGaFhZOWdEOEEzbS1pNEpjQ2NFb1dnTjNIbVFidmxRcFBfT21SWUk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3584,23 +3602,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>日本経済新聞社</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日本経済新聞社へのサイバー攻撃と情報漏洩 - 村上知也</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3619,7 +3632,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9RTU8yQ2ZMMDNtX3NROE9KN19iSHJlSW9RMV9qLUpFenQ4TDNWZ3JSVlBZUjVhdHhWZzM2T256YjZFV1BoemlOUFc1a2pPcnBiR0h2d2ZnTjR3NzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3631,24 +3644,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ）</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
+          <t>日本エネルギー経済研究所、Microsoft 365への不正アクセスでパスポートを含む個人情報漏洩の恐れ - 合同会社ロケットボーイズ</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3661,50 +3679,36 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPT1BxVHhwcnBrZ29rZDVHSkJzRHJiZWJNckU4YnBUQUVoWDJuTVBHQnZkcmNLeFJBTEYtUmNaTGhfVVNPLUtQUFkwUzJnSnBQcjVvQ0hETTIyY3BWSkZCcmFCcmRVNUsxdTZvODJpNS1ZMDBsQy1YTmRkMFowa1ctZHBOTGE1OHdCXzZGYjVUdTdKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>Nikkei BP（ disclosure ）</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Nikkei BP（ disclosure ） — Employee email account accessed; identified Sep 30. Credentials stolen through phishing from a Nikkei employee's address.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>12万</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>従業員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3717,7 +3721,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -3729,13 +3733,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
+          <t>第一ライフに不正アクセス 12万人分の従業員情報が流出か | NHKニュース | サイバー攻撃、IT・ネット - NHKニュース</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3743,7 +3752,16 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>12万</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>従業員情報</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -3759,7 +3777,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5hbjJmQnpsQ0R1bzBseUV6aExmdW9nWjUtV2ZNNV9BdDJWNnB0bEJNcExZWENlZXl1WTNJS1VOWUFFcEhYNFZwZTA2V29keVUwRHV0elVDckZCcWhTRk5r?oc=5</t>
         </is>
       </c>
     </row>
@@ -3771,24 +3789,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline）</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MoonStar（tracker headline） — Unauthorized access.</t>
+          <t>アバハウス、全顧客の個人情報流出か 「不審なメール」報告受け発覚 - 日本経済新聞</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3801,7 +3819,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBaejRkV1Q2QUpuclA1WThITGQwbGNUWkM2OHNZNWZjaDlMeWdyT0c4bDljUWkya2g5RDV6Uk9RcDhROVVhQ0NWOVNKbGZMN2JGQWYyNkRDZEktRl9JYWlyM08wcmZsWTBER1ZGcQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3813,13 +3831,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline）</t>
+          <t>MoonStar（tracker headline）</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Abahouse（tracker headline） — Unauthorized access.</t>
+          <t>MoonStar（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3855,37 +3873,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>アバハウスインターナショナル</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>返金</t>
-        </is>
-      </c>
+          <t>Abahouse（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Abahouse（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3898,29 +3903,29 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>アバハウスインターナショナル</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>問い合わせサービスがサイバー攻撃を受け</t>
+          <t>返金</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
+          <t>株式会社アバハウスインターナショナル（東京都渋谷区東／メンズ・レディスウェアや服飾雑貨の企画・製造・卸・小売）は2026年10月3日、社内システムが第三者による不正アクセスを受け、会員情報とEC受注情報を保管するデータベースから個人情報が漏えいした可能性があると公表した。不正アクセスは9月27日深夜から28日にかけてとみられ、9月28日に複数の顧客から「実際の注文情報と一致する不審な返金案内メールを受信した」との問い合わせを受けて発覚した。漏えいした可能性がある情報は会員ID・氏名・住所・電話番号・メールアドレス・生年月日・性別・注文情報で、対象件数は公表されていない。退会済みの顧客も対象に含まれる。</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3933,10 +3938,14 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, 会員情報</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -3949,7 +3958,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190952</t>
+          <t>https://incident.yagurasec.com/incidents/2026-10-04-abahouse-international-member-order-db-breach/</t>
         </is>
       </c>
     </row>
@@ -3961,13 +3970,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ジャパンタイムズ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>問い合わせサービスがサイバー攻撃を受け</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+          <t>佐川急便は、荷物問い合わせサービスがサイバー攻撃を受け、顧客の個人情報が流出した可能性があることを明らかにした。ウェブサービスの一部を停止している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3977,13 +3990,13 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -3996,7 +4009,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
+          <t>https://www.security-next.com/190952</t>
         </is>
       </c>
     </row>
@@ -4008,23 +4021,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>第一生命</t>
+          <t>ジャパンタイムズ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
+          <t>英字日刊紙のジャパンタイムズ、傘下が不正アクセス被害に 漏えいの有無は「調査中」 - Infoseek</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>12万</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -4043,7 +4056,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1YZUwyenNYcnRPTkwtNG85Qm13VDdyLXBxQ1RPTWVYeVRxRzlwc0plLTNWRXZXbUt2MXNBa1lmOU5wS2p5V3ROSmZBSUxPNHRSX0ZsV1pXU3Z0RU9La3R2dXRNSUZkMFM1WFNwMkU3SXlldTBLZERN0gF8QVVfeXFMUG1jUk1xZjVTd19aMW92TkF2YkJwTlJ3MHdSNENMUnlDSGVmbjh5eThScHp4cXNHMnlQR2pSMXoxUDVwcmRnekdUS0hSYnN5MHV1eVFySElMZVFqYUJNRlI5dVd6RnM3RTBoZ0pXWHRJN01HU1E3X0VLV2Y5dg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4068,13 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>第一生命</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
+          <t>第一ライフ、従業員12万人分情報漏えいか - Infoseek</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4071,7 +4084,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>12万</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -4090,7 +4103,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5iNzhpU1RUak02VXFyZjZnRk1FWFBXbjl1RlpfSWdaTHI0Q1RJZFRVVy1WRS1rTXpGSm9PMURzRWlWb1l2dW5jVDFUeHF3d2pJV0dBRGljS2lpQlQ2cGxEM1BTWXAxS0ZNSFB5Qk94RQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4102,18 +4115,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
+          <t>日本原子力研究開発機構</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>日本原子力研究開発機構で175人分の個人情報漏えい マイナンバー含む6人分も - ASCII.jp</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4123,7 +4131,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -4142,7 +4150,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9Xa2NGQXRWYnRIOUtmc3dtTjZjcXRGYzYxdGRrUXZXVFR6dkktVWtZQ2VMNkxncFN3WUw1VE9xN3ltdFQzMGJZdld2VWtXc1ZxTUMwQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4154,18 +4162,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>佐川急便</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>日本エネルギー経済研究所</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicrosoft 365 アカウントに不正アクセスがあり、メール及びファイルの閲覧による外部への情報漏えいの可能性、ファイルのダウンロードによる外部への情報漏えいが判明したというもの。 富山県立大学の Microsoft 365 学生アカウントから大量の迷惑メール送信 2026.7.23 Thu 8:05 TE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4173,10 +4185,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4189,7 +4210,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
         </is>
       </c>
     </row>
@@ -4201,13 +4222,13 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>佐川急便</t>
+          <t>日本エネルギー経済研究所</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
+          <t>日本エネルギー経済研究所、不正アクセスの続報 パスポート情報13件の漏えい確認 - ニコニコニュース</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4220,11 +4241,12 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>氏名, 住所</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -4240,7 +4262,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5MMG5iajVwTzdHMXY1NWg5bHVlZF96cmw5T2VGVThTa2FYb2MzazhVajRWMjc1TFJzRkNYOEpXTXVOZHN0QmRRMERFVEd1b1QzT05QV24yUkM3c2RmRDNVdTNMMnpoYU1XdmM0VXBwMjlYMXNudXc4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4274,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>イープラス</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>イープラス</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正アクセスがあり、同システム内に保管していた払戻しを実施するための情報に含まれていた顧客の個人情報の漏えいが判明したというもの。 一部顧客の情報が閲覧・編集・削除可能に ～ リセールサイト「RELIEF Ticket」 2025.7.3 Thu 8:05 CNプレイガイドへの不正アクセス、キョードー東京と</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4268,17 +4294,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>236,323</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>氏名, 住所</t>
+          <t>メールアドレス, クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4291,7 +4322,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html</t>
         </is>
       </c>
     </row>
@@ -4303,13 +4334,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
+          <t>佐川急便</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
+          <t>佐川急便、不正アクセスで個人情報流出の可能性 荷物追跡APIなど9サービス停止、集荷・配達は通常通り - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4322,11 +4353,7 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>顧客情報</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -4342,7 +4369,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9CUGJlTU1CenlDNDU5Rk1hOXJvaXJNSk1DQk0tTEFSclZwbnNhZE9QRklkU28wWXdsek1XQ3YwU0x5NU5nS3EzdFR1dXRPbjd6clN5aldJQkR6NTM5eTZyc2h4cTJrT2lpbWttdGVxbEt5WlNMUjBqdlUtLV9zTGs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4354,42 +4381,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>日本エネルギー経済研究所</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ecurity 2026.10.2 Fri 8:05 日本エネルギー経済研究所にフィッシング攻撃</t>
-        </is>
-      </c>
+          <t>佐川急便</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56376;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般財団法人日本エネルギー経済研究所は9月11日、不正アクセスによる情報漏えいについて発表した。 これは7月29日に外部機関から情報提供があり、外部専門機関と連携して調査を実施した結果、第三者によるフィッシング攻撃で同研究所の所員6名のMicrosoft 365 アカウントに不正アクセスがあり、メール及びファイルの閲覧による外部への情報漏えいの可能性、ファイルのダウンロードによる外部への情報漏えいが判明したというもの。 富山県立大学の Microsoft 365 学生アカウントから大量の迷惑メール送信 2026.7.23 Thu 8:05 TE</t>
+          <t>佐川急便、不正アクセスで個人情報流出か 住所や氏名など - 日本経済新聞</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4402,7 +4420,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56376.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ScUhlenhCNFpaaHlEQmJheWN0ZlFEak8taWZNU094elZoY1drQVBXa1JQRHBiV1Bpd0JOLTVsRmkxYmQzbFk0aUhVMDBzN0VjQWhZRGIyeDZ1UW9VdkpOVG8wX2NPMDI4RDQtYg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4414,17 +4432,13 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>イープラス</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56372;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社イープラスは9月29日、同社が運営するチケット販売プラットフォーム「イープラス」への不正アクセスについて発表した。 これは同社の電子チケット「スマチケ」管理システムのうち、公演中止・延期等に伴う払戻し情報を管理するシステムに第三者から不正アクセスがあり、同システム内に保管していた払戻しを実施するための情報に含まれていた顧客の個人情報の漏えいが判明したというもの。 一部顧客の情報が閲覧・編集・削除可能に ～ リセールサイト「RELIEF Ticket」 2025.7.3 Thu 8:05 CNプレイガイドへの不正アクセス、キョードー東京と</t>
+          <t>ヤマト運輸に不正アクセス、氏名や住所漏洩か 通販後払いで - 日本経済新聞</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4434,22 +4448,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>236,323</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報, 会員情報</t>
+          <t>氏名, 住所</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4462,7 +4471,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56372.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAwUWt2cVg0WUZNeThHZUl2SkZ0RjVFVEVkMUxpMG42cE5JMmhjcFhEWlJSZERTVzBUSWlBdllMYUtyZ1F2S3Fkb2gwLUI1RHRwa3ZvckdjUnpXLVpVaWpPdTZhLXFNWThxRndVQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4474,17 +4483,13 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>日本郵便</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>郵便局アプリ</t>
-        </is>
-      </c>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実施した結果、ゆうIDおよび郵便局アプリに関連する顧客情報が不正に取得されたことが判明している。 日本郵便 調査請求 Web受付サービスに不正アクセス、一時的に受付を停止 2026.9.30 Wed 8:05 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配</t>
+          <t>ヤマト運輸、後払いサービスに不正アクセス 顧客情報など漏えいの可能性（日本ネット経済新聞） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4497,32 +4502,27 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>顧客情報</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Google News / ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE02ZFFLRUhNMlNCdWt3WTRkLUk0bGFVWW8yQ2lwUm96VlpIN2pISktabkdIeVJvLUpPOGVDbjBjTFVTcTBoOFhienF4dUJwNlRQSG5nSTJKY3FkWlJRTzlhUnJ3NnJ0NzBzczc4UXRyeE14RG9zTTNPWS1CdDhSUzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4534,22 +4534,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>セイコーマート</t>
+          <t>日本郵便</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>セイコーマートアプリ</t>
+          <t>郵便局アプリ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした可能性が9月28日午後5時過ぎに判明したというもの。9月24日午後10時から11時の間に、不正にクラブカードの退会処理が行われたアカウントが1件あり発覚した。 「コープやまぐちLINEミニアプリ」に不正アクセス、データベースに保存されていた内容を精査し漏えいの可能性がある情報を確定 2026.9.24 T</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56370;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵政株式会社と日本郵便株式会社は9月29日、両社が提供する「郵便局アプリ」への不正アクセスについて発表した。 これは郵便局アプリに外部から不正アクセスがあり、9月25日午後10時30分頃にゆうIDおよび郵便局アプリの緊急メンテナンスを実施したというもの。不正アクセスに関する調査を実施した結果、ゆうIDおよび郵便局アプリに関連する顧客情報が不正に取得されたことが判明している。 日本郵便 調査請求 Web受付サービスに不正アクセス、一時的に受付を停止 2026.9.30 Wed 8:05 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4559,30 +4559,30 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE15Qm5zRVNxb2w4eUNGa0FlR3FiUUZPX3IwdFhiWEd4bkxjR3FYUWRXS1VYOGRlWldaZkxSWkZEVWViZ3RxOXFDaVE3aFhwY0V0UXl1YnZ2TXFmMV9LbmtZbTNJNkdRZEFlRldyRg?oc=5 / https://scan.netsecurity.ne.jp/article/2026/10/02/56370.html</t>
         </is>
       </c>
     </row>
@@ -4594,24 +4594,42 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>セイコーマート</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>セイコーマートアプリ</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56373;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社セイコーマートは9月29日、同社のスマートフォンアプリ「セイコーマートアプリ」への不正アクセスについて発表した。 これは「セイコーマートアプリ」のサーバを経由して、会員情報を保有するサーバに第三者が不正にアクセスし、会員情報が漏えいした可能性が9月28日午後5時過ぎに判明したというもの。9月24日午後10時から11時の間に、不正にクラブカードの退会処理が行われたアカウントが1件あり発覚した。 「コープやまぐちLINEミニアプリ」に不正アクセス、データベースに保存されていた内容を精査し漏えいの可能性がある情報を確定 2026.9.24 T</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4624,7 +4642,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/02/56373.html</t>
         </is>
       </c>
     </row>
@@ -4636,13 +4654,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline）</t>
+          <t>Toyobo MC（tracker headline）</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
+          <t>Toyobo MC（tracker headline） — Two employees' accounts accessed via phishing.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4678,13 +4696,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ）</t>
+          <t>Three educational institutions（tracker headline）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
+          <t>Three educational institutions（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4720,13 +4738,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline）</t>
+          <t>Kodansha BECK（ news report ）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
+          <t>Kodansha BECK（ news report ） — Long-running unauthorized access to a pre-merger Kodansha BC employee's email account, presumed credential acquisition. Suspicious emails sent Sep 14.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4762,13 +4780,13 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline）</t>
+          <t>Japan Cosmetic Industry Association（tracker headline）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
+          <t>Japan Cosmetic Industry Association（tracker headline） — Unauthorized access to Microsoft 365.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4804,13 +4822,13 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
+          <t>Institute of Energy Economics, Japan（tracker headline）</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
+          <t>Institute of Energy Economics, Japan（tracker headline） — Microsoft 365. Sep 16 notice described phishing-based access to six accounts and download of 2,798 files.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4841,34 +4859,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ）</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Dai-ichi Life Group / Dai-ichi Life Insurance（ disclosure ） — Unauthorized access to the two companies' HR system, detected Sep 24. Cause given as third-party unauthorized access. No unauthorized access to customer data confirmed.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -4881,7 +4894,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4912,7 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - ニコニコニュース</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4923,12 +4936,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5JS2JnYmxvMWd4cW5QczhjSzJrbm1Ed3Y4elhYVVNXV1FXQmpZOTl5QWpoeHdnRTZJZWR5Z09SZGxZd1FnNDBMYkV4YXlvX2syclFzX0lhMjlSdnBQcU5UVEZGcDdsb2pKS244cExIaTlleHY4bklF?oc=5</t>
         </is>
       </c>
     </row>
@@ -4940,33 +4953,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>佐賀大学</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>システムで</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
+          <t>日本原子力機構に不正アクセス 研究者の顔写真付き身分証など漏えい - Infoseek</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -4974,12 +4983,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190842</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5026,20 +5035,20 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura / Security NEXT / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315 / https://scan.netsecurity.ne.jp/article/2026/10/01/56356.html</t>
         </is>
       </c>
     </row>
@@ -5051,42 +5060,33 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>佐賀大学</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>オズモール</t>
+          <t>システムで</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56359;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); スターツ出版株式会社は9月27日、同社運営のウェブサイト「オズモール」への不正アクセスについて発表した。 これは9月26日に、「オズモール」への海外からの大量の不正アクセスを同社システム部門が検知したため、調査した結果、顧客の個人情報が閲覧された可能性が判明したというもの。 不正プログラム設置 ～ 東京大学大学院医学系研究科公共健康医学専攻ウェブサイトに不正アクセス 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 2026.9.29 Tue 8:05 「スマ</t>
+          <t>佐賀大学は、事務に利用する一部情報システムで、ランサムウェアによる被害が発生したことを明らかにした。引き続き調査を進めているが、業務は再開しているという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
+          <t>https://www.security-next.com/190842</t>
         </is>
       </c>
     </row>
@@ -5111,17 +5111,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーアプリ</t>
+          <t>オズモール</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56358;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ニッポンレンタカーサービス株式会社は9月26日、同社が運営する「ニッポンレンタカーアプリ」への不正アクセスについて発表した。 これは「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認したというもの。 カーシェアサービス「RIDENOW」に登録された運転免許証画像が漏えいした可能性 2024.3.25 Mon 8:05 名鉄協商にランサムウェア攻撃、カーシェア「カリテコ」の顧客情報が漏えいした可能性 2026.8.26 Wed 8:10 日本テレネットにランサムウェア型サイバー攻撃、大和リ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56359;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); スターツ出版株式会社は9月27日、同社運営のウェブサイト「オズモール」への不正アクセスについて発表した。 これは9月26日に、「オズモール」への海外からの大量の不正アクセスを同社システム部門が検知したため、調査した結果、顧客の個人情報が閲覧された可能性が判明したというもの。 不正プログラム設置 ～ 東京大学大学院医学系研究科公共健康医学専攻ウェブサイトに不正アクセス 2026.9.29 Tue 8:05 モンベル・グローバルサイトに不正アクセス、最大15名分の個人情報が第三者に不正に取得された可能性 2026.9.29 Tue 8:05 「スマ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56359.html</t>
         </is>
       </c>
     </row>
@@ -5171,17 +5171,13 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ヤマト運輸</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>クロネコ代金後払いサービス</t>
-        </is>
-      </c>
+          <t>日本原子力研究開発機構</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8:05 刑事告訴検討 ～ ヤマト運輸の元従業員が取引先企業に関する情報の一部を不正に持ち出し 2 社に流出 2025.10.20 Mon 8:05 シンガポールヤマト運輸に不正アクセス、個人情報の不正持ち出しが判明 2024.11.18 M</t>
+          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5191,22 +5187,13 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5219,7 +5206,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5231,13 +5218,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>日本原子力研究開発機構</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ニッポンレンタカーアプリ</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>「原子力機構」の研究用原子炉サイトに不正アクセス、１７５人分の運転免許証など個人情報漏えい - Infoseek</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56358;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ニッポンレンタカーサービス株式会社は9月26日、同社が運営する「ニッポンレンタカーアプリ」への不正アクセスについて発表した。 これは「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認したというもの。 カーシェアサービス「RIDENOW」に登録された運転免許証画像が漏えいした可能性 2024.3.25 Mon 8:05 名鉄協商にランサムウェア攻撃、カーシェア「カリテコ」の顧客情報が漏えいした可能性 2026.8.26 Wed 8:10 日本テレネットにランサムウェア型サイバー攻撃、大和リ</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5247,13 +5238,22 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY0YwVmxBWWtlNHZPUDJUbldqYmhZMnpRd1RSeXlEbDVEZUdBWkh0SnlNNng5b3pTT296TXNVbUdtVnlKaUJ1eEpVNUpsVTZxV2RjSmI0Wkx1ZXp5V2diQW9oR2RwRnpVeHM1OVdhVHJiQQ?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56358.html</t>
         </is>
       </c>
     </row>
@@ -5278,24 +5278,42 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>eplus（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>ヤマト運輸</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>クロネコ代金後払いサービス</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>eplus（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56361;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ヤマト運輸株式会社は9月29日、「クロネコ代金後払いサービス」への不正アクセスについて発表した。 これは9月28日に、「クロネコ代金後払いサービス」への第三者からの不正アクセスを確認したというもの。 流出先での営業活動が新たに判明 ～ ヤマト運輸の元従業員による情報不正持ち出し 2025.12.1 Mon 8:05 刑事告訴検討 ～ ヤマト運輸の元従業員が取引先企業に関する情報の一部を不正に持ち出し 2 社に流出 2025.10.20 Mon 8:05 シンガポールヤマト運輸に不正アクセス、個人情報の不正持ち出しが判明 2024.11.18 M</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5308,7 +5326,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/10/01/56361.html</t>
         </is>
       </c>
     </row>
@@ -5320,13 +5338,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline）</t>
+          <t>eplus（tracker headline）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
+          <t>eplus（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5362,13 +5380,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ）</t>
+          <t>Unirita（tracker headline）</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
+          <t>Unirita（tracker headline） — Unauthorized access and data theft claimed by ransomware group Everest.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5404,13 +5422,13 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline）</t>
+          <t>Starts Publishing (OZmall)（ disclosure ）</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
+          <t>Starts Publishing (OZmall)（ disclosure ） — Mass unauthorized access from overseas Sep 26. Countermeasures applied to the vulnerability.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5446,13 +5464,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline）</t>
+          <t>Shinano Mainichi Shimbun（tracker headline）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
+          <t>Shinano Mainichi Shimbun（tracker headline） — Unauthorized access to point-exchange system.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5488,13 +5506,13 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
+          <t>Lashinbang（tracker headline）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
+          <t>Lashinbang（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5530,13 +5548,13 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ）</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline）</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
+          <t>Japan Atomic Energy Agency (JRR-3)（tracker headline） — Unauthorized access and unauthorized downloads.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5567,43 +5585,29 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>日本郵便</t>
+          <t>ALSOK Joylife（ news report ）</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>ALSOK Joylife（ news report ） — Unauthorized access and remote operation of a terminal at a nursing home; identified Jul 4.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5611,12 +5615,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5638,7 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
+          <t>郵便局アプリに不正アクセス、19人分の個人情報流出 送り状の受取人住所や追跡番号も - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5647,7 +5651,16 @@
           <t>確認・可能性あり</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>Google News</t>
@@ -5658,12 +5671,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjMnhMTUVJUlVxYlNkU3FLX3FTMU5uWjVxNkZhcGNzMHpYN1JBYTFaZmpHcjM4alE0T3cyTkRHenh5bFlYZ3FaUjF3WVV4eWRCbXFCVE9VTGhrdGFGWUxjX0ZlcWN6N2JPSVE?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE9BZ2t1YXlpbXM5blIzZURycHBqRlBGNEZWOWk4VmhkMm1IY0MzbFJySGhOWEpiWUVQY1VlQzk5TXhSU09kdDQ1cHB4bmRDTTFvQ3FEOFo3cHFhazFJdlhycU9VcDUxM0g2czJTRzYwVFBGUDM2VGVWeEUwS3pybWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5675,42 +5688,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>警察庁が対策情報を紹介 警察庁</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>ランサムウェア被害拡大中</t>
-        </is>
-      </c>
+          <t>日本郵便</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア被害から学ぶ教訓集」～ 経営者のためのランサムウェア対策ハンドブック ～ https://www.ipa.go.jp/security/todokede/crack-virus/ransomware_lessons_learned.html 個人</t>
+          <t>郵便局アプリに不正アクセス 個人情報漏えいか - ASCII.jp</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE45VnNBSDlnWmc1SEJ1aEdNa3RGejZLQmZ3SHlORV9hT2NTcWo2S1R4S245ODBOMWd0cG41QWhDTWJ1cUhjeFVtUUl3cE43RVBTOWt5TA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5735,17 +5735,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学</t>
+          <t>警察庁が対策情報を紹介 警察庁</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>サイバー攻撃共同対処訓練</t>
+          <t>ランサムウェア被害拡大中</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 また、同訓練では、サイバー攻撃への対処の速さやサービスの継続性などをポイント化して競うチーム対抗形式のコンテストが実施され、同学数理情報科学科2年生（長尾柚葉氏、清水海凜氏、奥田陸斗氏、松岡俊汰氏）のチームが優勝している。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 </t>
+          <t>警察庁は9月18日、サイバー警察局便りR8Vol.16「ランサムウェア被害拡大中」を公開した。 同便りでは、令和8（2026）年上半期における国内のランサムウェア被害報告件数が123件で、半期の件数としては過去最多となっていることを取り上げている。 同便りでは、各機関からランサムウェア対策情報が公開中であるとし、下記を紹介している。 政府広報オンライン動画「中小企業で被害多数 ランサムウェア」 https://www.gov-online.go.jp/useful/202506/video-298784.html 日本サイバー犯罪対策センター（JC3）「JC3ポッドキャスト ランサムウェア・ダイアログ」 https://www.jc3.or.jp/news/2025/20251209-662.html 情報処理推進機構（IPA）「ランサムウェア被害から学ぶ教訓集」～ 経営者のためのランサムウェア対策ハンドブック ～ https://www.ipa.go.jp/security/todokede/crack-virus/ransomware_lessons_learned.html 個人</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56339.html</t>
         </is>
       </c>
     </row>
@@ -5795,22 +5795,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>処訓練」で約 90 名が Micro Hardening 演習 山陽小野田市立山口東京理科大学</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.30 Wed 8:05 日本郵便 調査請求 Web受付サービスに不正アクセ</t>
+          <t>サイバー攻撃共同対処訓練</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56344;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵便株式会社は9月25日、同社の国際郵便物の調査請求Web受付サービスへの不正アクセスについて発表した。 これは9月25日午後3時頃に、調査請求Web受付サービスで使用しているサーバに対し、外部から不正アクセスの可能性が発覚したというもの。 同社では現在、同サービスについて一時的に受付を停止している。 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配達資料を撮影 2025.1.28 Tue 8:05 保有ドメインへ不正アクセス、迷惑メール送信の踏み台に（日本郵便） 2020.2.18 Tue 10:00 弓削郵便局で居住者情報を記載</t>
+          <t xml:space="preserve">山陽小野田市立山口東京理科大学は9月15日、山口県警察の協力のもと、山口大学工学部で「サイバー攻撃共同対処訓練」を9月4日に実施したと発表した。 同訓練は、増加するサイバー犯罪への対応力向上を目的として、県内の大学、企業や警察などから、オンライン参加を含め約90名20チームが参加しており、同学数理情報科学科から3チームの学生が参加している。 同訓練では、商品販売サイトがサイバー攻撃を受けた状況を想定し、実践的なサイバーセキュリティ演習「Micro Hardening」が行われ、参加者はチームごとに役割を分担し、Webサイトの改ざんやアクセス障害など、次々と発生するサイバー攻撃の原因を特定しながら、システムの復旧や再発防止に取り組んでいる。 また、同訓練では、サイバー攻撃への対処の速さやサービスの継続性などをポイント化して競うチーム対抗形式のコンテストが実施され、同学数理情報科学科2年生（長尾柚葉氏、清水海凜氏、奥田陸斗氏、松岡俊汰氏）のチームが優勝している。 メール訓練の文面が無神経と批判を浴びてＣＥＯが謝罪 ～ セキュリティ教育には分別と敬意を 2026.8.25 Tue 8:15 </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>29,116</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html / https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56340.html</t>
         </is>
       </c>
     </row>
@@ -5860,17 +5860,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.30 Wed 8:05 保育上の不適切な対応も確認 ～ 鎌倉市児童発達支援</t>
+          <t>Web受付サービスに不正アクセス</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56341;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。 鎌倉市児童発達支援センターあおぞら園では6月に個人情報の誤送付事案が発生し、2025年3月にも同様の事案が判明したため、同市では6月23日付で指定管理者の社会福祉法人県央福祉会に対し、令和3（2021）年度以降の指定管理期間における管理業務の総点検と総合的な再発防止策の報告を指示している。 指定管理者から7月31日付で提出された総点検結果によると、5年間の指定管理期間を通じて、13件の個人情報管理</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56344;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本郵便株式会社は9月25日、同社の国際郵便物の調査請求Web受付サービスへの不正アクセスについて発表した。 これは9月25日午後3時頃に、調査請求Web受付サービスで使用しているサーバに対し、外部から不正アクセスの可能性が発覚したというもの。 同社では現在、同サービスについて一時的に受付を停止している。 「誤った配達をしないように」 ～ 同姓の顧客居住地域の配達資料を撮影 2025.1.28 Tue 8:05 保有ドメインへ不正アクセス、迷惑メール送信の踏み台に（日本郵便） 2020.2.18 Tue 10:00 弓削郵便局で居住者情報を記載</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29,116</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>氏名, 住所, クレジットカード情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56344.html</t>
         </is>
       </c>
     </row>
@@ -5915,22 +5915,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.30 Wed 8:05 京王電鉄にランサムウェア攻撃 京王電鉄株式会社は9</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支障はない。 「西武 旅するレストラン 『52 席の至福』」予約サイトで予約関連情報の一部が漏えい 2026.9.24 Thu 8:05 駅放送設備から意図しない音声が送出 ～ 西鉄福岡（天神）駅と薬院駅 2026</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56341;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 神奈川県鎌倉市は9月10日、鎌倉市児童発達支援センターあおぞら園での個人情報の誤送付について発表した。あわせて保育上の不適切な対応も確認されている。 鎌倉市児童発達支援センターあおぞら園では6月に個人情報の誤送付事案が発生し、2025年3月にも同様の事案が判明したため、同市では6月23日付で指定管理者の社会福祉法人県央福祉会に対し、令和3（2021）年度以降の指定管理期間における管理業務の総点検と総合的な再発防止策の報告を指示している。 指定管理者から7月31日付で提出された総点検結果によると、5年間の指定管理期間を通じて、13件の個人情報管理</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 従業員情報</t>
+          <t>氏名, 住所, クレジットカード情報</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56341.html</t>
         </is>
       </c>
     </row>
@@ -5975,22 +5975,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5 ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングス</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HALMEK up</t>
+          <t>システム障害について発表した</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56343;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。 これは社員1名のID・パスワードが窃取されたことが原因で、「HALMEK up」管理画面への不正アクセスの発生を9月9日に確認したというもの。 同社では不正アクセス確認後に、管理画面へのサイトアクセスに必要なパスワードの変更を実施するとともに、外部専門家の協力のもと調査を開始している。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56345;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 京王電鉄株式会社は9月26日、ランサムウェア攻撃によるシステム障害について発表した。 これは9月26日未明に、同社グループのサーバへのランサムウェア攻撃を確認したというもので、一部グループ会社の営業システムに支障が生じている。また、「お問合せフォーム」に登録された内容が同社で確認できない状態となっている。 なお、現時点で鉄道の運行には支障はない。 「西武 旅するレストラン 『52 席の至福』」予約サイトで予約関連情報の一部が漏えい 2026.9.24 Thu 8:05 駅放送設備から意図しない音声が送出 ～ 西鉄福岡（天神）駅と薬院駅 2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>978</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+          <t>クレジットカード情報, 従業員情報</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56345.html</t>
         </is>
       </c>
     </row>
@@ -6170,24 +6170,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>ID・パスワードが窃取が原因 ～「HALMEK up」に不正アクセス 株式会社ハルメクホールディングス</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HALMEK up</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>G-Point（tracker headline） — Unauthorized access.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56343;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ハルメクホールディングスは9月11日、同社グループのWebサイト「HALMEK up」への不正アクセスについて発表した。 これは社員1名のID・パスワードが窃取されたことが原因で、「HALMEK up」管理画面への不正アクセスの発生を9月9日に確認したというもの。 同社では不正アクセス確認後に、管理画面へのサイトアクセスに必要なパスワードの変更を実施するとともに、外部専門家の協力のもと調査を開始している。 マネジメントサービスセンターのホームページに不正アクセス、管理者権限の取得や改ざんを確認 2026.9.18 Fri 8:05 フィ</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6200,54 +6218,36 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/30/56343.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>WaterPlum</t>
-        </is>
-      </c>
+          <t>G-Point（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書によると、北朝鮮サイバー攻撃グループ「WaterPlum」は、警戒心の薄い求職者のコンピュータネットワークに密かに侵入し、機密情報の収集や暗号資産を盗み出すことを主な目的として、日本、米国、欧州及びその他の国々を標的としてサイバー攻撃を行っている。 警察庁とFBIでは、「WaterPlum」と一部の北朝鮮IT労働者が、北朝鮮朝鮮労働党（WPK）中央委員会軍需工業部313総局</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>G-Point（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -6272,22 +6272,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>サイトに不正アクセス - 個人情報流出の可能性</t>
+          <t>あいこんナビ</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56325;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 愛知県は9月22日、同県が管理・運営する出会いサポートポータルサイト「あいこんナビ」での個人情報の誤掲載について発表した。 これは「あいこんナビ」のイベント情報にて、イベント主催団体が保有する、イベントに直接関係のない非公開情報が誤掲載され、氏名、年齢等の個人情報が読み取れる状態になっていたというもの。9月20日午後2時30分頃に一般の人から連絡があり、発覚した。 埼玉県「公文書検索・閲覧システム」で不開示情報を誤掲載 2024.6.3 Mon 8:05 県実施ユーチューバートークイベントで申込者の個人情報が閲覧可能に 2023.11.8 We</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6295,10 +6295,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>5,261</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6311,7 +6320,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190798</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
         </is>
       </c>
     </row>
@@ -6323,34 +6332,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>6.9.29 Tue 8:00 求職者やエンジニアを狙うヘッドハンティング型攻撃 ～ 警察庁</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>WaterPlum</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
+          <t>警察庁は9月18日、北朝鮮サイバー攻撃グループ「WaterPlum」及び北朝鮮IT労働者に関する日本、米国、豪州及びドイツによるパブリック・アトリビューションについて発表した。 警察庁及び国家サイバー統括室は9月18日に、米国、豪州、ドイツとともに北朝鮮を背景とするサイバー攻撃グループ「WaterPlum」（関連名称：Contagious Interview）の攻撃手口や、北朝鮮IT労働者による外貨獲得活動及び採用応募活動の実態について、合同で文書を公表している。 北朝鮮に関する実態は、民間事業者からの情報提供や警察庁関東管区警察局サイバー特別捜査部及び都道府県警察の捜査・分析等を通じて明らかになったという。 同文書によると、北朝鮮サイバー攻撃グループ「WaterPlum」は、警戒心の薄い求職者のコンピュータネットワークに密かに侵入し、機密情報の収集や暗号資産を盗み出すことを主な目的として、日本、米国、欧州及びその他の国々を標的としてサイバー攻撃を行っている。 警察庁とFBIでは、「WaterPlum」と一部の北朝鮮IT労働者が、北朝鮮朝鮮労働党（WPK）中央委員会軍需工業部313総局</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6363,7 +6380,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56320.html</t>
         </is>
       </c>
     </row>
@@ -6380,12 +6397,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>あいこんナビ</t>
+          <t>個別お打合せのご提案</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56325;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 愛知県は9月22日、同県が管理・運営する出会いサポートポータルサイト「あいこんナビ」での個人情報の誤掲載について発表した。 これは「あいこんナビ」のイベント情報にて、イベント主催団体が保有する、イベントに直接関係のない非公開情報が誤掲載され、氏名、年齢等の個人情報が読み取れる状態になっていたというもの。9月20日午後2時30分頃に一般の人から連絡があり、発覚した。 埼玉県「公文書検索・閲覧システム」で不開示情報を誤掲載 2024.6.3 Mon 8:05 県実施ユーチューバートークイベントで申込者の個人情報が閲覧可能に 2023.11.8 We</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56330;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 選挙ドットコムを運営するイチニ株式会社は9月10日、メール誤送信によるメールアドレス漏えいについて発表した。 これは9月6日に、同社から送信した「個別お打合せのご提案」と題するメールについて、「BCC」等で送信すべき送信先メールアドレスを「宛先」で送信したことで、当該メールの受信者以外の他の顧客のメールアドレスが表示される状況となったというもの。 公益財団法人 九州先端科学技術研究所でメール誤送信、見積書を自治体 ML 宛に送信 2026.9.15 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 202</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6400,12 +6417,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>5,261</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>氏名, クレジットカード情報</t>
+          <t>メールアドレス, クレジットカード情報</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6423,7 +6440,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56325.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html</t>
         </is>
       </c>
     </row>
@@ -6435,22 +6452,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>Helpfeel</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>個別お打合せのご提案</t>
+          <t>モンベル・グローバルサイト</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56330;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 選挙ドットコムを運営するイチニ株式会社は9月10日、メール誤送信によるメールアドレス漏えいについて発表した。 これは9月6日に、同社から送信した「個別お打合せのご提案」と題するメールについて、「BCC」等で送信すべき送信先メールアドレスを「宛先」で送信したことで、当該メールの受信者以外の他の顧客のメールアドレスが表示される状況となったというもの。 公益財団法人 九州先端科学技術研究所でメール誤送信、見積書を自治体 ML 宛に送信 2026.9.15 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 202</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。 REXTにランサムウェア攻撃、流出した可能性のある情報の一部がインターネット上に掲載 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6460,12 +6477,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>メールアドレス, クレジットカード情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6483,7 +6500,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56330.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
         </is>
       </c>
     </row>
@@ -6495,17 +6512,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>モンベル・グローバルサイト</t>
+          <t>サイトに不正アクセス - 個人情報流出の可能性</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56332;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); モンベルグループは9月18日、同社が運営する「モンベル・グローバルサイト」への不正アクセスについて発表した。 これは「モンベル・グローバルサイト」に外部から不正アクセスがあり、一部顧客の個人情報が漏えいした可能性が9月12日に判明したというもの。 REXTにランサムウェア攻撃、流出した可能性のある情報の一部がインターネット上に掲載 2026.9.28 Mon 8:05 画像共有サービス「Gyazo」に不正アクセス、約2,362万件のユーザーに関するデータが流出 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス、一時閉</t>
+          <t>アウトドア用品の製造、販売を手がけるモンベルは、海外向けの発送を取り扱うグローバルサイトが不正アクセスを受け、顧客の個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6518,19 +6535,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6543,7 +6551,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56332.html</t>
+          <t>https://www.security-next.com/190798</t>
         </is>
       </c>
     </row>
@@ -6555,17 +6563,13 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>ワンストップジョブサイトくまもと</t>
-        </is>
-      </c>
+          <t>ニッポンレンタカーサービス</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56326;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 熊本県は9月9日、同県が運営する「ワンストップジョブサイトくまもと」への不正アクセスについて発表した。 これは「ワンストップジョブサイトくまもと」に外部から不正アクセスがあり、一部内容が改ざんされたというもの。当該サイトの利用登録画面で会員規約の同意ボタンをクリックすると、「ウイルスが検出された」等の偽の警告で不安を煽り、有料アプリのインストールへ誘導する「フェイクアラート（偽の警告広告）」が表示される状態となっていたという。 熊本県「白塗り」PDF 公開 ～ 他自治体の黒塗り PDF 案件報道で確認したところ発覚 2025.10.30 Thu</t>
+          <t>ニッポンレンタカーにも不正アクセスで41名の情報漏洩 免許証情報も（Impress Watch） - Yahoo!ニュース</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6575,22 +6579,18 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29,451</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9GRVUweTgwQ09HcjFfZ292bUhuSE56clBVSVZ5MFE5alBfaXVXaHFFWW9FR3ByZ0ljdUR3UXV2bnp6TDhuMXNyWG1hTHRjdVNoRUdvWEgwcmhhbHF2WFdVUmhocjc0OFlRdzdmSV85RUhSdFdvSzF1Q0dCZ2JSTDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6662,17 +6662,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>メトポ</t>
+          <t>ワンストップジョブサイトくまもと</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56326;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 熊本県は9月9日、同県が運営する「ワンストップジョブサイトくまもと」への不正アクセスについて発表した。 これは「ワンストップジョブサイトくまもと」に外部から不正アクセスがあり、一部内容が改ざんされたというもの。当該サイトの利用登録画面で会員規約の同意ボタンをクリックすると、「ウイルスが検出された」等の偽の警告で不安を煽り、有料アプリのインストールへ誘導する「フェイクアラート（偽の警告広告）」が表示される状態となっていたという。 熊本県「白塗り」PDF 公開 ～ 他自治体の黒塗り PDF 案件報道で確認したところ発覚 2025.10.30 Thu</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6682,13 +6682,22 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29,451</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6701,7 +6710,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190791</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/29/56326.html</t>
         </is>
       </c>
     </row>
@@ -6713,24 +6722,33 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>メトポ</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
+          <t>東京地下鉄（東京メトロ）は、ポイントサービス「メトロポイントクラブ（メトポ）」が第三者によって侵害されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -6743,7 +6761,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190791</t>
         </is>
       </c>
     </row>
@@ -6755,13 +6773,13 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline）</t>
+          <t>Toyobo Textile（tracker headline）</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Saga University（tracker headline） — Ransomware.</t>
+          <t>Toyobo Textile（tracker headline） — Unauthorized access to an email account.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6797,13 +6815,13 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ）</t>
+          <t>Saga University（tracker headline）</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
+          <t>Saga University（tracker headline） — Ransomware.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6839,13 +6857,13 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline）</t>
+          <t>QUO Card（ news report ）</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
+          <t>QUO Card（ news report ） — Unauthorized access to official LINE account campaign system. Entry route not stated.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6881,13 +6899,13 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+          <t>International House of Japan (library)（tracker headline）</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
+          <t>International House of Japan (library)（tracker headline） — Unauthorized access to library catalog system (OPAC).</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6923,42 +6941,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>イープラス</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>スマチケ</t>
-        </is>
-      </c>
+          <t>Aiphone (Australian subsidiary)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Aiphone (Australian subsidiary)（tracker headline） — Unauthorized access to internal network.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>1,463</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>氏名, メールアドレス, 口座情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -6971,29 +6971,29 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁</t>
+          <t>イープラス</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大</t>
+          <t>スマチケ</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのURLをブックマーク登録しておき、ブックマークからアクセスする。 3.インターネット取引サービスを利用する際は、各証券会社が提供しているセキュリティ強化機能（ログイン時・取引実行時・出金時の多要素認証や通知サービス）を有効にして、不審な取引に注意する。 4.パスワードの使いまわしを</t>
+          <t>株式会社イープラス（東京都渋谷区恵比寿／チケット販売サイト「e+」の運営）は2026年9月29日、電子チケット「スマチケ」の払戻し情報を管理するシステムが第三者から不正アクセスを受け、個人情報が漏えいしたと公表した。対象は2022年6月30日から2026年9月11日までに払戻しを申請した利用者の計1,463件で、全件にカナ氏名・メールアドレス・払戻し対象公演の情報が含まれ、うち751件には金融機関名・支店名・口座番号などの振込先口座情報が含まれる。不正アクセスは9月11日夜から12日未明にかけて複数回発生し、9月15日に遮断されている。</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7003,22 +7003,22 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1,463</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+          <t>氏名, メールアドレス, 口座情報</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-30-eplus-sumachike-refund-system-breach/</t>
         </is>
       </c>
     </row>
@@ -7043,17 +7043,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>金融庁が注意喚起 2026年8月は4社で25件の不正取引 金融庁</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>サーバに不正アクセスか - 詳細は調査中</t>
+          <t>ecurity 2026.9.28 Mon 8:00 ネット証券等の不正取引被害が拡大</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>金融庁は9月9日、インターネット取引サービスへの不正アクセス・不正取引による被害への注意喚起を発表した。 同庁によると、実在する証券会社のウェブサイトを装った偽のウェブサイト（フィッシングサイト）等で窃取した顧客情報によるインターネット取引サービスでの不正アクセス・不正取引の被害について、2026年8月は不正取引が発生した証券会社数が4社、不正アクセス件数が39件、不正取引件数が25件発生している。 同庁では、被害に遭わないために、証券会社のインターネット取引サービスを利用しているすべてのユーザーに下記の点に注意するよう呼びかけている。 1.見覚えのある送信者からのメールやSMS等であっても、メッセージに掲載されたリンクを開かない。 2.利用する証券会社のウェブサイトへのアクセスは、事前に正しいウェブサイトのURLをブックマーク登録しておき、ブックマークからアクセスする。 3.インターネット取引サービスを利用する際は、各証券会社が提供しているセキュリティ強化機能（ログイン時・取引実行時・出金時の多要素認証や通知サービス）を有効にして、不審な取引に注意する。 4.パスワードの使いまわしを</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7063,13 +7063,22 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7082,7 +7091,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190734</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56308.html</t>
         </is>
       </c>
     </row>
@@ -7094,51 +7103,55 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>日本大学</t>
+          <t>Helpfeel</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>メールアカウントが不正アクセスを受けたことを明らかにした</t>
+          <t>Gyazo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>日本大学は、教員5人のメールアカウントが不正アクセスを受けたことを明らかにした。迷惑メールなども送信されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆弱性を悪用し、第三者が同社のシステム上で任意のコマンドを実行する不正アクセスがあり、同社では同日夜に不正な挙動を検知し、調査および対応を開始していた。 「はいチーズ！フォト」に不正アクセス、漏えい件数の公表は顧客の保護と二次被害防止の観点から差し控える 2026.8.20 Thu 8:05 「はいチーズ！フォト」への不正アクセス、漏</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura / ScanNetSecurity</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190319</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
         </is>
       </c>
     </row>
@@ -7150,33 +7163,42 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>京王電鉄</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>システムに影響 - 京王電鉄</t>
+          <t>山東聖泉</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記録を対象家庭に匿名で郵送、市職員 生活福祉課 主幹 50歳 逮捕 2026.9.16 Wed 8:05 個人情報を無断で持ち出し 不正競争防止法違反容疑で逮捕 2026.7.31 Fri 8:05 器物損壊罪等で逮捕された津田塾大学元職員、個人情</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7189,7 +7211,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190761</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
         </is>
       </c>
     </row>
@@ -7201,17 +7223,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Helpfeel</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Gyazo</t>
+          <t>サーバに不正アクセスか - 詳細は調査中</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56313;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社Helpfeelは9月25日、9月16日に公表した同社提供の画像共有サービス「Gyazo」への不正アクセスについて、第二報を発表した。 同社では9月11日に、「Gyazo」の画像アップロードサーバに存在した脆弱性を悪用し、第三者が同社のシステム上で任意のコマンドを実行する不正アクセスがあり、同社では同日夜に不正な挙動を検知し、調査および対応を開始していた。 「はいチーズ！フォト」に不正アクセス、漏えい件数の公表は顧客の保護と二次被害防止の観点から差し控える 2026.8.20 Thu 8:05 「はいチーズ！フォト」への不正アクセス、漏</t>
+          <t>日本郵便は、国際郵便物の調査請求ウェブ受付サービスで使用しているサーバが、不正アクセスを受けた可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7221,35 +7243,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yagura / ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-19-helpfeel-gyazo-upload-server-breach/ / https://scan.netsecurity.ne.jp/article/2026/09/28/56313.html</t>
+          <t>https://www.security-next.com/190734</t>
         </is>
       </c>
     </row>
@@ -7261,42 +7274,33 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>旭化成</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>山東聖泉</t>
+          <t>システムに影響 - 京王電鉄</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56311;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 旭化成株式会社は9月17日、元従業員の逮捕について発表した。 これは同社の元従業員が、在職中に入手した同社の潜在性硬化剤に関わる機密情報を不正に持ち出し、第三者である中国の山東聖泉新材料股份有限公司（山東聖泉）へ流出させたとして、不正競争防止法違反の容疑で愛知県警に逮捕されたというもの。 家庭児童相談記録を対象家庭に匿名で郵送、市職員 生活福祉課 主幹 50歳 逮捕 2026.9.16 Wed 8:05 個人情報を無断で持ち出し 不正競争防止法違反容疑で逮捕 2026.7.31 Fri 8:05 器物損壊罪等で逮捕された津田塾大学元職員、個人情</t>
+          <t>京王電鉄は、同社グループのサーバがランサムウェア攻撃を受け、一部でシステム障害が発生していることを明らかにした。鉄道運行への影響は否定している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/28/56311.html</t>
+          <t>https://www.security-next.com/190761</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7330,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.28 Mon 8:05 PCデポのメールドメインの認証情報を不正利用</t>
+          <t>メールドメインの認証情報を不正利用</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7386,7 +7390,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.28 Mon 8:05 JA遠州夢咲ホームページに不正アクセス</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7784,22 +7788,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026年8月の情報漏えい</t>
+          <t>メール誤送信</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知らないところで漏えい事件は起き続けている。 頼まれもしないのに月ごとの情報漏えいの動向を勝手にウォッチしている、虫の音ならぬ虫の息のような本連載、今月も一寸の虫のようにひっそりと掲載である。 ●インシデント原因内訳 さて、先月 2026 年 8 月に本誌が取り上げた事故・インシデント記事は 2026 年 7 月の 84 本から 42 本増となる全</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56301;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社京都パープルサンガは9月8日、ファンクラブ会員情報の誤送信による個人情報漏えいについて発表した。 これは9月2日午前11時15分に、同社の担当者が取引先企業の担当者へメールを送信した際、誤ってファンクラブ会員情報が記載されたファイルを添付したというもの。メールを受信した11名のうち2名がファイルを開封したことを確認している。 京都サンガF.C.公式サイトで未発表の試合情報が漏えい 2022.2.8 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 2026.7.16 Thu 8:05 フィルタを解</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7809,12 +7813,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
+          <t>クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7827,12 +7831,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html</t>
         </is>
       </c>
     </row>
@@ -7844,22 +7848,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.25 Fri 8:05 京都パープルサンガでメール誤送信</t>
+          <t>2026年8月の情報漏えい</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56301;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社京都パープルサンガは9月8日、ファンクラブ会員情報の誤送信による個人情報漏えいについて発表した。 これは9月2日午前11時15分に、同社の担当者が取引先企業の担当者へメールを送信した際、誤ってファンクラブ会員情報が記載されたファイルを添付したというもの。メールを受信した11名のうち2名がファイルを開封したことを確認している。 京都サンガF.C.公式サイトで未発表の試合情報が漏えい 2022.2.8 Tue 8:05 取引先に送付した「注文書フォーム」エクセルファイル内に顧客リストが残存 2026.7.16 Thu 8:05 フィルタを解</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56306;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 今日もどこかで情報漏えいは起きている。 大きいところでは誰もが社名を耳にしたことがある東証プライム上場企業や霞ヶ関の政府機関、小さなところでは従業員数名規模の企業や市町村役場に至るまで、毎日、あなたの知らないところで漏えい事件は起き続けている。 頼まれもしないのに月ごとの情報漏えいの動向を勝手にウォッチしている、虫の音ならぬ虫の息のような本連載、今月も一寸の虫のようにひっそりと掲載である。 ●インシデント原因内訳 さて、先月 2026 年 8 月に本誌が取り上げた事故・インシデント記事は 2026 年 7 月の 84 本から 42 本増となる全</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7869,12 +7873,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7887,12 +7891,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56143.html / https://scan.netsecurity.ne.jp/article/2026/09/08/56157.html / https://scan.netsecurity.ne.jp/article/2026/09/25/56301.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/25/56306.html</t>
         </is>
       </c>
     </row>
@@ -8061,22 +8065,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
+          <t>非常勤講師が外部SNSサービス「hyocom」を利用 関西学院大学</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正</t>
+          <t>hyocom</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証するセキュリティモデル）を」と求め、VPNで「ゼロトラスト」が働く境界の手前の領域も含めた防御の再構築を促している。 VPNの脆弱性を利用 ～ デジタル庁が運用するガバメントソリューションサービス（GSS）に不正アクセス、約24.6万件の個人情報が漏えいした可能性 2026.9.14 Mon 8:05 「ガバメントソリ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56290;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。 これは同学の非常勤講師が授業運営に際し、同学と無関係の外部SNSサービス「hyocom」を利用し、学生の個人情報を公開した上、公開範囲の管理を適切に行っていなかったことから、個人情報が外部から閲覧可能な状態となっていたというもの。外部から公益通報受付窓口に寄せられた情報提供を受けて、2026年7月に発覚している。 誤ってフィッシングサイトにアクセス、学生や卒業生ら1,466人分の個人情報の</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8086,7 +8090,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>1,466</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8104,12 +8108,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
         </is>
       </c>
     </row>
@@ -8121,22 +8125,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>非常勤講師が外部SNSサービス「hyocom」を利用 関西学院大学</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>hyocom</t>
+          <t>ecurity 2026.9.24 Thu 8:00 ガバメントソリューションサービス（GSS）への不正</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56290;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 関西学院大学は9月1日、同学の非常勤講師が授業運営のために利用していた外部SNSサービス「hyocom」で学生の個人情報が閲覧可能な状態にあったと発表した。 これは同学の非常勤講師が授業運営に際し、同学と無関係の外部SNSサービス「hyocom」を利用し、学生の個人情報を公開した上、公開範囲の管理を適切に行っていなかったことから、個人情報が外部から閲覧可能な状態となっていたというもの。外部から公益通報受付窓口に寄せられた情報提供を受けて、2026年7月に発覚している。 誤ってフィッシングサイトにアクセス、学生や卒業生ら1,466人分の個人情報の</t>
+          <t>自由民主党（自民党）は9月15日、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について、政府から説明を受けたと発表した。 党国家サイバーセキュリティ戦略本部とデジタル社会推進本部は9月15日に合同会議を開き、ガバメントソリューションサービス（GSS）への不正アクセスによる個人情報漏えい事案について政府から説明を受け、原因究明や再発防止策について協議したという。 党国家サイバーセキュリティ戦略本部の平将明本部長（衆院議員）は「政府の信用を大きく傷つける深刻な問題」と指摘するとともに、システム面の問題にとどまらない影響にも懸念を示し「国民の情報がもれなくてよかったという話ではない」と強調した上で「本当のゼロトラスト（通信ごとに安全性を検証するセキュリティモデル）を」と求め、VPNで「ゼロトラスト」が働く境界の手前の領域も含めた防御の再構築を促している。 VPNの脆弱性を利用 ～ デジタル庁が運用するガバメントソリューションサービス（GSS）に不正アクセス、約24.6万件の個人情報が漏えいした可能性 2026.9.14 Mon 8:05 「ガバメントソリ</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8146,7 +8150,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1,466</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8164,12 +8168,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56290.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8353,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56287.html</t>
         </is>
       </c>
     </row>
@@ -8529,33 +8533,42 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>日本大学</t>
+          <t>原田産業</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>メールが送信 - 日大</t>
+          <t>ECプラットフォームに不正アクセス 株式会社カインドオルは8月28日</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56270;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社カインドオルは8月28日、同社が運営するECサイトで利用しているECプラットフォームのスタッフアカウントへの不正アクセスについて発表した。 これは8月24日に、同社が通常業務として注文情報の出力を行った際に、ECプラットフォームのスタッフアカウントに登録されているメールアドレスが同社で使用していないものに変更されていることを確認したため、ECプラットフォームの運営会社に調査を依頼したところ、当該スタッフアカウントに第三者から不正アクセスが行われた後、8月23日に顧客情報の一括エクスポートが2回行われていたことが判明したというもの。 EC</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>メールアドレス, クレジットカード情報, 認証情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8568,7 +8581,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190198</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
         </is>
       </c>
     </row>
@@ -8580,33 +8593,42 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>サイト改ざん</t>
+          <t>捜査に必要と求められ</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56269;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社安藤・間（安藤ハザマ）は8月31日、名刺情報の外部流出について発表した。 これは8月16日から8月23日にかけて、同社社員が警察官を名乗る者から、交友関係の捜査に必要であるとして名刺情報を提出するよう求められ、当該社員は8月17日に同社の名刺管理システムに保管していた名刺情報をダウンロードの上、相手方にメールで提出したというもの。 名刺管理システムへ不正アクセス、サービス運営会社からの連絡で発覚 2023.5.9 Tue 8:05 名刺管理システムへの不正アクセス ～ 当の名刺管理システム会社名乗り電話とメールでIDパスワード詐取 20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8619,7 +8641,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189792</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html</t>
         </is>
       </c>
     </row>
@@ -8631,42 +8653,33 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>原田産業</t>
+          <t>日本大学</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.18 Fri 8:05 顧客情報の一括エクスポートを確認 ～ カインドオル</t>
+          <t>メールが送信 - 日大</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56270;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社カインドオルは8月28日、同社が運営するECサイトで利用しているECプラットフォームのスタッフアカウントへの不正アクセスについて発表した。 これは8月24日に、同社が通常業務として注文情報の出力を行った際に、ECプラットフォームのスタッフアカウントに登録されているメールアドレスが同社で使用していないものに変更されていることを確認したため、ECプラットフォームの運営会社に調査を依頼したところ、当該スタッフアカウントに第三者から不正アクセスが行われた後、8月23日に顧客情報の一括エクスポートが2回行われていたことが判明したというもの。 EC</t>
+          <t>日本大学は、フィッシング攻撃により、教職員のメールアカウントが乗っ取られたことを明らかにした。同アカウントから不審なメールが送信されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報, 認証情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8679,7 +8692,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56270.html</t>
+          <t>https://www.security-next.com/190198</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8709,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>捜査に必要と求められ</t>
+          <t>交通安全施設損壊事案報告書</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56269;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社安藤・間（安藤ハザマ）は8月31日、名刺情報の外部流出について発表した。 これは8月16日から8月23日にかけて、同社社員が警察官を名乗る者から、交友関係の捜査に必要であるとして名刺情報を提出するよう求められ、当該社員は8月17日に同社の名刺管理システムに保管していた名刺情報をダウンロードの上、相手方にメールで提出したというもの。 名刺管理システムへ不正アクセス、サービス運営会社からの連絡で発覚 2023.5.9 Tue 8:05 名刺管理システムへの不正アクセス ～ 当の名刺管理システム会社名乗り電話とメールでIDパスワード詐取 20</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56275;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 長野県警察は9月7日、塩尻警察署交通課での個人情報の所在不明について発表した。 これは塩尻警察署交通課が、令和3（2021）年度中に交通事故や自然災害等で交通安全施設の損壊等が発生した際に作成した「交通安全施設損壊事案報告書」「交通安全施設修繕執行伺」「交通安全施設修理結果表」「道路標識標示工事監督等指示書」、交通安全施設への意見・要望が寄せられた際に作成した「信号機BOX」が所在不明となったというもの。 12 名の個人情報記載した「交通切符等引継簿」紛失 ～ 釧路方面弟子屈警察署 2026.5.12 Tue 8:05 拾得物として届けられ回収</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8716,12 +8729,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8739,7 +8752,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56269.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html</t>
         </is>
       </c>
     </row>
@@ -8751,42 +8764,33 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>交通安全施設損壊事案報告書</t>
+          <t>サイト改ざん</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56275;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 長野県警察は9月7日、塩尻警察署交通課での個人情報の所在不明について発表した。 これは塩尻警察署交通課が、令和3（2021）年度中に交通事故や自然災害等で交通安全施設の損壊等が発生した際に作成した「交通安全施設損壊事案報告書」「交通安全施設修繕執行伺」「交通安全施設修理結果表」「道路標識標示工事監督等指示書」、交通安全施設への意見・要望が寄せられた際に作成した「信号機BOX」が所在不明となったというもの。 12 名の個人情報記載した「交通切符等引継簿」紛失 ～ 釧路方面弟子屈警察署 2026.5.12 Tue 8:05 拾得物として届けられ回収</t>
+          <t>コンサルティングサービスを提供しているマネジメントサービスセンターは、ウェブサイトが第三者により不正アクセスを受け、改ざんされたことを明らかにした。サイト内部には個人情報が保存されていたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -8799,7 +8803,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56275.html</t>
+          <t>https://www.security-next.com/189792</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8820,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.18 Fri 8:05 マネジメントサービスセンターのホームページに不正ア</t>
+          <t>サーバ上にバックドア等の不正プログラムを設置 ～ 繋が運営するコーポレートサイトに不正アクセス 株式会社繋</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56274;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社マネジメントサービスセンターは8月25日、同社ホームページへの不正アクセスについて発表した。 これは7月に、同社ホームページへの第三者からの不正アクセスおよびホームページ改ざんを確認したというもの。 まんだらけサーバに不正アクセス、「大オークション大会」の開催を延期 2026.9.2 Wed 8:05 イエローハットWEB作業予約システムへの不正プログラムによる攻撃、最大1,801,499名の会員情報が漏えいした可能性 2026.9.2 Wed 8:05 「うんこミュージアム公式サイト」に不正アクセス、サイトの一部が改ざんされる被害 2</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56271;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社繋は8月27日、同社が運営するコーポレートサイト（ https://tsng.co.jp/ ）への不正アクセスについて発表した。 これは6月29日に、当該サイトで異常を確認したため公開を停止し、調査および証拠保全等の対応を開始し、その後、外部専門機関による調査を行った結果、管理者権限を持つアカウントが第三者によって不正に作成され、サーバ上にバックドア等の不正プログラムが設置されていたことが判明したというもの。 人気の無料ソフト公式サイトを侵害、Linux 標的としたバックドア 3 年間拡散 2023.10.17 Tue 8:00 無料提</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8836,12 +8840,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1,801,499</t>
+          <t>1,668</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8854,12 +8858,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html / https://scan.netsecurity.ne.jp/article/2026/09/18/56274.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/18/56271.html</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8875,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.18 Fri 8:05 ウェブ画面設定誤りが原因「オペラ銀河鉄道</t>
+          <t>ウェブ画面設定誤りが原因「オペラ銀河鉄道</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8973,22 +8977,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>同区の指定管理者である公益財団法人大田区文化振興協会</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>メールが送信 - ホテル運営会社</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56257;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東京都大田区は9月4日、同区の指定管理者である公益財団法人大田区文化振興協会が管理運営する大田区民プラザでの情報漏えいの可能性について発表した。 これは8月22日午前11時15分頃に、施設職員が施設配備パソコン端末でインターネットを閲覧中に画面に警告が表示されたため、表示された連絡先に電話し指示に従いパソコンを操作したところ、端末を操作できなくなり、その後、当該端末をネットワークから隔離したが、その間、当該端末に不正アクセスされたことから、個人情報を含む情報漏えいの可能性があというもの。 エスケーアイマネージメントへのサポート詐欺、Lansco</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8996,10 +9000,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9012,7 +9025,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189987</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html</t>
         </is>
       </c>
     </row>
@@ -9024,22 +9037,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>同区の指定管理者である公益財団法人大田区文化振興協会</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.17 Thu 8:05 表示された連絡先に電話 指示に従いパソコン操作 ～</t>
+          <t>CINRA JOB</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56257;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東京都大田区は9月4日、同区の指定管理者である公益財団法人大田区文化振興協会が管理運営する大田区民プラザでの情報漏えいの可能性について発表した。 これは8月22日午前11時15分頃に、施設職員が施設配備パソコン端末でインターネットを閲覧中に画面に警告が表示されたため、表示された連絡先に電話し指示に従いパソコンを操作したところ、端末を操作できなくなり、その後、当該端末をネットワークから隔離したが、その間、当該端末に不正アクセスされたことから、個人情報を含む情報漏えいの可能性があというもの。 エスケーアイマネージメントへのサポート詐欺、Lansco</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56252;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社cinraは8月27日、同社が運営する求人サービス「CINRA JOB」（ https://job.cinra.net/ ）への不正アクセスについて発表した。 これは8月18日に、「CINRA JOB」のシステム環境（クラウドサービス）にて、同社が管理する認証情報が第三者に取得され、不正アクセスされたことを確認したというもの。 「doda」販売代理店向けシステムに不備、549,195 名の個人情報が閲覧された可能性 2024.10.1 Tue 8:05 求人情報サイト「バイトル」へ不正ログイン、新たにアローズコーポレーションでも判明 2</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9049,12 +9062,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>549,195</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9072,7 +9085,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56257.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56252.html</t>
         </is>
       </c>
     </row>
@@ -9084,17 +9097,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>洛西進学教室</t>
+          <t>メールが送信 - ホテル運営会社</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56256;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アップは9月4日、同社が運営するプロモーションサイト「洛西進学教室」及び「進学館」への不正アクセスについて発表した。 これは8月24日に、当該サイトが利用していた外部ソフトウェア（プラグイン）の脆弱性を悪用した不正アクセスがあり、サーバ内に不正なプログラムが設置されたことが判明したというもの。当該サーバ内に保管されていた採用応募者の個人情報及び社内サイト管理者の個人情報が閲覧された可能性があるという。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 VOISI</t>
+          <t>ホテルの運営を手がけるTRUNKは、メールアカウントが不正アクセスを受け、個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9107,19 +9120,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>17,559</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9132,7 +9136,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html</t>
+          <t>https://www.security-next.com/189987</t>
         </is>
       </c>
     </row>
@@ -9144,17 +9148,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>コープやまぐちLINEミニアプリ</t>
+          <t>洛西進学教室</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」のデータベースに第三者から不正アクセスがあり、データベース内の全てのデータが削除される事象が発生したというもの。 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 メール配信システム「める配くん」の一部サーバに不正アクセス、配信先情報の一部が外部に取得されていた事実を確認</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56256;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社アップは9月4日、同社が運営するプロモーションサイト「洛西進学教室」及び「進学館」への不正アクセスについて発表した。 これは8月24日に、当該サイトが利用していた外部ソフトウェア（プラグイン）の脆弱性を悪用した不正アクセスがあり、サーバ内に不正なプログラムが設置されたことが判明したというもの。当該サーバ内に保管されていた採用応募者の個人情報及び社内サイト管理者の個人情報が閲覧された可能性があるという。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 VOISI</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9169,7 +9173,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>17,559</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9192,7 +9196,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56256.html</t>
         </is>
       </c>
     </row>
@@ -9204,17 +9208,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>日本交通</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>さくらのレンタルサーバ</t>
+          <t>コープやまぐちLINEミニアプリ</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56259;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。 同社では8月9日に、同社のレンタルサーバサービス「さくらのレンタルサーバ」のメンテナンス用サーバで異常を検知し、事実確認および影響範囲を調査した結果、下記の事象を確認していた。 さくらインターネットへの不正アクセス、案内ページを公開 2026.9.8 Tue 8:05 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 </t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56258;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 生活協同組合コープやまぐちは8月28日、同組合が提供する「コープやまぐちLINEミニアプリ」への不正アクセスについて発表した。 これは8月27日に、同組合が開発・運用を外部事業者に委託して運営している「コープやまぐちLINEミニアプリ」のデータベースに第三者から不正アクセスがあり、データベース内の全てのデータが削除される事象が発生したというもの。 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 メール配信システム「める配くん」の一部サーバに不正アクセス、配信先情報の一部が外部に取得されていた事実を確認</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9229,12 +9233,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1,360,563</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 会員情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9247,12 +9251,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56258.html</t>
         </is>
       </c>
     </row>
@@ -9264,22 +9268,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>tSecurity 2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.17 Thu 8:05 54サイトが閲覧不可に ～ 山梨大学が契約している</t>
+          <t>さくらのレンタルサーバ</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56253;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。 これは同学が契約しているレンタルサーバで発生したセキュリティインシデントに伴い、当該サーバ上で開設していた複数のWebサイトで公開を停止したというもの。 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 福岡大学の委託先ノストラムに不正アクセス、攻撃者のサイト上に窃取したデータを公開する旨の告知 2026.7.27 Mon 8:05 日本大学の学生・卒業生</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56259;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); さくらインターネット株式会社は9月10日、8月17日に公表した同社レンタルサーバサービスの一部環境への不正アクセスについて、第三報を発表した。 同社では8月9日に、同社のレンタルサーバサービス「さくらのレンタルサーバ」のメンテナンス用サーバで異常を検知し、事実確認および影響範囲を調査した結果、下記の事象を確認していた。 さくらインターネットへの不正アクセス、案内ページを公開 2026.9.8 Tue 8:05 さくらインターネットに不正アクセス、会員情報 1,360,563 アカウントが影響を受けた可能性 2026.8.20 Thu 8:05 </t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9289,12 +9293,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1,360,563</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 会員情報</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9307,12 +9311,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56156.html / https://scan.netsecurity.ne.jp/article/2026/09/17/56259.html</t>
         </is>
       </c>
     </row>
@@ -9487,27 +9491,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>54サイトが閲覧不可に ～ 山梨大学</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>システムが侵害され</t>
+          <t>サイトが閲覧不可に ～ 山梨大学が契約しているレンタルサーバでのWebサイト改ざん 国立大学法人山梨大学は</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56253;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人山梨大学は8月27日、レンタルサーバ上のWebサイト改ざんについて発表した。 これは同学が契約しているレンタルサーバで発生したセキュリティインシデントに伴い、当該サーバ上で開設していた複数のWebサイトで公開を停止したというもの。 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 福岡大学の委託先ノストラムに不正アクセス、攻撃者のサイト上に窃取したデータを公開する旨の告知 2026.7.27 Mon 8:05 日本大学の学生・卒業生</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9515,10 +9519,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -9531,7 +9544,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190377</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/17/56253.html</t>
         </is>
       </c>
     </row>
@@ -9543,22 +9556,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CINRA JOB</t>
+          <t>システムにランサムウェア攻撃</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56244;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 鳥取県は9月3日、モニタリングポストの放射線量率等の測定データを収集・監視する鳥取県環境放射線モニタリングシステムへのサイバー攻撃について発表した。 これは鳥取県環境放射線モニタリングシステムで、庁内に設置していた主監視局（主サーバ）へのランサムウェア攻撃を判明したというもの。同サーバ内の電子ファイルが暗号化され、主監視局に障害が発生しシステム停止している。 「白塗り」に気付けなかったのは決裁を紙文書でやっていたから ～ 消防防災航空センターホームページで個人情報が閲覧可能に 2024.5.30 Thu 8:05 食パラダイス鳥取県公式インスタ</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9566,14 +9579,19 @@
           <t>可能性あり</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>会員情報</t>
+          <t>氏名, クレジットカード情報</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189866</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
         </is>
       </c>
     </row>
@@ -9603,17 +9621,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.16 Wed 8:05 鳥取県環境放射線モニタリングシステムにランサムウェ</t>
+          <t>引越し見積もり</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56244;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 鳥取県は9月3日、モニタリングポストの放射線量率等の測定データを収集・監視する鳥取県環境放射線モニタリングシステムへのサイバー攻撃について発表した。 これは鳥取県環境放射線モニタリングシステムで、庁内に設置していた主監視局（主サーバ）へのランサムウェア攻撃を判明したというもの。同サーバ内の電子ファイルが暗号化され、主監視局に障害が発生しシステム停止している。 「白塗り」に気付けなかったのは決裁を紙文書でやっていたから ～ 消防防災航空センターホームページで個人情報が閲覧可能に 2024.5.30 Thu 8:05 食パラダイス鳥取県公式インスタ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56246;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日鉄興和不動産株式会社は8月26日、同社が利用するクラウドサービスへの不正アクセスについて発表した。 これは8月25日に、同社が利用するクラウドサービスの一部への第三者からの不正アクセスを確認したというもの。 青山財産ネットワークス グループ会社にランサムウェア攻撃、日本資産総研と日東不動産以外での影響は確認されず 2026.8.21 Fri 8:05 名鉄協商へのランサムウェア攻撃、中電不動産の顧客情報 約4,000件が漏えいした可能性 2026.8.18 Tue 8:05 九電不動産 再委託先の日本テレネットにランサムウェア攻撃 2026.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9623,12 +9641,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>氏名, クレジットカード情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -9641,12 +9659,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/16/56244.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html / https://scan.netsecurity.ne.jp/article/2026/09/16/56246.html</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9681,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.16 Wed 8:05 大阪高等裁判所で特定の事件に係る Microsof</t>
+          <t>メール・通知からアクセスした際にユーザー名とメールアドレスが閲覧できる状態に 大阪高等裁判所は9月4日</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9718,24 +9736,33 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>システムが侵害され</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
+          <t>ロート製薬は、通信販売で利用しているシステムが侵害され、顧客との通話音声データなどが流出した可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -9748,7 +9775,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190377</t>
         </is>
       </c>
     </row>
@@ -9760,24 +9787,37 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CINRA JOB</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
+          <t>クリエイティブ業界向け求人サービス「CINRA JOB」が不正アクセスを受け、会員情報が外部に流出した可能性があることがわかった。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>会員情報</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -9790,90 +9830,67 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189866</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>円谷プロダクション</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>当選</t>
-        </is>
-      </c>
+          <t>Rohto Pharmaceutical（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>円谷プロダクションは、同社店舗「ULTRA MART」で利用する購入抽選システムが不正アクセスを受けたことを明らかにした。購入抽選システムの当選結果が改ざんされたという。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Rohto Pharmaceutical（tracker headline） — Unauthorized access to EC site.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Yagura / Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/ / https://www.security-next.com/190315</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>予約サイトなどで侵害</t>
-        </is>
-      </c>
+          <t>Helpfeel (Gyazo)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Helpfeel (Gyazo)（ disclosure ） — Image-upload server vulnerability exploited to execute arbitrary commands Sep 11.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -9884,7 +9901,7 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -9897,7 +9914,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189665</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9931,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.15 Tue 8:05 町職員（57歳・女性）が廃棄対象の公文書等を持ち帰</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9974,7 +9991,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.15 Tue 8:05 日本大学理工学部教職員のアカウントに対し巧妙に偽装</t>
+          <t>メールを送信 日本大学理工学部は9月8日</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10034,7 +10051,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.15 Tue 8:05 公益財団法人 九州先端科学技術研究所でメール誤送信</t>
+          <t>メール誤送信</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10089,13 +10106,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ）</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>予約サイトなどで侵害</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
+          <t>審美歯科のフランチャイズチェーン「ホワイトエッセンス」を展開するホワイトエッセンスは、予約サイトや基幹システムが第三者により侵害されたことを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10106,7 +10132,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -10119,7 +10145,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189665</t>
         </is>
       </c>
     </row>
@@ -10131,13 +10157,13 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ）</t>
+          <t>Murauchi.com（ news report ）</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
+          <t>Murauchi.com（ news report ） — INTERNET Watch reports a vulnerability in part of the web system as the entry point. Company's second-report text unchecked.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10173,13 +10199,13 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline）</t>
+          <t>LEAN BODY（ disclosure ）</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
+          <t>LEAN BODY（ disclosure ） — Internal Metabase analytics-tool vulnerability. Company says failure to check vulnerability information and perform necessary updates likely also contributed.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10215,38 +10241,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
-        </is>
-      </c>
+          <t>Fuso Dentsu（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Fuso Dentsu（tracker headline） — Unauthorized access to cloud storage.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -10259,7 +10271,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -10271,39 +10283,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
+          <t>メールが5か月間読まれる — なりすまし入金指示で取引先に金銭被害 続報を注視中 重大 株式会社小田原エン</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。</t>
+          <t>株式会社小田原エンジニアリング（神奈川県足柄上郡松田町／モーター用巻線設備の製造）は2026年9月15日、ドイツ子会社へ出向していた従業員1人のメールアカウントが2026年3月27日から8月31日まで第三者に不正アクセスされ、取引先担当者の個人情報を含む約3,500通が閲覧されたと公表した。第三者はやり取りの内容を踏まえて同社従業員になりすまし、取引先へ入金を指示するメールを送信しており、一部の取引先で金銭被害が発生している。侵入経路は公表されていない。</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>6,811</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Yagura</t>
@@ -10319,14 +10327,14 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-17-odawara-engineering-mail-account-bec/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10336,12 +10344,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>第367回 個人情報保護委員会</t>
+          <t>Webシステムの脆弱性を起点に複数システムへ侵入 全容判明 深刻 株式会社ムラウチドットコム（東京都八王子</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機関等が43件であった。 民間事業者に対しては、不正アクセスを原因とする漏えい等事案を中心に、安全管理措置の不備等について指導を行っており、外部からの不正アクセス等の防止の不備（21件）、アクセス者の識別と認証の不備（14件）、委託先に対する監督の不備（12件）、情報システムの使用に伴う漏えい等の防止の不備（3件）の他、</t>
+          <t>株式会社ムラウチドットコム（東京都八王子市北野町／インターネット通信販売・インターネットメディア事業）は2026年9月15日、7月15日に確認された一部システムへの不正アクセスについて外部専門会社によるフォレンジック調査が完了し、771万6,811件の個人情報の漏えいが確認されたと公表した。Webシステムの一部に存在した脆弱性の悪用を起点に複数のシステムへ不正アクセスされたもので、クレジットカード情報とパスワードは含まれていないとしている。</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10351,22 +10359,22 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>6,101</t>
+          <t>6,811</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -10379,7 +10387,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
+          <t>https://incident.yagurasec.com/incidents/2026-07-24-murauchi-dotcom-unauthorized-access/</t>
         </is>
       </c>
     </row>
@@ -10391,28 +10399,42 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>第367回 個人情報保護委員会</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
+          <t>個人情報保護委員会は9月2日、「第367回 個人情報保護委員会」を同日開催したと発表した。あわせて同会での資料も公開している。 同会での議題は下記の通り。 1.独自利用事務の情報連携に係る届出について 2.監視・監督について 3.令和8年度第1四半期における監視・監督の状況について 4.令和8年度第1四半期における総合的な案内所（個人情報保護法相談ダイヤル）及びマイナンバー苦情あっせん相談窓口の受付状況について 同会によると、令和8年度第1四半期の漏えい等報告の処理件数は、個人情報6,101件、特定個人情報113件であった。 同会では令和8年度第1四半期に、個人情報保護法 第147条又は第157条に基づき指導・助言を計141件行っており、そのうち民間事業者が98件、行政機関等が43件であった。 民間事業者に対しては、不正アクセスを原因とする漏えい等事案を中心に、安全管理措置の不備等について指導を行っており、外部からの不正アクセス等の防止の不備（21件）、アクセス者の識別と認証の不備（14件）、委託先に対する監督の不備（12件）、情報システムの使用に伴う漏えい等の防止の不備（3件）の他、</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>6,101</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -10425,7 +10447,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189985</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56211.html</t>
         </is>
       </c>
     </row>
@@ -10437,42 +10459,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ファンくる</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56222;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ファンくるは8月25日、8月24日に公表した同社が運営する「ファンくる」への不正ログインについて、第二報を発表した。 同社では、同社システム内への外部からのリスト型攻撃とみられる不正ログインを検知したため、二次被害の防止と安全確保のため「ファンくる」のサービスを一時停止していた。 全会員のパスワードを一新 ～「ミドルの転職」へのリスト型攻撃で不正ログイン 2,503 件 2026.6.15 Mon 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 ポイント不正利用 444 件</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>宮崎県は、県立学校地区生徒寮の運営を委託している宮崎県奨学会がサポート詐欺に遭ったことを明らかにした。内部に個人情報が保存されたパソコンが遠隔操作されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>2,503</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -10485,7 +10493,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html</t>
+          <t>https://www.security-next.com/189985</t>
         </is>
       </c>
     </row>
@@ -10497,17 +10505,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>日本交通</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.14 Mon 8:05 Weverseサービスにセキュリティ脆弱性</t>
+          <t>ファンくる</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56219;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); WEVERSE JAPAN株式会社は9月6日、一部顧客の個人情報流出について発表した。 これは9月3日に、韓国インターネット振興院（KISA）より外部の報告者からWeverseサービスのセキュリティ脆弱性に関する指摘があった旨の連絡があり、社内点検を実施した結果、一部顧客の個人情報が流出した事実を確認したというもの。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 ソディックの</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56222;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社ファンくるは8月25日、8月24日に公表した同社が運営する「ファンくる」への不正ログインについて、第二報を発表した。 同社では、同社システム内への外部からのリスト型攻撃とみられる不正ログインを検知したため、二次被害の防止と安全確保のため「ファンくる」のサービスを一時停止していた。 全会員のパスワードを一新 ～「ミドルの転職」へのリスト型攻撃で不正ログイン 2,503 件 2026.6.15 Mon 8:05 個人情報ページの閲覧形跡なし「毎日新聞デジタル」へリスト型攻撃 2025.9.25 Thu 8:05 ポイント不正利用 444 件</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10522,12 +10530,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>17,559</t>
+          <t>2,503</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -10545,7 +10553,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56222.html</t>
         </is>
       </c>
     </row>
@@ -10557,24 +10565,42 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>日本交通</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56219;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); WEVERSE JAPAN株式会社は9月6日、一部顧客の個人情報流出について発表した。 これは9月3日に、韓国インターネット振興院（KISA）より外部の報告者からWeverseサービスのセキュリティ脆弱性に関する指摘があった旨の連絡があり、社内点検を実施した結果、一部顧客の個人情報が流出した事実を確認したというもの。 ダークウェブへの 17,559 名の情報流出を確認 ～ ロジックベインの不正アクセス被害 2026.9.7 Mon 8:05 日本交通への不正アクセス、保有ファイルの一部が外部流出 2026.9.4 Fri 8:05 ソディックの</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>17,559</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -10587,7 +10613,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56219.html</t>
         </is>
       </c>
     </row>
@@ -10599,13 +10625,13 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
+          <t>Nippon Trex（tracker headline）</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10636,47 +10662,29 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
-        </is>
-      </c>
+          <t>Five Foxes（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -10689,7 +10697,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -10701,33 +10709,42 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
+          <t>合計17,668件の迷惑メールを送信 立教大学</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>メールを送信 立教大学は9月8日</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>デジタル庁は、同庁が運用する「ガバメントソリューションサービス（GSS）」が不正アクセスを受けたことを明らかにした。機器の脆弱性を突かれて侵入され、保守運用アカウントが侵害されたという。 ：Security NEXT</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -10740,7 +10757,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190208</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
         </is>
       </c>
     </row>
@@ -10752,28 +10769,42 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>サカイホールディングス</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>カリテコ</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -10786,7 +10817,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188880</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
         </is>
       </c>
     </row>
@@ -10798,22 +10829,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>GMO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.11 Fri 8:05 日本スウェージロックFST にランサムウェア攻撃</t>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
+          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -10823,12 +10854,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10846,7 +10877,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
         </is>
       </c>
     </row>
@@ -10858,42 +10889,33 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.11 Fri 8:05 いまでやが管理する注文情報が外部流出した可能性</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
+          <t>デジタル庁は、同庁が運用する「ガバメントソリューションサービス（GSS）」が不正アクセスを受けたことを明らかにした。機器の脆弱性を突かれて侵入され、保守運用アカウントが侵害されたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -10906,7 +10928,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
+          <t>https://www.security-next.com/190208</t>
         </is>
       </c>
     </row>
@@ -10918,42 +10940,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>合計17,668件の迷惑メールを送信 立教大学</t>
+          <t>サカイホールディングス</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.11 Fri 8:00 立教大学利用のGoogeアカウントに不正アクセス</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -10966,7 +10974,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
+          <t>https://www.security-next.com/188880</t>
         </is>
       </c>
     </row>
@@ -10978,33 +10986,42 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>東京外環プロジェクト</t>
+          <t>サイト上でカード情報を入力する被害も 株式会社いまでやは8月21日</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -11017,7 +11034,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
         </is>
       </c>
     </row>
@@ -11029,13 +11046,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>東京外環プロジェクト</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11046,7 +11072,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -11059,7 +11085,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190203</t>
         </is>
       </c>
     </row>
@@ -11071,13 +11097,13 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11113,42 +11139,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>GSS</t>
-        </is>
-      </c>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -11161,34 +11169,34 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>飲食店の経営を手がけるきちりホールディングス</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11196,10 +11204,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -11212,7 +11229,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
         </is>
       </c>
     </row>
@@ -11224,33 +11241,42 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>システムがランサム被害</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56186;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般社団法人グランファミリア 海老名こじろう耳鼻咽喉科は8月19日、個人情報を含む書類の不適切な取り扱いについて発表した。 同院では、保管期間を経過し廃棄予定であった過去の問診票について、本来は適切に廃棄すべきところ、その一部を印刷用紙の裏紙として使用し、その後、当該用紙の一部がプリンタ内に残ったまま通常業務に移行したことで、患者に渡す資料の裏面に、別の患者の問診票の内容が記載された状態で交付したという。 気付いた生徒が撮影拡散、生徒39名の成績一覧表を裏紙として利用 2024.2.1 Thu 8:05 大学元職員が裏紙利用のため資料持ち出し </t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -11263,7 +11289,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html</t>
         </is>
       </c>
     </row>
@@ -11275,22 +11301,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>東京科学大学</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.10 Thu 8:05 耳鼻咽喉科の廃棄予定の問診票を裏紙使用し患者に交付</t>
+          <t>東海大学山中湖セミナーハウス</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56186;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 一般社団法人グランファミリア 海老名こじろう耳鼻咽喉科は8月19日、個人情報を含む書類の不適切な取り扱いについて発表した。 同院では、保管期間を経過し廃棄予定であった過去の問診票について、本来は適切に廃棄すべきところ、その一部を印刷用紙の裏紙として使用し、その後、当該用紙の一部がプリンタ内に残ったまま通常業務に移行したことで、患者に渡す資料の裏面に、別の患者の問診票の内容が記載された状態で交付したという。 気付いた生徒が撮影拡散、生徒39名の成績一覧表を裏紙として利用 2024.2.1 Thu 8:05 大学元職員が裏紙利用のため資料持ち出し </t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11300,7 +11326,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3,177</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -11318,12 +11344,12 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56186.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
         </is>
       </c>
     </row>
@@ -11335,17 +11361,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>情報漏えい ScanNetSecurity 2026.9.10 Thu 8:05 東京科学大学</t>
+          <t>飲食店の経営を手がけるきちりホールディングス</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.10 Thu 8:05 東京科学大学の情報基盤に不正アクセス</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
+          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11358,19 +11384,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>3,177</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -11383,7 +11400,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+          <t>https://www.security-next.com/190132</t>
         </is>
       </c>
     </row>
@@ -11395,42 +11412,33 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.10 Thu 8:05 REVISIO 役職員が使用する PC がマルウェ</t>
+          <t>システムがランサム被害</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56189;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 これは3月20日に、同社役職員が使用するPCでマルウェア感染および不審な挙動が確認されたため、当該PCをネットワークから遮断し、各種アカウントを停止した上で、外部専門会社によるフォレンジック調査を行ったところ、外部からのリモート接続やサーバへの不正アクセスは確認されなかったものの、当該PC内部のローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できないとの報告があったというもの。 PC端末がマルウェア感染しアカウントの認証情報が窃取、海外から継続的な不正</t>
+          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>マルウェア</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -11438,12 +11446,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
+          <t>https://www.security-next.com/189674</t>
         </is>
       </c>
     </row>
@@ -11455,24 +11463,42 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>ムラウチドットコム</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ドズル社ストア</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56185;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社エリッツは8月20日、個人情報流出の可能性について発表した。 同社では、入居申込者とのメールで取り交わした情報を格納したファイルをクラウド環境で保管していたが、不正アクセス制限に脆弱性が存在することが外部の調査会社の指摘で8月17日に発覚したという。 穴吹ハウジングサービスへのランサムウェア攻撃、松山市営住宅入居者の個人情報が漏えい 2026.5.8 Fri 8:05 建物名・所在地・部屋番号・入居者名ほか約 4,200 件が闇サイトで販売 2025.10.17 Fri 8:05 県営住宅入居者の個人情報漏えい可能性、迷惑メールが届いた</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -11485,40 +11511,54 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>Booking.com</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56189;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 これは3月20日に、同社役職員が使用するPCでマルウェア感染および不審な挙動が確認されたため、当該PCをネットワークから遮断し、各種アカウントを停止した上で、外部専門会社によるフォレンジック調査を行ったところ、外部からのリモート接続やサーバへの不正アクセスは確認されなかったものの、当該PC内部のローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できないとの報告があったというもの。 PC端末がマルウェア感染しアカウントの認証情報が窃取、海外から継続的な不正</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -11526,39 +11566,30 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189902</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56172.html / https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>立教大学</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Googleアカウント</t>
-        </is>
-      </c>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11569,7 +11600,7 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -11582,14 +11613,14 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190050</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11599,17 +11630,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>フィッシング対策セミナー2026</t>
+          <t>IRメールマガジン</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6039/eCrv5d/M?S=nepdq0lcl0k オンライン参加（Webex） https://antiphishingjp.webex.com/weblink/register/r80bc37361931544860d6329aee56afaf 申</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56190;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 東日本高速道路株式会社（NEXCO東日本）は9月4日、東京外環プロジェクトホームページの一時公開停止について発表した。 これは同社関東支社東京外環工事事務所が運営する東京外環プロジェクトホームページにて、第三者から不正アクセスの疑いが確認されたため、当該ホームページの公開を一時停止したというもの。 NEXCO東日本「IRメールマガジン」BCC運用、誤送信で計383名のアドレス漏えい 2023.5.29 Mon 8:05 NEXCO西日本、車両制限令等違反車両に関する取締り計画のSNS流出を確認 2021.4.16 Fri 8:00 ムラウチドッ</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11619,12 +11650,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>383</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11642,7 +11673,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56190.html</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11690,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.9 Wed 8:05 東邦通信システムズが利用する外部ホスティングサーバに</t>
+          <t>システムズが利用する外部ホスティングサーバに不正アクセス</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11714,13 +11745,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
+          <t>東京都大田区は、同区施設の職員がパソコンを利用した際にサポート詐欺に遭い、第三者によって端末がアクセスされたことを明らかにした。内部には個人情報が保存されていたという。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -11731,7 +11766,7 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -11744,7 +11779,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/189902</t>
         </is>
       </c>
     </row>
@@ -11756,13 +11791,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
+          <t>立教大学</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Googleアカウント</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
+          <t>立教大学は、同大関係者が利用する「Googleアカウント」が不正アクセスを受けたことを明らかにした。迷惑メールの送信に悪用されたという。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -11773,7 +11817,7 @@
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J220" t="n">
@@ -11786,14 +11830,14 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/190050</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11803,17 +11847,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>被害経験なし</t>
+          <t>フィッシング対策セミナー2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定されるため、一社単独ではなく、他企業・官民連携による対策が必要と感じる。」、「取引先がランサムウェア攻撃を受け、商品の出荷が停止となる影響が生じた。」などが寄せられている。 「富士山噴火による影響の懸念・事業継続への影響」について尋ねたところ、富士山噴火（広域降灰）による影響を懸念する企業が</t>
+          <t>フィッシング対策協議会は9月1日、「フィッシング対策セミナー2026」を11月19日に開催すると発表した。 同セミナーでは、最新のフィッシング詐欺の巧妙な手口や具体的な被害実態を詳しく解説するとともに、最前線で対応にあたる法執行機関、金融機関、サービス事業者の専門家が、それぞれの視点から実践的な防御策や最新の取り組みについて紹介する。 また、会場にはフィッシング対策サービスや各種ソリューションの展示ブースを設置し、来場者が最新の対策やサービスに触れられる機会を提供する。 ・概要 日程：11月19日 開催時間：13:00～18:00（終了予定） 受付開始：12:15～ 会場：大崎ブライトコアホール3階 オンライン：Webex ウェビナー 参加費：無料 申込：会場参加 https://area18.smp.ne.jp/area/card/6039/eCrv5d/M?S=nepdq0lcl0k オンライン参加（Webex） https://antiphishingjp.webex.com/weblink/register/r80bc37361931544860d6329aee56afaf 申</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -11823,12 +11867,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>13,156</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11846,54 +11890,36 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/09/56166.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>ニッポンレンタカーアプリ</t>
-        </is>
-      </c>
+          <t>Rikkyo University（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ニッポンレンタカーサービス株式会社は10月1日、9月26日に公表した同社運営の「ニッポンレンタカーアプリ」への不正アクセスについて、続報を発表した。 同社では「ニッポンレンタカーアプリ」のシステムに第三者から不正アクセスがあり、会員情報が不正に閲覧された可能性を確認していた。 同社では9月29日に、9月26日に公表した不正アクセスの調査の過程で、9月26日公表のものとは異なる手法による別の不正アクセスが判明している。 新たに判明した不正アクセスは、「ニッポンレンタカーアプリ」のシステムに対し、9月19日から21日にかけて行われた攻撃で、会員55名の会員情報ページへの不正なアクセスを確認しているという。 閲覧された可能性があるのは、氏名、電話番号、メールアドレス、ログインID、利用履歴、予約情報で、運転免許証情報又はクレジットカード情報を登録していた会員については、運転免許証情報（免許証番号、住所及び生年月日）、クレジットカード番号下4桁及び名義人名も対象となる。 同社では、対象となる会員にメールにて個別に連絡を行う。 同社では、本件不正アクセスについては必要な対策と封じ込め措置を実施し</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Rikkyo University（tracker headline） — Unauthorized access to six Google accounts.</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス, 生年月日, クレジットカード情報, 顧客情報, 会員情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -11906,34 +11932,25 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/10/07/56403.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>YAMAGoya</t>
-        </is>
-      </c>
+          <t>REVISIO（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>REVISIO（tracker headline） — Malware infection on a work PC.</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -11944,7 +11961,7 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J223" t="n">
@@ -11957,7 +11974,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/177455</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -11969,22 +11986,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>システムに不正アクセス</t>
+          <t>被害経験なし</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>東京商工会議所は8月24日、「会員企業の災害・リスク対策に関するアンケート」2026年調査結果を発表した。 同調査では4月20日から5月8日に、東商会員企業13,156件を対象にメール、郵送で調査票を送付し、得られた1,381件の回答結果をまとめたもの。 同調査で、サイバー攻撃の被害経験について尋ねたところ、「被害・影響を受けたことはない」と回答した企業は約6割となり、2024年調査の約7割より減少している。「取引先や委託先が被害を受け、自社業務に影響したことがある」企業は約2割となり、2024年調査より10ポイント超増加している。「自社がサイバー攻撃を受けたことがある」と回答したのは9.7％であった。 その他、企業の声として「サイバー攻撃によるリスクの増大に伴い、サプライチェーン全体への影響も想定されるため、一社単独ではなく、他企業・官民連携による対策が必要と感じる。」、「取引先がランサムウェア攻撃を受け、商品の出荷が停止となる影響が生じた。」などが寄せられている。 「富士山噴火による影響の懸念・事業継続への影響」について尋ねたところ、富士山噴火（広域降灰）による影響を懸念する企業が</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -11992,10 +12009,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>13,156</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -12008,7 +12034,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189789</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/08/56151.html</t>
         </is>
       </c>
     </row>
@@ -12025,12 +12051,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SonicWall SMA 100</t>
+          <t>YAMAGoya</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
+          <t>JPCERTコーディネーションセンター（JPCERT/CC）は、メモリやログにおける挙動をもとに脅威ハンティングできるオープンソースソフトウェア「YAMAGoya」をGitHubで公開した。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -12059,7 +12085,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/174925</t>
+          <t>https://www.security-next.com/177455</t>
         </is>
       </c>
     </row>
@@ -12076,12 +12102,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Catalyst SD-WAN Manager</t>
+          <t>システムに不正アクセス</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
+          <t>三井不動産は、同社グループが利用するシステムが不正アクセスを受け、同社およびグループ会社の役職員、社外関係者の個人情報が流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -12091,7 +12117,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -12110,7 +12136,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190883</t>
+          <t>https://www.security-next.com/189789</t>
         </is>
       </c>
     </row>
@@ -12122,13 +12148,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline）</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
+          <t>企業・組織名要確認</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SonicWall SMA 100</t>
+        </is>
+      </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
+          <t>SonicWallは、リモートアクセス製品「SMA 100」シリーズ向けにマルウェアの除去機能などを追加したファームウェアのアップデートをリリースした。 ：Security NEXT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12139,7 +12174,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -12152,29 +12187,29 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://www.security-next.com/174925</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>サーバが侵害</t>
+          <t>Catalyst SD-WAN Manager</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
+          <t>Cisco Systemsは、「Cisco Catalyst SD-WAN Manager」に脆弱性が明らかになったとして、セキュリティアップデートをリリースした。すでに悪用も確認されている。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -12184,7 +12219,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -12203,54 +12238,36 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188534</t>
+          <t>https://www.security-next.com/190883</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GMO</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Japan Vulnerability Notes（JVN）</t>
-        </is>
-      </c>
+          <t>UP Inc. (classroom website)（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。GMOサイバーセキュリティ byイエラエ株式会社の黒須宏道氏と上田将嗣氏が報告を行っている。影響を受けるシステムは以下の通り。 PALLET CONTROL Ver. 6.3 パッチ 5 およびそれ以前 PalletControl 10 Update 8 およびそれ以前 PalletControl クラウド（PalletControl 10 Update 8）およびそれ以前 JALデジタル株式会社が提供するPALLET CONTROL製品には、バックグラウンドで動作し一定の機能を提供するサービスプログラムが複数含まれているが、サービスプログラムとの通信に適切なアクセス権限が設定されておらず、管理者権限を持たない一般ユーザによりアクセスが可能となる脆弱性（CVE-2026-81302）が存在する。 想定される影響と</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>UP Inc. (classroom website)（tracker headline） — Plugin vulnerability exploited.</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J229" t="n">
@@ -12263,7 +12280,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -12275,17 +12292,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ムラウチドットコム</t>
+          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングス</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.7 Mon 8:05 資格情報の不正利用でシステム閲覧被害 ～ 三井不動産</t>
+          <t>サーバが侵害</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56140;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 三井不動産株式会社は9月1日、同社グループが利用する一部のシステムへの不正アクセスによる情報漏えいの可能性について発表した。 これは8月28日に、同社が利用する一部のシステムへの不正アクセスを確認したため調査したところ、同社が利用する一部のシステムに係る資格情報が不正に利用され、第三者から情報の一部を閲覧された可能性を確認したというもの。 青山財産ネットワークス グループ会社にランサムウェア攻撃、日本資産総研と日東不動産以外での影響は確認されず 2026.8.21 Fri 8:05 名鉄協商へのランサムウェア攻撃、中電不動産の顧客情報 約4,0</t>
+          <t>マンションの賃貸管理や賃貸仲介を手がけるアンビションDXホールディングスは、ファイルサーバが第三者によって侵害され、一部情報が流出したことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -12295,22 +12312,13 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J230" t="n">
@@ -12318,12 +12326,12 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html / https://scan.netsecurity.ne.jp/article/2026/09/07/56140.html</t>
+          <t>https://www.security-next.com/188534</t>
         </is>
       </c>
     </row>
@@ -12335,17 +12343,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ント・情報漏えい ScanNetSecurity 2026.9.7 Mon 8:05 01銀行</t>
+          <t>企業・組織名要確認</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ecurity 2026.9.7 Mon 8:05 01銀行のシステムに不正アクセス</t>
+          <t>まんだらけ</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56142;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。 これは8月17日に、同行のシステムへの不正アクセスを検知し、調査した結果、顧客情報の漏えいが発生した事実を確認したというもの。 阿波銀行への不正アクセス、原因はテスト環境の「管理不備」と発表 関係役員らの処分も 2026.6.8 Mon 8:05 事態を重く受け止め「第65回 博多どんたく港まつり」への参加自粛 ～ 西日本シティ銀行 2026.5.12 Tue 8:05 メットライフ生命保険のサーバで不正に取得保管 ～ きらぼし銀行の顧客 95 名の保険契約情報が漏え</t>
+          <t>コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -12358,19 +12366,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 顧客情報</t>
-        </is>
-      </c>
+      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -12383,7 +12382,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html</t>
+          <t>https://www.security-next.com/189663</t>
         </is>
       </c>
     </row>
@@ -12395,17 +12394,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>企業・組織名要確認</t>
+          <t>ムラウチドットコム</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>まんだらけ</t>
+          <t>システムBIツール（ビジネスインテリジェンスツール）への不正アクセスについて発表した</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>コレクターズアイテムを販売するショップ「まんだらけ」のサーバが侵害され、一部顧客の個人情報が流出した可能性があることがわかった。一時オンラインショップやオークションを停止したが、いずれも再開している。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56144;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); アイドルサポート事業などを行う株式会社VOISINGは8月18日、同社が社内で利用しているデータ分析システムBIツール（ビジネスインテリジェンスツール）への不正アクセスについて発表した。 これは8月10日午前1時2分頃から、BIツールへの外部からの不正アクセスが開始され、8月16日午後6時47分から8時21分にかけ、同ツール内に保管されていたデータが不正に取得（ダウンロード）されたことを確認したというもの。 REXTへのランサムウェア攻撃、JEANS MATE店舗での支払いは原則として現金のみに 2026.8.20 Thu 8:05 ニデックW</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12418,10 +12417,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>62,691</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報, 会員情報</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J232" t="n">
@@ -12434,12 +12442,132 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189663</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56144.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>GMO</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Japan Vulnerability Notes（JVN）</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>独立行政法人情報処理推進機構（IPA）および一般社団法人JPCERT コーディネーションセンター（JPCERT/CC）は9月1日、PALLET CONTROL製品におけるアクセス制御不備の脆弱性について「Japan Vulnerability Notes（JVN）」で発表した。GMOサイバーセキュリティ byイエラエ株式会社の黒須宏道氏と上田将嗣氏が報告を行っている。影響を受けるシステムは以下の通り。 PALLET CONTROL Ver. 6.3 パッチ 5 およびそれ以前 PalletControl 10 Update 8 およびそれ以前 PalletControl クラウド（PalletControl 10 Update 8）およびそれ以前 JALデジタル株式会社が提供するPALLET CONTROL製品には、バックグラウンドで動作し一定の機能を提供するサービスプログラムが複数含まれているが、サービスプログラムとの通信に適切なアクセス権限が設定されておらず、管理者権限を持たない一般ユーザによりアクセスが可能となる脆弱性（CVE-2026-81302）が存在する。 想定される影響と</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56134.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>01銀行</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>システムに不正アクセス</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56142;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 01銀行株式会社は8月27日、同行システムへの不正アクセスについて発表した。 これは8月17日に、同行のシステムへの不正アクセスを検知し、調査した結果、顧客情報の漏えいが発生した事実を確認したというもの。 阿波銀行への不正アクセス、原因はテスト環境の「管理不備」と発表 関係役員らの処分も 2026.6.8 Mon 8:05 事態を重く受け止め「第65回 博多どんたく港まつり」への参加自粛 ～ 西日本シティ銀行 2026.5.12 Tue 8:05 メットライフ生命保険のサーバで不正に取得保管 ～ きらぼし銀行の顧客 95 名の保険契約情報が漏え</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 顧客情報</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>ScanNetSecurity</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/07/56142.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L232"/>
+  <autoFilter ref="A1:L234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12484,7 +12612,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
@@ -12519,7 +12647,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:39:16.369760+00:00</t>
+          <t>2026-10-07T00:40:38.339605+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -4988,7 +4988,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07T00:40:38.339605+00:00</t>
+          <t>2026-10-07T00:41:24.358149+00:00</t>
         </is>
       </c>
     </row>

--- a/japan_cyber_incidents_1month.xlsx
+++ b/japan_cyber_incidents_1month.xlsx
@@ -11,7 +11,7 @@
     <sheet name="概要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$322</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'国内サイバーインシデント'!$A$1:$L$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L322"/>
+  <dimension ref="A1:L321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE94V2trWWZwRDhaOEo3ajV6cWtwVktyaGhuMFJLb1R0RDJBeW1FQzhvek4xN1libEZTbFVpcERRYmpVUmEyN0JXRkdiLXQzd3pfUHdNRGJOQUxERjlvNVlIRzU1ZS0ycGJDbXJILUMyb9IBdEFVX3lxTE80RFY0X1VyNVh1al9tTWVzc3pHLW9PWDk0SXdoSWNxTHZNenh6OUwweTh0Wk9SZGl0ZENodmVDVEpLdFoxR3h6TlQyVGU2NjNsVjBwT0wwRXhBblRUMTN3aVA1UUpWYTU1Tzc0OG9zZF9pWDM1?oc=5 / https://news.google.com/rss/articles/CBMif0FVX3lxTE1Ub0xVTmY1N1ZxUWstRTZLZmhKMjJuQ0gyVWVjdUJmc0xmSk5FbTFGVUxMLUl6bnhGZmltWWtzNlhEZmJtWmFhS2VhX3MxbmNFVkJzTGNZRWpfRUhEaGJ1VElaczFzcUhGWW8teWVhNDdoMkg3ZG8xRWMyTVlMMVE?oc=5 / https://news.google.com/rss/articles/CBMid0FVX3lxTFA2TF9lSXVjc0V3RFgtVGdpc0lVczZZa3Z0MlkzWXNJczhicV9adTQ4T2VKeEFFR3ZTa3FNQkFrRVBHWTRVc0dMV3ZwNG1MV2lod0kyZXo3eU9iVUdTRnRhU1BlbUNzSWJwYnhJalg4S05FT2hYVENV0gF8QVVfeXFMUHdkZGMzS00zZXJRa1FhemRWLU9SS3ZWejdjdmgyaWNJb0tCazBjenNPQllFOWkwbnhwVUlXMjRMS1E1LWhKMUtWWm5XYkotZEQ3WlRnU1VsdDRGUV9FbVBMRnpmUlRXbkNOb1doSF9vdDBoaERiWmdhejJwSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html / https://scan.netsecurity.ne.jp/article/2026/09/24/56283.html</t>
         </is>
       </c>
     </row>
@@ -14390,22 +14390,22 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
+          <t>株式会社TRUNK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>VPNを使用しない</t>
+          <t>メールアカウントに不正アクセス</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56223;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); デジタル庁は9月11日、ガバメントソリューションサービスへの不正アクセスについて発表した。 これはデジタル庁が運用するガバメントソリューションサービス（GSS）に外部から不正アクセスがあり、GSS上で取り扱っていた個人情報を含むファイルの一部が外部に漏えいした可能性が判明したというもの。 再発防止策「VPNを使用しない」株式会社イセトー 2024.10.15 Tue 8:05 侵入経路となった VPN は使用しない ～ オリエンタルダイヤモンドへのランサムウェア攻撃 2026.5.26 Tue 8:05 VPN 脆弱性の放置や安易なパスワードで</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56218;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ホテル企画運営を行う株式会社TRUNKは9月1日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは同社従業員のメールアカウントに第三者から不正アクセスがあり、同社が保有している情報の一部が外部に漏えいしたというもの。同社では、第三者が当該メールアカウントを不正に利用し、同社および同社従業員になりすまして不審メールを送信していたことを確認している。 一正蒲鉾社員のメールアカウントに不正アクセス、取引先と社員の個人情報が閲覧された可能性 2026.8.31 Mon 8:05 藤倉コンポジットのメールアカウントに不正アクセス、す</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 認証情報</t>
+          <t>メールアドレス, クレジットカード情報, 認証情報</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56223.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html</t>
         </is>
       </c>
     </row>
@@ -14450,42 +14450,24 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>株式会社TRUNK</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>メールアカウントに不正アクセス</t>
-        </is>
-      </c>
+          <t>Nippon Trex（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56218;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); ホテル企画運営を行う株式会社TRUNKは9月1日、同社従業員のメールアカウントへの不正アクセスについて発表した。 これは同社従業員のメールアカウントに第三者から不正アクセスがあり、同社が保有している情報の一部が外部に漏えいしたというもの。同社では、第三者が当該メールアカウントを不正に利用し、同社および同社従業員になりすまして不審メールを送信していたことを確認している。 一正蒲鉾社員のメールアカウントに不正アクセス、取引先と社員の個人情報が閲覧された可能性 2026.8.31 Mon 8:05 藤倉コンポジットのメールアカウントに不正アクセス、す</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>アカウント侵害</t>
+          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>メールアドレス, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J268" t="n">
@@ -14498,7 +14480,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/14/56218.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -14510,13 +14492,13 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline）</t>
+          <t>Five Foxes（tracker headline）</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Nippon Trex（tracker headline） — Ransomware group INC Ransom claimed responsibility.</t>
+          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -14547,18 +14529,18 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline）</t>
+          <t>サイバーセキュリティメディア</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Five Foxes（tracker headline） — Unauthorized access.</t>
+          <t>日本WAF市場、2035年に約18.8億ドル規模へ成長か 高度化するサイバー攻撃とクラウド化が需要を牽引 - サイバーセキュリティメディア</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -14569,7 +14551,7 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J270" t="n">
@@ -14582,36 +14564,54 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTE5Ob1l6WloxWmQ2QnFvQnpJTThXcFl2Smx5RlRrODlMLXl6UTNjVDN0VGNWUzdMbDdWX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>サイバーセキュリティメディア</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
+          <t>合計17,668件の迷惑メールを送信 立教大学</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>メールを送信 立教大学は9月8日</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>日本WAF市場、2035年に約18.8億ドル規模へ成長か 高度化するサイバー攻撃とクラウド化が需要を牽引 - サイバーセキュリティメディア</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTE5Ob1l6WloxWmQ2QnFvQnpJTThXcFl2Smx5RlRrODlMLXl6UTNjVDN0VGNWUzdMbDdWX3c?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
         </is>
       </c>
     </row>
@@ -14636,22 +14636,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>合計17,668件の迷惑メールを送信 立教大学</t>
+          <t>株式会社日本ビジネスデータープロセシングセンター</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>メールを送信 立教大学は9月8日</t>
+          <t>システムへの不正アクセスについて発表した</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56203;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 立教大学は9月8日、同学で利用しているGoogeアカウントへの不正アクセスによる迷惑メール送信について発表した。 これは4月27日から8月24日にかけて、同学学生4名および卒業生2名の合計6名のGoogeアカウントに不正アクセスがあり、当該アカウントから合計17,668件の迷惑メールが不正に送信されたというもの。 立教大学、VPN接続時 多要素認証必須化 2025.10.30 Thu 8:00 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウント乗っ取り」 2026.8.28 Fri </t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56207;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社日本ビジネスデータープロセシングセンターは8月24日、同社システムへの不正アクセスについて発表した。 これは8月20日午前11時53分に、同社システムで不正アクセスを確認したというもの。 「虫退治ドットコム」に不正アクセス、カード情報が漏えいした可能性 2026.8.26 Wed 8:10 全日空商事「選べるe-GIFT」に不正アクセス、第三者に不正に交換された事象も確認 2026.8.27 Thu 8:05 海月館グループの宿泊施設に不正アクセス、顧客の個人情報が流出した可能性 2026.8.27 Thu 8:05 中部電力の一部のシ</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56203.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html</t>
         </is>
       </c>
     </row>
@@ -14696,22 +14696,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>株式会社日本ビジネスデータープロセシングセンター</t>
+          <t>日本スウェージロックFST にランサムウェア攻撃 日本スウェージロックFST株式会社</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>システムへの不正アクセスについて発表した</t>
+          <t>カリテコ</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56207;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社日本ビジネスデータープロセシングセンターは8月24日、同社システムへの不正アクセスについて発表した。 これは8月20日午前11時53分に、同社システムで不正アクセスを確認したというもの。 「虫退治ドットコム」に不正アクセス、カード情報が漏えいした可能性 2026.8.26 Wed 8:10 全日空商事「選べるe-GIFT」に不正アクセス、第三者に不正に交換された事象も確認 2026.8.27 Thu 8:05 海月館グループの宿泊施設に不正アクセス、顧客の個人情報が流出した可能性 2026.8.27 Thu 8:05 中部電力の一部のシ</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -14721,12 +14721,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>7,716,811</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>クレジットカード情報</t>
+          <t>クレジットカード情報, 顧客情報</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56207.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
         </is>
       </c>
     </row>
@@ -14756,22 +14756,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>日本スウェージロックFST にランサムウェア攻撃 日本スウェージロックFST株式会社</t>
+          <t>サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>カリテコ</t>
+          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56209;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 日本スウェージロックFST株式会社は8月26日、同社へのランサムウェア攻撃について発表した。 これは3月10日に、同社の一部サーバに対し外部から不正アクセスおよびランサムウェア攻撃があったというもの。 サイバー保険がランサムウェアを生み出したのか 2026.7.24 Fri 8:10 フェースへのランサムウェア攻撃、VPN 機器を経由して第三者が不正に侵入 2026.8.27 Thu 8:05 ニデック 台湾子会社にランサムウェア攻撃、ダークウェブ上でフォルダ・ファイル名のリストの一部を公開 2026.8.27 Thu 8:05 名鉄協商にラン</t>
+          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>7,716,811</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>クレジットカード情報, 顧客情報</t>
+          <t>クレジットカード情報</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56209.html</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
         </is>
       </c>
     </row>
@@ -14816,17 +14816,13 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用 GMOサイバーセキュリティ byイエラエ株式会社</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>ネット de 診断 AIホワイトハッカー侵入テスト</t>
-        </is>
-      </c>
+          <t>日本経済新聞</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>GMOサイバーセキュリティ byイエラエ株式会社は9月3日、「ネット de 診断 AIホワイトハッカー侵入テスト」を同日から順次提供すると発表した。 「ネット de 診断 AIホワイトハッカー侵入テスト」は、サイバーセキュリティ特化AI基盤「AIホワイトハッカー byGMO」を活用し、未知の脆弱性の探索から、実際にサイバー攻撃が成立するかの検証までをAIが自動で行う機能で、同機能を「GMOサイバー攻撃 ネット de 診断 ASM」に搭載することで、従来の既知の脆弱性の検出に加え、実際に悪用される可能性の高い脆弱性までが把握可能となる。 同機能の特長は下記の通り。 ・攻撃が成立するかをAIが自動で確認 脆弱性を検出するだけでなく、実際にその脆弱性を悪用した攻撃が成立するかどうかまでをAIが自動で確認し、成立を確認したものだけを報告。 ・既知の脆弱性の照合にとどまらず、未公表のものも含めて探索 「AIホワイトハッカー byGMO」は、一般に利用可能なフロンティアAIと、同社独自の検証基盤、ホワイトハッカーの知見を組み合わせて構成しており、既知の診断観点に分類されていない攻撃手法も含めて探索</t>
+          <t>政府システムに不正アクセス、職員ら情報24万件漏洩か デジタル庁 - 日本経済新聞</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -14836,22 +14832,18 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>可能性あり</t>
+          <t>確認・可能性あり</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>24万</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J275" t="n">
@@ -14864,7 +14856,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56195.html</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE45eWd6V1lyMWxFbElHYVhUUXRWb0R4ek5Jc0xPUlhDWEs0eEFpYUJuX05kdW1lakJYSVhzcXBkb2h5Y3RPSjUwaWY0ZGt5elBaNEVIdGc5MFNOcHkwZDlFWVV3SG16eWJGSWFrZg?oc=5</t>
         </is>
       </c>
     </row>
@@ -14876,28 +14868,23 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>日本経済新聞</t>
+          <t>静岡新聞DIGITAL</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>政府システムに不正アクセス、職員ら情報24万件漏洩か デジタル庁 - 日本経済新聞</t>
+          <t>ランサムウエア被害最多 攻防激化で体制整備急ぐ 手口高度化「特効薬なし」【表層深層】 - 静岡新聞DIGITAL</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>24万</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
@@ -14916,7 +14903,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE45eWd6V1lyMWxFbElHYVhUUXRWb0R4ek5Jc0xPUlhDWEs0eEFpYUJuX05kdW1lakJYSVhzcXBkb2h5Y3RPSjUwaWY0ZGt5elBaNEVIdGc5MFNOcHkwZDlFWVV3SG16eWJGSWFrZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5WMTdWdEpfV01XcU8yVTk3dTJCUXQxTTlfbEJfTVpqanpiWGRNZnNSWTJVVW9qWlNwMTVLaXZxQ0tVd2VOSEZNaWFLUEMwdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -14928,13 +14915,13 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>静岡新聞DIGITAL</t>
+          <t>サイバーセキュリティメディア</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ランサムウエア被害最多 攻防激化で体制整備急ぐ 手口高度化「特効薬なし」【表層深層】 - 静岡新聞DIGITAL</t>
+          <t>ネクストリード、ランサムウェア被害増加受け「Microsoft 365攻撃兆候診断」を中堅中小企業に無償提供 - サイバーセキュリティメディア</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14963,7 +14950,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5WMTdWdEpfV01XcU8yVTk3dTJCUXQxTTlfbEJfTVpqanpiWGRNZnNSWTJVVW9qWlNwMTVLaXZxQ0tVd2VOSEZNaWFLUEMwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTFBYdzBhUjQ2dnQ3NEVOb2hDQ0txUmVqRVZ6OEpfcEdWdTlHbHZxUGl1dUxXMGJBNV9rTFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -14975,18 +14962,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>サイバーセキュリティメディア</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
+          <t>サカイHD子会社</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>ecurity NEXT</t>
+        </is>
+      </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ネクストリード、ランサムウェア被害増加受け「Microsoft 365攻撃兆候診断」を中堅中小企業に無償提供 - サイバーセキュリティメディア</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>ランサムウェア</t>
+          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -14997,7 +14983,7 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J278" t="n">
@@ -15010,7 +14996,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiOkFVX3lxTFBYdzBhUjQ2dnQ3NEVOb2hDQ0txUmVqRVZ6OEpfcEdWdTlHbHZxUGl1dUxXMGJBNV9rTFE?oc=5</t>
+          <t>https://www.security-next.com/188880</t>
         </is>
       </c>
     </row>
@@ -15022,28 +15008,42 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>サカイHD子会社</t>
+          <t>株式会社いまでや</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>サイト上でカード情報を入力する被害も 株式会社いまでやは8月21日</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>サカイホールディングスのグループ会社で葬祭事業を手がけるエスケーアイマネージメントは、従業員がサポート詐欺に遭い、パソコンに遠隔操作ツールがダウンロードされ、端末内の個人情報を含むファイルが大量に削除されたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>フィッシング</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>氏名, クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J279" t="n">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/188880</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
         </is>
       </c>
     </row>
@@ -15068,42 +15068,33 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>株式会社いまでや</t>
+          <t>東日本高速道路</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>サイト上でカード情報を入力する被害も 株式会社いまでやは8月21日</t>
+          <t>東京外環プロジェクト</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56206;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社いまでやは8月21日、同社が管理する顧客の注文情報が外部流出した可能性について発表した。同社ウェブサイトを一時停止したため、PR TIMESで公表している。 同社では8月20日夜に、同社を装った不審なメール（フィッシングメール）を受信したとの問い合わせが30件ほどあり、不審メールには受信した顧客本人の氏名、注文番号、注文金額が正確に記載されていたことから、無作為に送信されたものではなく、同社保有の注文情報が第三者に取得された可能性が高いと判断している。 連絡先情報が窃取されフィッシングメール大量送信 ～ 取引先を偽装したフィッシングメー</t>
+          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>フィッシング</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>氏名, クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J280" t="n">
@@ -15116,7 +15107,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56206.html</t>
+          <t>https://www.security-next.com/190203</t>
         </is>
       </c>
     </row>
@@ -15128,17 +15119,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>東日本高速道路</t>
+          <t>CMSで脆弱性が公表されたことを受け調査し発覚 カバー株式会社</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>東京外環プロジェクト</t>
+          <t>hololive OFFICIAL CARD GAME</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>国土交通省、東日本高速道路、中日本高速道路は、東京外かく環状道路の関連サイトが侵害された可能性があることを明らかにした。 ：Security NEXT</t>
+          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56208;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); カバー株式会社は8月25日、「hololive OFFICIAL CARD GAME」公式サイトヘの不正アクセスの可能性について発表した。 これは7月17日に、同社が利用するCMSで脆弱性が公表されたことを受け、社内で調査を実施した結果、当該サイトのCMSで不正アクセスの痕跡を確認したというもの。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri </t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15148,13 +15139,22 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>1,950,165</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J281" t="n">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190203</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html</t>
         </is>
       </c>
     </row>
@@ -15179,42 +15179,24 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CMSで脆弱性が公表されたことを受け調査し発覚 カバー株式会社</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>hololive OFFICIAL CARD GAME</t>
-        </is>
-      </c>
+          <t>Digital Agency (GSS)（ disclosure ）</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56208;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); カバー株式会社は8月25日、「hololive OFFICIAL CARD GAME」公式サイトヘの不正アクセスの可能性について発表した。 これは7月17日に、同社が利用するCMSで脆弱性が公表されたことを受け、社内で調査を実施した結果、当該サイトのCMSで不正アクセスの痕跡を確認したというもの。 「wp2shell」の攻撃検知速報を公表、修正版公開から9日間で累計1,950,165件を検知 2026.8.14 Fri 8:00 WordPress 6.9 以降で 2 件の脆弱性の組み合わせで遠隔コード実行の可能性 2026.7.24 Fri </t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>1,950,165</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>SmartScope</t>
         </is>
       </c>
       <c r="J282" t="n">
@@ -15227,7 +15209,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/11/56208.html</t>
+          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
         </is>
       </c>
     </row>
@@ -15239,13 +15221,13 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ）</t>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Digital Agency (GSS)（ disclosure ） — VPN/network-device vulnerability exploited; maintenance operator's account used. Detected Jun 25, identified Jul 9, disclosed Sep 11.</t>
+          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -15281,24 +15263,38 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ）</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
+          <t>株式会社円谷プロダクション（東京都渋谷区／映像制作）とmogily株式会社</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>ULTRA MART</t>
+        </is>
+      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ApplyNow (recruitment management; clients including Yoshinoya and Hanamaru also disclosed)（ disclosure ） — Analytics-tool vulnerability exploited Aug 9–Sep 7. Outside-service damage from client companies' perspective.</t>
+          <t>株式会社円谷プロダクション（東京都渋谷区／映像制作）とmogily株式会社は2026年9月11日、直営店「ULTRA MART」がLINEアプリ上で実施した購入抽選に使うデジタル整理券システム「mogily」の管理システムが2026年9月9日から10日にかけて外部から不正アクセスを受け、本来「当選」だった133人の当落データが「落選」に書き換えられていたと公表。個人情報の漏えいは確認されておらず、対象者の状態はすべて「当選」に復旧済み。</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SmartScope</t>
+          <t>Yagura</t>
         </is>
       </c>
       <c r="J284" t="n">
@@ -15311,7 +15307,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>https://smartscope.blog/en/blog/japan-data-breach-list-tier-2026-09-10/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/</t>
         </is>
       </c>
     </row>
@@ -15323,35 +15319,39 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>株式会社円谷プロダクション（東京都渋谷区／映像制作）とmogily株式会社</t>
+          <t>デジタル庁</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ULTRA MART</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>株式会社円谷プロダクション（東京都渋谷区／映像制作）とmogily株式会社は2026年9月11日、直営店「ULTRA MART」がLINEアプリ上で実施した購入抽選に使うデジタル整理券システム「mogily」の管理システムが2026年9月9日から10日にかけて外部から不正アクセスを受け、本来「当選」だった133人の当落データが「落選」に書き換えられていたと公表。個人情報の漏えいは確認されておらず、対象者の状態はすべて「当選」に復旧済み。</t>
+          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
+          <t>可能性あり</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr"/>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>氏名, 住所, 電話番号, メールアドレス</t>
+        </is>
+      </c>
       <c r="I285" t="inlineStr">
         <is>
           <t>Yagura</t>
@@ -15367,54 +15367,41 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-16-tsuburaya-mogily-lottery-tampering/</t>
+          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>デジタル庁</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>GSS</t>
-        </is>
-      </c>
+          <t>読売新聞</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>デジタル庁は2026年9月11日、同庁が運用する政府共通の業務実施環境「ガバメントソリューションサービス（GSS）」がVPN機器の脆弱性を悪用した不正アクセスを受け、保守運用担当者のアカウントが悪用されて職員・事業者ら計約24万6,000件（職員等18万9,000件、事業者・個人5万7,000件）の個人情報が外部流出のおそれがあると公表。5月下旬に侵入、6月25日に大量ファイルアクセスを検知、7月9日に侵害アカウントを停止・外部通信を遮断。氏名・メールアドレス・電話番号・住所が対象で、マイナンバー・金融情報は非該当。</t>
+          <t>身代金要求「ランサムウェア」被害、上半期１２３件で過去最多…サイバー攻撃の「予兆」は前年同期比５割増 - 読売新聞</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>氏名, 住所, 電話番号, メールアドレス</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Yagura</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J286" t="n">
@@ -15427,7 +15414,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>https://incident.yagurasec.com/incidents/2026-09-14-digital-agency-gss-vpn-unauthorized-access/</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE92YlF6MkFFS1l1YTZWN0l3R2lDVWNNR2M5Nk9zZ3BkOE44d1BOQzlFZThjdW1nRzRrMDE3MWxXUWExczFhdnFJQWJNSzVLZW5sYV9Dckd0SGw2V0pLcU1vOWw4c2ViZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -15439,29 +15426,42 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>読売新聞</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr"/>
+          <t>国立大学法人東京科学大学</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>東海大学山中湖セミナーハウス</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>身代金要求「ランサムウェア」被害、上半期１２３件で過去最多…サイバー攻撃の「予兆」は前年同期比５割増 - 読売新聞</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>3,177</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J287" t="n">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE92YlF6MkFFS1l1YTZWN0l3R2lDVWNNR2M5Nk9zZ3BkOE44d1BOQzlFZThjdW1nRzRrMDE3MWxXUWExczFhdnFJQWJNSzVLZW5sYV9Dckd0SGw2V0pLcU1vOWw4c2ViZw?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
         </is>
       </c>
     </row>
@@ -15486,17 +15486,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>国立大学法人東京科学大学</t>
+          <t>きちりHD子会社</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>東海大学山中湖セミナーハウス</t>
+          <t>ecurity NEXT</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56191;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 国立大学法人東京科学大学は9月7日、同学の情報基盤への不正アクセスについて発表した。 これは同学の情報基盤に第三者から不正アクセスがあり、個人情報が漏えいした可能性が判明したというもの。 東工大でメール誤送信、約1万件の学生情報を含むファイルを添付 2023.7.20 Thu 8:05 「東海大学山中湖セミナーハウス」ウェブサイトに不正アクセス「宿泊予約に関する情報」が漏えいした可能性を否定できず 2026.8.26 Wed 8:10 3,177件の不審メールを送信 ～ 日本大学法学部教職員への巧妙に偽装されたフィッシングメールによる「アカウン</t>
+          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -15509,19 +15509,10 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>3,177</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J288" t="n">
@@ -15534,7 +15525,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56191.html</t>
+          <t>https://www.security-next.com/190132</t>
         </is>
       </c>
     </row>
@@ -15546,22 +15537,22 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>きちりHD子会社</t>
+          <t>株式会社スプーン</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ecurity NEXT</t>
+          <t>サイトが改ざん被害</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>飲食店の経営を手がけるきちりホールディングスは、子会社が提供するサービスが不正アクセスを受け、個人情報が外部へ流出した可能性があることを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56187;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社スプーンは8月20日、同社ウェブサイトの不正改ざんについて発表した。 これは同社ウェブサイト（ spoonsports.jp ）の一部が第三者に不正に改ざんされ、特定のページを閲覧した際に、偽のセキュリティ確認画面等が表示される事象を確認したというもの。 日本大学文理学部のウェブサイトが改ざん被害、カジノサイトを模した不正な画面が表示 2026.6.12 Fri 8:05 「FNJPNews」が改ざん被害、Google reCAPTCHA を模した偽のポップアップが表示される状態に 2026.4.17 Fri 8:05 厚生労働省運営「</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>不正アクセス</t>
+          <t>アカウント侵害</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -15569,10 +15560,19 @@
           <t>可能性あり</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J289" t="n">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/190132</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html</t>
         </is>
       </c>
     </row>
@@ -15597,42 +15597,33 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>株式会社スプーン</t>
+          <t>インキメーカー</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>サイトが改ざん被害</t>
+          <t>システムがランサム被害</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56187;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社スプーンは8月20日、同社ウェブサイトの不正改ざんについて発表した。 これは同社ウェブサイト（ spoonsports.jp ）の一部が第三者に不正に改ざんされ、特定のページを閲覧した際に、偽のセキュリティ確認画面等が表示される事象を確認したというもの。 日本大学文理学部のウェブサイトが改ざん被害、カジノサイトを模した不正な画面が表示 2026.6.12 Fri 8:05 「FNJPNews」が改ざん被害、Google reCAPTCHA を模した偽のポップアップが表示される状態に 2026.4.17 Fri 8:05 厚生労働省運営「</t>
+          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>アカウント侵害</t>
+          <t>ランサムウェア</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Security NEXT</t>
         </is>
       </c>
       <c r="J290" t="n">
@@ -15645,7 +15636,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56187.html</t>
+          <t>https://www.security-next.com/189674</t>
         </is>
       </c>
     </row>
@@ -15657,33 +15648,42 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>インキメーカー</t>
+          <t>株式会社エリッツ</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>システムがランサム被害</t>
+          <t>ドズル社ストア</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>印刷用インキの製造、販売を手がけるT&amp;K TOKAは、システムがランサムウェアによるサイバー攻撃を受けたことを明らかにした。 ：Security NEXT</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56185;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社エリッツは8月20日、個人情報流出の可能性について発表した。 同社では、入居申込者とのメールで取り交わした情報を格納したファイルをクラウド環境で保管していたが、不正アクセス制限に脆弱性が存在することが外部の調査会社の指摘で8月17日に発覚したという。 穴吹ハウジングサービスへのランサムウェア攻撃、松山市営住宅入居者の個人情報が漏えい 2026.5.8 Fri 8:05 建物名・所在地・部屋番号・入居者名ほか約 4,200 件が闇サイトで販売 2025.10.17 Fri 8:05 県営住宅入居者の個人情報漏えい可能性、迷惑メールが届いた</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>ランサムウェア</t>
+          <t>不正アクセス</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>クレジットカード情報</t>
+        </is>
+      </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Security NEXT</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J291" t="n">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>https://www.security-next.com/189674</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html</t>
         </is>
       </c>
     </row>
@@ -15708,42 +15708,24 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>株式会社エリッツ</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>ドズル社ストア</t>
-        </is>
-      </c>
+          <t>PR TIMES</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56185;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); 株式会社エリッツは8月20日、個人情報流出の可能性について発表した。 同社では、入居申込者とのメールで取り交わした情報を格納したファイルをクラウド環境で保管していたが、不正アクセス制限に脆弱性が存在することが外部の調査会社の指摘で8月17日に発覚したという。 穴吹ハウジングサービスへのランサムウェア攻撃、松山市営住宅入居者の個人情報が漏えい 2026.5.8 Fri 8:05 建物名・所在地・部屋番号・入居者名ほか約 4,200 件が闇サイトで販売 2025.10.17 Fri 8:05 県営住宅入居者の個人情報漏えい可能性、迷惑メールが届いた</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>不正アクセス</t>
+          <t>「美容医療プラットフォーム Unni（カンナムオンニ）」個人情報漏えい事案に関するお詫びと漏洩項目精査のご報告 - PR TIMES</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>クレジットカード情報</t>
-        </is>
-      </c>
+          <t>確認・可能性あり</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>ScanNetSecurity</t>
+          <t>Google News</t>
         </is>
       </c>
       <c r="J292" t="n">
@@ -15756,7 +15738,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56185.html</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE55QmF3NU5PVm0yZ192MUlHb2ZTaUxpTEZTT1JtanQzdzJuWHl0VVl2a3JnUlVtemZVUDhkV2VvR0lWVE5ISmFFU1BqWTZMN2ZBTjdvcjRYMU4wb2lZWjFIcVlIN3VnejNSdkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -15768,24 +15750,42 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PR TIMES</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
+          <t>ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず REVISIO株式会社</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>「美容医療プラットフォーム Unni（カンナムオンニ）」個人情報漏えい事案に関するお詫びと漏洩項目精査のご報告 - PR TIMES</t>
+          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56189;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 これは3月20日に、同社役職員が使用するPCでマルウェア感染および不審な挙動が確認されたため、当該PCをネットワークから遮断し、各種アカウントを停止した上で、外部専門会社によるフォレンジック調査を行ったところ、外部からのリモート接続やサーバへの不正アクセスは確認されなかったものの、当該PC内部のローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できないとの報告があったというもの。 PC端末がマルウェア感染しアカウントの認証情報が窃取、海外から継続的な不正</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>マルウェア</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>確認・可能性あり</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr"/>
+          <t>可能性あり</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>7,716,811</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>クレジットカード情報, 認証情報</t>
+        </is>
+      </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>ScanNetSecurity</t>
         </is>
       </c>
       <c r="J293" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE55QmF3NU5PVm0yZ192MUlHb2ZTaUxpTEZTT1JtanQzdzJuWHl0VVl2a3JnUlVtemZVUDhkV2VvR0lWVE5ISmFFU1BqWTZMN2ZBTjdvcjRYMU4wb2lZWjFIcVlIN3VnejNSdkE?oc=5</t>
+          <t>https://scan.netsecurity.ne.jp/article/2026/09/10/56189.html</t>
         </is>
       </c>
     </row>
@@ -15810,42 +15810,24 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できず REVISIO株式会社</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
+          <t>Nihon University College of Science and Technology（tracker headline）</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>var expireDate_mms_content_id = new Date(); expireDate_mms_content_id.setDate(expireDate_mms_content_id.getDate() + 1); document.cookie = "mms-content-id=56189;path=/;" + "expires=" + expireDate_mms_content_id.toUTCString(); REVISIO株式会社は9月8日、同社PCのマルウェア感染について発表した。 これは3月20日に、同社役職員が使用するPCでマルウェア感染および不審な挙動が確認されたため、当該PCをネットワークから遮断し、各種アカウントを停止した上で、外部専門会社によるフォレンジック調査を行ったところ、外部からのリモート接続やサーバへの不正アクセスは確認されなかったものの、当該PC内部のローカル環境に保存されていた個人情報が外部漏えいした可能性を否定できないとの報告があったというもの。 PC端末がマルウェア感染しアカウントの認証情報が窃取、海外から継続的な不正</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>マルウェア</t>
+          <t>Nihon University College of Science and Technology（tracker headline） — Email takeover via phishing.</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>可能性あり</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>7,716,811</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>クレジットカード情報, 認証情報</t>
-        </is>
-      </c>
+     